--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KZNACalendar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KZNASwimmingCalendar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46B3DC9-0D1B-4273-AAA0-D9A1B28BCC95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D66AED5-9E73-4B36-9017-CF170432A0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calendar" sheetId="1" r:id="rId1"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="G8" s="6" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G7)*(EventsTable[End Date]&gt;=G7))), "")</f>
-        <v>• Seals Gala 1</v>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="C10" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C9)*(EventsTable[End Date]&gt;=C9))), "")</f>
-        <v/>
+        <v>• Seals Gala 1</v>
       </c>
       <c r="D10" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D9)*(EventsTable[End Date]&gt;=D9))), "")</f>
@@ -4959,12 +4959,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -4973,6 +4967,12 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5254,10 +5254,10 @@
         <v>27</v>
       </c>
       <c r="B21" s="42">
-        <v>46180</v>
+        <v>46183</v>
       </c>
       <c r="C21" s="42">
-        <v>46180</v>
+        <v>46183</v>
       </c>
       <c r="D21" s="40" t="s">
         <v>28</v>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KZNASwimmingCalendar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5617b328f11ff4f1/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D66AED5-9E73-4B36-9017-CF170432A0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{36AE3919-C410-47C1-B0F3-98BD0090094D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{792C031F-01C3-4286-8DC8-50D906B5CF79}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calendar" sheetId="1" r:id="rId1"/>
@@ -1238,6 +1238,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EventsTable" displayName="EventsTable" ref="A9:G127">
   <autoFilter ref="A9:G127" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
@@ -1650,7 +1654,7 @@
       </c>
       <c r="G8" s="6" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G7)*(EventsTable[End Date]&gt;=G7))), "")</f>
-        <v/>
+        <v>• Seals Gala 1</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1687,7 +1691,7 @@
       </c>
       <c r="C10" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C9)*(EventsTable[End Date]&gt;=C9))), "")</f>
-        <v>• Seals Gala 1</v>
+        <v/>
       </c>
       <c r="D10" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D9)*(EventsTable[End Date]&gt;=D9))), "")</f>
@@ -4959,6 +4963,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -4967,12 +4977,6 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5254,10 +5258,10 @@
         <v>27</v>
       </c>
       <c r="B21" s="42">
-        <v>46183</v>
+        <v>46180</v>
       </c>
       <c r="C21" s="42">
-        <v>46183</v>
+        <v>46180</v>
       </c>
       <c r="D21" s="40" t="s">
         <v>28</v>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5617b328f11ff4f1/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{36AE3919-C410-47C1-B0F3-98BD0090094D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{792C031F-01C3-4286-8DC8-50D906B5CF79}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23256" windowHeight="13176" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Calendar" sheetId="1" r:id="rId1"/>
     <sheet name="Events List" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="207">
   <si>
     <t>KZNA Calendar Season 2026–2027</t>
   </si>
@@ -652,12 +646,15 @@
   </si>
   <si>
     <t>SA Schools</t>
+  </si>
+  <si>
+    <t>Jollife Pool Pmb</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="15">
     <numFmt numFmtId="164" formatCode="d"/>
     <numFmt numFmtId="165" formatCode="d&quot; - Youth Day&quot;"/>
@@ -675,7 +672,7 @@
     <numFmt numFmtId="177" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1077,20 +1074,20 @@
     <xf numFmtId="0" fontId="25" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="datetime" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="day_only" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="datetime" xfId="1"/>
+    <cellStyle name="day_only" xfId="2"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="pro_day_only_🏊UnsanctionedCalendar" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="pro_day_only_🏊UnsanctionedCalendar" xfId="3"/>
   </cellStyles>
   <dxfs count="7">
     <dxf>
@@ -1163,7 +1160,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1208,7 +1205,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1243,16 +1240,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EventsTable" displayName="EventsTable" ref="A9:G127">
-  <autoFilter ref="A9:G127" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G127">
+  <autoFilter ref="A9:G127"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Event Name"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start Date"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="End Date"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Host"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Venue"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Status"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Gala Level"/>
+    <tableColumn id="1" name="Event Name"/>
+    <tableColumn id="2" name="Start Date"/>
+    <tableColumn id="3" name="End Date"/>
+    <tableColumn id="4" name="Host"/>
+    <tableColumn id="5" name="Venue"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="Gala Level"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1542,18 +1539,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G163"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="28.42578125" customWidth="1"/>
-    <col min="7" max="7" width="30.28515625" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" customWidth="1"/>
+    <col min="7" max="7" width="30.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="45"/>
@@ -1562,7 +1559,7 @@
       <c r="F1" s="45"/>
       <c r="G1" s="45"/>
     </row>
-    <row r="2" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="24.9" customHeight="1">
       <c r="B2" s="47"/>
       <c r="C2" s="45"/>
       <c r="D2" s="45"/>
@@ -1570,8 +1567,8 @@
       <c r="F2" s="45"/>
       <c r="G2" s="45"/>
     </row>
-    <row r="5" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="46" t="s">
+    <row r="5" spans="1:7" ht="35.1" customHeight="1">
+      <c r="A5" s="44" t="s">
         <v>185</v>
       </c>
       <c r="B5" s="45"/>
@@ -1581,7 +1578,7 @@
       <c r="F5" s="45"/>
       <c r="G5" s="45"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15">
       <c r="A6" s="2" t="s">
         <v>186</v>
       </c>
@@ -1604,7 +1601,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="3">
         <v>46174</v>
       </c>
@@ -1627,7 +1624,7 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="75" customHeight="1">
       <c r="A8" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A7)*(EventsTable[End Date]&gt;=A7))), "")</f>
         <v/>
@@ -1657,7 +1654,7 @@
         <v>• Seals Gala 1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="3">
         <v>46181</v>
       </c>
@@ -1680,7 +1677,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="75" customHeight="1">
       <c r="A10" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A9)*(EventsTable[End Date]&gt;=A9))), "")</f>
         <v/>
@@ -1710,7 +1707,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3">
         <v>46188</v>
       </c>
@@ -1733,7 +1730,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="75" customHeight="1">
       <c r="A12" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A11)*(EventsTable[End Date]&gt;=A11))), "")</f>
         <v/>
@@ -1764,7 +1761,7 @@
 • Seals Gala 2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="3">
         <v>46195</v>
       </c>
@@ -1787,7 +1784,7 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="75" customHeight="1">
       <c r="A14" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A13)*(EventsTable[End Date]&gt;=A13))), "")</f>
         <v/>
@@ -1817,7 +1814,7 @@
         <v>• Grand Prix SC Pre CWG</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3">
         <v>46202</v>
       </c>
@@ -1830,7 +1827,7 @@
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="75" customHeight="1">
       <c r="A16" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A15)*(EventsTable[End Date]&gt;=A15))), "")</f>
         <v>• Grand Prix SC Pre CWG</v>
@@ -1845,8 +1842,8 @@
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
     </row>
-    <row r="18" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="46" t="s">
+    <row r="18" spans="1:7" ht="35.1" customHeight="1">
+      <c r="A18" s="44" t="s">
         <v>193</v>
       </c>
       <c r="B18" s="45"/>
@@ -1856,7 +1853,7 @@
       <c r="F18" s="45"/>
       <c r="G18" s="45"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
         <v>186</v>
       </c>
@@ -1879,7 +1876,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="3">
@@ -1898,7 +1895,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
       <c r="C21" s="5" t="str">
@@ -1922,7 +1919,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="3">
         <v>46209</v>
       </c>
@@ -1945,7 +1942,7 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="75" customHeight="1">
       <c r="A23" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A22)*(EventsTable[End Date]&gt;=A22))), "")</f>
         <v/>
@@ -1975,7 +1972,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="3">
         <v>46216</v>
       </c>
@@ -1998,7 +1995,7 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="75" customHeight="1">
       <c r="A25" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A24)*(EventsTable[End Date]&gt;=A24))), "")</f>
         <v/>
@@ -2028,7 +2025,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A26" s="3">
         <v>46223</v>
       </c>
@@ -2051,7 +2048,7 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="75" customHeight="1">
       <c r="A27" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A26)*(EventsTable[End Date]&gt;=A26))), "")</f>
         <v/>
@@ -2083,7 +2080,7 @@
 • MSC Gala - Margate</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="3">
         <v>46230</v>
       </c>
@@ -2102,7 +2099,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="75" customHeight="1">
       <c r="A29" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A28)*(EventsTable[End Date]&gt;=A28))), "")</f>
         <v/>
@@ -2126,8 +2123,8 @@
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
     </row>
-    <row r="31" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+    <row r="31" spans="1:7" ht="35.1" customHeight="1">
+      <c r="A31" s="44" t="s">
         <v>194</v>
       </c>
       <c r="B31" s="45"/>
@@ -2137,7 +2134,7 @@
       <c r="F31" s="45"/>
       <c r="G31" s="45"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
         <v>186</v>
       </c>
@@ -2160,7 +2157,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -2173,7 +2170,7 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
@@ -2188,7 +2185,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A35" s="3">
         <v>46237</v>
       </c>
@@ -2211,7 +2208,7 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="75" customHeight="1">
       <c r="A36" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A35)*(EventsTable[End Date]&gt;=A35))), "")</f>
         <v/>
@@ -2242,7 +2239,7 @@
 • National Women's Day</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A37" s="12">
         <v>46244</v>
       </c>
@@ -2265,7 +2262,7 @@
         <v>46250</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="75" customHeight="1">
       <c r="A38" s="6" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A37)*(EventsTable[End Date]&gt;=A37))), "")</f>
         <v>• National Women's Day</v>
@@ -2296,7 +2293,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A39" s="3">
         <v>46251</v>
       </c>
@@ -2319,7 +2316,7 @@
         <v>46257</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="75" customHeight="1">
       <c r="A40" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A39)*(EventsTable[End Date]&gt;=A39))), "")</f>
         <v/>
@@ -2349,7 +2346,7 @@
         <v>• KZN Short Course Championships</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A41" s="3">
         <v>46258</v>
       </c>
@@ -2372,7 +2369,7 @@
         <v>46264</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="75" customHeight="1">
       <c r="A42" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A41)*(EventsTable[End Date]&gt;=A41))), "")</f>
         <v>• KZN Short Course Championships</v>
@@ -2402,7 +2399,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A43" s="3">
         <v>46265</v>
       </c>
@@ -2413,7 +2410,7 @@
       <c r="F43" s="9"/>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="75" customHeight="1">
       <c r="A44" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A43)*(EventsTable[End Date]&gt;=A43))), "")</f>
         <v/>
@@ -2425,8 +2422,8 @@
       <c r="F44" s="11"/>
       <c r="G44" s="11"/>
     </row>
-    <row r="46" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="46" t="s">
+    <row r="46" spans="1:7" ht="35.1" customHeight="1">
+      <c r="A46" s="44" t="s">
         <v>195</v>
       </c>
       <c r="B46" s="45"/>
@@ -2436,7 +2433,7 @@
       <c r="F46" s="45"/>
       <c r="G46" s="45"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
         <v>186</v>
       </c>
@@ -2459,7 +2456,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A48" s="8"/>
       <c r="B48" s="3">
         <v>46266</v>
@@ -2480,7 +2477,7 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B48)*(EventsTable[End Date]&gt;=B48))), "")</f>
@@ -2508,7 +2505,7 @@
         <v>• EDA Gala 3 &amp; 4</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A50" s="3">
         <v>46272</v>
       </c>
@@ -2531,7 +2528,7 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="75" customHeight="1">
       <c r="A51" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A50)*(EventsTable[End Date]&gt;=A50))), "")</f>
         <v/>
@@ -2561,7 +2558,7 @@
         <v>• Beavers SC Championships</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A52" s="3">
         <v>46279</v>
       </c>
@@ -2584,7 +2581,7 @@
         <v>46285</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="75" customHeight="1">
       <c r="A53" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A52)*(EventsTable[End Date]&gt;=A52))), "")</f>
         <v/>
@@ -2614,7 +2611,7 @@
         <v>• UMG AG 1</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A54" s="3">
         <v>46286</v>
       </c>
@@ -2637,7 +2634,7 @@
         <v>46292</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="75" customHeight="1">
       <c r="A55" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A54)*(EventsTable[End Date]&gt;=A54))), "")</f>
         <v/>
@@ -2674,7 +2671,7 @@
 • MSC Sprints</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A56" s="3">
         <v>46293</v>
       </c>
@@ -2689,7 +2686,7 @@
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
     </row>
-    <row r="57" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="75" customHeight="1">
       <c r="A57" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A56)*(EventsTable[End Date]&gt;=A56))), "")</f>
         <v>• MSC Sprints</v>
@@ -2707,8 +2704,8 @@
       <c r="F57" s="11"/>
       <c r="G57" s="11"/>
     </row>
-    <row r="59" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="46" t="s">
+    <row r="59" spans="1:7" ht="35.1" customHeight="1">
+      <c r="A59" s="44" t="s">
         <v>196</v>
       </c>
       <c r="B59" s="45"/>
@@ -2718,7 +2715,7 @@
       <c r="F59" s="45"/>
       <c r="G59" s="45"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
         <v>186</v>
       </c>
@@ -2741,7 +2738,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -2758,7 +2755,7 @@
         <v>46299</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
@@ -2782,7 +2779,7 @@
 • KZN Junior Championships LC</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A63" s="3">
         <v>46300</v>
       </c>
@@ -2805,7 +2802,7 @@
         <v>46306</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="75" customHeight="1">
       <c r="A64" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A63)*(EventsTable[End Date]&gt;=A63))), "")</f>
         <v/>
@@ -2835,7 +2832,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A65" s="3">
         <v>46307</v>
       </c>
@@ -2858,7 +2855,7 @@
         <v>46313</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="75" customHeight="1">
       <c r="A66" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A65)*(EventsTable[End Date]&gt;=A65))), "")</f>
         <v/>
@@ -2889,7 +2886,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A67" s="3">
         <v>46314</v>
       </c>
@@ -2912,7 +2909,7 @@
         <v>46320</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="75" customHeight="1">
       <c r="A68" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A67)*(EventsTable[End Date]&gt;=A67))), "")</f>
         <v/>
@@ -2942,7 +2939,7 @@
         <v>• MAC Championships</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A69" s="3">
         <v>46321</v>
       </c>
@@ -2963,7 +2960,7 @@
       </c>
       <c r="G69" s="9"/>
     </row>
-    <row r="70" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="75" customHeight="1">
       <c r="A70" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A69)*(EventsTable[End Date]&gt;=A69))), "")</f>
         <v/>
@@ -2990,8 +2987,8 @@
       </c>
       <c r="G70" s="11"/>
     </row>
-    <row r="72" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="46" t="s">
+    <row r="72" spans="1:7" ht="35.1" customHeight="1">
+      <c r="A72" s="44" t="s">
         <v>197</v>
       </c>
       <c r="B72" s="45"/>
@@ -3001,7 +2998,7 @@
       <c r="F72" s="45"/>
       <c r="G72" s="45"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
         <v>186</v>
       </c>
@@ -3024,7 +3021,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A74" s="8"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -3035,7 +3032,7 @@
         <v>46327</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
@@ -3047,7 +3044,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A76" s="3">
         <v>46328</v>
       </c>
@@ -3070,7 +3067,7 @@
         <v>46334</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="75" customHeight="1">
       <c r="A77" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A76)*(EventsTable[End Date]&gt;=A76))), "")</f>
         <v/>
@@ -3100,7 +3097,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A78" s="3">
         <v>46335</v>
       </c>
@@ -3123,7 +3120,7 @@
         <v>46341</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="75" customHeight="1">
       <c r="A79" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A78)*(EventsTable[End Date]&gt;=A78))), "")</f>
         <v/>
@@ -3153,7 +3150,7 @@
         <v>• Baynsfield Seeding Swim 1</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A80" s="3">
         <v>46342</v>
       </c>
@@ -3176,7 +3173,7 @@
         <v>46348</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="75" customHeight="1">
       <c r="A81" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A80)*(EventsTable[End Date]&gt;=A80))), "")</f>
         <v/>
@@ -3207,7 +3204,7 @@
         <v>• Capital K</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A82" s="3">
         <v>46349</v>
       </c>
@@ -3230,7 +3227,7 @@
         <v>46355</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="75" customHeight="1">
       <c r="A83" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A82)*(EventsTable[End Date]&gt;=A82))), "")</f>
         <v/>
@@ -3261,7 +3258,7 @@
         <v>• WSCSeals - LC OR SC</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A84" s="3">
         <v>46356</v>
       </c>
@@ -3272,7 +3269,7 @@
       <c r="F84" s="9"/>
       <c r="G84" s="9"/>
     </row>
-    <row r="85" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="75" customHeight="1">
       <c r="A85" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A84)*(EventsTable[End Date]&gt;=A84))), "")</f>
         <v/>
@@ -3284,8 +3281,8 @@
       <c r="F85" s="11"/>
       <c r="G85" s="11"/>
     </row>
-    <row r="87" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="46" t="s">
+    <row r="87" spans="1:7" ht="35.1" customHeight="1">
+      <c r="A87" s="44" t="s">
         <v>198</v>
       </c>
       <c r="B87" s="45"/>
@@ -3295,7 +3292,7 @@
       <c r="F87" s="45"/>
       <c r="G87" s="45"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
         <v>186</v>
       </c>
@@ -3318,7 +3315,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A89" s="8"/>
       <c r="B89" s="3">
         <v>46357</v>
@@ -3339,7 +3336,7 @@
         <v>46362</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B89)*(EventsTable[End Date]&gt;=B89))), "")</f>
@@ -3366,7 +3363,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="3">
         <v>46363</v>
       </c>
@@ -3389,7 +3386,7 @@
         <v>46369</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="75" customHeight="1">
       <c r="A92" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A91)*(EventsTable[End Date]&gt;=A91))), "")</f>
         <v/>
@@ -3421,7 +3418,7 @@
 • KZN Premier Championships (Level 2 &amp; Above)</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A93" s="3">
         <v>46370</v>
       </c>
@@ -3444,7 +3441,7 @@
         <v>46376</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" ht="75" customHeight="1">
       <c r="A94" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A93)*(EventsTable[End Date]&gt;=A93))), "")</f>
         <v>• KZN Premier Championships (Level 2 &amp; Above)</v>
@@ -3474,7 +3471,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A95" s="3">
         <v>46377</v>
       </c>
@@ -3497,7 +3494,7 @@
         <v>46383</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" ht="75" customHeight="1">
       <c r="A96" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A95)*(EventsTable[End Date]&gt;=A95))), "")</f>
         <v/>
@@ -3527,7 +3524,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A97" s="3">
         <v>46384</v>
       </c>
@@ -3544,7 +3541,7 @@
       <c r="F97" s="9"/>
       <c r="G97" s="9"/>
     </row>
-    <row r="98" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="75" customHeight="1">
       <c r="A98" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A97)*(EventsTable[End Date]&gt;=A97))), "")</f>
         <v/>
@@ -3565,8 +3562,8 @@
       <c r="F98" s="11"/>
       <c r="G98" s="11"/>
     </row>
-    <row r="100" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="46" t="s">
+    <row r="100" spans="1:7" ht="35.1" customHeight="1">
+      <c r="A100" s="44" t="s">
         <v>199</v>
       </c>
       <c r="B100" s="45"/>
@@ -3576,7 +3573,7 @@
       <c r="F100" s="45"/>
       <c r="G100" s="45"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
         <v>186</v>
       </c>
@@ -3599,7 +3596,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A102" s="8"/>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
@@ -3614,7 +3611,7 @@
         <v>46390</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
@@ -3632,7 +3629,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A104" s="3">
         <v>46391</v>
       </c>
@@ -3655,7 +3652,7 @@
         <v>46397</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="75" customHeight="1">
       <c r="A105" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A104)*(EventsTable[End Date]&gt;=A104))), "")</f>
         <v/>
@@ -3686,7 +3683,7 @@
         <v>• EDA Gala 5&amp;6 &amp; KZNA Age Group (Level 3 and above) LC</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A106" s="3">
         <v>46398</v>
       </c>
@@ -3709,7 +3706,7 @@
         <v>46404</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="98.25" customHeight="1">
       <c r="A107" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A106)*(EventsTable[End Date]&gt;=A106))), "")</f>
         <v/>
@@ -3745,7 +3742,7 @@
 • UMG AG2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A108" s="3">
         <v>46405</v>
       </c>
@@ -3768,7 +3765,7 @@
         <v>46411</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="75" customHeight="1">
       <c r="A109" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A108)*(EventsTable[End Date]&gt;=A108))), "")</f>
         <v/>
@@ -3798,7 +3795,7 @@
         <v>• Ilembe School Trials</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A110" s="3">
         <v>46412</v>
       </c>
@@ -3821,7 +3818,7 @@
         <v>46418</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="75" customHeight="1">
       <c r="A111" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A110)*(EventsTable[End Date]&gt;=A110))), "")</f>
         <v/>
@@ -3859,8 +3856,8 @@
 • PADSSA &amp; Umlazi Schools</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="46" t="s">
+    <row r="113" spans="1:7" ht="35.1" customHeight="1">
+      <c r="A113" s="44" t="s">
         <v>200</v>
       </c>
       <c r="B113" s="45"/>
@@ -3870,7 +3867,7 @@
       <c r="F113" s="45"/>
       <c r="G113" s="45"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
         <v>186</v>
       </c>
@@ -3893,7 +3890,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A115" s="3">
         <v>46419</v>
       </c>
@@ -3916,7 +3913,7 @@
         <v>46425</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="75" customHeight="1">
       <c r="A116" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A115)*(EventsTable[End Date]&gt;=A115))), "")</f>
         <v/>
@@ -3948,7 +3945,7 @@
         <v>• KZNA Long Course Meet 2 LC</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A117" s="3">
         <v>46426</v>
       </c>
@@ -3971,7 +3968,7 @@
         <v>46432</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="75" customHeight="1">
       <c r="A118" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A117)*(EventsTable[End Date]&gt;=A117))), "")</f>
         <v/>
@@ -4002,7 +3999,7 @@
         <v>• Midmar Mile</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A119" s="3">
         <v>46433</v>
       </c>
@@ -4025,7 +4022,7 @@
         <v>46439</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="75" customHeight="1">
       <c r="A120" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A119)*(EventsTable[End Date]&gt;=A119))), "")</f>
         <v/>
@@ -4055,7 +4052,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A121" s="3">
         <v>46440</v>
       </c>
@@ -4078,7 +4075,7 @@
         <v>46446</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="75" customHeight="1">
       <c r="A122" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A121)*(EventsTable[End Date]&gt;=A121))), "")</f>
         <v/>
@@ -4108,8 +4105,8 @@
         <v>• KZN Schools</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="46" t="s">
+    <row r="124" spans="1:7" ht="35.1" customHeight="1">
+      <c r="A124" s="44" t="s">
         <v>201</v>
       </c>
       <c r="B124" s="45"/>
@@ -4119,7 +4116,7 @@
       <c r="F124" s="45"/>
       <c r="G124" s="45"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
         <v>186</v>
       </c>
@@ -4142,7 +4139,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A126" s="3">
         <v>46447</v>
       </c>
@@ -4165,7 +4162,7 @@
         <v>46453</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="75" customHeight="1">
       <c r="A127" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A126)*(EventsTable[End Date]&gt;=A126))), "")</f>
         <v>• F, C League</v>
@@ -4195,7 +4192,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A128" s="3">
         <v>46454</v>
       </c>
@@ -4218,7 +4215,7 @@
         <v>46460</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="75" customHeight="1">
       <c r="A129" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A128)*(EventsTable[End Date]&gt;=A128))), "")</f>
         <v/>
@@ -4248,7 +4245,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A130" s="3">
         <v>46461</v>
       </c>
@@ -4271,7 +4268,7 @@
         <v>46467</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="75" customHeight="1">
       <c r="A131" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A130)*(EventsTable[End Date]&gt;=A130))), "")</f>
         <v/>
@@ -4302,7 +4299,7 @@
 • Human Rights Day</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A132" s="18">
         <v>46468</v>
       </c>
@@ -4325,7 +4322,7 @@
         <v>46474</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="75" customHeight="1">
       <c r="A133" s="6" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A132)*(EventsTable[End Date]&gt;=A132))), "")</f>
         <v>• SA Junior Nationals
@@ -4356,7 +4353,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A134" s="20">
         <v>46475</v>
       </c>
@@ -4371,7 +4368,7 @@
       <c r="F134" s="9"/>
       <c r="G134" s="9"/>
     </row>
-    <row r="135" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="75" customHeight="1">
       <c r="A135" s="6" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A134)*(EventsTable[End Date]&gt;=A134))), "")</f>
         <v>• Family Day</v>
@@ -4389,8 +4386,8 @@
       <c r="F135" s="11"/>
       <c r="G135" s="11"/>
     </row>
-    <row r="137" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="46" t="s">
+    <row r="137" spans="1:7" ht="35.1" customHeight="1">
+      <c r="A137" s="44" t="s">
         <v>202</v>
       </c>
       <c r="B137" s="45"/>
@@ -4400,7 +4397,7 @@
       <c r="F137" s="45"/>
       <c r="G137" s="45"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
         <v>186</v>
       </c>
@@ -4423,7 +4420,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A139" s="8"/>
       <c r="B139" s="8"/>
       <c r="C139" s="8"/>
@@ -4440,7 +4437,7 @@
         <v>46481</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="75" customHeight="1">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
@@ -4461,7 +4458,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A141" s="3">
         <v>46482</v>
       </c>
@@ -4484,7 +4481,7 @@
         <v>46488</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="75" customHeight="1">
       <c r="A142" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A141)*(EventsTable[End Date]&gt;=A141))), "")</f>
         <v>• Level 2</v>
@@ -4514,7 +4511,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A143" s="3">
         <v>46489</v>
       </c>
@@ -4537,7 +4534,7 @@
         <v>46495</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="75" customHeight="1">
       <c r="A144" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A143)*(EventsTable[End Date]&gt;=A143))), "")</f>
         <v/>
@@ -4567,7 +4564,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A145" s="3">
         <v>46496</v>
       </c>
@@ -4590,7 +4587,7 @@
         <v>46502</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="75" customHeight="1">
       <c r="A146" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A145)*(EventsTable[End Date]&gt;=A145))), "")</f>
         <v/>
@@ -4620,7 +4617,7 @@
         <v>• SA School</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A147" s="3">
         <v>46503</v>
       </c>
@@ -4639,7 +4636,7 @@
       <c r="F147" s="9"/>
       <c r="G147" s="9"/>
     </row>
-    <row r="148" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="75" customHeight="1">
       <c r="A148" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A147)*(EventsTable[End Date]&gt;=A147))), "")</f>
         <v>• SA School</v>
@@ -4664,8 +4661,8 @@
       <c r="F148" s="11"/>
       <c r="G148" s="11"/>
     </row>
-    <row r="150" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="46" t="s">
+    <row r="150" spans="1:7" ht="35.1" customHeight="1">
+      <c r="A150" s="44" t="s">
         <v>203</v>
       </c>
       <c r="B150" s="45"/>
@@ -4675,7 +4672,7 @@
       <c r="F150" s="45"/>
       <c r="G150" s="45"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7">
       <c r="A151" s="2" t="s">
         <v>186</v>
       </c>
@@ -4698,7 +4695,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A152" s="8"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -4711,7 +4708,7 @@
         <v>46509</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="75" customHeight="1">
       <c r="A153" s="10"/>
       <c r="B153" s="10"/>
       <c r="C153" s="10"/>
@@ -4726,7 +4723,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A154" s="3">
         <v>46510</v>
       </c>
@@ -4749,7 +4746,7 @@
         <v>46516</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="75" customHeight="1">
       <c r="A155" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A154)*(EventsTable[End Date]&gt;=A154))), "")</f>
         <v/>
@@ -4779,7 +4776,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A156" s="3">
         <v>46517</v>
       </c>
@@ -4802,7 +4799,7 @@
         <v>46523</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="75" customHeight="1">
       <c r="A157" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A156)*(EventsTable[End Date]&gt;=A156))), "")</f>
         <v/>
@@ -4832,7 +4829,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A158" s="3">
         <v>46524</v>
       </c>
@@ -4855,7 +4852,7 @@
         <v>46530</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="75" customHeight="1">
       <c r="A159" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A158)*(EventsTable[End Date]&gt;=A158))), "")</f>
         <v/>
@@ -4885,7 +4882,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A160" s="3">
         <v>46531</v>
       </c>
@@ -4908,7 +4905,7 @@
         <v>46537</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="75" customHeight="1">
       <c r="A161" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A160)*(EventsTable[End Date]&gt;=A160))), "")</f>
         <v/>
@@ -4938,7 +4935,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A162" s="3">
         <v>46538</v>
       </c>
@@ -4949,7 +4946,7 @@
       <c r="F162" s="9"/>
       <c r="G162" s="9"/>
     </row>
-    <row r="163" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="75" customHeight="1">
       <c r="A163" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A162)*(EventsTable[End Date]&gt;=A162))), "")</f>
         <v/>
@@ -4963,12 +4960,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -4977,6 +4968,12 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -4984,20 +4981,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G127"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="35" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="44" t="s">
+    <row r="1" spans="1:7" ht="60" customHeight="1">
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="45"/>
@@ -5006,12 +5003,12 @@
       <c r="F1" s="45"/>
       <c r="G1" s="32"/>
     </row>
-    <row r="2" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="24.9" customHeight="1">
       <c r="E2" s="43" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15">
       <c r="B3" s="33" t="s">
         <v>2</v>
       </c>
@@ -5025,7 +5022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="24.9" customHeight="1">
       <c r="B4" s="37" t="s">
         <v>6</v>
       </c>
@@ -5037,7 +5034,7 @@
       </c>
       <c r="E4" s="40"/>
     </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="23"/>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
@@ -5046,7 +5043,7 @@
       <c r="F5" s="24"/>
       <c r="G5" s="24"/>
     </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="25"/>
       <c r="B6" s="26"/>
       <c r="C6" s="27"/>
@@ -5055,7 +5052,7 @@
       <c r="F6" s="30"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="24"/>
       <c r="B7" s="24"/>
       <c r="C7" s="24"/>
@@ -5064,7 +5061,7 @@
       <c r="F7" s="24"/>
       <c r="G7" s="24"/>
     </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="24"/>
       <c r="B8" s="24"/>
       <c r="C8" s="24"/>
@@ -5073,7 +5070,7 @@
       <c r="F8" s="24"/>
       <c r="G8" s="24"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="15">
       <c r="A9" s="40" t="s">
         <v>9</v>
       </c>
@@ -5096,7 +5093,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="24.9" customHeight="1">
       <c r="A10" s="41" t="s">
         <v>16</v>
       </c>
@@ -5107,7 +5104,7 @@
       <c r="F10" s="41"/>
       <c r="G10" s="41"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15">
       <c r="A11" s="40" t="s">
         <v>17</v>
       </c>
@@ -5124,7 +5121,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="24.9" customHeight="1">
       <c r="A12" s="41" t="s">
         <v>18</v>
       </c>
@@ -5135,7 +5132,7 @@
       <c r="F12" s="41"/>
       <c r="G12" s="41"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15">
       <c r="A13" s="40" t="s">
         <v>19</v>
       </c>
@@ -5152,7 +5149,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="17.25" customHeight="1">
       <c r="A14" s="41" t="s">
         <v>20</v>
       </c>
@@ -5163,7 +5160,7 @@
       <c r="F14" s="41"/>
       <c r="G14" s="41"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="15">
       <c r="A15" s="40" t="s">
         <v>21</v>
       </c>
@@ -5180,7 +5177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15">
       <c r="A16" s="40" t="s">
         <v>22</v>
       </c>
@@ -5197,7 +5194,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="15">
       <c r="A17" s="40" t="s">
         <v>23</v>
       </c>
@@ -5214,7 +5211,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="24.9" customHeight="1">
       <c r="A18" s="41" t="s">
         <v>24</v>
       </c>
@@ -5225,7 +5222,7 @@
       <c r="F18" s="41"/>
       <c r="G18" s="41"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15">
       <c r="A19" s="40" t="s">
         <v>25</v>
       </c>
@@ -5242,7 +5239,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="17.25" customHeight="1">
       <c r="A20" s="41" t="s">
         <v>26</v>
       </c>
@@ -5253,7 +5250,7 @@
       <c r="F20" s="41"/>
       <c r="G20" s="41"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="15">
       <c r="A21" s="40" t="s">
         <v>27</v>
       </c>
@@ -5276,7 +5273,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="15">
       <c r="A22" s="40" t="s">
         <v>31</v>
       </c>
@@ -5293,7 +5290,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="24.9" customHeight="1">
       <c r="A23" s="40" t="s">
         <v>32</v>
       </c>
@@ -5316,7 +5313,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15">
       <c r="A24" s="40" t="s">
         <v>35</v>
       </c>
@@ -5339,7 +5336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="15">
       <c r="A25" s="40" t="s">
         <v>37</v>
       </c>
@@ -5362,7 +5359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="17.25" customHeight="1">
       <c r="A26" s="41" t="s">
         <v>40</v>
       </c>
@@ -5373,7 +5370,7 @@
       <c r="F26" s="41"/>
       <c r="G26" s="41"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="40" t="s">
         <v>41</v>
       </c>
@@ -5387,7 +5384,7 @@
         <v>28</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>39</v>
+        <v>206</v>
       </c>
       <c r="F27" s="40" t="s">
         <v>30</v>
@@ -5396,7 +5393,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="40" t="s">
         <v>42</v>
       </c>
@@ -5419,7 +5416,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="40" t="s">
         <v>45</v>
       </c>
@@ -5442,7 +5439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="40" t="s">
         <v>48</v>
       </c>
@@ -5465,7 +5462,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="24.9" customHeight="1">
       <c r="A31" s="41" t="s">
         <v>51</v>
       </c>
@@ -5476,7 +5473,7 @@
       <c r="F31" s="41"/>
       <c r="G31" s="41"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" s="40" t="s">
         <v>52</v>
       </c>
@@ -5499,7 +5496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33" s="40" t="s">
         <v>53</v>
       </c>
@@ -5516,7 +5513,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34" s="40" t="s">
         <v>53</v>
       </c>
@@ -5533,7 +5530,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35" s="40" t="s">
         <v>54</v>
       </c>
@@ -5556,7 +5553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36" s="40" t="s">
         <v>55</v>
       </c>
@@ -5579,7 +5576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37" s="40" t="s">
         <v>57</v>
       </c>
@@ -5602,7 +5599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38" s="40" t="s">
         <v>60</v>
       </c>
@@ -5625,7 +5622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="17.25" customHeight="1">
       <c r="A39" s="41" t="s">
         <v>63</v>
       </c>
@@ -5636,7 +5633,7 @@
       <c r="F39" s="41"/>
       <c r="G39" s="41"/>
     </row>
-    <row r="40" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="24.9" customHeight="1">
       <c r="A40" s="40" t="s">
         <v>64</v>
       </c>
@@ -5659,7 +5656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41" s="40" t="s">
         <v>67</v>
       </c>
@@ -5682,7 +5679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42" s="40" t="s">
         <v>68</v>
       </c>
@@ -5705,7 +5702,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43" s="40" t="s">
         <v>71</v>
       </c>
@@ -5728,7 +5725,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="A44" s="40" t="s">
         <v>74</v>
       </c>
@@ -5745,7 +5742,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45" s="40" t="s">
         <v>75</v>
       </c>
@@ -5768,7 +5765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46" s="40" t="s">
         <v>78</v>
       </c>
@@ -5791,7 +5788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47" s="40" t="s">
         <v>81</v>
       </c>
@@ -5814,7 +5811,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="24.9" customHeight="1">
       <c r="A48" s="41" t="s">
         <v>83</v>
       </c>
@@ -5825,7 +5822,7 @@
       <c r="F48" s="41"/>
       <c r="G48" s="41"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49" s="40" t="s">
         <v>84</v>
       </c>
@@ -5848,7 +5845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7">
       <c r="A50" s="40" t="s">
         <v>87</v>
       </c>
@@ -5871,7 +5868,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7">
       <c r="A51" s="40" t="s">
         <v>89</v>
       </c>
@@ -5894,7 +5891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7">
       <c r="A52" s="40" t="s">
         <v>91</v>
       </c>
@@ -5917,7 +5914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7">
       <c r="A53" s="40" t="s">
         <v>93</v>
       </c>
@@ -5940,7 +5937,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7">
       <c r="A54" s="40" t="s">
         <v>96</v>
       </c>
@@ -5963,7 +5960,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="24.9" customHeight="1">
       <c r="A55" s="40" t="s">
         <v>99</v>
       </c>
@@ -5986,7 +5983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="17.25" customHeight="1">
       <c r="A56" s="41" t="s">
         <v>100</v>
       </c>
@@ -5997,7 +5994,7 @@
       <c r="F56" s="41"/>
       <c r="G56" s="41"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7">
       <c r="A57" s="40" t="s">
         <v>101</v>
       </c>
@@ -6020,7 +6017,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7">
       <c r="A58" s="40" t="s">
         <v>103</v>
       </c>
@@ -6043,7 +6040,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7">
       <c r="A59" s="40" t="s">
         <v>106</v>
       </c>
@@ -6066,7 +6063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7">
       <c r="A60" s="40" t="s">
         <v>108</v>
       </c>
@@ -6089,7 +6086,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7">
       <c r="A61" s="40" t="s">
         <v>110</v>
       </c>
@@ -6112,7 +6109,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="24.9" customHeight="1">
       <c r="A62" s="40" t="s">
         <v>112</v>
       </c>
@@ -6135,7 +6132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="17.25" customHeight="1">
       <c r="A63" s="41" t="s">
         <v>113</v>
       </c>
@@ -6146,7 +6143,7 @@
       <c r="F63" s="41"/>
       <c r="G63" s="41"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7">
       <c r="A64" s="40" t="s">
         <v>114</v>
       </c>
@@ -6169,7 +6166,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65" s="40" t="s">
         <v>115</v>
       </c>
@@ -6192,7 +6189,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66" s="40" t="s">
         <v>116</v>
       </c>
@@ -6215,7 +6212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67" s="40" t="s">
         <v>118</v>
       </c>
@@ -6232,7 +6229,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68" s="40" t="s">
         <v>119</v>
       </c>
@@ -6249,7 +6246,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69" s="40" t="s">
         <v>120</v>
       </c>
@@ -6266,7 +6263,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="17.25" customHeight="1">
       <c r="A70" s="41" t="s">
         <v>121</v>
       </c>
@@ -6277,7 +6274,7 @@
       <c r="F70" s="41"/>
       <c r="G70" s="41"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71" s="40" t="s">
         <v>17</v>
       </c>
@@ -6294,7 +6291,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72" s="40" t="s">
         <v>122</v>
       </c>
@@ -6317,7 +6314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73" s="40" t="s">
         <v>124</v>
       </c>
@@ -6340,7 +6337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74" s="40" t="s">
         <v>125</v>
       </c>
@@ -6363,7 +6360,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75" s="40" t="s">
         <v>126</v>
       </c>
@@ -6386,7 +6383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76" s="40" t="s">
         <v>127</v>
       </c>
@@ -6409,7 +6406,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77" s="40" t="s">
         <v>129</v>
       </c>
@@ -6432,7 +6429,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78" s="40" t="s">
         <v>130</v>
       </c>
@@ -6455,7 +6452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79" s="40" t="s">
         <v>131</v>
       </c>
@@ -6478,7 +6475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="24.9" customHeight="1">
       <c r="A80" s="40" t="s">
         <v>134</v>
       </c>
@@ -6501,7 +6498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7">
       <c r="A81" s="40" t="s">
         <v>136</v>
       </c>
@@ -6524,7 +6521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7">
       <c r="A82" s="40" t="s">
         <v>141</v>
       </c>
@@ -6547,7 +6544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7">
       <c r="A83" s="40" t="s">
         <v>139</v>
       </c>
@@ -6570,7 +6567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84" s="40" t="s">
         <v>143</v>
       </c>
@@ -6593,7 +6590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85" s="40" t="s">
         <v>146</v>
       </c>
@@ -6616,7 +6613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="17.25" customHeight="1">
       <c r="A86" s="40" t="s">
         <v>149</v>
       </c>
@@ -6639,7 +6636,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="24.9" customHeight="1">
       <c r="A87" s="40" t="s">
         <v>151</v>
       </c>
@@ -6662,7 +6659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="16.8">
       <c r="A88" s="41" t="s">
         <v>154</v>
       </c>
@@ -6673,7 +6670,7 @@
       <c r="F88" s="41"/>
       <c r="G88" s="41"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7">
       <c r="A89" s="40" t="s">
         <v>155</v>
       </c>
@@ -6696,7 +6693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7">
       <c r="A90" s="40" t="s">
         <v>48</v>
       </c>
@@ -6719,7 +6716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="40" t="s">
         <v>157</v>
       </c>
@@ -6742,7 +6739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7">
       <c r="A92" s="40" t="s">
         <v>158</v>
       </c>
@@ -6765,7 +6762,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7">
       <c r="A93" s="40" t="s">
         <v>159</v>
       </c>
@@ -6788,7 +6785,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="40" t="s">
         <v>160</v>
       </c>
@@ -6811,7 +6808,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" ht="17.25" customHeight="1">
       <c r="A95" s="40" t="s">
         <v>161</v>
       </c>
@@ -6834,7 +6831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7">
       <c r="A96" s="40" t="s">
         <v>162</v>
       </c>
@@ -6857,7 +6854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="16.8">
       <c r="A97" s="41" t="s">
         <v>165</v>
       </c>
@@ -6868,7 +6865,7 @@
       <c r="F97" s="41"/>
       <c r="G97" s="41"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7">
       <c r="A98" s="40" t="s">
         <v>166</v>
       </c>
@@ -6891,7 +6888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7">
       <c r="A99" s="40" t="s">
         <v>168</v>
       </c>
@@ -6914,7 +6911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7">
       <c r="A100" s="40" t="s">
         <v>169</v>
       </c>
@@ -6937,7 +6934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7">
       <c r="A101" s="40" t="s">
         <v>170</v>
       </c>
@@ -6960,7 +6957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7">
       <c r="A102" s="40" t="s">
         <v>171</v>
       </c>
@@ -6983,7 +6980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7">
       <c r="A103" s="40" t="s">
         <v>173</v>
       </c>
@@ -7006,7 +7003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="24.9" customHeight="1">
       <c r="A104" s="40" t="s">
         <v>19</v>
       </c>
@@ -7023,7 +7020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7">
       <c r="A105" s="40" t="s">
         <v>19</v>
       </c>
@@ -7040,7 +7037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="24.9" customHeight="1">
       <c r="A106" s="40" t="s">
         <v>21</v>
       </c>
@@ -7057,7 +7054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="17.25" customHeight="1">
       <c r="A107" s="40" t="s">
         <v>22</v>
       </c>
@@ -7074,7 +7071,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="24.9" customHeight="1">
       <c r="A108" s="40" t="s">
         <v>174</v>
       </c>
@@ -7097,7 +7094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="16.8">
       <c r="A109" s="41" t="s">
         <v>176</v>
       </c>
@@ -7108,7 +7105,7 @@
       <c r="F109" s="41"/>
       <c r="G109" s="41"/>
     </row>
-    <row r="110" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="24.9" customHeight="1">
       <c r="A110" s="40" t="s">
         <v>174</v>
       </c>
@@ -7131,7 +7128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7">
       <c r="A111" s="40" t="s">
         <v>177</v>
       </c>
@@ -7154,7 +7151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" s="24" customFormat="1">
       <c r="A112" s="40" t="s">
         <v>179</v>
       </c>
@@ -7177,7 +7174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="24.9" customHeight="1">
       <c r="A113" s="40" t="s">
         <v>204</v>
       </c>
@@ -7200,7 +7197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7">
       <c r="A114" s="40" t="s">
         <v>23</v>
       </c>
@@ -7217,7 +7214,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="17.25" customHeight="1">
       <c r="A115" s="41" t="s">
         <v>180</v>
       </c>
@@ -7228,7 +7225,7 @@
       <c r="F115" s="41"/>
       <c r="G115" s="41"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7">
       <c r="A116" s="40" t="s">
         <v>25</v>
       </c>
@@ -7245,7 +7242,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="17.25" customHeight="1">
       <c r="A117" s="41" t="s">
         <v>181</v>
       </c>
@@ -7256,7 +7253,7 @@
       <c r="F117" s="41"/>
       <c r="G117" s="41"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7">
       <c r="A118" s="40" t="s">
         <v>31</v>
       </c>
@@ -7273,7 +7270,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="17.25" customHeight="1">
       <c r="A119" s="41" t="s">
         <v>182</v>
       </c>
@@ -7284,7 +7281,7 @@
       <c r="F119" s="41"/>
       <c r="G119" s="41"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7">
       <c r="A120" s="40" t="s">
         <v>53</v>
       </c>
@@ -7301,7 +7298,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="17.25" customHeight="1">
       <c r="A121" s="41" t="s">
         <v>183</v>
       </c>
@@ -7312,7 +7309,7 @@
       <c r="F121" s="41"/>
       <c r="G121" s="41"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122" s="40" t="s">
         <v>74</v>
       </c>
@@ -7329,7 +7326,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="16.8">
       <c r="A123" s="41" t="s">
         <v>184</v>
       </c>
@@ -7340,7 +7337,7 @@
       <c r="F123" s="41"/>
       <c r="G123" s="41"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7">
       <c r="A124" s="40" t="s">
         <v>118</v>
       </c>
@@ -7357,7 +7354,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125" s="40" t="s">
         <v>119</v>
       </c>
@@ -7374,7 +7371,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7">
       <c r="A126" s="40" t="s">
         <v>120</v>
       </c>
@@ -7391,7 +7388,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7">
       <c r="A127" s="40" t="s">
         <v>120</v>
       </c>
@@ -7436,12 +7433,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G203" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G203">
       <formula1>"Club gala,District gala,Provincial gala,National gala,Open Water,Schools gala,Public Holiday"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="E2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId2"/>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -207,9 +207,6 @@
     <t>KZNA</t>
   </si>
   <si>
-    <t>Kloof, Beavers</t>
-  </si>
-  <si>
     <t>Beavers SC Championships</t>
   </si>
   <si>
@@ -649,6 +646,9 @@
   </si>
   <si>
     <t>Jollife Pool Pmb</t>
+  </si>
+  <si>
+    <t>Kloof/Joliffe/Reddam</t>
   </si>
 </sst>
 </file>
@@ -1543,7 +1543,8 @@
   <dimension ref="A1:G163"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="5" width="24" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="28.44140625" customWidth="1"/>
     <col min="7" max="7" width="30.33203125" customWidth="1"/>
   </cols>
@@ -1569,7 +1570,7 @@
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
       <c r="A5" s="44" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B5" s="45"/>
       <c r="C5" s="45"/>
@@ -1578,27 +1579,27 @@
       <c r="F5" s="45"/>
       <c r="G5" s="45"/>
     </row>
-    <row r="6" spans="1:7" ht="15">
+    <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -1844,7 +1845,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
       <c r="A18" s="44" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B18" s="45"/>
       <c r="C18" s="45"/>
@@ -1855,25 +1856,25 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2125,7 +2126,7 @@
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
       <c r="A31" s="44" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B31" s="45"/>
       <c r="C31" s="45"/>
@@ -2136,25 +2137,25 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2424,7 +2425,7 @@
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
       <c r="A46" s="44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B46" s="45"/>
       <c r="C46" s="45"/>
@@ -2435,25 +2436,25 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2706,7 +2707,7 @@
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
       <c r="A59" s="44" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B59" s="45"/>
       <c r="C59" s="45"/>
@@ -2717,25 +2718,25 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2989,7 +2990,7 @@
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
       <c r="A72" s="44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B72" s="45"/>
       <c r="C72" s="45"/>
@@ -3000,25 +3001,25 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="G73" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3283,7 +3284,7 @@
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
       <c r="A87" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B87" s="45"/>
       <c r="C87" s="45"/>
@@ -3294,25 +3295,25 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3564,7 +3565,7 @@
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
       <c r="A100" s="44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B100" s="45"/>
       <c r="C100" s="45"/>
@@ -3575,25 +3576,25 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F101" s="2" t="s">
+      <c r="G101" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3858,7 +3859,7 @@
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
       <c r="A113" s="44" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B113" s="45"/>
       <c r="C113" s="45"/>
@@ -3869,25 +3870,25 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="F114" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F114" s="2" t="s">
+      <c r="G114" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4107,7 +4108,7 @@
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
       <c r="A124" s="44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B124" s="45"/>
       <c r="C124" s="45"/>
@@ -4118,25 +4119,25 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="E125" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="G125" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4388,7 +4389,7 @@
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
       <c r="A137" s="44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B137" s="45"/>
       <c r="C137" s="45"/>
@@ -4399,25 +4400,25 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="D138" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="E138" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="F138" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F138" s="2" t="s">
+      <c r="G138" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4663,7 +4664,7 @@
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
       <c r="A150" s="44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B150" s="45"/>
       <c r="C150" s="45"/>
@@ -4674,25 +4675,25 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C151" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="D151" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="E151" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="F151" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F151" s="2" t="s">
+      <c r="G151" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -5008,7 +5009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:7">
       <c r="B3" s="33" t="s">
         <v>2</v>
       </c>
@@ -5070,7 +5071,7 @@
       <c r="F8" s="24"/>
       <c r="G8" s="24"/>
     </row>
-    <row r="9" spans="1:7" ht="15">
+    <row r="9" spans="1:7">
       <c r="A9" s="40" t="s">
         <v>9</v>
       </c>
@@ -5104,7 +5105,7 @@
       <c r="F10" s="41"/>
       <c r="G10" s="41"/>
     </row>
-    <row r="11" spans="1:7" ht="15">
+    <row r="11" spans="1:7">
       <c r="A11" s="40" t="s">
         <v>17</v>
       </c>
@@ -5132,7 +5133,7 @@
       <c r="F12" s="41"/>
       <c r="G12" s="41"/>
     </row>
-    <row r="13" spans="1:7" ht="15">
+    <row r="13" spans="1:7">
       <c r="A13" s="40" t="s">
         <v>19</v>
       </c>
@@ -5160,7 +5161,7 @@
       <c r="F14" s="41"/>
       <c r="G14" s="41"/>
     </row>
-    <row r="15" spans="1:7" ht="15">
+    <row r="15" spans="1:7">
       <c r="A15" s="40" t="s">
         <v>21</v>
       </c>
@@ -5177,7 +5178,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15">
+    <row r="16" spans="1:7">
       <c r="A16" s="40" t="s">
         <v>22</v>
       </c>
@@ -5194,7 +5195,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15">
+    <row r="17" spans="1:7">
       <c r="A17" s="40" t="s">
         <v>23</v>
       </c>
@@ -5222,7 +5223,7 @@
       <c r="F18" s="41"/>
       <c r="G18" s="41"/>
     </row>
-    <row r="19" spans="1:7" ht="15">
+    <row r="19" spans="1:7">
       <c r="A19" s="40" t="s">
         <v>25</v>
       </c>
@@ -5250,7 +5251,7 @@
       <c r="F20" s="41"/>
       <c r="G20" s="41"/>
     </row>
-    <row r="21" spans="1:7" ht="15">
+    <row r="21" spans="1:7">
       <c r="A21" s="40" t="s">
         <v>27</v>
       </c>
@@ -5273,7 +5274,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15">
+    <row r="22" spans="1:7">
       <c r="A22" s="40" t="s">
         <v>31</v>
       </c>
@@ -5313,7 +5314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15">
+    <row r="24" spans="1:7">
       <c r="A24" s="40" t="s">
         <v>35</v>
       </c>
@@ -5336,7 +5337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15">
+    <row r="25" spans="1:7">
       <c r="A25" s="40" t="s">
         <v>37</v>
       </c>
@@ -5384,7 +5385,7 @@
         <v>28</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F27" s="40" t="s">
         <v>30</v>
@@ -5590,10 +5591,10 @@
         <v>58</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>59</v>
+        <v>206</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G37" s="40" t="s">
         <v>3</v>
@@ -5601,7 +5602,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B38" s="42">
         <v>46277</v>
@@ -5610,10 +5611,10 @@
         <v>46278</v>
       </c>
       <c r="D38" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" s="40" t="s">
         <v>61</v>
-      </c>
-      <c r="E38" s="40" t="s">
-        <v>62</v>
       </c>
       <c r="F38" s="40" t="s">
         <v>30</v>
@@ -5624,7 +5625,7 @@
     </row>
     <row r="39" spans="1:7" ht="17.25" customHeight="1">
       <c r="A39" s="41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B39" s="41"/>
       <c r="C39" s="41"/>
@@ -5635,7 +5636,7 @@
     </row>
     <row r="40" spans="1:7" ht="24.9" customHeight="1">
       <c r="A40" s="40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B40" s="42">
         <v>46270</v>
@@ -5644,10 +5645,10 @@
         <v>46270</v>
       </c>
       <c r="D40" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="40" t="s">
         <v>65</v>
-      </c>
-      <c r="E40" s="40" t="s">
-        <v>66</v>
       </c>
       <c r="F40" s="40" t="s">
         <v>30</v>
@@ -5658,7 +5659,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B41" s="42">
         <v>46270</v>
@@ -5681,7 +5682,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B42" s="42">
         <v>46285</v>
@@ -5690,10 +5691,10 @@
         <v>46285</v>
       </c>
       <c r="D42" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42" s="40" t="s">
         <v>69</v>
-      </c>
-      <c r="E42" s="40" t="s">
-        <v>70</v>
       </c>
       <c r="F42" s="40" t="s">
         <v>30</v>
@@ -5704,7 +5705,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B43" s="42">
         <v>46289</v>
@@ -5713,10 +5714,10 @@
         <v>46292</v>
       </c>
       <c r="D43" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" s="40" t="s">
         <v>72</v>
-      </c>
-      <c r="E43" s="40" t="s">
-        <v>73</v>
       </c>
       <c r="F43" s="40" t="s">
         <v>30</v>
@@ -5727,7 +5728,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B44" s="42">
         <v>46289</v>
@@ -5744,7 +5745,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B45" s="42">
         <v>46290</v>
@@ -5753,10 +5754,10 @@
         <v>46292</v>
       </c>
       <c r="D45" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" s="40" t="s">
         <v>76</v>
-      </c>
-      <c r="E45" s="40" t="s">
-        <v>77</v>
       </c>
       <c r="F45" s="40" t="s">
         <v>30</v>
@@ -5767,7 +5768,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B46" s="42">
         <v>46291</v>
@@ -5776,10 +5777,10 @@
         <v>46291</v>
       </c>
       <c r="D46" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E46" s="40" t="s">
         <v>79</v>
-      </c>
-      <c r="E46" s="40" t="s">
-        <v>80</v>
       </c>
       <c r="F46" s="40" t="s">
         <v>30</v>
@@ -5790,7 +5791,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B47" s="42">
         <v>46291</v>
@@ -5799,7 +5800,7 @@
         <v>46293</v>
       </c>
       <c r="D47" s="40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E47" s="40" t="s">
         <v>50</v>
@@ -5813,7 +5814,7 @@
     </row>
     <row r="48" spans="1:7" ht="24.9" customHeight="1">
       <c r="A48" s="41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B48" s="41"/>
       <c r="C48" s="41"/>
@@ -5824,7 +5825,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B49" s="42">
         <v>46297</v>
@@ -5833,10 +5834,10 @@
         <v>46299</v>
       </c>
       <c r="D49" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="E49" s="40" t="s">
         <v>85</v>
-      </c>
-      <c r="E49" s="40" t="s">
-        <v>86</v>
       </c>
       <c r="F49" s="40" t="s">
         <v>30</v>
@@ -5847,7 +5848,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B50" s="42">
         <v>46298</v>
@@ -5856,10 +5857,10 @@
         <v>46298</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F50" s="40" t="s">
         <v>30</v>
@@ -5870,7 +5871,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B51" s="42">
         <v>46298</v>
@@ -5882,7 +5883,7 @@
         <v>58</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F51" s="40" t="s">
         <v>30</v>
@@ -5893,7 +5894,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B52" s="42">
         <v>46312</v>
@@ -5905,7 +5906,7 @@
         <v>43</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F52" s="40" t="s">
         <v>30</v>
@@ -5916,7 +5917,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B53" s="42">
         <v>46312</v>
@@ -5925,10 +5926,10 @@
         <v>46312</v>
       </c>
       <c r="D53" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E53" s="40" t="s">
         <v>94</v>
-      </c>
-      <c r="E53" s="40" t="s">
-        <v>95</v>
       </c>
       <c r="F53" s="40" t="s">
         <v>30</v>
@@ -5939,7 +5940,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B54" s="42">
         <v>46318</v>
@@ -5948,10 +5949,10 @@
         <v>46320</v>
       </c>
       <c r="D54" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="E54" s="40" t="s">
         <v>97</v>
-      </c>
-      <c r="E54" s="40" t="s">
-        <v>98</v>
       </c>
       <c r="F54" s="40" t="s">
         <v>30</v>
@@ -5962,7 +5963,7 @@
     </row>
     <row r="55" spans="1:7" ht="24.9" customHeight="1">
       <c r="A55" s="40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B55" s="42">
         <v>46326</v>
@@ -5971,10 +5972,10 @@
         <v>46326</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F55" s="40" t="s">
         <v>30</v>
@@ -5985,7 +5986,7 @@
     </row>
     <row r="56" spans="1:7" ht="17.25" customHeight="1">
       <c r="A56" s="41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B56" s="41"/>
       <c r="C56" s="41"/>
@@ -5996,7 +5997,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B57" s="42">
         <v>46333</v>
@@ -6005,7 +6006,7 @@
         <v>46333</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E57" s="40" t="s">
         <v>50</v>
@@ -6019,7 +6020,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B58" s="42">
         <v>46340</v>
@@ -6028,10 +6029,10 @@
         <v>46341</v>
       </c>
       <c r="D58" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58" s="40" t="s">
         <v>104</v>
-      </c>
-      <c r="E58" s="40" t="s">
-        <v>105</v>
       </c>
       <c r="F58" s="40" t="s">
         <v>30</v>
@@ -6042,7 +6043,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B59" s="42">
         <v>46347</v>
@@ -6051,10 +6052,10 @@
         <v>46347</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F59" s="40" t="s">
         <v>30</v>
@@ -6065,7 +6066,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="40" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B60" s="42">
         <v>46347</v>
@@ -6077,7 +6078,7 @@
         <v>56</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F60" s="40" t="s">
         <v>30</v>
@@ -6088,7 +6089,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B61" s="42">
         <v>46353</v>
@@ -6097,10 +6098,10 @@
         <v>46355</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F61" s="40" t="s">
         <v>30</v>
@@ -6111,7 +6112,7 @@
     </row>
     <row r="62" spans="1:7" ht="24.9" customHeight="1">
       <c r="A62" s="40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B62" s="42">
         <v>46354</v>
@@ -6120,10 +6121,10 @@
         <v>46354</v>
       </c>
       <c r="D62" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62" s="40" t="s">
         <v>94</v>
-      </c>
-      <c r="E62" s="40" t="s">
-        <v>95</v>
       </c>
       <c r="F62" s="40" t="s">
         <v>30</v>
@@ -6134,7 +6135,7 @@
     </row>
     <row r="63" spans="1:7" ht="17.25" customHeight="1">
       <c r="A63" s="41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B63" s="41"/>
       <c r="C63" s="41"/>
@@ -6145,7 +6146,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B64" s="42">
         <v>46360</v>
@@ -6154,10 +6155,10 @@
         <v>46361</v>
       </c>
       <c r="D64" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F64" s="40" t="s">
         <v>30</v>
@@ -6168,7 +6169,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B65" s="42">
         <v>46368</v>
@@ -6177,10 +6178,10 @@
         <v>46369</v>
       </c>
       <c r="D65" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="E65" s="40" t="s">
         <v>104</v>
-      </c>
-      <c r="E65" s="40" t="s">
-        <v>105</v>
       </c>
       <c r="F65" s="40" t="s">
         <v>30</v>
@@ -6191,7 +6192,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B66" s="42">
         <v>46366</v>
@@ -6200,10 +6201,10 @@
         <v>46370</v>
       </c>
       <c r="D66" s="40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F66" s="40" t="s">
         <v>30</v>
@@ -6214,7 +6215,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B67" s="42">
         <v>46372</v>
@@ -6231,7 +6232,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="40" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B68" s="42">
         <v>46381</v>
@@ -6248,7 +6249,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B69" s="42">
         <v>46382</v>
@@ -6265,7 +6266,7 @@
     </row>
     <row r="70" spans="1:7" ht="17.25" customHeight="1">
       <c r="A70" s="41" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B70" s="41"/>
       <c r="C70" s="41"/>
@@ -6293,7 +6294,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B72" s="42">
         <v>46395</v>
@@ -6302,10 +6303,10 @@
         <v>46396</v>
       </c>
       <c r="D72" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F72" s="40" t="s">
         <v>30</v>
@@ -6316,7 +6317,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B73" s="42">
         <v>46403</v>
@@ -6325,10 +6326,10 @@
         <v>46404</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F73" s="40" t="s">
         <v>30</v>
@@ -6339,7 +6340,7 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B74" s="42">
         <v>46403</v>
@@ -6348,10 +6349,10 @@
         <v>46404</v>
       </c>
       <c r="D74" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="E74" s="40" t="s">
         <v>104</v>
-      </c>
-      <c r="E74" s="40" t="s">
-        <v>105</v>
       </c>
       <c r="F74" s="40" t="s">
         <v>30</v>
@@ -6362,7 +6363,7 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B75" s="42">
         <v>46403</v>
@@ -6371,10 +6372,10 @@
         <v>46403</v>
       </c>
       <c r="D75" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E75" s="40" t="s">
         <v>94</v>
-      </c>
-      <c r="E75" s="40" t="s">
-        <v>95</v>
       </c>
       <c r="F75" s="40" t="s">
         <v>30</v>
@@ -6385,7 +6386,7 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B76" s="42">
         <v>46403</v>
@@ -6394,10 +6395,10 @@
         <v>46403</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F76" s="40" t="s">
         <v>30</v>
@@ -6408,7 +6409,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B77" s="42">
         <v>46403</v>
@@ -6431,7 +6432,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B78" s="42">
         <v>46396</v>
@@ -6443,7 +6444,7 @@
         <v>46</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F78" s="40" t="s">
         <v>30</v>
@@ -6454,7 +6455,7 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B79" s="42">
         <v>46404</v>
@@ -6463,10 +6464,10 @@
         <v>46404</v>
       </c>
       <c r="D79" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="E79" s="40" t="s">
         <v>132</v>
-      </c>
-      <c r="E79" s="40" t="s">
-        <v>133</v>
       </c>
       <c r="F79" s="40" t="s">
         <v>30</v>
@@ -6477,7 +6478,7 @@
     </row>
     <row r="80" spans="1:7" ht="24.9" customHeight="1">
       <c r="A80" s="40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B80" s="42">
         <v>46410</v>
@@ -6486,10 +6487,10 @@
         <v>46410</v>
       </c>
       <c r="D80" s="40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F80" s="40" t="s">
         <v>30</v>
@@ -6500,7 +6501,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B81" s="42">
         <v>46411</v>
@@ -6509,10 +6510,10 @@
         <v>46411</v>
       </c>
       <c r="D81" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="E81" s="40" t="s">
         <v>137</v>
-      </c>
-      <c r="E81" s="40" t="s">
-        <v>138</v>
       </c>
       <c r="F81" s="40" t="s">
         <v>30</v>
@@ -6523,7 +6524,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B82" s="42">
         <v>46415</v>
@@ -6532,10 +6533,10 @@
         <v>46415</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F82" s="40" t="s">
         <v>30</v>
@@ -6546,7 +6547,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B83" s="42">
         <v>46415</v>
@@ -6555,10 +6556,10 @@
         <v>46417</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F83" s="40" t="s">
         <v>30</v>
@@ -6569,7 +6570,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="40" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B84" s="42">
         <v>46416</v>
@@ -6578,10 +6579,10 @@
         <v>46416</v>
       </c>
       <c r="D84" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="E84" s="40" t="s">
         <v>144</v>
-      </c>
-      <c r="E84" s="40" t="s">
-        <v>145</v>
       </c>
       <c r="F84" s="40" t="s">
         <v>30</v>
@@ -6592,7 +6593,7 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B85" s="42">
         <v>46416</v>
@@ -6601,10 +6602,10 @@
         <v>46417</v>
       </c>
       <c r="D85" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="E85" s="40" t="s">
         <v>147</v>
-      </c>
-      <c r="E85" s="40" t="s">
-        <v>148</v>
       </c>
       <c r="F85" s="40" t="s">
         <v>30</v>
@@ -6615,7 +6616,7 @@
     </row>
     <row r="86" spans="1:7" ht="17.25" customHeight="1">
       <c r="A86" s="40" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B86" s="42">
         <v>46416</v>
@@ -6624,10 +6625,10 @@
         <v>46418</v>
       </c>
       <c r="D86" s="40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F86" s="40" t="s">
         <v>30</v>
@@ -6638,7 +6639,7 @@
     </row>
     <row r="87" spans="1:7" ht="24.9" customHeight="1">
       <c r="A87" s="40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B87" s="42">
         <v>46417</v>
@@ -6647,10 +6648,10 @@
         <v>46418</v>
       </c>
       <c r="D87" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="E87" s="40" t="s">
         <v>152</v>
-      </c>
-      <c r="E87" s="40" t="s">
-        <v>153</v>
       </c>
       <c r="F87" s="40" t="s">
         <v>30</v>
@@ -6661,7 +6662,7 @@
     </row>
     <row r="88" spans="1:7" ht="16.8">
       <c r="A88" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B88" s="41"/>
       <c r="C88" s="41"/>
@@ -6672,7 +6673,7 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B89" s="42">
         <v>46422</v>
@@ -6681,10 +6682,10 @@
         <v>46422</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F89" s="40" t="s">
         <v>30</v>
@@ -6718,7 +6719,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B91" s="42">
         <v>46424</v>
@@ -6727,10 +6728,10 @@
         <v>46424</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F91" s="40" t="s">
         <v>30</v>
@@ -6741,7 +6742,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B92" s="42">
         <v>46424</v>
@@ -6753,7 +6754,7 @@
         <v>58</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F92" s="40" t="s">
         <v>30</v>
@@ -6764,7 +6765,7 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B93" s="42">
         <v>46431</v>
@@ -6773,7 +6774,7 @@
         <v>46431</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E93" s="40" t="s">
         <v>50</v>
@@ -6787,7 +6788,7 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B94" s="42">
         <v>46431</v>
@@ -6796,10 +6797,10 @@
         <v>46432</v>
       </c>
       <c r="D94" s="40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F94" s="40" t="s">
         <v>30</v>
@@ -6810,7 +6811,7 @@
     </row>
     <row r="95" spans="1:7" ht="17.25" customHeight="1">
       <c r="A95" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B95" s="42">
         <v>46438</v>
@@ -6819,10 +6820,10 @@
         <v>46438</v>
       </c>
       <c r="D95" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E95" s="40" t="s">
         <v>94</v>
-      </c>
-      <c r="E95" s="40" t="s">
-        <v>95</v>
       </c>
       <c r="F95" s="40" t="s">
         <v>30</v>
@@ -6833,7 +6834,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B96" s="42">
         <v>46445</v>
@@ -6842,10 +6843,10 @@
         <v>46446</v>
       </c>
       <c r="D96" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="E96" s="40" t="s">
         <v>163</v>
-      </c>
-      <c r="E96" s="40" t="s">
-        <v>164</v>
       </c>
       <c r="F96" s="40" t="s">
         <v>30</v>
@@ -6856,7 +6857,7 @@
     </row>
     <row r="97" spans="1:7" ht="16.8">
       <c r="A97" s="41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B97" s="41"/>
       <c r="C97" s="41"/>
@@ -6867,7 +6868,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B98" s="42">
         <v>46447</v>
@@ -6876,7 +6877,7 @@
         <v>46447</v>
       </c>
       <c r="D98" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E98" s="40" t="s">
         <v>50</v>
@@ -6890,7 +6891,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B99" s="42">
         <v>46448</v>
@@ -6899,7 +6900,7 @@
         <v>46448</v>
       </c>
       <c r="D99" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E99" s="40" t="s">
         <v>50</v>
@@ -6913,7 +6914,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B100" s="42">
         <v>46449</v>
@@ -6922,7 +6923,7 @@
         <v>46449</v>
       </c>
       <c r="D100" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E100" s="40" t="s">
         <v>50</v>
@@ -6936,7 +6937,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B101" s="42">
         <v>46450</v>
@@ -6945,7 +6946,7 @@
         <v>46450</v>
       </c>
       <c r="D101" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E101" s="40" t="s">
         <v>50</v>
@@ -6959,7 +6960,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B102" s="42">
         <v>46462</v>
@@ -6968,7 +6969,7 @@
         <v>46464</v>
       </c>
       <c r="D102" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E102" s="40" t="s">
         <v>50</v>
@@ -6982,7 +6983,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B103" s="42">
         <v>46465</v>
@@ -6991,7 +6992,7 @@
         <v>46469</v>
       </c>
       <c r="D103" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E103" s="40" t="s">
         <v>50</v>
@@ -7073,7 +7074,7 @@
     </row>
     <row r="108" spans="1:7" ht="24.9" customHeight="1">
       <c r="A108" s="40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B108" s="42">
         <v>46477</v>
@@ -7085,7 +7086,7 @@
         <v>50</v>
       </c>
       <c r="E108" s="40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F108" s="40" t="s">
         <v>30</v>
@@ -7096,7 +7097,7 @@
     </row>
     <row r="109" spans="1:7" ht="16.8">
       <c r="A109" s="41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B109" s="41"/>
       <c r="C109" s="41"/>
@@ -7107,7 +7108,7 @@
     </row>
     <row r="110" spans="1:7" ht="24.9" customHeight="1">
       <c r="A110" s="40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B110" s="42">
         <v>46478</v>
@@ -7119,7 +7120,7 @@
         <v>50</v>
       </c>
       <c r="E110" s="40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F110" s="40" t="s">
         <v>30</v>
@@ -7130,7 +7131,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B111" s="42">
         <v>46482</v>
@@ -7142,7 +7143,7 @@
         <v>50</v>
       </c>
       <c r="E111" s="40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F111" s="40" t="s">
         <v>30</v>
@@ -7153,7 +7154,7 @@
     </row>
     <row r="112" spans="1:7" s="24" customFormat="1">
       <c r="A112" s="40" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B112" s="42">
         <v>46490</v>
@@ -7162,7 +7163,7 @@
         <v>46494</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E112" s="40" t="s">
         <v>50</v>
@@ -7176,7 +7177,7 @@
     </row>
     <row r="113" spans="1:7" ht="24.9" customHeight="1">
       <c r="A113" s="40" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B113" s="42">
         <v>46500</v>
@@ -7185,7 +7186,7 @@
         <v>46504</v>
       </c>
       <c r="D113" s="40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E113" s="40" t="s">
         <v>50</v>
@@ -7216,7 +7217,7 @@
     </row>
     <row r="115" spans="1:7" ht="17.25" customHeight="1">
       <c r="A115" s="41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B115" s="41"/>
       <c r="C115" s="41"/>
@@ -7244,7 +7245,7 @@
     </row>
     <row r="117" spans="1:7" ht="17.25" customHeight="1">
       <c r="A117" s="41" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B117" s="41"/>
       <c r="C117" s="41"/>
@@ -7272,7 +7273,7 @@
     </row>
     <row r="119" spans="1:7" ht="17.25" customHeight="1">
       <c r="A119" s="41" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B119" s="41"/>
       <c r="C119" s="41"/>
@@ -7300,7 +7301,7 @@
     </row>
     <row r="121" spans="1:7" ht="17.25" customHeight="1">
       <c r="A121" s="41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B121" s="41"/>
       <c r="C121" s="41"/>
@@ -7311,7 +7312,7 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B122" s="42">
         <v>46654</v>
@@ -7328,7 +7329,7 @@
     </row>
     <row r="123" spans="1:7" ht="16.8">
       <c r="A123" s="41" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B123" s="41"/>
       <c r="C123" s="41"/>
@@ -7339,7 +7340,7 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B124" s="42">
         <v>46737</v>
@@ -7356,7 +7357,7 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="40" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B125" s="42">
         <v>46746</v>
@@ -7373,7 +7374,7 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B126" s="42">
         <v>46747</v>
@@ -7390,7 +7391,7 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B127" s="42">
         <v>46748</v>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="206">
   <si>
     <t>KZNA Calendar Season 2026–2027</t>
   </si>
@@ -646,9 +646,6 @@
   </si>
   <si>
     <t>Jollife Pool Pmb</t>
-  </si>
-  <si>
-    <t>Kloof/Joliffe/Reddam</t>
   </si>
 </sst>
 </file>
@@ -5591,7 +5588,7 @@
         <v>58</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>206</v>
+        <v>50</v>
       </c>
       <c r="F37" s="40" t="s">
         <v>50</v>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -1071,11 +1071,11 @@
     <xf numFmtId="0" fontId="25" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1157,7 +1157,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1202,7 +1202,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1548,7 +1548,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="45"/>
@@ -1566,7 +1566,7 @@
       <c r="G2" s="45"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="46" t="s">
         <v>184</v>
       </c>
       <c r="B5" s="45"/>
@@ -1841,7 +1841,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="46" t="s">
         <v>192</v>
       </c>
       <c r="B18" s="45"/>
@@ -2122,7 +2122,7 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="44" t="s">
+      <c r="A31" s="46" t="s">
         <v>193</v>
       </c>
       <c r="B31" s="45"/>
@@ -2421,7 +2421,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="44" t="s">
+      <c r="A46" s="46" t="s">
         <v>194</v>
       </c>
       <c r="B46" s="45"/>
@@ -2703,7 +2703,7 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="44" t="s">
+      <c r="A59" s="46" t="s">
         <v>195</v>
       </c>
       <c r="B59" s="45"/>
@@ -2986,7 +2986,7 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="44" t="s">
+      <c r="A72" s="46" t="s">
         <v>196</v>
       </c>
       <c r="B72" s="45"/>
@@ -3280,7 +3280,7 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="44" t="s">
+      <c r="A87" s="46" t="s">
         <v>197</v>
       </c>
       <c r="B87" s="45"/>
@@ -3449,8 +3449,8 @@
         <v/>
       </c>
       <c r="C94" s="6" t="str">
-        <f t="array" ref="C94">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C93)*(EventsTable[End Date]&gt;=C93))), "")</f>
-        <v>• Day of Reconciliation</v>
+        <f t="array" aca="1" ref="C94" ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C93)*(EventsTable[End Date]&gt;=C93))), "")</f>
+        <v/>
       </c>
       <c r="D94" s="5" t="str">
         <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D93)*(EventsTable[End Date]&gt;=D93))), "")</f>
@@ -3561,7 +3561,7 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="44" t="s">
+      <c r="A100" s="46" t="s">
         <v>198</v>
       </c>
       <c r="B100" s="45"/>
@@ -3855,7 +3855,7 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="44" t="s">
+      <c r="A113" s="46" t="s">
         <v>199</v>
       </c>
       <c r="B113" s="45"/>
@@ -4104,7 +4104,7 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="44" t="s">
+      <c r="A124" s="46" t="s">
         <v>200</v>
       </c>
       <c r="B124" s="45"/>
@@ -4385,7 +4385,7 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="44" t="s">
+      <c r="A137" s="46" t="s">
         <v>201</v>
       </c>
       <c r="B137" s="45"/>
@@ -4660,7 +4660,7 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="44" t="s">
+      <c r="A150" s="46" t="s">
         <v>202</v>
       </c>
       <c r="B150" s="45"/>
@@ -4958,6 +4958,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -4966,12 +4972,6 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -4992,7 +4992,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="45"/>
@@ -5582,7 +5582,7 @@
         <v>46256</v>
       </c>
       <c r="C37" s="42">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="D37" s="40" t="s">
         <v>58</v>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Calendar" sheetId="1" r:id="rId1"/>
     <sheet name="Events List" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="204">
   <si>
     <t>KZNA Calendar Season 2026–2027</t>
   </si>
@@ -171,9 +172,6 @@
     <t>Ethekwini</t>
   </si>
   <si>
-    <t>Beavers, Kloof</t>
-  </si>
-  <si>
     <t>MSC Gala - Margate</t>
   </si>
   <si>
@@ -244,9 +242,6 @@
   </si>
   <si>
     <t>SA Swimming</t>
-  </si>
-  <si>
-    <t>TBC, Joliffe</t>
   </si>
   <si>
     <t>Heritage Day</t>
@@ -958,7 +953,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1079,6 +1074,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="datetime" xfId="1"/>
@@ -1086,7 +1082,91 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="pro_day_only_🏊UnsanctionedCalendar" xfId="3"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9F1239"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC026D3"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF15803D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFA16207"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7E22CE"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF0369A1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFEA580C"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9F1239"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC026D3"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF15803D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFA16207"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7E22CE"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF0369A1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFEA580C"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1237,8 +1317,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G127">
-  <autoFilter ref="A9:G127"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G128">
+  <autoFilter ref="A9:G128"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Event Name"/>
     <tableColumn id="2" name="Start Date"/>
@@ -1567,7 +1647,7 @@
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
       <c r="A5" s="46" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B5" s="45"/>
       <c r="C5" s="45"/>
@@ -1578,25 +1658,25 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -1624,32 +1704,32 @@
     </row>
     <row r="8" spans="1:7" ht="75" customHeight="1">
       <c r="A8" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A7)*(EventsTable[End Date]&gt;=A7))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A7)*(EventsTable[End Date]&gt;=A7))), "")</f>
         <v/>
       </c>
       <c r="B8" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B7)*(EventsTable[End Date]&gt;=B7))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B7)*(EventsTable[End Date]&gt;=B7))), "")</f>
         <v/>
       </c>
       <c r="C8" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C7)*(EventsTable[End Date]&gt;=C7))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C7)*(EventsTable[End Date]&gt;=C7))), "")</f>
         <v/>
       </c>
       <c r="D8" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D7)*(EventsTable[End Date]&gt;=D7))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D7)*(EventsTable[End Date]&gt;=D7))), "")</f>
         <v/>
       </c>
       <c r="E8" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E7)*(EventsTable[End Date]&gt;=E7))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E7)*(EventsTable[End Date]&gt;=E7))), "")</f>
         <v/>
       </c>
       <c r="F8" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F7)*(EventsTable[End Date]&gt;=F7))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F7)*(EventsTable[End Date]&gt;=F7))), "")</f>
         <v/>
       </c>
       <c r="G8" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G7)*(EventsTable[End Date]&gt;=G7))), "")</f>
-        <v>• Seals Gala 1</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G7)*(EventsTable[End Date]&gt;=G7))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -1677,31 +1757,31 @@
     </row>
     <row r="10" spans="1:7" ht="75" customHeight="1">
       <c r="A10" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A9)*(EventsTable[End Date]&gt;=A9))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A9)*(EventsTable[End Date]&gt;=A9))), "")</f>
         <v/>
       </c>
       <c r="B10" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B9)*(EventsTable[End Date]&gt;=B9))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B9)*(EventsTable[End Date]&gt;=B9))), "")</f>
         <v/>
       </c>
       <c r="C10" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C9)*(EventsTable[End Date]&gt;=C9))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C9)*(EventsTable[End Date]&gt;=C9))), "")</f>
         <v/>
       </c>
       <c r="D10" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D9)*(EventsTable[End Date]&gt;=D9))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D9)*(EventsTable[End Date]&gt;=D9))), "")</f>
         <v/>
       </c>
       <c r="E10" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E9)*(EventsTable[End Date]&gt;=E9))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E9)*(EventsTable[End Date]&gt;=E9))), "")</f>
         <v/>
       </c>
       <c r="F10" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F9)*(EventsTable[End Date]&gt;=F9))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F9)*(EventsTable[End Date]&gt;=F9))), "")</f>
         <v/>
       </c>
       <c r="G10" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G9)*(EventsTable[End Date]&gt;=G9))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G9)*(EventsTable[End Date]&gt;=G9))), "")</f>
         <v/>
       </c>
     </row>
@@ -1730,33 +1810,32 @@
     </row>
     <row r="12" spans="1:7" ht="75" customHeight="1">
       <c r="A12" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A11)*(EventsTable[End Date]&gt;=A11))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A11)*(EventsTable[End Date]&gt;=A11))), "")</f>
         <v/>
       </c>
       <c r="B12" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B11)*(EventsTable[End Date]&gt;=B11))), "")</f>
-        <v>• Youth Day</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B11)*(EventsTable[End Date]&gt;=B11))), "")</f>
+        <v/>
       </c>
       <c r="C12" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C11)*(EventsTable[End Date]&gt;=C11))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C11)*(EventsTable[End Date]&gt;=C11))), "")</f>
         <v/>
       </c>
       <c r="D12" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D11)*(EventsTable[End Date]&gt;=D11))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D11)*(EventsTable[End Date]&gt;=D11))), "")</f>
         <v/>
       </c>
       <c r="E12" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E11)*(EventsTable[End Date]&gt;=E11))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E11)*(EventsTable[End Date]&gt;=E11))), "")</f>
         <v/>
       </c>
       <c r="F12" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F11)*(EventsTable[End Date]&gt;=F11))), "")</f>
-        <v>• Kloof Winter Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F11)*(EventsTable[End Date]&gt;=F11))), "")</f>
+        <v/>
       </c>
       <c r="G12" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G11)*(EventsTable[End Date]&gt;=G11))), "")</f>
-        <v>• Kloof Winter Championships
-• Seals Gala 2</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G11)*(EventsTable[End Date]&gt;=G11))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -1784,32 +1863,32 @@
     </row>
     <row r="14" spans="1:7" ht="75" customHeight="1">
       <c r="A14" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A13)*(EventsTable[End Date]&gt;=A13))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A13)*(EventsTable[End Date]&gt;=A13))), "")</f>
         <v/>
       </c>
       <c r="B14" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B13)*(EventsTable[End Date]&gt;=B13))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B13)*(EventsTable[End Date]&gt;=B13))), "")</f>
         <v/>
       </c>
       <c r="C14" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C13)*(EventsTable[End Date]&gt;=C13))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C13)*(EventsTable[End Date]&gt;=C13))), "")</f>
         <v/>
       </c>
       <c r="D14" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D13)*(EventsTable[End Date]&gt;=D13))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D13)*(EventsTable[End Date]&gt;=D13))), "")</f>
         <v/>
       </c>
       <c r="E14" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E13)*(EventsTable[End Date]&gt;=E13))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E13)*(EventsTable[End Date]&gt;=E13))), "")</f>
         <v/>
       </c>
       <c r="F14" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F13)*(EventsTable[End Date]&gt;=F13))), "")</f>
-        <v>• Grand Prix SC Pre CWG</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F13)*(EventsTable[End Date]&gt;=F13))), "")</f>
+        <v/>
       </c>
       <c r="G14" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G13)*(EventsTable[End Date]&gt;=G13))), "")</f>
-        <v>• Grand Prix SC Pre CWG</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G13)*(EventsTable[End Date]&gt;=G13))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -1827,11 +1906,11 @@
     </row>
     <row r="16" spans="1:7" ht="75" customHeight="1">
       <c r="A16" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A15)*(EventsTable[End Date]&gt;=A15))), "")</f>
-        <v>• Grand Prix SC Pre CWG</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A15)*(EventsTable[End Date]&gt;=A15))), "")</f>
+        <v/>
       </c>
       <c r="B16" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B15)*(EventsTable[End Date]&gt;=B15))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B15)*(EventsTable[End Date]&gt;=B15))), "")</f>
         <v/>
       </c>
       <c r="C16" s="10"/>
@@ -1842,7 +1921,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
       <c r="A18" s="46" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B18" s="45"/>
       <c r="C18" s="45"/>
@@ -1853,25 +1932,25 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -1897,23 +1976,23 @@
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
       <c r="C21" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C20)*(EventsTable[End Date]&gt;=C20))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C20)*(EventsTable[End Date]&gt;=C20))), "")</f>
         <v/>
       </c>
       <c r="D21" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D20)*(EventsTable[End Date]&gt;=D20))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D20)*(EventsTable[End Date]&gt;=D20))), "")</f>
         <v/>
       </c>
       <c r="E21" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E20)*(EventsTable[End Date]&gt;=E20))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E20)*(EventsTable[End Date]&gt;=E20))), "")</f>
         <v/>
       </c>
       <c r="F21" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F20)*(EventsTable[End Date]&gt;=F20))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F20)*(EventsTable[End Date]&gt;=F20))), "")</f>
         <v/>
       </c>
       <c r="G21" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G20)*(EventsTable[End Date]&gt;=G20))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G20)*(EventsTable[End Date]&gt;=G20))), "")</f>
         <v/>
       </c>
     </row>
@@ -1942,31 +2021,31 @@
     </row>
     <row r="23" spans="1:7" ht="75" customHeight="1">
       <c r="A23" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A22)*(EventsTable[End Date]&gt;=A22))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A22)*(EventsTable[End Date]&gt;=A22))), "")</f>
         <v/>
       </c>
       <c r="B23" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B22)*(EventsTable[End Date]&gt;=B22))), "")</f>
-        <v>• Prestige LC Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B22)*(EventsTable[End Date]&gt;=B22))), "")</f>
+        <v/>
       </c>
       <c r="C23" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C22)*(EventsTable[End Date]&gt;=C22))), "")</f>
-        <v>• Prestige LC Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C22)*(EventsTable[End Date]&gt;=C22))), "")</f>
+        <v/>
       </c>
       <c r="D23" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D22)*(EventsTable[End Date]&gt;=D22))), "")</f>
-        <v>• Prestige LC Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D22)*(EventsTable[End Date]&gt;=D22))), "")</f>
+        <v/>
       </c>
       <c r="E23" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E22)*(EventsTable[End Date]&gt;=E22))), "")</f>
-        <v>• Prestige LC Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E22)*(EventsTable[End Date]&gt;=E22))), "")</f>
+        <v/>
       </c>
       <c r="F23" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F22)*(EventsTable[End Date]&gt;=F22))), "")</f>
-        <v>• Prestige LC Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F22)*(EventsTable[End Date]&gt;=F22))), "")</f>
+        <v/>
       </c>
       <c r="G23" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G22)*(EventsTable[End Date]&gt;=G22))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G22)*(EventsTable[End Date]&gt;=G22))), "")</f>
         <v/>
       </c>
     </row>
@@ -1995,31 +2074,31 @@
     </row>
     <row r="25" spans="1:7" ht="75" customHeight="1">
       <c r="A25" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A24)*(EventsTable[End Date]&gt;=A24))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A24)*(EventsTable[End Date]&gt;=A24))), "")</f>
         <v/>
       </c>
       <c r="B25" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B24)*(EventsTable[End Date]&gt;=B24))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B24)*(EventsTable[End Date]&gt;=B24))), "")</f>
         <v/>
       </c>
       <c r="C25" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C24)*(EventsTable[End Date]&gt;=C24))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C24)*(EventsTable[End Date]&gt;=C24))), "")</f>
         <v/>
       </c>
       <c r="D25" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D24)*(EventsTable[End Date]&gt;=D24))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D24)*(EventsTable[End Date]&gt;=D24))), "")</f>
         <v/>
       </c>
       <c r="E25" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E24)*(EventsTable[End Date]&gt;=E24))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E24)*(EventsTable[End Date]&gt;=E24))), "")</f>
         <v/>
       </c>
       <c r="F25" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F24)*(EventsTable[End Date]&gt;=F24))), "")</f>
-        <v>• UDA District Gala 1</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F24)*(EventsTable[End Date]&gt;=F24))), "")</f>
+        <v/>
       </c>
       <c r="G25" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G24)*(EventsTable[End Date]&gt;=G24))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G24)*(EventsTable[End Date]&gt;=G24))), "")</f>
         <v/>
       </c>
     </row>
@@ -2048,34 +2127,32 @@
     </row>
     <row r="27" spans="1:7" ht="75" customHeight="1">
       <c r="A27" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A26)*(EventsTable[End Date]&gt;=A26))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A26)*(EventsTable[End Date]&gt;=A26))), "")</f>
         <v/>
       </c>
       <c r="B27" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B26)*(EventsTable[End Date]&gt;=B26))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B26)*(EventsTable[End Date]&gt;=B26))), "")</f>
         <v/>
       </c>
       <c r="C27" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C26)*(EventsTable[End Date]&gt;=C26))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C26)*(EventsTable[End Date]&gt;=C26))), "")</f>
         <v/>
       </c>
       <c r="D27" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D26)*(EventsTable[End Date]&gt;=D26))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D26)*(EventsTable[End Date]&gt;=D26))), "")</f>
         <v/>
       </c>
       <c r="E27" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E26)*(EventsTable[End Date]&gt;=E26))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E26)*(EventsTable[End Date]&gt;=E26))), "")</f>
         <v/>
       </c>
       <c r="F27" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F26)*(EventsTable[End Date]&gt;=F26))), "")</f>
-        <v>• EDA Gala 1&amp; 2 SC - TBC
-• MSC Gala - Margate</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F26)*(EventsTable[End Date]&gt;=F26))), "")</f>
+        <v/>
       </c>
       <c r="G27" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G26)*(EventsTable[End Date]&gt;=G26))), "")</f>
-        <v>• EDA Gala 1&amp; 2 SC - TBC
-• MSC Gala - Margate</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G26)*(EventsTable[End Date]&gt;=G26))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2099,23 +2176,23 @@
     </row>
     <row r="29" spans="1:7" ht="75" customHeight="1">
       <c r="A29" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A28)*(EventsTable[End Date]&gt;=A28))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A28)*(EventsTable[End Date]&gt;=A28))), "")</f>
         <v/>
       </c>
       <c r="B29" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B28)*(EventsTable[End Date]&gt;=B28))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B28)*(EventsTable[End Date]&gt;=B28))), "")</f>
         <v/>
       </c>
       <c r="C29" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C28)*(EventsTable[End Date]&gt;=C28))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C28)*(EventsTable[End Date]&gt;=C28))), "")</f>
         <v/>
       </c>
       <c r="D29" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D28)*(EventsTable[End Date]&gt;=D28))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D28)*(EventsTable[End Date]&gt;=D28))), "")</f>
         <v/>
       </c>
       <c r="E29" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E28)*(EventsTable[End Date]&gt;=E28))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E28)*(EventsTable[End Date]&gt;=E28))), "")</f>
         <v/>
       </c>
       <c r="F29" s="11"/>
@@ -2123,7 +2200,7 @@
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
       <c r="A31" s="46" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B31" s="45"/>
       <c r="C31" s="45"/>
@@ -2134,25 +2211,25 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2175,11 +2252,11 @@
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
       <c r="F34" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F33)*(EventsTable[End Date]&gt;=F33))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F33)*(EventsTable[End Date]&gt;=F33))), "")</f>
         <v/>
       </c>
       <c r="G34" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G33)*(EventsTable[End Date]&gt;=G33))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G33)*(EventsTable[End Date]&gt;=G33))), "")</f>
         <v/>
       </c>
     </row>
@@ -2208,33 +2285,32 @@
     </row>
     <row r="36" spans="1:7" ht="75" customHeight="1">
       <c r="A36" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A35)*(EventsTable[End Date]&gt;=A35))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A35)*(EventsTable[End Date]&gt;=A35))), "")</f>
         <v/>
       </c>
       <c r="B36" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B35)*(EventsTable[End Date]&gt;=B35))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B35)*(EventsTable[End Date]&gt;=B35))), "")</f>
         <v/>
       </c>
       <c r="C36" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C35)*(EventsTable[End Date]&gt;=C35))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C35)*(EventsTable[End Date]&gt;=C35))), "")</f>
         <v/>
       </c>
       <c r="D36" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D35)*(EventsTable[End Date]&gt;=D35))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D35)*(EventsTable[End Date]&gt;=D35))), "")</f>
         <v/>
       </c>
       <c r="E36" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E35)*(EventsTable[End Date]&gt;=E35))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E35)*(EventsTable[End Date]&gt;=E35))), "")</f>
         <v/>
       </c>
       <c r="F36" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F35)*(EventsTable[End Date]&gt;=F35))), "")</f>
-        <v>• Kloof Age Group Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F35)*(EventsTable[End Date]&gt;=F35))), "")</f>
+        <v/>
       </c>
       <c r="G36" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G35)*(EventsTable[End Date]&gt;=G35))), "")</f>
-        <v>• Kloof Age Group Championships
-• National Women's Day</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G35)*(EventsTable[End Date]&gt;=G35))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="37" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2262,32 +2338,31 @@
     </row>
     <row r="38" spans="1:7" ht="75" customHeight="1">
       <c r="A38" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A37)*(EventsTable[End Date]&gt;=A37))), "")</f>
-        <v>• National Women's Day</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A37)*(EventsTable[End Date]&gt;=A37))), "")</f>
+        <v/>
       </c>
       <c r="B38" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B37)*(EventsTable[End Date]&gt;=B37))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B37)*(EventsTable[End Date]&gt;=B37))), "")</f>
         <v/>
       </c>
       <c r="C38" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C37)*(EventsTable[End Date]&gt;=C37))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C37)*(EventsTable[End Date]&gt;=C37))), "")</f>
         <v/>
       </c>
       <c r="D38" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D37)*(EventsTable[End Date]&gt;=D37))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D37)*(EventsTable[End Date]&gt;=D37))), "")</f>
         <v/>
       </c>
       <c r="E38" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E37)*(EventsTable[End Date]&gt;=E37))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E37)*(EventsTable[End Date]&gt;=E37))), "")</f>
         <v/>
       </c>
       <c r="F38" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F37)*(EventsTable[End Date]&gt;=F37))), "")</f>
-        <v>• UDA District Gala
-• AG Gala - Penguins</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F37)*(EventsTable[End Date]&gt;=F37))), "")</f>
+        <v/>
       </c>
       <c r="G38" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G37)*(EventsTable[End Date]&gt;=G37))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G37)*(EventsTable[End Date]&gt;=G37))), "")</f>
         <v/>
       </c>
     </row>
@@ -2316,32 +2391,32 @@
     </row>
     <row r="40" spans="1:7" ht="75" customHeight="1">
       <c r="A40" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A39)*(EventsTable[End Date]&gt;=A39))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A39)*(EventsTable[End Date]&gt;=A39))), "")</f>
         <v/>
       </c>
       <c r="B40" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B39)*(EventsTable[End Date]&gt;=B39))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B39)*(EventsTable[End Date]&gt;=B39))), "")</f>
         <v/>
       </c>
       <c r="C40" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C39)*(EventsTable[End Date]&gt;=C39))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C39)*(EventsTable[End Date]&gt;=C39))), "")</f>
         <v/>
       </c>
       <c r="D40" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D39)*(EventsTable[End Date]&gt;=D39))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D39)*(EventsTable[End Date]&gt;=D39))), "")</f>
         <v/>
       </c>
       <c r="E40" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E39)*(EventsTable[End Date]&gt;=E39))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E39)*(EventsTable[End Date]&gt;=E39))), "")</f>
         <v/>
       </c>
       <c r="F40" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F39)*(EventsTable[End Date]&gt;=F39))), "")</f>
-        <v>• KZN Short Course Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F39)*(EventsTable[End Date]&gt;=F39))), "")</f>
+        <v/>
       </c>
       <c r="G40" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G39)*(EventsTable[End Date]&gt;=G39))), "")</f>
-        <v>• KZN Short Course Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G39)*(EventsTable[End Date]&gt;=G39))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="41" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2369,31 +2444,31 @@
     </row>
     <row r="42" spans="1:7" ht="75" customHeight="1">
       <c r="A42" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A41)*(EventsTable[End Date]&gt;=A41))), "")</f>
-        <v>• KZN Short Course Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A41)*(EventsTable[End Date]&gt;=A41))), "")</f>
+        <v/>
       </c>
       <c r="B42" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B41)*(EventsTable[End Date]&gt;=B41))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B41)*(EventsTable[End Date]&gt;=B41))), "")</f>
         <v/>
       </c>
       <c r="C42" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C41)*(EventsTable[End Date]&gt;=C41))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C41)*(EventsTable[End Date]&gt;=C41))), "")</f>
         <v/>
       </c>
       <c r="D42" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D41)*(EventsTable[End Date]&gt;=D41))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D41)*(EventsTable[End Date]&gt;=D41))), "")</f>
         <v/>
       </c>
       <c r="E42" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E41)*(EventsTable[End Date]&gt;=E41))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E41)*(EventsTable[End Date]&gt;=E41))), "")</f>
         <v/>
       </c>
       <c r="F42" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F41)*(EventsTable[End Date]&gt;=F41))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F41)*(EventsTable[End Date]&gt;=F41))), "")</f>
         <v/>
       </c>
       <c r="G42" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G41)*(EventsTable[End Date]&gt;=G41))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G41)*(EventsTable[End Date]&gt;=G41))), "")</f>
         <v/>
       </c>
     </row>
@@ -2410,7 +2485,7 @@
     </row>
     <row r="44" spans="1:7" ht="75" customHeight="1">
       <c r="A44" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A43)*(EventsTable[End Date]&gt;=A43))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A43)*(EventsTable[End Date]&gt;=A43))), "")</f>
         <v/>
       </c>
       <c r="B44" s="10"/>
@@ -2422,7 +2497,7 @@
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
       <c r="A46" s="46" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B46" s="45"/>
       <c r="C46" s="45"/>
@@ -2433,25 +2508,25 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2478,29 +2553,28 @@
     <row r="49" spans="1:7" ht="75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B48)*(EventsTable[End Date]&gt;=B48))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B48)*(EventsTable[End Date]&gt;=B48))), "")</f>
         <v/>
       </c>
       <c r="C49" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C48)*(EventsTable[End Date]&gt;=C48))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C48)*(EventsTable[End Date]&gt;=C48))), "")</f>
         <v/>
       </c>
       <c r="D49" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D48)*(EventsTable[End Date]&gt;=D48))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D48)*(EventsTable[End Date]&gt;=D48))), "")</f>
         <v/>
       </c>
       <c r="E49" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E48)*(EventsTable[End Date]&gt;=E48))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E48)*(EventsTable[End Date]&gt;=E48))), "")</f>
         <v/>
       </c>
       <c r="F49" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F48)*(EventsTable[End Date]&gt;=F48))), "")</f>
-        <v>• Hamilton Aqua-Gym SC Gala
-• EDA Gala 3 &amp; 4</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F48)*(EventsTable[End Date]&gt;=F48))), "")</f>
+        <v/>
       </c>
       <c r="G49" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G48)*(EventsTable[End Date]&gt;=G48))), "")</f>
-        <v>• EDA Gala 3 &amp; 4</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G48)*(EventsTable[End Date]&gt;=G48))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="50" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2528,32 +2602,32 @@
     </row>
     <row r="51" spans="1:7" ht="75" customHeight="1">
       <c r="A51" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A50)*(EventsTable[End Date]&gt;=A50))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A50)*(EventsTable[End Date]&gt;=A50))), "")</f>
         <v/>
       </c>
       <c r="B51" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B50)*(EventsTable[End Date]&gt;=B50))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B50)*(EventsTable[End Date]&gt;=B50))), "")</f>
         <v/>
       </c>
       <c r="C51" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C50)*(EventsTable[End Date]&gt;=C50))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C50)*(EventsTable[End Date]&gt;=C50))), "")</f>
         <v/>
       </c>
       <c r="D51" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D50)*(EventsTable[End Date]&gt;=D50))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D50)*(EventsTable[End Date]&gt;=D50))), "")</f>
         <v/>
       </c>
       <c r="E51" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E50)*(EventsTable[End Date]&gt;=E50))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E50)*(EventsTable[End Date]&gt;=E50))), "")</f>
         <v/>
       </c>
       <c r="F51" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F50)*(EventsTable[End Date]&gt;=F50))), "")</f>
-        <v>• Beavers SC Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F50)*(EventsTable[End Date]&gt;=F50))), "")</f>
+        <v/>
       </c>
       <c r="G51" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G50)*(EventsTable[End Date]&gt;=G50))), "")</f>
-        <v>• Beavers SC Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G50)*(EventsTable[End Date]&gt;=G50))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="52" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2581,32 +2655,32 @@
     </row>
     <row r="53" spans="1:7" ht="75" customHeight="1">
       <c r="A53" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A52)*(EventsTable[End Date]&gt;=A52))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A52)*(EventsTable[End Date]&gt;=A52))), "")</f>
         <v/>
       </c>
       <c r="B53" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B52)*(EventsTable[End Date]&gt;=B52))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B52)*(EventsTable[End Date]&gt;=B52))), "")</f>
         <v/>
       </c>
       <c r="C53" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C52)*(EventsTable[End Date]&gt;=C52))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C52)*(EventsTable[End Date]&gt;=C52))), "")</f>
         <v/>
       </c>
       <c r="D53" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D52)*(EventsTable[End Date]&gt;=D52))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D52)*(EventsTable[End Date]&gt;=D52))), "")</f>
         <v/>
       </c>
       <c r="E53" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E52)*(EventsTable[End Date]&gt;=E52))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E52)*(EventsTable[End Date]&gt;=E52))), "")</f>
         <v/>
       </c>
       <c r="F53" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F52)*(EventsTable[End Date]&gt;=F52))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F52)*(EventsTable[End Date]&gt;=F52))), "")</f>
         <v/>
       </c>
       <c r="G53" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G52)*(EventsTable[End Date]&gt;=G52))), "")</f>
-        <v>• UMG AG 1</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G52)*(EventsTable[End Date]&gt;=G52))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2634,39 +2708,32 @@
     </row>
     <row r="55" spans="1:7" ht="75" customHeight="1">
       <c r="A55" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A54)*(EventsTable[End Date]&gt;=A54))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A54)*(EventsTable[End Date]&gt;=A54))), "")</f>
         <v/>
       </c>
       <c r="B55" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B54)*(EventsTable[End Date]&gt;=B54))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B54)*(EventsTable[End Date]&gt;=B54))), "")</f>
         <v/>
       </c>
       <c r="C55" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C54)*(EventsTable[End Date]&gt;=C54))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C54)*(EventsTable[End Date]&gt;=C54))), "")</f>
         <v/>
       </c>
       <c r="D55" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D54)*(EventsTable[End Date]&gt;=D54))), "")</f>
-        <v>• SA National Short Course
-• Heritage Day</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D54)*(EventsTable[End Date]&gt;=D54))), "")</f>
+        <v/>
       </c>
       <c r="E55" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E54)*(EventsTable[End Date]&gt;=E54))), "")</f>
-        <v>• SA National Short Course
-• Seagulls Annual Winter Gala</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E54)*(EventsTable[End Date]&gt;=E54))), "")</f>
+        <v/>
       </c>
       <c r="F55" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F54)*(EventsTable[End Date]&gt;=F54))), "")</f>
-        <v>• SA National Short Course
-• Seagulls Annual Winter Gala
-• Fish Eagles SC
-• MSC Sprints</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F54)*(EventsTable[End Date]&gt;=F54))), "")</f>
+        <v/>
       </c>
       <c r="G55" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G54)*(EventsTable[End Date]&gt;=G54))), "")</f>
-        <v>• SA National Short Course
-• Seagulls Annual Winter Gala
-• MSC Sprints</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G54)*(EventsTable[End Date]&gt;=G54))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2686,15 +2753,15 @@
     </row>
     <row r="57" spans="1:7" ht="75" customHeight="1">
       <c r="A57" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A56)*(EventsTable[End Date]&gt;=A56))), "")</f>
-        <v>• MSC Sprints</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A56)*(EventsTable[End Date]&gt;=A56))), "")</f>
+        <v/>
       </c>
       <c r="B57" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B56)*(EventsTable[End Date]&gt;=B56))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B56)*(EventsTable[End Date]&gt;=B56))), "")</f>
         <v/>
       </c>
       <c r="C57" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C56)*(EventsTable[End Date]&gt;=C56))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C56)*(EventsTable[End Date]&gt;=C56))), "")</f>
         <v/>
       </c>
       <c r="D57" s="10"/>
@@ -2704,7 +2771,7 @@
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
       <c r="A59" s="46" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B59" s="45"/>
       <c r="C59" s="45"/>
@@ -2715,25 +2782,25 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2758,23 +2825,20 @@
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
       <c r="D62" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D61)*(EventsTable[End Date]&gt;=D61))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D61)*(EventsTable[End Date]&gt;=D61))), "")</f>
         <v/>
       </c>
       <c r="E62" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E61)*(EventsTable[End Date]&gt;=E61))), "")</f>
-        <v>• Curro Elite</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E61)*(EventsTable[End Date]&gt;=E61))), "")</f>
+        <v/>
       </c>
       <c r="F62" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F61)*(EventsTable[End Date]&gt;=F61))), "")</f>
-        <v>• Curro Elite
-• KCD Age Group 1
-• KZN Junior Championships LC</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F61)*(EventsTable[End Date]&gt;=F61))), "")</f>
+        <v/>
       </c>
       <c r="G62" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G61)*(EventsTable[End Date]&gt;=G61))), "")</f>
-        <v>• Curro Elite
-• KZN Junior Championships LC</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G61)*(EventsTable[End Date]&gt;=G61))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2802,31 +2866,31 @@
     </row>
     <row r="64" spans="1:7" ht="75" customHeight="1">
       <c r="A64" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A63)*(EventsTable[End Date]&gt;=A63))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A63)*(EventsTable[End Date]&gt;=A63))), "")</f>
         <v/>
       </c>
       <c r="B64" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B63)*(EventsTable[End Date]&gt;=B63))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B63)*(EventsTable[End Date]&gt;=B63))), "")</f>
         <v/>
       </c>
       <c r="C64" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C63)*(EventsTable[End Date]&gt;=C63))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C63)*(EventsTable[End Date]&gt;=C63))), "")</f>
         <v/>
       </c>
       <c r="D64" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D63)*(EventsTable[End Date]&gt;=D63))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D63)*(EventsTable[End Date]&gt;=D63))), "")</f>
         <v/>
       </c>
       <c r="E64" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E63)*(EventsTable[End Date]&gt;=E63))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E63)*(EventsTable[End Date]&gt;=E63))), "")</f>
         <v/>
       </c>
       <c r="F64" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F63)*(EventsTable[End Date]&gt;=F63))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F63)*(EventsTable[End Date]&gt;=F63))), "")</f>
         <v/>
       </c>
       <c r="G64" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G63)*(EventsTable[End Date]&gt;=G63))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G63)*(EventsTable[End Date]&gt;=G63))), "")</f>
         <v/>
       </c>
     </row>
@@ -2855,32 +2919,31 @@
     </row>
     <row r="66" spans="1:7" ht="75" customHeight="1">
       <c r="A66" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A65)*(EventsTable[End Date]&gt;=A65))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A65)*(EventsTable[End Date]&gt;=A65))), "")</f>
         <v/>
       </c>
       <c r="B66" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B65)*(EventsTable[End Date]&gt;=B65))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B65)*(EventsTable[End Date]&gt;=B65))), "")</f>
         <v/>
       </c>
       <c r="C66" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C65)*(EventsTable[End Date]&gt;=C65))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C65)*(EventsTable[End Date]&gt;=C65))), "")</f>
         <v/>
       </c>
       <c r="D66" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D65)*(EventsTable[End Date]&gt;=D65))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D65)*(EventsTable[End Date]&gt;=D65))), "")</f>
         <v/>
       </c>
       <c r="E66" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E65)*(EventsTable[End Date]&gt;=E65))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E65)*(EventsTable[End Date]&gt;=E65))), "")</f>
         <v/>
       </c>
       <c r="F66" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F65)*(EventsTable[End Date]&gt;=F65))), "")</f>
-        <v>• UDA District Gala 3
-• Uthukela Age Group 1</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F65)*(EventsTable[End Date]&gt;=F65))), "")</f>
+        <v/>
       </c>
       <c r="G66" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G65)*(EventsTable[End Date]&gt;=G65))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G65)*(EventsTable[End Date]&gt;=G65))), "")</f>
         <v/>
       </c>
     </row>
@@ -2909,32 +2972,32 @@
     </row>
     <row r="68" spans="1:7" ht="75" customHeight="1">
       <c r="A68" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A67)*(EventsTable[End Date]&gt;=A67))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A67)*(EventsTable[End Date]&gt;=A67))), "")</f>
         <v/>
       </c>
       <c r="B68" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B67)*(EventsTable[End Date]&gt;=B67))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B67)*(EventsTable[End Date]&gt;=B67))), "")</f>
         <v/>
       </c>
       <c r="C68" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C67)*(EventsTable[End Date]&gt;=C67))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C67)*(EventsTable[End Date]&gt;=C67))), "")</f>
         <v/>
       </c>
       <c r="D68" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D67)*(EventsTable[End Date]&gt;=D67))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D67)*(EventsTable[End Date]&gt;=D67))), "")</f>
         <v/>
       </c>
       <c r="E68" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E67)*(EventsTable[End Date]&gt;=E67))), "")</f>
-        <v>• MAC Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E67)*(EventsTable[End Date]&gt;=E67))), "")</f>
+        <v/>
       </c>
       <c r="F68" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F67)*(EventsTable[End Date]&gt;=F67))), "")</f>
-        <v>• MAC Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F67)*(EventsTable[End Date]&gt;=F67))), "")</f>
+        <v/>
       </c>
       <c r="G68" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G67)*(EventsTable[End Date]&gt;=G67))), "")</f>
-        <v>• MAC Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G67)*(EventsTable[End Date]&gt;=G67))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2960,34 +3023,34 @@
     </row>
     <row r="70" spans="1:7" ht="75" customHeight="1">
       <c r="A70" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A69)*(EventsTable[End Date]&gt;=A69))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A69)*(EventsTable[End Date]&gt;=A69))), "")</f>
         <v/>
       </c>
       <c r="B70" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B69)*(EventsTable[End Date]&gt;=B69))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B69)*(EventsTable[End Date]&gt;=B69))), "")</f>
         <v/>
       </c>
       <c r="C70" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C69)*(EventsTable[End Date]&gt;=C69))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C69)*(EventsTable[End Date]&gt;=C69))), "")</f>
         <v/>
       </c>
       <c r="D70" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D69)*(EventsTable[End Date]&gt;=D69))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D69)*(EventsTable[End Date]&gt;=D69))), "")</f>
         <v/>
       </c>
       <c r="E70" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E69)*(EventsTable[End Date]&gt;=E69))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E69)*(EventsTable[End Date]&gt;=E69))), "")</f>
         <v/>
       </c>
       <c r="F70" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F69)*(EventsTable[End Date]&gt;=F69))), "")</f>
-        <v>• KCDA Age Group 2</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F69)*(EventsTable[End Date]&gt;=F69))), "")</f>
+        <v/>
       </c>
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
       <c r="A72" s="46" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B72" s="45"/>
       <c r="C72" s="45"/>
@@ -2998,25 +3061,25 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="G73" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3038,7 +3101,7 @@
       <c r="E75" s="10"/>
       <c r="F75" s="11"/>
       <c r="G75" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G74)*(EventsTable[End Date]&gt;=G74))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G74)*(EventsTable[End Date]&gt;=G74))), "")</f>
         <v/>
       </c>
     </row>
@@ -3067,31 +3130,31 @@
     </row>
     <row r="77" spans="1:7" ht="75" customHeight="1">
       <c r="A77" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A76)*(EventsTable[End Date]&gt;=A76))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A76)*(EventsTable[End Date]&gt;=A76))), "")</f>
         <v/>
       </c>
       <c r="B77" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B76)*(EventsTable[End Date]&gt;=B76))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B76)*(EventsTable[End Date]&gt;=B76))), "")</f>
         <v/>
       </c>
       <c r="C77" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C76)*(EventsTable[End Date]&gt;=C76))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C76)*(EventsTable[End Date]&gt;=C76))), "")</f>
         <v/>
       </c>
       <c r="D77" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D76)*(EventsTable[End Date]&gt;=D76))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D76)*(EventsTable[End Date]&gt;=D76))), "")</f>
         <v/>
       </c>
       <c r="E77" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E76)*(EventsTable[End Date]&gt;=E76))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E76)*(EventsTable[End Date]&gt;=E76))), "")</f>
         <v/>
       </c>
       <c r="F77" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F76)*(EventsTable[End Date]&gt;=F76))), "")</f>
-        <v>• Zululand SC Champs</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F76)*(EventsTable[End Date]&gt;=F76))), "")</f>
+        <v/>
       </c>
       <c r="G77" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G76)*(EventsTable[End Date]&gt;=G76))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G76)*(EventsTable[End Date]&gt;=G76))), "")</f>
         <v/>
       </c>
     </row>
@@ -3120,32 +3183,32 @@
     </row>
     <row r="79" spans="1:7" ht="75" customHeight="1">
       <c r="A79" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A78)*(EventsTable[End Date]&gt;=A78))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A78)*(EventsTable[End Date]&gt;=A78))), "")</f>
         <v/>
       </c>
       <c r="B79" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B78)*(EventsTable[End Date]&gt;=B78))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B78)*(EventsTable[End Date]&gt;=B78))), "")</f>
         <v/>
       </c>
       <c r="C79" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C78)*(EventsTable[End Date]&gt;=C78))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C78)*(EventsTable[End Date]&gt;=C78))), "")</f>
         <v/>
       </c>
       <c r="D79" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D78)*(EventsTable[End Date]&gt;=D78))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D78)*(EventsTable[End Date]&gt;=D78))), "")</f>
         <v/>
       </c>
       <c r="E79" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E78)*(EventsTable[End Date]&gt;=E78))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E78)*(EventsTable[End Date]&gt;=E78))), "")</f>
         <v/>
       </c>
       <c r="F79" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F78)*(EventsTable[End Date]&gt;=F78))), "")</f>
-        <v>• Baynsfield Seeding Swim 1</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F78)*(EventsTable[End Date]&gt;=F78))), "")</f>
+        <v/>
       </c>
       <c r="G79" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G78)*(EventsTable[End Date]&gt;=G78))), "")</f>
-        <v>• Baynsfield Seeding Swim 1</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G78)*(EventsTable[End Date]&gt;=G78))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="80" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3173,33 +3236,32 @@
     </row>
     <row r="81" spans="1:7" ht="75" customHeight="1">
       <c r="A81" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A80)*(EventsTable[End Date]&gt;=A80))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A80)*(EventsTable[End Date]&gt;=A80))), "")</f>
         <v/>
       </c>
       <c r="B81" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B80)*(EventsTable[End Date]&gt;=B80))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B80)*(EventsTable[End Date]&gt;=B80))), "")</f>
         <v/>
       </c>
       <c r="C81" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C80)*(EventsTable[End Date]&gt;=C80))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C80)*(EventsTable[End Date]&gt;=C80))), "")</f>
         <v/>
       </c>
       <c r="D81" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D80)*(EventsTable[End Date]&gt;=D80))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D80)*(EventsTable[End Date]&gt;=D80))), "")</f>
         <v/>
       </c>
       <c r="E81" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E80)*(EventsTable[End Date]&gt;=E80))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E80)*(EventsTable[End Date]&gt;=E80))), "")</f>
         <v/>
       </c>
       <c r="F81" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F80)*(EventsTable[End Date]&gt;=F80))), "")</f>
-        <v>• KCDA Age Group 3
-• Capital K</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F80)*(EventsTable[End Date]&gt;=F80))), "")</f>
+        <v/>
       </c>
       <c r="G81" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G80)*(EventsTable[End Date]&gt;=G80))), "")</f>
-        <v>• Capital K</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G80)*(EventsTable[End Date]&gt;=G80))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="82" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3227,33 +3289,32 @@
     </row>
     <row r="83" spans="1:7" ht="75" customHeight="1">
       <c r="A83" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A82)*(EventsTable[End Date]&gt;=A82))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A82)*(EventsTable[End Date]&gt;=A82))), "")</f>
         <v/>
       </c>
       <c r="B83" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B82)*(EventsTable[End Date]&gt;=B82))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B82)*(EventsTable[End Date]&gt;=B82))), "")</f>
         <v/>
       </c>
       <c r="C83" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C82)*(EventsTable[End Date]&gt;=C82))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C82)*(EventsTable[End Date]&gt;=C82))), "")</f>
         <v/>
       </c>
       <c r="D83" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D82)*(EventsTable[End Date]&gt;=D82))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D82)*(EventsTable[End Date]&gt;=D82))), "")</f>
         <v/>
       </c>
       <c r="E83" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E82)*(EventsTable[End Date]&gt;=E82))), "")</f>
-        <v>• WSCSeals - LC OR SC</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E82)*(EventsTable[End Date]&gt;=E82))), "")</f>
+        <v/>
       </c>
       <c r="F83" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F82)*(EventsTable[End Date]&gt;=F82))), "")</f>
-        <v>• WSCSeals - LC OR SC
-• Uthukela Age Group 2</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F82)*(EventsTable[End Date]&gt;=F82))), "")</f>
+        <v/>
       </c>
       <c r="G83" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G82)*(EventsTable[End Date]&gt;=G82))), "")</f>
-        <v>• WSCSeals - LC OR SC</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G82)*(EventsTable[End Date]&gt;=G82))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="84" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3269,7 +3330,7 @@
     </row>
     <row r="85" spans="1:7" ht="75" customHeight="1">
       <c r="A85" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A84)*(EventsTable[End Date]&gt;=A84))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A84)*(EventsTable[End Date]&gt;=A84))), "")</f>
         <v/>
       </c>
       <c r="B85" s="10"/>
@@ -3281,7 +3342,7 @@
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
       <c r="A87" s="46" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B87" s="45"/>
       <c r="C87" s="45"/>
@@ -3292,25 +3353,25 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3337,27 +3398,27 @@
     <row r="90" spans="1:7" ht="75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B89)*(EventsTable[End Date]&gt;=B89))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B89)*(EventsTable[End Date]&gt;=B89))), "")</f>
         <v/>
       </c>
       <c r="C90" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C89)*(EventsTable[End Date]&gt;=C89))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C89)*(EventsTable[End Date]&gt;=C89))), "")</f>
         <v/>
       </c>
       <c r="D90" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D89)*(EventsTable[End Date]&gt;=D89))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D89)*(EventsTable[End Date]&gt;=D89))), "")</f>
         <v/>
       </c>
       <c r="E90" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E89)*(EventsTable[End Date]&gt;=E89))), "")</f>
-        <v>• Stingrays</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E89)*(EventsTable[End Date]&gt;=E89))), "")</f>
+        <v/>
       </c>
       <c r="F90" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F89)*(EventsTable[End Date]&gt;=F89))), "")</f>
-        <v>• Stingrays</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F89)*(EventsTable[End Date]&gt;=F89))), "")</f>
+        <v/>
       </c>
       <c r="G90" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G89)*(EventsTable[End Date]&gt;=G89))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G89)*(EventsTable[End Date]&gt;=G89))), "")</f>
         <v/>
       </c>
     </row>
@@ -3386,34 +3447,32 @@
     </row>
     <row r="92" spans="1:7" ht="75" customHeight="1">
       <c r="A92" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A91)*(EventsTable[End Date]&gt;=A91))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A91)*(EventsTable[End Date]&gt;=A91))), "")</f>
         <v/>
       </c>
       <c r="B92" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B91)*(EventsTable[End Date]&gt;=B91))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B91)*(EventsTable[End Date]&gt;=B91))), "")</f>
         <v/>
       </c>
       <c r="C92" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C91)*(EventsTable[End Date]&gt;=C91))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C91)*(EventsTable[End Date]&gt;=C91))), "")</f>
         <v/>
       </c>
       <c r="D92" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D91)*(EventsTable[End Date]&gt;=D91))), "")</f>
-        <v>• KZN Premier Championships (Level 2 &amp; Above)</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D91)*(EventsTable[End Date]&gt;=D91))), "")</f>
+        <v/>
       </c>
       <c r="E92" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E91)*(EventsTable[End Date]&gt;=E91))), "")</f>
-        <v>• KZN Premier Championships (Level 2 &amp; Above)</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E91)*(EventsTable[End Date]&gt;=E91))), "")</f>
+        <v/>
       </c>
       <c r="F92" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F91)*(EventsTable[End Date]&gt;=F91))), "")</f>
-        <v>• Baynsfield Seeding Swim 2 / KZNA Open Water Champs
-• KZN Premier Championships (Level 2 &amp; Above)</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F91)*(EventsTable[End Date]&gt;=F91))), "")</f>
+        <v/>
       </c>
       <c r="G92" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G91)*(EventsTable[End Date]&gt;=G91))), "")</f>
-        <v>• Baynsfield Seeding Swim 2 / KZNA Open Water Champs
-• KZN Premier Championships (Level 2 &amp; Above)</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G91)*(EventsTable[End Date]&gt;=G91))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="93" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3441,11 +3500,11 @@
     </row>
     <row r="94" spans="1:7" ht="75" customHeight="1">
       <c r="A94" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A93)*(EventsTable[End Date]&gt;=A93))), "")</f>
-        <v>• KZN Premier Championships (Level 2 &amp; Above)</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A93)*(EventsTable[End Date]&gt;=A93))), "")</f>
+        <v/>
       </c>
       <c r="B94" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B93)*(EventsTable[End Date]&gt;=B93))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B93)*(EventsTable[End Date]&gt;=B93))), "")</f>
         <v/>
       </c>
       <c r="C94" s="6" t="str">
@@ -3453,19 +3512,19 @@
         <v/>
       </c>
       <c r="D94" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D93)*(EventsTable[End Date]&gt;=D93))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D93)*(EventsTable[End Date]&gt;=D93))), "")</f>
         <v/>
       </c>
       <c r="E94" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E93)*(EventsTable[End Date]&gt;=E93))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E93)*(EventsTable[End Date]&gt;=E93))), "")</f>
         <v/>
       </c>
       <c r="F94" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F93)*(EventsTable[End Date]&gt;=F93))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F93)*(EventsTable[End Date]&gt;=F93))), "")</f>
         <v/>
       </c>
       <c r="G94" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G93)*(EventsTable[End Date]&gt;=G93))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G93)*(EventsTable[End Date]&gt;=G93))), "")</f>
         <v/>
       </c>
     </row>
@@ -3494,31 +3553,31 @@
     </row>
     <row r="96" spans="1:7" ht="75" customHeight="1">
       <c r="A96" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A95)*(EventsTable[End Date]&gt;=A95))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A95)*(EventsTable[End Date]&gt;=A95))), "")</f>
         <v/>
       </c>
       <c r="B96" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B95)*(EventsTable[End Date]&gt;=B95))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B95)*(EventsTable[End Date]&gt;=B95))), "")</f>
         <v/>
       </c>
       <c r="C96" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C95)*(EventsTable[End Date]&gt;=C95))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C95)*(EventsTable[End Date]&gt;=C95))), "")</f>
         <v/>
       </c>
       <c r="D96" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D95)*(EventsTable[End Date]&gt;=D95))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D95)*(EventsTable[End Date]&gt;=D95))), "")</f>
         <v/>
       </c>
       <c r="E96" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E95)*(EventsTable[End Date]&gt;=E95))), "")</f>
-        <v>• Christmas Day</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E95)*(EventsTable[End Date]&gt;=E95))), "")</f>
+        <v/>
       </c>
       <c r="F96" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F95)*(EventsTable[End Date]&gt;=F95))), "")</f>
-        <v>• Day of Goodwill</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F95)*(EventsTable[End Date]&gt;=F95))), "")</f>
+        <v/>
       </c>
       <c r="G96" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G95)*(EventsTable[End Date]&gt;=G95))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G95)*(EventsTable[End Date]&gt;=G95))), "")</f>
         <v/>
       </c>
     </row>
@@ -3541,19 +3600,19 @@
     </row>
     <row r="98" spans="1:7" ht="75" customHeight="1">
       <c r="A98" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A97)*(EventsTable[End Date]&gt;=A97))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A97)*(EventsTable[End Date]&gt;=A97))), "")</f>
         <v/>
       </c>
       <c r="B98" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B97)*(EventsTable[End Date]&gt;=B97))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B97)*(EventsTable[End Date]&gt;=B97))), "")</f>
         <v/>
       </c>
       <c r="C98" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C97)*(EventsTable[End Date]&gt;=C97))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C97)*(EventsTable[End Date]&gt;=C97))), "")</f>
         <v/>
       </c>
       <c r="D98" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D97)*(EventsTable[End Date]&gt;=D97))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D97)*(EventsTable[End Date]&gt;=D97))), "")</f>
         <v/>
       </c>
       <c r="E98" s="10"/>
@@ -3562,7 +3621,7 @@
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
       <c r="A100" s="46" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B100" s="45"/>
       <c r="C100" s="45"/>
@@ -3573,25 +3632,25 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="G101" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3615,15 +3674,15 @@
       <c r="C103" s="10"/>
       <c r="D103" s="10"/>
       <c r="E103" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E102)*(EventsTable[End Date]&gt;=E102))), "")</f>
-        <v>• New Year's Day</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E102)*(EventsTable[End Date]&gt;=E102))), "")</f>
+        <v/>
       </c>
       <c r="F103" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F102)*(EventsTable[End Date]&gt;=F102))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F102)*(EventsTable[End Date]&gt;=F102))), "")</f>
         <v/>
       </c>
       <c r="G103" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G102)*(EventsTable[End Date]&gt;=G102))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G102)*(EventsTable[End Date]&gt;=G102))), "")</f>
         <v/>
       </c>
     </row>
@@ -3652,33 +3711,32 @@
     </row>
     <row r="105" spans="1:7" ht="75" customHeight="1">
       <c r="A105" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A104)*(EventsTable[End Date]&gt;=A104))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A104)*(EventsTable[End Date]&gt;=A104))), "")</f>
         <v/>
       </c>
       <c r="B105" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B104)*(EventsTable[End Date]&gt;=B104))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B104)*(EventsTable[End Date]&gt;=B104))), "")</f>
         <v/>
       </c>
       <c r="C105" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C104)*(EventsTable[End Date]&gt;=C104))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C104)*(EventsTable[End Date]&gt;=C104))), "")</f>
         <v/>
       </c>
       <c r="D105" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D104)*(EventsTable[End Date]&gt;=D104))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D104)*(EventsTable[End Date]&gt;=D104))), "")</f>
         <v/>
       </c>
       <c r="E105" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E104)*(EventsTable[End Date]&gt;=E104))), "")</f>
-        <v>• 1st Grand Prix</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E104)*(EventsTable[End Date]&gt;=E104))), "")</f>
+        <v/>
       </c>
       <c r="F105" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F104)*(EventsTable[End Date]&gt;=F104))), "")</f>
-        <v>• 1st Grand Prix
-• EDA Gala 5&amp;6 &amp; KZNA Age Group (Level 3 and above) LC</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F104)*(EventsTable[End Date]&gt;=F104))), "")</f>
+        <v/>
       </c>
       <c r="G105" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G104)*(EventsTable[End Date]&gt;=G104))), "")</f>
-        <v>• EDA Gala 5&amp;6 &amp; KZNA Age Group (Level 3 and above) LC</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G104)*(EventsTable[End Date]&gt;=G104))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="106" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3706,38 +3764,32 @@
     </row>
     <row r="107" spans="1:7" ht="98.25" customHeight="1">
       <c r="A107" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A106)*(EventsTable[End Date]&gt;=A106))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A106)*(EventsTable[End Date]&gt;=A106))), "")</f>
         <v/>
       </c>
       <c r="B107" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B106)*(EventsTable[End Date]&gt;=B106))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B106)*(EventsTable[End Date]&gt;=B106))), "")</f>
         <v/>
       </c>
       <c r="C107" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C106)*(EventsTable[End Date]&gt;=C106))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C106)*(EventsTable[End Date]&gt;=C106))), "")</f>
         <v/>
       </c>
       <c r="D107" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D106)*(EventsTable[End Date]&gt;=D106))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D106)*(EventsTable[End Date]&gt;=D106))), "")</f>
         <v/>
       </c>
       <c r="E107" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E106)*(EventsTable[End Date]&gt;=E106))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E106)*(EventsTable[End Date]&gt;=E106))), "")</f>
         <v/>
       </c>
       <c r="F107" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F106)*(EventsTable[End Date]&gt;=F106))), "")</f>
-        <v>• KZN Level 1 Championships
-• Baynesfield Seeding Swim 3
-• Uthukela Age Group 3
-• Fish Eagles LC Champs
-• UDA District Gala 4</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F106)*(EventsTable[End Date]&gt;=F106))), "")</f>
+        <v/>
       </c>
       <c r="G107" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G106)*(EventsTable[End Date]&gt;=G106))), "")</f>
-        <v>• KZN Level 1 Championships
-• Baynesfield Seeding Swim 3
-• UMG AG2</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G106)*(EventsTable[End Date]&gt;=G106))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="108" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3765,32 +3817,32 @@
     </row>
     <row r="109" spans="1:7" ht="75" customHeight="1">
       <c r="A109" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A108)*(EventsTable[End Date]&gt;=A108))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A108)*(EventsTable[End Date]&gt;=A108))), "")</f>
         <v/>
       </c>
       <c r="B109" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B108)*(EventsTable[End Date]&gt;=B108))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B108)*(EventsTable[End Date]&gt;=B108))), "")</f>
         <v/>
       </c>
       <c r="C109" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C108)*(EventsTable[End Date]&gt;=C108))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C108)*(EventsTable[End Date]&gt;=C108))), "")</f>
         <v/>
       </c>
       <c r="D109" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D108)*(EventsTable[End Date]&gt;=D108))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D108)*(EventsTable[End Date]&gt;=D108))), "")</f>
         <v/>
       </c>
       <c r="E109" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E108)*(EventsTable[End Date]&gt;=E108))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E108)*(EventsTable[End Date]&gt;=E108))), "")</f>
         <v/>
       </c>
       <c r="F109" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F108)*(EventsTable[End Date]&gt;=F108))), "")</f>
-        <v>• Hamilton-Aqua Gym SC Gala</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F108)*(EventsTable[End Date]&gt;=F108))), "")</f>
+        <v/>
       </c>
       <c r="G109" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G108)*(EventsTable[End Date]&gt;=G108))), "")</f>
-        <v>• Ilembe School Trials</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G108)*(EventsTable[End Date]&gt;=G108))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="110" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3818,45 +3870,37 @@
     </row>
     <row r="111" spans="1:7" ht="75" customHeight="1">
       <c r="A111" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A110)*(EventsTable[End Date]&gt;=A110))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A110)*(EventsTable[End Date]&gt;=A110))), "")</f>
         <v/>
       </c>
       <c r="B111" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B110)*(EventsTable[End Date]&gt;=B110))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B110)*(EventsTable[End Date]&gt;=B110))), "")</f>
         <v/>
       </c>
       <c r="C111" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C110)*(EventsTable[End Date]&gt;=C110))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C110)*(EventsTable[End Date]&gt;=C110))), "")</f>
         <v/>
       </c>
       <c r="D111" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D110)*(EventsTable[End Date]&gt;=D110))), "")</f>
-        <v>• KCDA School Trials
-• Umgungundlovu School Trials</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D110)*(EventsTable[End Date]&gt;=D110))), "")</f>
+        <v/>
       </c>
       <c r="E111" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E110)*(EventsTable[End Date]&gt;=E110))), "")</f>
-        <v>• Umgungundlovu School Trials
-• Vryheid School Trials
-• SKZN School Trials
-• Ushaka Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E110)*(EventsTable[End Date]&gt;=E110))), "")</f>
+        <v/>
       </c>
       <c r="F111" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F110)*(EventsTable[End Date]&gt;=F110))), "")</f>
-        <v>• Umgungundlovu School Trials
-• SKZN School Trials
-• Ushaka Championships
-• PADSSA &amp; Umlazi Schools</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F110)*(EventsTable[End Date]&gt;=F110))), "")</f>
+        <v/>
       </c>
       <c r="G111" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G110)*(EventsTable[End Date]&gt;=G110))), "")</f>
-        <v>• Ushaka Championships
-• PADSSA &amp; Umlazi Schools</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G110)*(EventsTable[End Date]&gt;=G110))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
       <c r="A113" s="46" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B113" s="45"/>
       <c r="C113" s="45"/>
@@ -3867,25 +3911,25 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="F114" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="G114" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3913,34 +3957,32 @@
     </row>
     <row r="116" spans="1:7" ht="75" customHeight="1">
       <c r="A116" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A115)*(EventsTable[End Date]&gt;=A115))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A115)*(EventsTable[End Date]&gt;=A115))), "")</f>
         <v/>
       </c>
       <c r="B116" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B115)*(EventsTable[End Date]&gt;=B115))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B115)*(EventsTable[End Date]&gt;=B115))), "")</f>
         <v/>
       </c>
       <c r="C116" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C115)*(EventsTable[End Date]&gt;=C115))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C115)*(EventsTable[End Date]&gt;=C115))), "")</f>
         <v/>
       </c>
       <c r="D116" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D115)*(EventsTable[End Date]&gt;=D115))), "")</f>
-        <v>• Uthukela District Trials
-• MSC Gala - Margate</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D115)*(EventsTable[End Date]&gt;=D115))), "")</f>
+        <v/>
       </c>
       <c r="E116" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E115)*(EventsTable[End Date]&gt;=E115))), "")</f>
-        <v>• MSC Gala - Margate</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E115)*(EventsTable[End Date]&gt;=E115))), "")</f>
+        <v/>
       </c>
       <c r="F116" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F115)*(EventsTable[End Date]&gt;=F115))), "")</f>
-        <v>• KCDA Age Group 4
-• KZNA Long Course Meet 2 LC</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F115)*(EventsTable[End Date]&gt;=F115))), "")</f>
+        <v/>
       </c>
       <c r="G116" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G115)*(EventsTable[End Date]&gt;=G115))), "")</f>
-        <v>• KZNA Long Course Meet 2 LC</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G115)*(EventsTable[End Date]&gt;=G115))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="117" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3968,33 +4010,32 @@
     </row>
     <row r="118" spans="1:7" ht="75" customHeight="1">
       <c r="A118" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A117)*(EventsTable[End Date]&gt;=A117))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A117)*(EventsTable[End Date]&gt;=A117))), "")</f>
         <v/>
       </c>
       <c r="B118" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B117)*(EventsTable[End Date]&gt;=B117))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B117)*(EventsTable[End Date]&gt;=B117))), "")</f>
         <v/>
       </c>
       <c r="C118" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C117)*(EventsTable[End Date]&gt;=C117))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C117)*(EventsTable[End Date]&gt;=C117))), "")</f>
         <v/>
       </c>
       <c r="D118" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D117)*(EventsTable[End Date]&gt;=D117))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D117)*(EventsTable[End Date]&gt;=D117))), "")</f>
         <v/>
       </c>
       <c r="E118" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E117)*(EventsTable[End Date]&gt;=E117))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E117)*(EventsTable[End Date]&gt;=E117))), "")</f>
         <v/>
       </c>
       <c r="F118" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F117)*(EventsTable[End Date]&gt;=F117))), "")</f>
-        <v>• Zululand Inter Club Challenge (50m)
-• Midmar Mile</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F117)*(EventsTable[End Date]&gt;=F117))), "")</f>
+        <v/>
       </c>
       <c r="G118" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G117)*(EventsTable[End Date]&gt;=G117))), "")</f>
-        <v>• Midmar Mile</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G117)*(EventsTable[End Date]&gt;=G117))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="119" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4022,31 +4063,31 @@
     </row>
     <row r="120" spans="1:7" ht="75" customHeight="1">
       <c r="A120" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A119)*(EventsTable[End Date]&gt;=A119))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A119)*(EventsTable[End Date]&gt;=A119))), "")</f>
         <v/>
       </c>
       <c r="B120" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B119)*(EventsTable[End Date]&gt;=B119))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B119)*(EventsTable[End Date]&gt;=B119))), "")</f>
         <v/>
       </c>
       <c r="C120" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C119)*(EventsTable[End Date]&gt;=C119))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C119)*(EventsTable[End Date]&gt;=C119))), "")</f>
         <v/>
       </c>
       <c r="D120" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D119)*(EventsTable[End Date]&gt;=D119))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D119)*(EventsTable[End Date]&gt;=D119))), "")</f>
         <v/>
       </c>
       <c r="E120" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E119)*(EventsTable[End Date]&gt;=E119))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E119)*(EventsTable[End Date]&gt;=E119))), "")</f>
         <v/>
       </c>
       <c r="F120" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F119)*(EventsTable[End Date]&gt;=F119))), "")</f>
-        <v>• Uthukela Age Group</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F119)*(EventsTable[End Date]&gt;=F119))), "")</f>
+        <v/>
       </c>
       <c r="G120" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G119)*(EventsTable[End Date]&gt;=G119))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G119)*(EventsTable[End Date]&gt;=G119))), "")</f>
         <v/>
       </c>
     </row>
@@ -4075,37 +4116,37 @@
     </row>
     <row r="122" spans="1:7" ht="75" customHeight="1">
       <c r="A122" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A121)*(EventsTable[End Date]&gt;=A121))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A121)*(EventsTable[End Date]&gt;=A121))), "")</f>
         <v/>
       </c>
       <c r="B122" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B121)*(EventsTable[End Date]&gt;=B121))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B121)*(EventsTable[End Date]&gt;=B121))), "")</f>
         <v/>
       </c>
       <c r="C122" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C121)*(EventsTable[End Date]&gt;=C121))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C121)*(EventsTable[End Date]&gt;=C121))), "")</f>
         <v/>
       </c>
       <c r="D122" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D121)*(EventsTable[End Date]&gt;=D121))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D121)*(EventsTable[End Date]&gt;=D121))), "")</f>
         <v/>
       </c>
       <c r="E122" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E121)*(EventsTable[End Date]&gt;=E121))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E121)*(EventsTable[End Date]&gt;=E121))), "")</f>
         <v/>
       </c>
       <c r="F122" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F121)*(EventsTable[End Date]&gt;=F121))), "")</f>
-        <v>• KZN Schools</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F121)*(EventsTable[End Date]&gt;=F121))), "")</f>
+        <v/>
       </c>
       <c r="G122" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G121)*(EventsTable[End Date]&gt;=G121))), "")</f>
-        <v>• KZN Schools</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G121)*(EventsTable[End Date]&gt;=G121))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
       <c r="A124" s="46" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B124" s="45"/>
       <c r="C124" s="45"/>
@@ -4116,25 +4157,25 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="E125" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="G125" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4162,31 +4203,31 @@
     </row>
     <row r="127" spans="1:7" ht="75" customHeight="1">
       <c r="A127" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A126)*(EventsTable[End Date]&gt;=A126))), "")</f>
-        <v>• F, C League</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A126)*(EventsTable[End Date]&gt;=A126))), "")</f>
+        <v/>
       </c>
       <c r="B127" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B126)*(EventsTable[End Date]&gt;=B126))), "")</f>
-        <v>• E League, Girls High A League</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B126)*(EventsTable[End Date]&gt;=B126))), "")</f>
+        <v/>
       </c>
       <c r="C127" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C126)*(EventsTable[End Date]&gt;=C126))), "")</f>
-        <v>• CoEd High Schools, Primary Girls A</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C126)*(EventsTable[End Date]&gt;=C126))), "")</f>
+        <v/>
       </c>
       <c r="D127" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D126)*(EventsTable[End Date]&gt;=D126))), "")</f>
-        <v>• D, B, Primary Boys A</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D126)*(EventsTable[End Date]&gt;=D126))), "")</f>
+        <v/>
       </c>
       <c r="E127" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E126)*(EventsTable[End Date]&gt;=E126))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E126)*(EventsTable[End Date]&gt;=E126))), "")</f>
         <v/>
       </c>
       <c r="F127" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F126)*(EventsTable[End Date]&gt;=F126))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F126)*(EventsTable[End Date]&gt;=F126))), "")</f>
         <v/>
       </c>
       <c r="G127" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G126)*(EventsTable[End Date]&gt;=G126))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G126)*(EventsTable[End Date]&gt;=G126))), "")</f>
         <v/>
       </c>
     </row>
@@ -4215,31 +4256,31 @@
     </row>
     <row r="129" spans="1:7" ht="75" customHeight="1">
       <c r="A129" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A128)*(EventsTable[End Date]&gt;=A128))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A128)*(EventsTable[End Date]&gt;=A128))), "")</f>
         <v/>
       </c>
       <c r="B129" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B128)*(EventsTable[End Date]&gt;=B128))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B128)*(EventsTable[End Date]&gt;=B128))), "")</f>
         <v/>
       </c>
       <c r="C129" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C128)*(EventsTable[End Date]&gt;=C128))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C128)*(EventsTable[End Date]&gt;=C128))), "")</f>
         <v/>
       </c>
       <c r="D129" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D128)*(EventsTable[End Date]&gt;=D128))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D128)*(EventsTable[End Date]&gt;=D128))), "")</f>
         <v/>
       </c>
       <c r="E129" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E128)*(EventsTable[End Date]&gt;=E128))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E128)*(EventsTable[End Date]&gt;=E128))), "")</f>
         <v/>
       </c>
       <c r="F129" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F128)*(EventsTable[End Date]&gt;=F128))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F128)*(EventsTable[End Date]&gt;=F128))), "")</f>
         <v/>
       </c>
       <c r="G129" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G128)*(EventsTable[End Date]&gt;=G128))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G128)*(EventsTable[End Date]&gt;=G128))), "")</f>
         <v/>
       </c>
     </row>
@@ -4268,33 +4309,32 @@
     </row>
     <row r="131" spans="1:7" ht="75" customHeight="1">
       <c r="A131" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A130)*(EventsTable[End Date]&gt;=A130))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A130)*(EventsTable[End Date]&gt;=A130))), "")</f>
         <v/>
       </c>
       <c r="B131" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B130)*(EventsTable[End Date]&gt;=B130))), "")</f>
-        <v>• Youth Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B130)*(EventsTable[End Date]&gt;=B130))), "")</f>
+        <v/>
       </c>
       <c r="C131" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C130)*(EventsTable[End Date]&gt;=C130))), "")</f>
-        <v>• Youth Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C130)*(EventsTable[End Date]&gt;=C130))), "")</f>
+        <v/>
       </c>
       <c r="D131" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D130)*(EventsTable[End Date]&gt;=D130))), "")</f>
-        <v>• Youth Championships</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D130)*(EventsTable[End Date]&gt;=D130))), "")</f>
+        <v/>
       </c>
       <c r="E131" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E130)*(EventsTable[End Date]&gt;=E130))), "")</f>
-        <v>• SA Junior Nationals</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E130)*(EventsTable[End Date]&gt;=E130))), "")</f>
+        <v/>
       </c>
       <c r="F131" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F130)*(EventsTable[End Date]&gt;=F130))), "")</f>
-        <v>• SA Junior Nationals</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F130)*(EventsTable[End Date]&gt;=F130))), "")</f>
+        <v/>
       </c>
       <c r="G131" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G130)*(EventsTable[End Date]&gt;=G130))), "")</f>
-        <v>• SA Junior Nationals
-• Human Rights Day</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G130)*(EventsTable[End Date]&gt;=G130))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="132" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4322,32 +4362,31 @@
     </row>
     <row r="133" spans="1:7" ht="75" customHeight="1">
       <c r="A133" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A132)*(EventsTable[End Date]&gt;=A132))), "")</f>
-        <v>• SA Junior Nationals
-• Human Rights Day</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A132)*(EventsTable[End Date]&gt;=A132))), "")</f>
+        <v/>
       </c>
       <c r="B133" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B132)*(EventsTable[End Date]&gt;=B132))), "")</f>
-        <v>• SA Junior Nationals</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B132)*(EventsTable[End Date]&gt;=B132))), "")</f>
+        <v/>
       </c>
       <c r="C133" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C132)*(EventsTable[End Date]&gt;=C132))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C132)*(EventsTable[End Date]&gt;=C132))), "")</f>
         <v/>
       </c>
       <c r="D133" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D132)*(EventsTable[End Date]&gt;=D132))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D132)*(EventsTable[End Date]&gt;=D132))), "")</f>
         <v/>
       </c>
       <c r="E133" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E132)*(EventsTable[End Date]&gt;=E132))), "")</f>
-        <v>• Good Friday</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E132)*(EventsTable[End Date]&gt;=E132))), "")</f>
+        <v/>
       </c>
       <c r="F133" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F132)*(EventsTable[End Date]&gt;=F132))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F132)*(EventsTable[End Date]&gt;=F132))), "")</f>
         <v/>
       </c>
       <c r="G133" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G132)*(EventsTable[End Date]&gt;=G132))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G132)*(EventsTable[End Date]&gt;=G132))), "")</f>
         <v/>
       </c>
     </row>
@@ -4368,16 +4407,16 @@
     </row>
     <row r="135" spans="1:7" ht="75" customHeight="1">
       <c r="A135" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A134)*(EventsTable[End Date]&gt;=A134))), "")</f>
-        <v>• Family Day</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A134)*(EventsTable[End Date]&gt;=A134))), "")</f>
+        <v/>
       </c>
       <c r="B135" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B134)*(EventsTable[End Date]&gt;=B134))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B134)*(EventsTable[End Date]&gt;=B134))), "")</f>
         <v/>
       </c>
       <c r="C135" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C134)*(EventsTable[End Date]&gt;=C134))), "")</f>
-        <v>• Level 3</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C134)*(EventsTable[End Date]&gt;=C134))), "")</f>
+        <v/>
       </c>
       <c r="D135" s="10"/>
       <c r="E135" s="10"/>
@@ -4386,7 +4425,7 @@
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
       <c r="A137" s="46" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B137" s="45"/>
       <c r="C137" s="45"/>
@@ -4397,25 +4436,25 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="D138" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="E138" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="F138" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="G138" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4440,19 +4479,19 @@
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
       <c r="D140" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D139)*(EventsTable[End Date]&gt;=D139))), "")</f>
-        <v>• Level 3</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D139)*(EventsTable[End Date]&gt;=D139))), "")</f>
+        <v/>
       </c>
       <c r="E140" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E139)*(EventsTable[End Date]&gt;=E139))), "")</f>
-        <v>• Level 3</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E139)*(EventsTable[End Date]&gt;=E139))), "")</f>
+        <v/>
       </c>
       <c r="F140" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F139)*(EventsTable[End Date]&gt;=F139))), "")</f>
-        <v>• Level 3</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F139)*(EventsTable[End Date]&gt;=F139))), "")</f>
+        <v/>
       </c>
       <c r="G140" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G139)*(EventsTable[End Date]&gt;=G139))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G139)*(EventsTable[End Date]&gt;=G139))), "")</f>
         <v/>
       </c>
     </row>
@@ -4481,31 +4520,31 @@
     </row>
     <row r="142" spans="1:7" ht="75" customHeight="1">
       <c r="A142" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A141)*(EventsTable[End Date]&gt;=A141))), "")</f>
-        <v>• Level 2</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A141)*(EventsTable[End Date]&gt;=A141))), "")</f>
+        <v/>
       </c>
       <c r="B142" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B141)*(EventsTable[End Date]&gt;=B141))), "")</f>
-        <v>• Level 2</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B141)*(EventsTable[End Date]&gt;=B141))), "")</f>
+        <v/>
       </c>
       <c r="C142" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C141)*(EventsTable[End Date]&gt;=C141))), "")</f>
-        <v>• Level 2</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C141)*(EventsTable[End Date]&gt;=C141))), "")</f>
+        <v/>
       </c>
       <c r="D142" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D141)*(EventsTable[End Date]&gt;=D141))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D141)*(EventsTable[End Date]&gt;=D141))), "")</f>
         <v/>
       </c>
       <c r="E142" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E141)*(EventsTable[End Date]&gt;=E141))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E141)*(EventsTable[End Date]&gt;=E141))), "")</f>
         <v/>
       </c>
       <c r="F142" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F141)*(EventsTable[End Date]&gt;=F141))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F141)*(EventsTable[End Date]&gt;=F141))), "")</f>
         <v/>
       </c>
       <c r="G142" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G141)*(EventsTable[End Date]&gt;=G141))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G141)*(EventsTable[End Date]&gt;=G141))), "")</f>
         <v/>
       </c>
     </row>
@@ -4534,31 +4573,31 @@
     </row>
     <row r="144" spans="1:7" ht="75" customHeight="1">
       <c r="A144" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A143)*(EventsTable[End Date]&gt;=A143))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A143)*(EventsTable[End Date]&gt;=A143))), "")</f>
         <v/>
       </c>
       <c r="B144" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B143)*(EventsTable[End Date]&gt;=B143))), "")</f>
-        <v>• SA Nationals - Swimming</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B143)*(EventsTable[End Date]&gt;=B143))), "")</f>
+        <v/>
       </c>
       <c r="C144" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C143)*(EventsTable[End Date]&gt;=C143))), "")</f>
-        <v>• SA Nationals - Swimming</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C143)*(EventsTable[End Date]&gt;=C143))), "")</f>
+        <v/>
       </c>
       <c r="D144" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D143)*(EventsTable[End Date]&gt;=D143))), "")</f>
-        <v>• SA Nationals - Swimming</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D143)*(EventsTable[End Date]&gt;=D143))), "")</f>
+        <v/>
       </c>
       <c r="E144" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E143)*(EventsTable[End Date]&gt;=E143))), "")</f>
-        <v>• SA Nationals - Swimming</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E143)*(EventsTable[End Date]&gt;=E143))), "")</f>
+        <v/>
       </c>
       <c r="F144" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F143)*(EventsTable[End Date]&gt;=F143))), "")</f>
-        <v>• SA Nationals - Swimming</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F143)*(EventsTable[End Date]&gt;=F143))), "")</f>
+        <v/>
       </c>
       <c r="G144" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G143)*(EventsTable[End Date]&gt;=G143))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G143)*(EventsTable[End Date]&gt;=G143))), "")</f>
         <v/>
       </c>
     </row>
@@ -4587,32 +4626,32 @@
     </row>
     <row r="146" spans="1:7" ht="75" customHeight="1">
       <c r="A146" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A145)*(EventsTable[End Date]&gt;=A145))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A145)*(EventsTable[End Date]&gt;=A145))), "")</f>
         <v/>
       </c>
       <c r="B146" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B145)*(EventsTable[End Date]&gt;=B145))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B145)*(EventsTable[End Date]&gt;=B145))), "")</f>
         <v/>
       </c>
       <c r="C146" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C145)*(EventsTable[End Date]&gt;=C145))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C145)*(EventsTable[End Date]&gt;=C145))), "")</f>
         <v/>
       </c>
       <c r="D146" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D145)*(EventsTable[End Date]&gt;=D145))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D145)*(EventsTable[End Date]&gt;=D145))), "")</f>
         <v/>
       </c>
       <c r="E146" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E145)*(EventsTable[End Date]&gt;=E145))), "")</f>
-        <v>• SA School</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E145)*(EventsTable[End Date]&gt;=E145))), "")</f>
+        <v/>
       </c>
       <c r="F146" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F145)*(EventsTable[End Date]&gt;=F145))), "")</f>
-        <v>• SA School</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F145)*(EventsTable[End Date]&gt;=F145))), "")</f>
+        <v/>
       </c>
       <c r="G146" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G145)*(EventsTable[End Date]&gt;=G145))), "")</f>
-        <v>• SA School</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G145)*(EventsTable[End Date]&gt;=G145))), "")</f>
+        <v/>
       </c>
     </row>
     <row r="147" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4636,24 +4675,23 @@
     </row>
     <row r="148" spans="1:7" ht="75" customHeight="1">
       <c r="A148" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A147)*(EventsTable[End Date]&gt;=A147))), "")</f>
-        <v>• SA School</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A147)*(EventsTable[End Date]&gt;=A147))), "")</f>
+        <v/>
       </c>
       <c r="B148" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B147)*(EventsTable[End Date]&gt;=B147))), "")</f>
-        <v>• SA School
-• Freedom Day</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B147)*(EventsTable[End Date]&gt;=B147))), "")</f>
+        <v/>
       </c>
       <c r="C148" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C147)*(EventsTable[End Date]&gt;=C147))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C147)*(EventsTable[End Date]&gt;=C147))), "")</f>
         <v/>
       </c>
       <c r="D148" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D147)*(EventsTable[End Date]&gt;=D147))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D147)*(EventsTable[End Date]&gt;=D147))), "")</f>
         <v/>
       </c>
       <c r="E148" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E147)*(EventsTable[End Date]&gt;=E147))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E147)*(EventsTable[End Date]&gt;=E147))), "")</f>
         <v/>
       </c>
       <c r="F148" s="11"/>
@@ -4661,7 +4699,7 @@
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
       <c r="A150" s="46" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B150" s="45"/>
       <c r="C150" s="45"/>
@@ -4672,25 +4710,25 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="D151" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="E151" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="F151" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="G151" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4713,11 +4751,11 @@
       <c r="D153" s="10"/>
       <c r="E153" s="10"/>
       <c r="F153" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F152)*(EventsTable[End Date]&gt;=F152))), "")</f>
-        <v>• Workers' Day</v>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F152)*(EventsTable[End Date]&gt;=F152))), "")</f>
+        <v/>
       </c>
       <c r="G153" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G152)*(EventsTable[End Date]&gt;=G152))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G152)*(EventsTable[End Date]&gt;=G152))), "")</f>
         <v/>
       </c>
     </row>
@@ -4746,31 +4784,31 @@
     </row>
     <row r="155" spans="1:7" ht="75" customHeight="1">
       <c r="A155" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A154)*(EventsTable[End Date]&gt;=A154))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A154)*(EventsTable[End Date]&gt;=A154))), "")</f>
         <v/>
       </c>
       <c r="B155" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B154)*(EventsTable[End Date]&gt;=B154))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B154)*(EventsTable[End Date]&gt;=B154))), "")</f>
         <v/>
       </c>
       <c r="C155" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C154)*(EventsTable[End Date]&gt;=C154))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C154)*(EventsTable[End Date]&gt;=C154))), "")</f>
         <v/>
       </c>
       <c r="D155" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D154)*(EventsTable[End Date]&gt;=D154))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D154)*(EventsTable[End Date]&gt;=D154))), "")</f>
         <v/>
       </c>
       <c r="E155" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E154)*(EventsTable[End Date]&gt;=E154))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E154)*(EventsTable[End Date]&gt;=E154))), "")</f>
         <v/>
       </c>
       <c r="F155" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F154)*(EventsTable[End Date]&gt;=F154))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F154)*(EventsTable[End Date]&gt;=F154))), "")</f>
         <v/>
       </c>
       <c r="G155" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G154)*(EventsTable[End Date]&gt;=G154))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G154)*(EventsTable[End Date]&gt;=G154))), "")</f>
         <v/>
       </c>
     </row>
@@ -4799,31 +4837,31 @@
     </row>
     <row r="157" spans="1:7" ht="75" customHeight="1">
       <c r="A157" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A156)*(EventsTable[End Date]&gt;=A156))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A156)*(EventsTable[End Date]&gt;=A156))), "")</f>
         <v/>
       </c>
       <c r="B157" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B156)*(EventsTable[End Date]&gt;=B156))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B156)*(EventsTable[End Date]&gt;=B156))), "")</f>
         <v/>
       </c>
       <c r="C157" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C156)*(EventsTable[End Date]&gt;=C156))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C156)*(EventsTable[End Date]&gt;=C156))), "")</f>
         <v/>
       </c>
       <c r="D157" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D156)*(EventsTable[End Date]&gt;=D156))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D156)*(EventsTable[End Date]&gt;=D156))), "")</f>
         <v/>
       </c>
       <c r="E157" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E156)*(EventsTable[End Date]&gt;=E156))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E156)*(EventsTable[End Date]&gt;=E156))), "")</f>
         <v/>
       </c>
       <c r="F157" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F156)*(EventsTable[End Date]&gt;=F156))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F156)*(EventsTable[End Date]&gt;=F156))), "")</f>
         <v/>
       </c>
       <c r="G157" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G156)*(EventsTable[End Date]&gt;=G156))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G156)*(EventsTable[End Date]&gt;=G156))), "")</f>
         <v/>
       </c>
     </row>
@@ -4852,31 +4890,31 @@
     </row>
     <row r="159" spans="1:7" ht="75" customHeight="1">
       <c r="A159" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A158)*(EventsTable[End Date]&gt;=A158))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A158)*(EventsTable[End Date]&gt;=A158))), "")</f>
         <v/>
       </c>
       <c r="B159" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B158)*(EventsTable[End Date]&gt;=B158))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B158)*(EventsTable[End Date]&gt;=B158))), "")</f>
         <v/>
       </c>
       <c r="C159" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C158)*(EventsTable[End Date]&gt;=C158))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C158)*(EventsTable[End Date]&gt;=C158))), "")</f>
         <v/>
       </c>
       <c r="D159" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D158)*(EventsTable[End Date]&gt;=D158))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D158)*(EventsTable[End Date]&gt;=D158))), "")</f>
         <v/>
       </c>
       <c r="E159" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E158)*(EventsTable[End Date]&gt;=E158))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E158)*(EventsTable[End Date]&gt;=E158))), "")</f>
         <v/>
       </c>
       <c r="F159" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F158)*(EventsTable[End Date]&gt;=F158))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F158)*(EventsTable[End Date]&gt;=F158))), "")</f>
         <v/>
       </c>
       <c r="G159" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G158)*(EventsTable[End Date]&gt;=G158))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G158)*(EventsTable[End Date]&gt;=G158))), "")</f>
         <v/>
       </c>
     </row>
@@ -4905,31 +4943,31 @@
     </row>
     <row r="161" spans="1:7" ht="75" customHeight="1">
       <c r="A161" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A160)*(EventsTable[End Date]&gt;=A160))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A160)*(EventsTable[End Date]&gt;=A160))), "")</f>
         <v/>
       </c>
       <c r="B161" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B160)*(EventsTable[End Date]&gt;=B160))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=B160)*(EventsTable[End Date]&gt;=B160))), "")</f>
         <v/>
       </c>
       <c r="C161" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C160)*(EventsTable[End Date]&gt;=C160))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=C160)*(EventsTable[End Date]&gt;=C160))), "")</f>
         <v/>
       </c>
       <c r="D161" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D160)*(EventsTable[End Date]&gt;=D160))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=D160)*(EventsTable[End Date]&gt;=D160))), "")</f>
         <v/>
       </c>
       <c r="E161" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E160)*(EventsTable[End Date]&gt;=E160))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=E160)*(EventsTable[End Date]&gt;=E160))), "")</f>
         <v/>
       </c>
       <c r="F161" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F160)*(EventsTable[End Date]&gt;=F160))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=F160)*(EventsTable[End Date]&gt;=F160))), "")</f>
         <v/>
       </c>
       <c r="G161" s="6" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G160)*(EventsTable[End Date]&gt;=G160))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=G160)*(EventsTable[End Date]&gt;=G160))), "")</f>
         <v/>
       </c>
     </row>
@@ -4946,7 +4984,7 @@
     </row>
     <row r="163" spans="1:7" ht="75" customHeight="1">
       <c r="A163" s="5" t="str">
-        <f>IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A162)*(EventsTable[End Date]&gt;=A162))), "")</f>
+        <f ca="1">IFERROR(_xlfn.TEXTJOIN(CHAR(10), TRUE, "• " &amp; _xlfn._xlws.FILTER(EventsTable[Event Name], (EventsTable[Start Date]&lt;=A162)*(EventsTable[End Date]&gt;=A162))), "")</f>
         <v/>
       </c>
       <c r="B163" s="10"/>
@@ -4980,7 +5018,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -5382,7 +5420,7 @@
         <v>28</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F27" s="40" t="s">
         <v>30</v>
@@ -5428,7 +5466,7 @@
         <v>46</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F29" s="40" t="s">
         <v>30</v>
@@ -5439,7 +5477,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B30" s="42">
         <v>46228</v>
@@ -5448,10 +5486,10 @@
         <v>46229</v>
       </c>
       <c r="D30" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="40" t="s">
         <v>49</v>
-      </c>
-      <c r="E30" s="40" t="s">
-        <v>50</v>
       </c>
       <c r="F30" s="40" t="s">
         <v>30</v>
@@ -5462,7 +5500,7 @@
     </row>
     <row r="31" spans="1:7" ht="24.9" customHeight="1">
       <c r="A31" s="41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" s="41"/>
       <c r="C31" s="41"/>
@@ -5473,7 +5511,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" s="42">
         <v>46242</v>
@@ -5496,7 +5534,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B33" s="42">
         <v>46243</v>
@@ -5513,7 +5551,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B34" s="42">
         <v>46244</v>
@@ -5530,7 +5568,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B35" s="42">
         <v>46249</v>
@@ -5553,7 +5591,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B36" s="42">
         <v>46249</v>
@@ -5562,10 +5600,10 @@
         <v>46249</v>
       </c>
       <c r="D36" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F36" s="40" t="s">
         <v>30</v>
@@ -5576,7 +5614,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B37" s="42">
         <v>46256</v>
@@ -5585,13 +5623,13 @@
         <v>46257</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G37" s="40" t="s">
         <v>3</v>
@@ -5599,7 +5637,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B38" s="42">
         <v>46277</v>
@@ -5608,10 +5646,10 @@
         <v>46278</v>
       </c>
       <c r="D38" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="40" t="s">
         <v>60</v>
-      </c>
-      <c r="E38" s="40" t="s">
-        <v>61</v>
       </c>
       <c r="F38" s="40" t="s">
         <v>30</v>
@@ -5622,7 +5660,7 @@
     </row>
     <row r="39" spans="1:7" ht="17.25" customHeight="1">
       <c r="A39" s="41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B39" s="41"/>
       <c r="C39" s="41"/>
@@ -5633,7 +5671,7 @@
     </row>
     <row r="40" spans="1:7" ht="24.9" customHeight="1">
       <c r="A40" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B40" s="42">
         <v>46270</v>
@@ -5642,10 +5680,10 @@
         <v>46270</v>
       </c>
       <c r="D40" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="E40" s="40" t="s">
         <v>64</v>
-      </c>
-      <c r="E40" s="40" t="s">
-        <v>65</v>
       </c>
       <c r="F40" s="40" t="s">
         <v>30</v>
@@ -5656,7 +5694,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B41" s="42">
         <v>46270</v>
@@ -5668,7 +5706,7 @@
         <v>46</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F41" s="40" t="s">
         <v>30</v>
@@ -5679,7 +5717,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B42" s="42">
         <v>46285</v>
@@ -5688,10 +5726,10 @@
         <v>46285</v>
       </c>
       <c r="D42" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="E42" s="40" t="s">
         <v>68</v>
-      </c>
-      <c r="E42" s="40" t="s">
-        <v>69</v>
       </c>
       <c r="F42" s="40" t="s">
         <v>30</v>
@@ -5702,7 +5740,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B43" s="42">
         <v>46289</v>
@@ -5711,13 +5749,13 @@
         <v>46292</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="F43" s="40" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="G43" s="40" t="s">
         <v>2</v>
@@ -5725,7 +5763,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B44" s="42">
         <v>46289</v>
@@ -5742,7 +5780,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B45" s="42">
         <v>46290</v>
@@ -5751,10 +5789,10 @@
         <v>46292</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F45" s="40" t="s">
         <v>30</v>
@@ -5765,7 +5803,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="40" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B46" s="42">
         <v>46291</v>
@@ -5774,10 +5812,10 @@
         <v>46291</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F46" s="40" t="s">
         <v>30</v>
@@ -5788,7 +5826,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B47" s="42">
         <v>46291</v>
@@ -5797,10 +5835,10 @@
         <v>46293</v>
       </c>
       <c r="D47" s="40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F47" s="40" t="s">
         <v>30</v>
@@ -5811,7 +5849,7 @@
     </row>
     <row r="48" spans="1:7" ht="24.9" customHeight="1">
       <c r="A48" s="41" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B48" s="41"/>
       <c r="C48" s="41"/>
@@ -5822,7 +5860,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="40" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B49" s="42">
         <v>46297</v>
@@ -5831,10 +5869,10 @@
         <v>46299</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E49" s="40" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F49" s="40" t="s">
         <v>30</v>
@@ -5845,7 +5883,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B50" s="42">
         <v>46298</v>
@@ -5854,10 +5892,10 @@
         <v>46298</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F50" s="40" t="s">
         <v>30</v>
@@ -5868,7 +5906,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B51" s="42">
         <v>46298</v>
@@ -5877,10 +5915,10 @@
         <v>46299</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F51" s="40" t="s">
         <v>30</v>
@@ -5891,7 +5929,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B52" s="42">
         <v>46312</v>
@@ -5903,7 +5941,7 @@
         <v>43</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F52" s="40" t="s">
         <v>30</v>
@@ -5914,7 +5952,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B53" s="42">
         <v>46312</v>
@@ -5923,10 +5961,10 @@
         <v>46312</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F53" s="40" t="s">
         <v>30</v>
@@ -5937,7 +5975,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="40" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B54" s="42">
         <v>46318</v>
@@ -5946,10 +5984,10 @@
         <v>46320</v>
       </c>
       <c r="D54" s="40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F54" s="40" t="s">
         <v>30</v>
@@ -5960,7 +5998,7 @@
     </row>
     <row r="55" spans="1:7" ht="24.9" customHeight="1">
       <c r="A55" s="40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B55" s="42">
         <v>46326</v>
@@ -5969,10 +6007,10 @@
         <v>46326</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F55" s="40" t="s">
         <v>30</v>
@@ -5983,7 +6021,7 @@
     </row>
     <row r="56" spans="1:7" ht="17.25" customHeight="1">
       <c r="A56" s="41" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B56" s="41"/>
       <c r="C56" s="41"/>
@@ -5994,7 +6032,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B57" s="42">
         <v>46333</v>
@@ -6003,10 +6041,10 @@
         <v>46333</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F57" s="40" t="s">
         <v>30</v>
@@ -6017,7 +6055,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="40" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B58" s="42">
         <v>46340</v>
@@ -6026,10 +6064,10 @@
         <v>46341</v>
       </c>
       <c r="D58" s="40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F58" s="40" t="s">
         <v>30</v>
@@ -6040,7 +6078,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B59" s="42">
         <v>46347</v>
@@ -6049,10 +6087,10 @@
         <v>46347</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F59" s="40" t="s">
         <v>30</v>
@@ -6063,7 +6101,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="40" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B60" s="42">
         <v>46347</v>
@@ -6072,10 +6110,10 @@
         <v>46348</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F60" s="40" t="s">
         <v>30</v>
@@ -6086,7 +6124,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B61" s="42">
         <v>46353</v>
@@ -6095,10 +6133,10 @@
         <v>46355</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F61" s="40" t="s">
         <v>30</v>
@@ -6109,7 +6147,7 @@
     </row>
     <row r="62" spans="1:7" ht="24.9" customHeight="1">
       <c r="A62" s="40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B62" s="42">
         <v>46354</v>
@@ -6118,10 +6156,10 @@
         <v>46354</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F62" s="40" t="s">
         <v>30</v>
@@ -6132,7 +6170,7 @@
     </row>
     <row r="63" spans="1:7" ht="17.25" customHeight="1">
       <c r="A63" s="41" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B63" s="41"/>
       <c r="C63" s="41"/>
@@ -6143,7 +6181,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B64" s="42">
         <v>46360</v>
@@ -6152,10 +6190,10 @@
         <v>46361</v>
       </c>
       <c r="D64" s="40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F64" s="40" t="s">
         <v>30</v>
@@ -6166,7 +6204,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="40" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B65" s="42">
         <v>46368</v>
@@ -6175,10 +6213,10 @@
         <v>46369</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F65" s="40" t="s">
         <v>30</v>
@@ -6189,7 +6227,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B66" s="42">
         <v>46366</v>
@@ -6198,10 +6236,10 @@
         <v>46370</v>
       </c>
       <c r="D66" s="40" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F66" s="40" t="s">
         <v>30</v>
@@ -6212,7 +6250,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="40" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B67" s="42">
         <v>46372</v>
@@ -6229,7 +6267,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="40" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B68" s="42">
         <v>46381</v>
@@ -6246,7 +6284,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B69" s="42">
         <v>46382</v>
@@ -6263,7 +6301,7 @@
     </row>
     <row r="70" spans="1:7" ht="17.25" customHeight="1">
       <c r="A70" s="41" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B70" s="41"/>
       <c r="C70" s="41"/>
@@ -6291,7 +6329,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="40" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B72" s="42">
         <v>46395</v>
@@ -6300,10 +6338,10 @@
         <v>46396</v>
       </c>
       <c r="D72" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F72" s="40" t="s">
         <v>30</v>
@@ -6314,7 +6352,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B73" s="42">
         <v>46403</v>
@@ -6323,10 +6361,10 @@
         <v>46404</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F73" s="40" t="s">
         <v>30</v>
@@ -6337,7 +6375,7 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="40" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B74" s="42">
         <v>46403</v>
@@ -6346,10 +6384,10 @@
         <v>46404</v>
       </c>
       <c r="D74" s="40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F74" s="40" t="s">
         <v>30</v>
@@ -6360,7 +6398,7 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="40" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B75" s="42">
         <v>46403</v>
@@ -6369,10 +6407,10 @@
         <v>46403</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F75" s="40" t="s">
         <v>30</v>
@@ -6383,7 +6421,7 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B76" s="42">
         <v>46403</v>
@@ -6392,10 +6430,10 @@
         <v>46403</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F76" s="40" t="s">
         <v>30</v>
@@ -6406,7 +6444,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B77" s="42">
         <v>46403</v>
@@ -6429,7 +6467,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B78" s="42">
         <v>46396</v>
@@ -6441,7 +6479,7 @@
         <v>46</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F78" s="40" t="s">
         <v>30</v>
@@ -6452,7 +6490,7 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B79" s="42">
         <v>46404</v>
@@ -6461,10 +6499,10 @@
         <v>46404</v>
       </c>
       <c r="D79" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F79" s="40" t="s">
         <v>30</v>
@@ -6475,7 +6513,7 @@
     </row>
     <row r="80" spans="1:7" ht="24.9" customHeight="1">
       <c r="A80" s="40" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B80" s="42">
         <v>46410</v>
@@ -6484,10 +6522,10 @@
         <v>46410</v>
       </c>
       <c r="D80" s="40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F80" s="40" t="s">
         <v>30</v>
@@ -6498,7 +6536,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="40" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B81" s="42">
         <v>46411</v>
@@ -6507,10 +6545,10 @@
         <v>46411</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F81" s="40" t="s">
         <v>30</v>
@@ -6521,7 +6559,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B82" s="42">
         <v>46415</v>
@@ -6530,10 +6568,10 @@
         <v>46415</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F82" s="40" t="s">
         <v>30</v>
@@ -6544,7 +6582,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="40" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B83" s="42">
         <v>46415</v>
@@ -6553,10 +6591,10 @@
         <v>46417</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F83" s="40" t="s">
         <v>30</v>
@@ -6567,7 +6605,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="40" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B84" s="42">
         <v>46416</v>
@@ -6576,10 +6614,10 @@
         <v>46416</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F84" s="40" t="s">
         <v>30</v>
@@ -6590,7 +6628,7 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="40" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B85" s="42">
         <v>46416</v>
@@ -6599,10 +6637,10 @@
         <v>46417</v>
       </c>
       <c r="D85" s="40" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F85" s="40" t="s">
         <v>30</v>
@@ -6613,7 +6651,7 @@
     </row>
     <row r="86" spans="1:7" ht="17.25" customHeight="1">
       <c r="A86" s="40" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B86" s="42">
         <v>46416</v>
@@ -6622,10 +6660,10 @@
         <v>46418</v>
       </c>
       <c r="D86" s="40" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F86" s="40" t="s">
         <v>30</v>
@@ -6636,7 +6674,7 @@
     </row>
     <row r="87" spans="1:7" ht="24.9" customHeight="1">
       <c r="A87" s="40" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B87" s="42">
         <v>46417</v>
@@ -6645,10 +6683,10 @@
         <v>46418</v>
       </c>
       <c r="D87" s="40" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F87" s="40" t="s">
         <v>30</v>
@@ -6659,7 +6697,7 @@
     </row>
     <row r="88" spans="1:7" ht="16.8">
       <c r="A88" s="41" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B88" s="41"/>
       <c r="C88" s="41"/>
@@ -6670,7 +6708,7 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B89" s="42">
         <v>46422</v>
@@ -6679,10 +6717,10 @@
         <v>46422</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F89" s="40" t="s">
         <v>30</v>
@@ -6693,7 +6731,7 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B90" s="42">
         <v>46422</v>
@@ -6702,10 +6740,10 @@
         <v>46423</v>
       </c>
       <c r="D90" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E90" s="40" t="s">
         <v>49</v>
-      </c>
-      <c r="E90" s="40" t="s">
-        <v>50</v>
       </c>
       <c r="F90" s="40" t="s">
         <v>30</v>
@@ -6716,7 +6754,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B91" s="42">
         <v>46424</v>
@@ -6725,10 +6763,10 @@
         <v>46424</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F91" s="40" t="s">
         <v>30</v>
@@ -6739,7 +6777,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="40" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B92" s="42">
         <v>46424</v>
@@ -6748,10 +6786,10 @@
         <v>46425</v>
       </c>
       <c r="D92" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F92" s="40" t="s">
         <v>30</v>
@@ -6762,7 +6800,7 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="40" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B93" s="42">
         <v>46431</v>
@@ -6771,10 +6809,10 @@
         <v>46431</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F93" s="40" t="s">
         <v>30</v>
@@ -6785,7 +6823,7 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="40" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B94" s="42">
         <v>46431</v>
@@ -6794,10 +6832,10 @@
         <v>46432</v>
       </c>
       <c r="D94" s="40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F94" s="40" t="s">
         <v>30</v>
@@ -6808,7 +6846,7 @@
     </row>
     <row r="95" spans="1:7" ht="17.25" customHeight="1">
       <c r="A95" s="40" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B95" s="42">
         <v>46438</v>
@@ -6817,10 +6855,10 @@
         <v>46438</v>
       </c>
       <c r="D95" s="40" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F95" s="40" t="s">
         <v>30</v>
@@ -6831,7 +6869,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="40" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B96" s="42">
         <v>46445</v>
@@ -6840,10 +6878,10 @@
         <v>46446</v>
       </c>
       <c r="D96" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E96" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F96" s="40" t="s">
         <v>30</v>
@@ -6854,7 +6892,7 @@
     </row>
     <row r="97" spans="1:7" ht="16.8">
       <c r="A97" s="41" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B97" s="41"/>
       <c r="C97" s="41"/>
@@ -6865,7 +6903,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="40" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B98" s="42">
         <v>46447</v>
@@ -6874,10 +6912,10 @@
         <v>46447</v>
       </c>
       <c r="D98" s="40" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E98" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F98" s="40" t="s">
         <v>30</v>
@@ -6888,7 +6926,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="40" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B99" s="42">
         <v>46448</v>
@@ -6897,10 +6935,10 @@
         <v>46448</v>
       </c>
       <c r="D99" s="40" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E99" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F99" s="40" t="s">
         <v>30</v>
@@ -6911,7 +6949,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="40" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B100" s="42">
         <v>46449</v>
@@ -6920,10 +6958,10 @@
         <v>46449</v>
       </c>
       <c r="D100" s="40" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E100" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F100" s="40" t="s">
         <v>30</v>
@@ -6934,7 +6972,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B101" s="42">
         <v>46450</v>
@@ -6943,10 +6981,10 @@
         <v>46450</v>
       </c>
       <c r="D101" s="40" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E101" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F101" s="40" t="s">
         <v>30</v>
@@ -6957,7 +6995,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="40" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B102" s="42">
         <v>46462</v>
@@ -6966,10 +7004,10 @@
         <v>46464</v>
       </c>
       <c r="D102" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E102" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F102" s="40" t="s">
         <v>30</v>
@@ -6980,7 +7018,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B103" s="42">
         <v>46465</v>
@@ -6989,10 +7027,10 @@
         <v>46469</v>
       </c>
       <c r="D103" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E103" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F103" s="40" t="s">
         <v>30</v>
@@ -7071,7 +7109,7 @@
     </row>
     <row r="108" spans="1:7" ht="24.9" customHeight="1">
       <c r="A108" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B108" s="42">
         <v>46477</v>
@@ -7080,10 +7118,10 @@
         <v>46477</v>
       </c>
       <c r="D108" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E108" s="40" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F108" s="40" t="s">
         <v>30</v>
@@ -7094,7 +7132,7 @@
     </row>
     <row r="109" spans="1:7" ht="16.8">
       <c r="A109" s="41" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B109" s="41"/>
       <c r="C109" s="41"/>
@@ -7105,7 +7143,7 @@
     </row>
     <row r="110" spans="1:7" ht="24.9" customHeight="1">
       <c r="A110" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B110" s="42">
         <v>46478</v>
@@ -7114,10 +7152,10 @@
         <v>46480</v>
       </c>
       <c r="D110" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E110" s="40" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F110" s="40" t="s">
         <v>30</v>
@@ -7128,7 +7166,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B111" s="42">
         <v>46482</v>
@@ -7137,10 +7175,10 @@
         <v>46484</v>
       </c>
       <c r="D111" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E111" s="40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F111" s="40" t="s">
         <v>30</v>
@@ -7149,21 +7187,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" s="24" customFormat="1">
+    <row r="112" spans="1:7" s="48" customFormat="1">
       <c r="A112" s="40" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B112" s="42">
-        <v>46490</v>
+        <v>46485</v>
       </c>
       <c r="C112" s="42">
-        <v>46494</v>
+        <v>46489</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="E112" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F112" s="40" t="s">
         <v>30</v>
@@ -7172,195 +7210,201 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="24.9" customHeight="1">
+    <row r="113" spans="1:7" s="24" customFormat="1">
       <c r="A113" s="40" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="B113" s="42">
-        <v>46500</v>
+        <v>46490</v>
       </c>
       <c r="C113" s="42">
-        <v>46504</v>
+        <v>46494</v>
       </c>
       <c r="D113" s="40" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="E113" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F113" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G113" s="40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="13.2" customHeight="1">
       <c r="A114" s="40" t="s">
-        <v>23</v>
+        <v>201</v>
       </c>
       <c r="B114" s="42">
-        <v>46504</v>
+        <v>46500</v>
       </c>
       <c r="C114" s="42">
         <v>46504</v>
       </c>
-      <c r="D114" s="40"/>
-      <c r="E114" s="40"/>
-      <c r="F114" s="40"/>
+      <c r="D114" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="E114" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="F114" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G114" s="40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B115" s="42">
+        <v>46504</v>
+      </c>
+      <c r="C115" s="42">
+        <v>46504</v>
+      </c>
+      <c r="D115" s="40"/>
+      <c r="E115" s="40"/>
+      <c r="F115" s="40"/>
+      <c r="G115" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A115" s="41" t="s">
+    <row r="116" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A116" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="B116" s="41"/>
+      <c r="C116" s="41"/>
+      <c r="D116" s="41"/>
+      <c r="E116" s="41"/>
+      <c r="F116" s="41"/>
+      <c r="G116" s="41"/>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B117" s="42">
+        <v>46508</v>
+      </c>
+      <c r="C117" s="42">
+        <v>46508</v>
+      </c>
+      <c r="D117" s="40"/>
+      <c r="E117" s="40"/>
+      <c r="F117" s="40"/>
+      <c r="G117" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A118" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="B118" s="41"/>
+      <c r="C118" s="41"/>
+      <c r="D118" s="41"/>
+      <c r="E118" s="41"/>
+      <c r="F118" s="41"/>
+      <c r="G118" s="41"/>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B119" s="42">
+        <v>46554</v>
+      </c>
+      <c r="C119" s="42">
+        <v>46554</v>
+      </c>
+      <c r="D119" s="40"/>
+      <c r="E119" s="40"/>
+      <c r="F119" s="40"/>
+      <c r="G119" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A120" s="41" t="s">
         <v>179</v>
       </c>
-      <c r="B115" s="41"/>
-      <c r="C115" s="41"/>
-      <c r="D115" s="41"/>
-      <c r="E115" s="41"/>
-      <c r="F115" s="41"/>
-      <c r="G115" s="41"/>
-    </row>
-    <row r="116" spans="1:7">
-      <c r="A116" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B116" s="42">
-        <v>46508</v>
-      </c>
-      <c r="C116" s="42">
-        <v>46508</v>
-      </c>
-      <c r="D116" s="40"/>
-      <c r="E116" s="40"/>
-      <c r="F116" s="40"/>
-      <c r="G116" s="40" t="s">
+      <c r="B120" s="41"/>
+      <c r="C120" s="41"/>
+      <c r="D120" s="41"/>
+      <c r="E120" s="41"/>
+      <c r="F120" s="41"/>
+      <c r="G120" s="41"/>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B121" s="42">
+        <v>46608</v>
+      </c>
+      <c r="C121" s="42">
+        <v>46608</v>
+      </c>
+      <c r="D121" s="40"/>
+      <c r="E121" s="40"/>
+      <c r="F121" s="40"/>
+      <c r="G121" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A117" s="41" t="s">
+    <row r="122" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A122" s="41" t="s">
         <v>180</v>
       </c>
-      <c r="B117" s="41"/>
-      <c r="C117" s="41"/>
-      <c r="D117" s="41"/>
-      <c r="E117" s="41"/>
-      <c r="F117" s="41"/>
-      <c r="G117" s="41"/>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="B118" s="42">
-        <v>46554</v>
-      </c>
-      <c r="C118" s="42">
-        <v>46554</v>
-      </c>
-      <c r="D118" s="40"/>
-      <c r="E118" s="40"/>
-      <c r="F118" s="40"/>
-      <c r="G118" s="40" t="s">
+      <c r="B122" s="41"/>
+      <c r="C122" s="41"/>
+      <c r="D122" s="41"/>
+      <c r="E122" s="41"/>
+      <c r="F122" s="41"/>
+      <c r="G122" s="41"/>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B123" s="42">
+        <v>46654</v>
+      </c>
+      <c r="C123" s="42">
+        <v>46654</v>
+      </c>
+      <c r="D123" s="40"/>
+      <c r="E123" s="40"/>
+      <c r="F123" s="40"/>
+      <c r="G123" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A119" s="41" t="s">
+    <row r="124" spans="1:7" ht="16.8">
+      <c r="A124" s="41" t="s">
         <v>181</v>
       </c>
-      <c r="B119" s="41"/>
-      <c r="C119" s="41"/>
-      <c r="D119" s="41"/>
-      <c r="E119" s="41"/>
-      <c r="F119" s="41"/>
-      <c r="G119" s="41"/>
-    </row>
-    <row r="120" spans="1:7">
-      <c r="A120" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B120" s="42">
-        <v>46608</v>
-      </c>
-      <c r="C120" s="42">
-        <v>46608</v>
-      </c>
-      <c r="D120" s="40"/>
-      <c r="E120" s="40"/>
-      <c r="F120" s="40"/>
-      <c r="G120" s="40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A121" s="41" t="s">
-        <v>182</v>
-      </c>
-      <c r="B121" s="41"/>
-      <c r="C121" s="41"/>
-      <c r="D121" s="41"/>
-      <c r="E121" s="41"/>
-      <c r="F121" s="41"/>
-      <c r="G121" s="41"/>
-    </row>
-    <row r="122" spans="1:7">
-      <c r="A122" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="B122" s="42">
-        <v>46654</v>
-      </c>
-      <c r="C122" s="42">
-        <v>46654</v>
-      </c>
-      <c r="D122" s="40"/>
-      <c r="E122" s="40"/>
-      <c r="F122" s="40"/>
-      <c r="G122" s="40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="16.8">
-      <c r="A123" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="B123" s="41"/>
-      <c r="C123" s="41"/>
-      <c r="D123" s="41"/>
-      <c r="E123" s="41"/>
-      <c r="F123" s="41"/>
-      <c r="G123" s="41"/>
-    </row>
-    <row r="124" spans="1:7">
-      <c r="A124" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="B124" s="42">
-        <v>46737</v>
-      </c>
-      <c r="C124" s="42">
-        <v>46737</v>
-      </c>
-      <c r="D124" s="40"/>
-      <c r="E124" s="40"/>
-      <c r="F124" s="40"/>
-      <c r="G124" s="40" t="s">
-        <v>8</v>
-      </c>
+      <c r="B124" s="41"/>
+      <c r="C124" s="41"/>
+      <c r="D124" s="41"/>
+      <c r="E124" s="41"/>
+      <c r="F124" s="41"/>
+      <c r="G124" s="41"/>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="40" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B125" s="42">
-        <v>46746</v>
+        <v>46737</v>
       </c>
       <c r="C125" s="42">
-        <v>46746</v>
+        <v>46737</v>
       </c>
       <c r="D125" s="40"/>
       <c r="E125" s="40"/>
@@ -7371,13 +7415,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="40" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B126" s="42">
-        <v>46747</v>
+        <v>46746</v>
       </c>
       <c r="C126" s="42">
-        <v>46747</v>
+        <v>46746</v>
       </c>
       <c r="D126" s="40"/>
       <c r="E126" s="40"/>
@@ -7388,13 +7432,13 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B127" s="42">
-        <v>46748</v>
+        <v>46747</v>
       </c>
       <c r="C127" s="42">
-        <v>46748</v>
+        <v>46747</v>
       </c>
       <c r="D127" s="40"/>
       <c r="E127" s="40"/>
@@ -7403,35 +7447,52 @@
         <v>8</v>
       </c>
     </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="B128" s="42">
+        <v>46748</v>
+      </c>
+      <c r="C128" s="42">
+        <v>46748</v>
+      </c>
+      <c r="D128" s="40"/>
+      <c r="E128" s="40"/>
+      <c r="F128" s="40"/>
+      <c r="G128" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A10:G127">
-    <cfRule type="expression" dxfId="6" priority="8">
+  <conditionalFormatting sqref="A10:G128">
+    <cfRule type="expression" dxfId="20" priority="8">
       <formula>$G10="National gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="9">
+    <cfRule type="expression" dxfId="19" priority="9">
       <formula>$G10="Provincial gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="10">
+    <cfRule type="expression" dxfId="18" priority="10">
       <formula>$G10="District gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="11">
+    <cfRule type="expression" dxfId="17" priority="11">
       <formula>$G10="Schools gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="12">
+    <cfRule type="expression" dxfId="16" priority="12">
       <formula>$G10="Club gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="13">
+    <cfRule type="expression" dxfId="15" priority="13">
       <formula>$G10="Open Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="14" priority="14">
       <formula>$G10="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G203">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G204">
       <formula1>"Club gala,District gala,Provincial gala,National gala,Open Water,Schools gala,Public Holiday"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7444,4 +7505,13 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -166,9 +166,6 @@
     <t>Curro Creston College</t>
   </si>
   <si>
-    <t>EDA Gala 1&amp; 2 SC - TBC</t>
-  </si>
-  <si>
     <t>Ethekwini</t>
   </si>
   <si>
@@ -641,6 +638,9 @@
   </si>
   <si>
     <t>Jollife Pool Pmb</t>
+  </si>
+  <si>
+    <t>EDA Gala 1&amp; 2 SC</t>
   </si>
 </sst>
 </file>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
       <c r="A5" s="46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B5" s="45"/>
       <c r="C5" s="45"/>
@@ -1658,25 +1658,25 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -1921,7 +1921,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
       <c r="A18" s="46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B18" s="45"/>
       <c r="C18" s="45"/>
@@ -1932,25 +1932,25 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2200,7 +2200,7 @@
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
       <c r="A31" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B31" s="45"/>
       <c r="C31" s="45"/>
@@ -2211,25 +2211,25 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2497,7 +2497,7 @@
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
       <c r="A46" s="46" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B46" s="45"/>
       <c r="C46" s="45"/>
@@ -2508,25 +2508,25 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2771,7 +2771,7 @@
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
       <c r="A59" s="46" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B59" s="45"/>
       <c r="C59" s="45"/>
@@ -2782,25 +2782,25 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3050,7 +3050,7 @@
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
       <c r="A72" s="46" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B72" s="45"/>
       <c r="C72" s="45"/>
@@ -3061,25 +3061,25 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="G73" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3342,7 +3342,7 @@
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
       <c r="A87" s="46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B87" s="45"/>
       <c r="C87" s="45"/>
@@ -3353,25 +3353,25 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3621,7 +3621,7 @@
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
       <c r="A100" s="46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B100" s="45"/>
       <c r="C100" s="45"/>
@@ -3632,25 +3632,25 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F101" s="2" t="s">
+      <c r="G101" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3900,7 +3900,7 @@
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
       <c r="A113" s="46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B113" s="45"/>
       <c r="C113" s="45"/>
@@ -3911,25 +3911,25 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="F114" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F114" s="2" t="s">
+      <c r="G114" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4146,7 +4146,7 @@
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
       <c r="A124" s="46" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B124" s="45"/>
       <c r="C124" s="45"/>
@@ -4157,25 +4157,25 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="E125" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="G125" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4425,7 +4425,7 @@
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
       <c r="A137" s="46" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B137" s="45"/>
       <c r="C137" s="45"/>
@@ -4436,25 +4436,25 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="D138" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="E138" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="F138" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F138" s="2" t="s">
+      <c r="G138" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4699,7 +4699,7 @@
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
       <c r="A150" s="46" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B150" s="45"/>
       <c r="C150" s="45"/>
@@ -4710,25 +4710,25 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C151" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="D151" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="E151" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="F151" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F151" s="2" t="s">
+      <c r="G151" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -5420,7 +5420,7 @@
         <v>28</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F27" s="40" t="s">
         <v>30</v>
@@ -5454,7 +5454,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="40" t="s">
-        <v>45</v>
+        <v>203</v>
       </c>
       <c r="B29" s="42">
         <v>46228</v>
@@ -5463,7 +5463,7 @@
         <v>46229</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" s="40" t="s">
         <v>33</v>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B30" s="42">
         <v>46228</v>
@@ -5486,10 +5486,10 @@
         <v>46229</v>
       </c>
       <c r="D30" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="40" t="s">
         <v>48</v>
-      </c>
-      <c r="E30" s="40" t="s">
-        <v>49</v>
       </c>
       <c r="F30" s="40" t="s">
         <v>30</v>
@@ -5500,7 +5500,7 @@
     </row>
     <row r="31" spans="1:7" ht="24.9" customHeight="1">
       <c r="A31" s="41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B31" s="41"/>
       <c r="C31" s="41"/>
@@ -5511,7 +5511,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B32" s="42">
         <v>46242</v>
@@ -5534,7 +5534,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B33" s="42">
         <v>46243</v>
@@ -5551,7 +5551,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B34" s="42">
         <v>46244</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B35" s="42">
         <v>46249</v>
@@ -5591,7 +5591,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B36" s="42">
         <v>46249</v>
@@ -5600,10 +5600,10 @@
         <v>46249</v>
       </c>
       <c r="D36" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F36" s="40" t="s">
         <v>30</v>
@@ -5614,7 +5614,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B37" s="42">
         <v>46256</v>
@@ -5623,13 +5623,13 @@
         <v>46257</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G37" s="40" t="s">
         <v>3</v>
@@ -5637,7 +5637,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B38" s="42">
         <v>46277</v>
@@ -5646,10 +5646,10 @@
         <v>46278</v>
       </c>
       <c r="D38" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="40" t="s">
         <v>59</v>
-      </c>
-      <c r="E38" s="40" t="s">
-        <v>60</v>
       </c>
       <c r="F38" s="40" t="s">
         <v>30</v>
@@ -5660,7 +5660,7 @@
     </row>
     <row r="39" spans="1:7" ht="17.25" customHeight="1">
       <c r="A39" s="41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B39" s="41"/>
       <c r="C39" s="41"/>
@@ -5671,7 +5671,7 @@
     </row>
     <row r="40" spans="1:7" ht="24.9" customHeight="1">
       <c r="A40" s="40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B40" s="42">
         <v>46270</v>
@@ -5680,10 +5680,10 @@
         <v>46270</v>
       </c>
       <c r="D40" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="40" t="s">
         <v>63</v>
-      </c>
-      <c r="E40" s="40" t="s">
-        <v>64</v>
       </c>
       <c r="F40" s="40" t="s">
         <v>30</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B41" s="42">
         <v>46270</v>
@@ -5703,10 +5703,10 @@
         <v>46271</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F41" s="40" t="s">
         <v>30</v>
@@ -5717,7 +5717,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B42" s="42">
         <v>46285</v>
@@ -5726,10 +5726,10 @@
         <v>46285</v>
       </c>
       <c r="D42" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E42" s="40" t="s">
         <v>67</v>
-      </c>
-      <c r="E42" s="40" t="s">
-        <v>68</v>
       </c>
       <c r="F42" s="40" t="s">
         <v>30</v>
@@ -5740,7 +5740,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B43" s="42">
         <v>46289</v>
@@ -5749,13 +5749,13 @@
         <v>46292</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F43" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G43" s="40" t="s">
         <v>2</v>
@@ -5763,7 +5763,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B44" s="42">
         <v>46289</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B45" s="42">
         <v>46290</v>
@@ -5789,10 +5789,10 @@
         <v>46292</v>
       </c>
       <c r="D45" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" s="40" t="s">
         <v>73</v>
-      </c>
-      <c r="E45" s="40" t="s">
-        <v>74</v>
       </c>
       <c r="F45" s="40" t="s">
         <v>30</v>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B46" s="42">
         <v>46291</v>
@@ -5812,10 +5812,10 @@
         <v>46291</v>
       </c>
       <c r="D46" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="40" t="s">
         <v>76</v>
-      </c>
-      <c r="E46" s="40" t="s">
-        <v>77</v>
       </c>
       <c r="F46" s="40" t="s">
         <v>30</v>
@@ -5826,7 +5826,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B47" s="42">
         <v>46291</v>
@@ -5835,10 +5835,10 @@
         <v>46293</v>
       </c>
       <c r="D47" s="40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F47" s="40" t="s">
         <v>30</v>
@@ -5849,7 +5849,7 @@
     </row>
     <row r="48" spans="1:7" ht="24.9" customHeight="1">
       <c r="A48" s="41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B48" s="41"/>
       <c r="C48" s="41"/>
@@ -5860,7 +5860,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B49" s="42">
         <v>46297</v>
@@ -5869,10 +5869,10 @@
         <v>46299</v>
       </c>
       <c r="D49" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="E49" s="40" t="s">
         <v>82</v>
-      </c>
-      <c r="E49" s="40" t="s">
-        <v>83</v>
       </c>
       <c r="F49" s="40" t="s">
         <v>30</v>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B50" s="42">
         <v>46298</v>
@@ -5892,10 +5892,10 @@
         <v>46298</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F50" s="40" t="s">
         <v>30</v>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B51" s="42">
         <v>46298</v>
@@ -5915,10 +5915,10 @@
         <v>46299</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F51" s="40" t="s">
         <v>30</v>
@@ -5929,7 +5929,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B52" s="42">
         <v>46312</v>
@@ -5941,7 +5941,7 @@
         <v>43</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F52" s="40" t="s">
         <v>30</v>
@@ -5952,7 +5952,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B53" s="42">
         <v>46312</v>
@@ -5961,10 +5961,10 @@
         <v>46312</v>
       </c>
       <c r="D53" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="E53" s="40" t="s">
         <v>91</v>
-      </c>
-      <c r="E53" s="40" t="s">
-        <v>92</v>
       </c>
       <c r="F53" s="40" t="s">
         <v>30</v>
@@ -5975,7 +5975,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B54" s="42">
         <v>46318</v>
@@ -5984,10 +5984,10 @@
         <v>46320</v>
       </c>
       <c r="D54" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54" s="40" t="s">
         <v>94</v>
-      </c>
-      <c r="E54" s="40" t="s">
-        <v>95</v>
       </c>
       <c r="F54" s="40" t="s">
         <v>30</v>
@@ -5998,7 +5998,7 @@
     </row>
     <row r="55" spans="1:7" ht="24.9" customHeight="1">
       <c r="A55" s="40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B55" s="42">
         <v>46326</v>
@@ -6007,10 +6007,10 @@
         <v>46326</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F55" s="40" t="s">
         <v>30</v>
@@ -6021,7 +6021,7 @@
     </row>
     <row r="56" spans="1:7" ht="17.25" customHeight="1">
       <c r="A56" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B56" s="41"/>
       <c r="C56" s="41"/>
@@ -6032,7 +6032,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B57" s="42">
         <v>46333</v>
@@ -6041,10 +6041,10 @@
         <v>46333</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F57" s="40" t="s">
         <v>30</v>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B58" s="42">
         <v>46340</v>
@@ -6064,10 +6064,10 @@
         <v>46341</v>
       </c>
       <c r="D58" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="E58" s="40" t="s">
         <v>101</v>
-      </c>
-      <c r="E58" s="40" t="s">
-        <v>102</v>
       </c>
       <c r="F58" s="40" t="s">
         <v>30</v>
@@ -6078,7 +6078,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B59" s="42">
         <v>46347</v>
@@ -6087,10 +6087,10 @@
         <v>46347</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F59" s="40" t="s">
         <v>30</v>
@@ -6101,7 +6101,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B60" s="42">
         <v>46347</v>
@@ -6110,10 +6110,10 @@
         <v>46348</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F60" s="40" t="s">
         <v>30</v>
@@ -6124,7 +6124,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B61" s="42">
         <v>46353</v>
@@ -6133,10 +6133,10 @@
         <v>46355</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F61" s="40" t="s">
         <v>30</v>
@@ -6147,7 +6147,7 @@
     </row>
     <row r="62" spans="1:7" ht="24.9" customHeight="1">
       <c r="A62" s="40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B62" s="42">
         <v>46354</v>
@@ -6156,10 +6156,10 @@
         <v>46354</v>
       </c>
       <c r="D62" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="E62" s="40" t="s">
         <v>91</v>
-      </c>
-      <c r="E62" s="40" t="s">
-        <v>92</v>
       </c>
       <c r="F62" s="40" t="s">
         <v>30</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="63" spans="1:7" ht="17.25" customHeight="1">
       <c r="A63" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B63" s="41"/>
       <c r="C63" s="41"/>
@@ -6181,7 +6181,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B64" s="42">
         <v>46360</v>
@@ -6190,10 +6190,10 @@
         <v>46361</v>
       </c>
       <c r="D64" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F64" s="40" t="s">
         <v>30</v>
@@ -6204,7 +6204,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B65" s="42">
         <v>46368</v>
@@ -6213,10 +6213,10 @@
         <v>46369</v>
       </c>
       <c r="D65" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="E65" s="40" t="s">
         <v>101</v>
-      </c>
-      <c r="E65" s="40" t="s">
-        <v>102</v>
       </c>
       <c r="F65" s="40" t="s">
         <v>30</v>
@@ -6227,7 +6227,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B66" s="42">
         <v>46366</v>
@@ -6236,10 +6236,10 @@
         <v>46370</v>
       </c>
       <c r="D66" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F66" s="40" t="s">
         <v>30</v>
@@ -6250,7 +6250,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B67" s="42">
         <v>46372</v>
@@ -6267,7 +6267,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B68" s="42">
         <v>46381</v>
@@ -6284,7 +6284,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B69" s="42">
         <v>46382</v>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="70" spans="1:7" ht="17.25" customHeight="1">
       <c r="A70" s="41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B70" s="41"/>
       <c r="C70" s="41"/>
@@ -6329,7 +6329,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="40" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B72" s="42">
         <v>46395</v>
@@ -6338,10 +6338,10 @@
         <v>46396</v>
       </c>
       <c r="D72" s="40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F72" s="40" t="s">
         <v>30</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B73" s="42">
         <v>46403</v>
@@ -6361,10 +6361,10 @@
         <v>46404</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F73" s="40" t="s">
         <v>30</v>
@@ -6375,7 +6375,7 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B74" s="42">
         <v>46403</v>
@@ -6384,10 +6384,10 @@
         <v>46404</v>
       </c>
       <c r="D74" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="E74" s="40" t="s">
         <v>101</v>
-      </c>
-      <c r="E74" s="40" t="s">
-        <v>102</v>
       </c>
       <c r="F74" s="40" t="s">
         <v>30</v>
@@ -6398,7 +6398,7 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B75" s="42">
         <v>46403</v>
@@ -6407,10 +6407,10 @@
         <v>46403</v>
       </c>
       <c r="D75" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="E75" s="40" t="s">
         <v>91</v>
-      </c>
-      <c r="E75" s="40" t="s">
-        <v>92</v>
       </c>
       <c r="F75" s="40" t="s">
         <v>30</v>
@@ -6421,7 +6421,7 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B76" s="42">
         <v>46403</v>
@@ -6430,10 +6430,10 @@
         <v>46403</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F76" s="40" t="s">
         <v>30</v>
@@ -6444,7 +6444,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B77" s="42">
         <v>46403</v>
@@ -6467,7 +6467,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B78" s="42">
         <v>46396</v>
@@ -6476,10 +6476,10 @@
         <v>46397</v>
       </c>
       <c r="D78" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F78" s="40" t="s">
         <v>30</v>
@@ -6490,7 +6490,7 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B79" s="42">
         <v>46404</v>
@@ -6499,10 +6499,10 @@
         <v>46404</v>
       </c>
       <c r="D79" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E79" s="40" t="s">
         <v>129</v>
-      </c>
-      <c r="E79" s="40" t="s">
-        <v>130</v>
       </c>
       <c r="F79" s="40" t="s">
         <v>30</v>
@@ -6513,7 +6513,7 @@
     </row>
     <row r="80" spans="1:7" ht="24.9" customHeight="1">
       <c r="A80" s="40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B80" s="42">
         <v>46410</v>
@@ -6522,10 +6522,10 @@
         <v>46410</v>
       </c>
       <c r="D80" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F80" s="40" t="s">
         <v>30</v>
@@ -6536,7 +6536,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="40" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B81" s="42">
         <v>46411</v>
@@ -6545,10 +6545,10 @@
         <v>46411</v>
       </c>
       <c r="D81" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="E81" s="40" t="s">
         <v>134</v>
-      </c>
-      <c r="E81" s="40" t="s">
-        <v>135</v>
       </c>
       <c r="F81" s="40" t="s">
         <v>30</v>
@@ -6559,7 +6559,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B82" s="42">
         <v>46415</v>
@@ -6568,10 +6568,10 @@
         <v>46415</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F82" s="40" t="s">
         <v>30</v>
@@ -6582,7 +6582,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B83" s="42">
         <v>46415</v>
@@ -6591,10 +6591,10 @@
         <v>46417</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F83" s="40" t="s">
         <v>30</v>
@@ -6605,7 +6605,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B84" s="42">
         <v>46416</v>
@@ -6614,10 +6614,10 @@
         <v>46416</v>
       </c>
       <c r="D84" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="E84" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="E84" s="40" t="s">
-        <v>142</v>
       </c>
       <c r="F84" s="40" t="s">
         <v>30</v>
@@ -6628,7 +6628,7 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="40" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B85" s="42">
         <v>46416</v>
@@ -6637,10 +6637,10 @@
         <v>46417</v>
       </c>
       <c r="D85" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="E85" s="40" t="s">
         <v>144</v>
-      </c>
-      <c r="E85" s="40" t="s">
-        <v>145</v>
       </c>
       <c r="F85" s="40" t="s">
         <v>30</v>
@@ -6651,7 +6651,7 @@
     </row>
     <row r="86" spans="1:7" ht="17.25" customHeight="1">
       <c r="A86" s="40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B86" s="42">
         <v>46416</v>
@@ -6660,10 +6660,10 @@
         <v>46418</v>
       </c>
       <c r="D86" s="40" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F86" s="40" t="s">
         <v>30</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="87" spans="1:7" ht="24.9" customHeight="1">
       <c r="A87" s="40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B87" s="42">
         <v>46417</v>
@@ -6683,10 +6683,10 @@
         <v>46418</v>
       </c>
       <c r="D87" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="E87" s="40" t="s">
         <v>149</v>
-      </c>
-      <c r="E87" s="40" t="s">
-        <v>150</v>
       </c>
       <c r="F87" s="40" t="s">
         <v>30</v>
@@ -6697,7 +6697,7 @@
     </row>
     <row r="88" spans="1:7" ht="16.8">
       <c r="A88" s="41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B88" s="41"/>
       <c r="C88" s="41"/>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B89" s="42">
         <v>46422</v>
@@ -6717,10 +6717,10 @@
         <v>46422</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F89" s="40" t="s">
         <v>30</v>
@@ -6731,7 +6731,7 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B90" s="42">
         <v>46422</v>
@@ -6740,10 +6740,10 @@
         <v>46423</v>
       </c>
       <c r="D90" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E90" s="40" t="s">
         <v>48</v>
-      </c>
-      <c r="E90" s="40" t="s">
-        <v>49</v>
       </c>
       <c r="F90" s="40" t="s">
         <v>30</v>
@@ -6754,7 +6754,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="40" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B91" s="42">
         <v>46424</v>
@@ -6763,10 +6763,10 @@
         <v>46424</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F91" s="40" t="s">
         <v>30</v>
@@ -6777,7 +6777,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B92" s="42">
         <v>46424</v>
@@ -6786,10 +6786,10 @@
         <v>46425</v>
       </c>
       <c r="D92" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F92" s="40" t="s">
         <v>30</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="40" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B93" s="42">
         <v>46431</v>
@@ -6809,10 +6809,10 @@
         <v>46431</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F93" s="40" t="s">
         <v>30</v>
@@ -6823,7 +6823,7 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B94" s="42">
         <v>46431</v>
@@ -6832,10 +6832,10 @@
         <v>46432</v>
       </c>
       <c r="D94" s="40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F94" s="40" t="s">
         <v>30</v>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="95" spans="1:7" ht="17.25" customHeight="1">
       <c r="A95" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B95" s="42">
         <v>46438</v>
@@ -6855,10 +6855,10 @@
         <v>46438</v>
       </c>
       <c r="D95" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="E95" s="40" t="s">
         <v>91</v>
-      </c>
-      <c r="E95" s="40" t="s">
-        <v>92</v>
       </c>
       <c r="F95" s="40" t="s">
         <v>30</v>
@@ -6869,7 +6869,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B96" s="42">
         <v>46445</v>
@@ -6878,10 +6878,10 @@
         <v>46446</v>
       </c>
       <c r="D96" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="E96" s="40" t="s">
         <v>160</v>
-      </c>
-      <c r="E96" s="40" t="s">
-        <v>161</v>
       </c>
       <c r="F96" s="40" t="s">
         <v>30</v>
@@ -6892,7 +6892,7 @@
     </row>
     <row r="97" spans="1:7" ht="16.8">
       <c r="A97" s="41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B97" s="41"/>
       <c r="C97" s="41"/>
@@ -6903,7 +6903,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B98" s="42">
         <v>46447</v>
@@ -6912,10 +6912,10 @@
         <v>46447</v>
       </c>
       <c r="D98" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E98" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F98" s="40" t="s">
         <v>30</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B99" s="42">
         <v>46448</v>
@@ -6935,10 +6935,10 @@
         <v>46448</v>
       </c>
       <c r="D99" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E99" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F99" s="40" t="s">
         <v>30</v>
@@ -6949,7 +6949,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B100" s="42">
         <v>46449</v>
@@ -6958,10 +6958,10 @@
         <v>46449</v>
       </c>
       <c r="D100" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E100" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F100" s="40" t="s">
         <v>30</v>
@@ -6972,7 +6972,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B101" s="42">
         <v>46450</v>
@@ -6981,10 +6981,10 @@
         <v>46450</v>
       </c>
       <c r="D101" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E101" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F101" s="40" t="s">
         <v>30</v>
@@ -6995,7 +6995,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B102" s="42">
         <v>46462</v>
@@ -7004,10 +7004,10 @@
         <v>46464</v>
       </c>
       <c r="D102" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E102" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F102" s="40" t="s">
         <v>30</v>
@@ -7018,7 +7018,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B103" s="42">
         <v>46465</v>
@@ -7027,10 +7027,10 @@
         <v>46469</v>
       </c>
       <c r="D103" s="40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E103" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F103" s="40" t="s">
         <v>30</v>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="108" spans="1:7" ht="24.9" customHeight="1">
       <c r="A108" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B108" s="42">
         <v>46477</v>
@@ -7118,10 +7118,10 @@
         <v>46477</v>
       </c>
       <c r="D108" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E108" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F108" s="40" t="s">
         <v>30</v>
@@ -7132,7 +7132,7 @@
     </row>
     <row r="109" spans="1:7" ht="16.8">
       <c r="A109" s="41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B109" s="41"/>
       <c r="C109" s="41"/>
@@ -7143,7 +7143,7 @@
     </row>
     <row r="110" spans="1:7" ht="24.9" customHeight="1">
       <c r="A110" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B110" s="42">
         <v>46478</v>
@@ -7152,10 +7152,10 @@
         <v>46480</v>
       </c>
       <c r="D110" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E110" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F110" s="40" t="s">
         <v>30</v>
@@ -7166,7 +7166,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B111" s="42">
         <v>46482</v>
@@ -7175,10 +7175,10 @@
         <v>46484</v>
       </c>
       <c r="D111" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E111" s="40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F111" s="40" t="s">
         <v>30</v>
@@ -7189,7 +7189,7 @@
     </row>
     <row r="112" spans="1:7" s="48" customFormat="1">
       <c r="A112" s="40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B112" s="42">
         <v>46485</v>
@@ -7198,10 +7198,10 @@
         <v>46489</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E112" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F112" s="40" t="s">
         <v>30</v>
@@ -7212,7 +7212,7 @@
     </row>
     <row r="113" spans="1:7" s="24" customFormat="1">
       <c r="A113" s="40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B113" s="42">
         <v>46490</v>
@@ -7221,10 +7221,10 @@
         <v>46494</v>
       </c>
       <c r="D113" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E113" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F113" s="40" t="s">
         <v>30</v>
@@ -7235,7 +7235,7 @@
     </row>
     <row r="114" spans="1:7" ht="13.2" customHeight="1">
       <c r="A114" s="40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B114" s="42">
         <v>46500</v>
@@ -7244,10 +7244,10 @@
         <v>46504</v>
       </c>
       <c r="D114" s="40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E114" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F114" s="40" t="s">
         <v>30</v>
@@ -7275,7 +7275,7 @@
     </row>
     <row r="116" spans="1:7" ht="17.25" customHeight="1">
       <c r="A116" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B116" s="41"/>
       <c r="C116" s="41"/>
@@ -7303,7 +7303,7 @@
     </row>
     <row r="118" spans="1:7" ht="17.25" customHeight="1">
       <c r="A118" s="41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B118" s="41"/>
       <c r="C118" s="41"/>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="120" spans="1:7" ht="17.25" customHeight="1">
       <c r="A120" s="41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B120" s="41"/>
       <c r="C120" s="41"/>
@@ -7342,7 +7342,7 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B121" s="42">
         <v>46608</v>
@@ -7359,7 +7359,7 @@
     </row>
     <row r="122" spans="1:7" ht="17.25" customHeight="1">
       <c r="A122" s="41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B122" s="41"/>
       <c r="C122" s="41"/>
@@ -7370,7 +7370,7 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B123" s="42">
         <v>46654</v>
@@ -7387,7 +7387,7 @@
     </row>
     <row r="124" spans="1:7" ht="16.8">
       <c r="A124" s="41" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B124" s="41"/>
       <c r="C124" s="41"/>
@@ -7398,7 +7398,7 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B125" s="42">
         <v>46737</v>
@@ -7415,7 +7415,7 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B126" s="42">
         <v>46746</v>
@@ -7432,7 +7432,7 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B127" s="42">
         <v>46747</v>
@@ -7449,7 +7449,7 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B128" s="42">
         <v>46748</v>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -154,9 +154,6 @@
     <t>JULY 2026</t>
   </si>
   <si>
-    <t>Prestige LC Championships</t>
-  </si>
-  <si>
     <t>UDA District Gala 1</t>
   </si>
   <si>
@@ -641,6 +638,9 @@
   </si>
   <si>
     <t>EDA Gala 1&amp; 2 SC</t>
+  </si>
+  <si>
+    <t>Prestige Championships</t>
   </si>
 </sst>
 </file>
@@ -1066,15 +1066,15 @@
     <xf numFmtId="0" fontId="25" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="datetime" xfId="1"/>
@@ -1082,91 +1082,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="pro_day_only_🏊UnsanctionedCalendar" xfId="3"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9F1239"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFC026D3"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF15803D"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFA16207"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7E22CE"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF0369A1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFEA580C"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9F1239"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFC026D3"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF15803D"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFA16207"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7E22CE"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF0369A1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFEA580C"/>
-      </font>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <b/>
@@ -1237,7 +1153,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1282,7 +1198,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1628,55 +1544,55 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" ht="24.9" customHeight="1">
-      <c r="B2" s="47"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="46" t="s">
-        <v>181</v>
-      </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
+      <c r="A5" s="45" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -1920,37 +1836,37 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="46" t="s">
-        <v>189</v>
-      </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
+      <c r="A18" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2199,37 +2115,37 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="46" t="s">
-        <v>190</v>
-      </c>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
+      <c r="A31" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2496,37 +2412,37 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
+      <c r="A46" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="B46" s="46"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2770,37 +2686,37 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="46" t="s">
-        <v>192</v>
-      </c>
-      <c r="B59" s="45"/>
-      <c r="C59" s="45"/>
-      <c r="D59" s="45"/>
-      <c r="E59" s="45"/>
-      <c r="F59" s="45"/>
-      <c r="G59" s="45"/>
+      <c r="A59" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="B59" s="46"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="46"/>
+      <c r="F59" s="46"/>
+      <c r="G59" s="46"/>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3049,37 +2965,37 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="B72" s="45"/>
-      <c r="C72" s="45"/>
-      <c r="D72" s="45"/>
-      <c r="E72" s="45"/>
-      <c r="F72" s="45"/>
-      <c r="G72" s="45"/>
+      <c r="A72" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="B72" s="46"/>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
+      <c r="F72" s="46"/>
+      <c r="G72" s="46"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="G73" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3341,37 +3257,37 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="B87" s="45"/>
-      <c r="C87" s="45"/>
-      <c r="D87" s="45"/>
-      <c r="E87" s="45"/>
-      <c r="F87" s="45"/>
-      <c r="G87" s="45"/>
+      <c r="A87" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="B87" s="46"/>
+      <c r="C87" s="46"/>
+      <c r="D87" s="46"/>
+      <c r="E87" s="46"/>
+      <c r="F87" s="46"/>
+      <c r="G87" s="46"/>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3620,37 +3536,37 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="46" t="s">
-        <v>195</v>
-      </c>
-      <c r="B100" s="45"/>
-      <c r="C100" s="45"/>
-      <c r="D100" s="45"/>
-      <c r="E100" s="45"/>
-      <c r="F100" s="45"/>
-      <c r="G100" s="45"/>
+      <c r="A100" s="45" t="s">
+        <v>194</v>
+      </c>
+      <c r="B100" s="46"/>
+      <c r="C100" s="46"/>
+      <c r="D100" s="46"/>
+      <c r="E100" s="46"/>
+      <c r="F100" s="46"/>
+      <c r="G100" s="46"/>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F101" s="2" t="s">
+      <c r="G101" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3899,37 +3815,37 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="B113" s="45"/>
-      <c r="C113" s="45"/>
-      <c r="D113" s="45"/>
-      <c r="E113" s="45"/>
-      <c r="F113" s="45"/>
-      <c r="G113" s="45"/>
+      <c r="A113" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="B113" s="46"/>
+      <c r="C113" s="46"/>
+      <c r="D113" s="46"/>
+      <c r="E113" s="46"/>
+      <c r="F113" s="46"/>
+      <c r="G113" s="46"/>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="F114" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F114" s="2" t="s">
+      <c r="G114" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4145,37 +4061,37 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="B124" s="45"/>
-      <c r="C124" s="45"/>
-      <c r="D124" s="45"/>
-      <c r="E124" s="45"/>
-      <c r="F124" s="45"/>
-      <c r="G124" s="45"/>
+      <c r="A124" s="45" t="s">
+        <v>196</v>
+      </c>
+      <c r="B124" s="46"/>
+      <c r="C124" s="46"/>
+      <c r="D124" s="46"/>
+      <c r="E124" s="46"/>
+      <c r="F124" s="46"/>
+      <c r="G124" s="46"/>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="E125" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="G125" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4424,37 +4340,37 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="B137" s="45"/>
-      <c r="C137" s="45"/>
-      <c r="D137" s="45"/>
-      <c r="E137" s="45"/>
-      <c r="F137" s="45"/>
-      <c r="G137" s="45"/>
+      <c r="A137" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="B137" s="46"/>
+      <c r="C137" s="46"/>
+      <c r="D137" s="46"/>
+      <c r="E137" s="46"/>
+      <c r="F137" s="46"/>
+      <c r="G137" s="46"/>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="D138" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="E138" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="F138" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F138" s="2" t="s">
+      <c r="G138" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4698,37 +4614,37 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="B150" s="45"/>
-      <c r="C150" s="45"/>
-      <c r="D150" s="45"/>
-      <c r="E150" s="45"/>
-      <c r="F150" s="45"/>
-      <c r="G150" s="45"/>
+      <c r="A150" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="B150" s="46"/>
+      <c r="C150" s="46"/>
+      <c r="D150" s="46"/>
+      <c r="E150" s="46"/>
+      <c r="F150" s="46"/>
+      <c r="G150" s="46"/>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C151" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="D151" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="E151" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="F151" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F151" s="2" t="s">
+      <c r="G151" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4996,12 +4912,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -5010,6 +4920,12 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5030,13 +4946,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
       <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7" ht="24.9" customHeight="1">
@@ -5408,7 +5324,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="40" t="s">
-        <v>41</v>
+        <v>203</v>
       </c>
       <c r="B27" s="42">
         <v>46210</v>
@@ -5420,7 +5336,7 @@
         <v>28</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F27" s="40" t="s">
         <v>30</v>
@@ -5431,7 +5347,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="42">
         <v>46221</v>
@@ -5440,10 +5356,10 @@
         <v>46221</v>
       </c>
       <c r="D28" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="40" t="s">
         <v>43</v>
-      </c>
-      <c r="E28" s="40" t="s">
-        <v>44</v>
       </c>
       <c r="F28" s="40" t="s">
         <v>30</v>
@@ -5454,7 +5370,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="40" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B29" s="42">
         <v>46228</v>
@@ -5463,7 +5379,7 @@
         <v>46229</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E29" s="40" t="s">
         <v>33</v>
@@ -5477,7 +5393,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B30" s="42">
         <v>46228</v>
@@ -5486,10 +5402,10 @@
         <v>46229</v>
       </c>
       <c r="D30" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="40" t="s">
         <v>47</v>
-      </c>
-      <c r="E30" s="40" t="s">
-        <v>48</v>
       </c>
       <c r="F30" s="40" t="s">
         <v>30</v>
@@ -5500,7 +5416,7 @@
     </row>
     <row r="31" spans="1:7" ht="24.9" customHeight="1">
       <c r="A31" s="41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B31" s="41"/>
       <c r="C31" s="41"/>
@@ -5511,7 +5427,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B32" s="42">
         <v>46242</v>
@@ -5534,7 +5450,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B33" s="42">
         <v>46243</v>
@@ -5551,7 +5467,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B34" s="42">
         <v>46244</v>
@@ -5568,7 +5484,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B35" s="42">
         <v>46249</v>
@@ -5577,10 +5493,10 @@
         <v>46249</v>
       </c>
       <c r="D35" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" s="40" t="s">
         <v>43</v>
-      </c>
-      <c r="E35" s="40" t="s">
-        <v>44</v>
       </c>
       <c r="F35" s="40" t="s">
         <v>30</v>
@@ -5591,7 +5507,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B36" s="42">
         <v>46249</v>
@@ -5600,10 +5516,10 @@
         <v>46249</v>
       </c>
       <c r="D36" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F36" s="40" t="s">
         <v>30</v>
@@ -5614,7 +5530,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B37" s="42">
         <v>46256</v>
@@ -5623,13 +5539,13 @@
         <v>46257</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G37" s="40" t="s">
         <v>3</v>
@@ -5637,7 +5553,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B38" s="42">
         <v>46277</v>
@@ -5646,10 +5562,10 @@
         <v>46278</v>
       </c>
       <c r="D38" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="40" t="s">
         <v>58</v>
-      </c>
-      <c r="E38" s="40" t="s">
-        <v>59</v>
       </c>
       <c r="F38" s="40" t="s">
         <v>30</v>
@@ -5660,7 +5576,7 @@
     </row>
     <row r="39" spans="1:7" ht="17.25" customHeight="1">
       <c r="A39" s="41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B39" s="41"/>
       <c r="C39" s="41"/>
@@ -5671,7 +5587,7 @@
     </row>
     <row r="40" spans="1:7" ht="24.9" customHeight="1">
       <c r="A40" s="40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" s="42">
         <v>46270</v>
@@ -5680,10 +5596,10 @@
         <v>46270</v>
       </c>
       <c r="D40" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" s="40" t="s">
         <v>62</v>
-      </c>
-      <c r="E40" s="40" t="s">
-        <v>63</v>
       </c>
       <c r="F40" s="40" t="s">
         <v>30</v>
@@ -5694,7 +5610,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B41" s="42">
         <v>46270</v>
@@ -5703,10 +5619,10 @@
         <v>46271</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F41" s="40" t="s">
         <v>30</v>
@@ -5717,7 +5633,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B42" s="42">
         <v>46285</v>
@@ -5726,10 +5642,10 @@
         <v>46285</v>
       </c>
       <c r="D42" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="E42" s="40" t="s">
         <v>66</v>
-      </c>
-      <c r="E42" s="40" t="s">
-        <v>67</v>
       </c>
       <c r="F42" s="40" t="s">
         <v>30</v>
@@ -5740,7 +5656,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B43" s="42">
         <v>46289</v>
@@ -5749,13 +5665,13 @@
         <v>46292</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F43" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G43" s="40" t="s">
         <v>2</v>
@@ -5763,7 +5679,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B44" s="42">
         <v>46289</v>
@@ -5780,7 +5696,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B45" s="42">
         <v>46290</v>
@@ -5789,10 +5705,10 @@
         <v>46292</v>
       </c>
       <c r="D45" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="E45" s="40" t="s">
         <v>72</v>
-      </c>
-      <c r="E45" s="40" t="s">
-        <v>73</v>
       </c>
       <c r="F45" s="40" t="s">
         <v>30</v>
@@ -5803,7 +5719,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B46" s="42">
         <v>46291</v>
@@ -5812,10 +5728,10 @@
         <v>46291</v>
       </c>
       <c r="D46" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="E46" s="40" t="s">
         <v>75</v>
-      </c>
-      <c r="E46" s="40" t="s">
-        <v>76</v>
       </c>
       <c r="F46" s="40" t="s">
         <v>30</v>
@@ -5826,7 +5742,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B47" s="42">
         <v>46291</v>
@@ -5835,10 +5751,10 @@
         <v>46293</v>
       </c>
       <c r="D47" s="40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F47" s="40" t="s">
         <v>30</v>
@@ -5849,7 +5765,7 @@
     </row>
     <row r="48" spans="1:7" ht="24.9" customHeight="1">
       <c r="A48" s="41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B48" s="41"/>
       <c r="C48" s="41"/>
@@ -5860,7 +5776,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B49" s="42">
         <v>46297</v>
@@ -5869,10 +5785,10 @@
         <v>46299</v>
       </c>
       <c r="D49" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="E49" s="40" t="s">
         <v>81</v>
-      </c>
-      <c r="E49" s="40" t="s">
-        <v>82</v>
       </c>
       <c r="F49" s="40" t="s">
         <v>30</v>
@@ -5883,7 +5799,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B50" s="42">
         <v>46298</v>
@@ -5892,10 +5808,10 @@
         <v>46298</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F50" s="40" t="s">
         <v>30</v>
@@ -5906,7 +5822,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B51" s="42">
         <v>46298</v>
@@ -5915,10 +5831,10 @@
         <v>46299</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F51" s="40" t="s">
         <v>30</v>
@@ -5929,7 +5845,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B52" s="42">
         <v>46312</v>
@@ -5938,10 +5854,10 @@
         <v>46312</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F52" s="40" t="s">
         <v>30</v>
@@ -5952,7 +5868,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B53" s="42">
         <v>46312</v>
@@ -5961,10 +5877,10 @@
         <v>46312</v>
       </c>
       <c r="D53" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="E53" s="40" t="s">
         <v>90</v>
-      </c>
-      <c r="E53" s="40" t="s">
-        <v>91</v>
       </c>
       <c r="F53" s="40" t="s">
         <v>30</v>
@@ -5975,7 +5891,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B54" s="42">
         <v>46318</v>
@@ -5984,10 +5900,10 @@
         <v>46320</v>
       </c>
       <c r="D54" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="E54" s="40" t="s">
         <v>93</v>
-      </c>
-      <c r="E54" s="40" t="s">
-        <v>94</v>
       </c>
       <c r="F54" s="40" t="s">
         <v>30</v>
@@ -5998,7 +5914,7 @@
     </row>
     <row r="55" spans="1:7" ht="24.9" customHeight="1">
       <c r="A55" s="40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B55" s="42">
         <v>46326</v>
@@ -6007,10 +5923,10 @@
         <v>46326</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F55" s="40" t="s">
         <v>30</v>
@@ -6021,7 +5937,7 @@
     </row>
     <row r="56" spans="1:7" ht="17.25" customHeight="1">
       <c r="A56" s="41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B56" s="41"/>
       <c r="C56" s="41"/>
@@ -6032,7 +5948,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B57" s="42">
         <v>46333</v>
@@ -6041,10 +5957,10 @@
         <v>46333</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F57" s="40" t="s">
         <v>30</v>
@@ -6055,7 +5971,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B58" s="42">
         <v>46340</v>
@@ -6064,10 +5980,10 @@
         <v>46341</v>
       </c>
       <c r="D58" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="E58" s="40" t="s">
         <v>100</v>
-      </c>
-      <c r="E58" s="40" t="s">
-        <v>101</v>
       </c>
       <c r="F58" s="40" t="s">
         <v>30</v>
@@ -6078,7 +5994,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B59" s="42">
         <v>46347</v>
@@ -6087,10 +6003,10 @@
         <v>46347</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F59" s="40" t="s">
         <v>30</v>
@@ -6101,7 +6017,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B60" s="42">
         <v>46347</v>
@@ -6110,10 +6026,10 @@
         <v>46348</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F60" s="40" t="s">
         <v>30</v>
@@ -6124,7 +6040,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B61" s="42">
         <v>46353</v>
@@ -6133,10 +6049,10 @@
         <v>46355</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F61" s="40" t="s">
         <v>30</v>
@@ -6147,7 +6063,7 @@
     </row>
     <row r="62" spans="1:7" ht="24.9" customHeight="1">
       <c r="A62" s="40" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B62" s="42">
         <v>46354</v>
@@ -6156,10 +6072,10 @@
         <v>46354</v>
       </c>
       <c r="D62" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="E62" s="40" t="s">
         <v>90</v>
-      </c>
-      <c r="E62" s="40" t="s">
-        <v>91</v>
       </c>
       <c r="F62" s="40" t="s">
         <v>30</v>
@@ -6170,7 +6086,7 @@
     </row>
     <row r="63" spans="1:7" ht="17.25" customHeight="1">
       <c r="A63" s="41" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B63" s="41"/>
       <c r="C63" s="41"/>
@@ -6181,7 +6097,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B64" s="42">
         <v>46360</v>
@@ -6190,10 +6106,10 @@
         <v>46361</v>
       </c>
       <c r="D64" s="40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F64" s="40" t="s">
         <v>30</v>
@@ -6204,7 +6120,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B65" s="42">
         <v>46368</v>
@@ -6213,10 +6129,10 @@
         <v>46369</v>
       </c>
       <c r="D65" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="E65" s="40" t="s">
         <v>100</v>
-      </c>
-      <c r="E65" s="40" t="s">
-        <v>101</v>
       </c>
       <c r="F65" s="40" t="s">
         <v>30</v>
@@ -6227,7 +6143,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B66" s="42">
         <v>46366</v>
@@ -6236,10 +6152,10 @@
         <v>46370</v>
       </c>
       <c r="D66" s="40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F66" s="40" t="s">
         <v>30</v>
@@ -6250,7 +6166,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B67" s="42">
         <v>46372</v>
@@ -6267,7 +6183,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B68" s="42">
         <v>46381</v>
@@ -6284,7 +6200,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B69" s="42">
         <v>46382</v>
@@ -6301,7 +6217,7 @@
     </row>
     <row r="70" spans="1:7" ht="17.25" customHeight="1">
       <c r="A70" s="41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B70" s="41"/>
       <c r="C70" s="41"/>
@@ -6329,7 +6245,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B72" s="42">
         <v>46395</v>
@@ -6338,10 +6254,10 @@
         <v>46396</v>
       </c>
       <c r="D72" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F72" s="40" t="s">
         <v>30</v>
@@ -6352,7 +6268,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B73" s="42">
         <v>46403</v>
@@ -6361,10 +6277,10 @@
         <v>46404</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F73" s="40" t="s">
         <v>30</v>
@@ -6375,7 +6291,7 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B74" s="42">
         <v>46403</v>
@@ -6384,10 +6300,10 @@
         <v>46404</v>
       </c>
       <c r="D74" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="E74" s="40" t="s">
         <v>100</v>
-      </c>
-      <c r="E74" s="40" t="s">
-        <v>101</v>
       </c>
       <c r="F74" s="40" t="s">
         <v>30</v>
@@ -6398,7 +6314,7 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B75" s="42">
         <v>46403</v>
@@ -6407,10 +6323,10 @@
         <v>46403</v>
       </c>
       <c r="D75" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="E75" s="40" t="s">
         <v>90</v>
-      </c>
-      <c r="E75" s="40" t="s">
-        <v>91</v>
       </c>
       <c r="F75" s="40" t="s">
         <v>30</v>
@@ -6421,7 +6337,7 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B76" s="42">
         <v>46403</v>
@@ -6430,10 +6346,10 @@
         <v>46403</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F76" s="40" t="s">
         <v>30</v>
@@ -6444,7 +6360,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B77" s="42">
         <v>46403</v>
@@ -6453,10 +6369,10 @@
         <v>46403</v>
       </c>
       <c r="D77" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E77" s="40" t="s">
         <v>43</v>
-      </c>
-      <c r="E77" s="40" t="s">
-        <v>44</v>
       </c>
       <c r="F77" s="40" t="s">
         <v>30</v>
@@ -6467,7 +6383,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B78" s="42">
         <v>46396</v>
@@ -6476,10 +6392,10 @@
         <v>46397</v>
       </c>
       <c r="D78" s="40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F78" s="40" t="s">
         <v>30</v>
@@ -6490,7 +6406,7 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B79" s="42">
         <v>46404</v>
@@ -6499,10 +6415,10 @@
         <v>46404</v>
       </c>
       <c r="D79" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="E79" s="40" t="s">
         <v>128</v>
-      </c>
-      <c r="E79" s="40" t="s">
-        <v>129</v>
       </c>
       <c r="F79" s="40" t="s">
         <v>30</v>
@@ -6513,7 +6429,7 @@
     </row>
     <row r="80" spans="1:7" ht="24.9" customHeight="1">
       <c r="A80" s="40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B80" s="42">
         <v>46410</v>
@@ -6522,10 +6438,10 @@
         <v>46410</v>
       </c>
       <c r="D80" s="40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F80" s="40" t="s">
         <v>30</v>
@@ -6536,7 +6452,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="40" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B81" s="42">
         <v>46411</v>
@@ -6545,10 +6461,10 @@
         <v>46411</v>
       </c>
       <c r="D81" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="E81" s="40" t="s">
         <v>133</v>
-      </c>
-      <c r="E81" s="40" t="s">
-        <v>134</v>
       </c>
       <c r="F81" s="40" t="s">
         <v>30</v>
@@ -6559,7 +6475,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B82" s="42">
         <v>46415</v>
@@ -6568,10 +6484,10 @@
         <v>46415</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F82" s="40" t="s">
         <v>30</v>
@@ -6582,7 +6498,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B83" s="42">
         <v>46415</v>
@@ -6591,10 +6507,10 @@
         <v>46417</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F83" s="40" t="s">
         <v>30</v>
@@ -6605,7 +6521,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B84" s="42">
         <v>46416</v>
@@ -6614,10 +6530,10 @@
         <v>46416</v>
       </c>
       <c r="D84" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="E84" s="40" t="s">
         <v>140</v>
-      </c>
-      <c r="E84" s="40" t="s">
-        <v>141</v>
       </c>
       <c r="F84" s="40" t="s">
         <v>30</v>
@@ -6628,7 +6544,7 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B85" s="42">
         <v>46416</v>
@@ -6637,10 +6553,10 @@
         <v>46417</v>
       </c>
       <c r="D85" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="E85" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="E85" s="40" t="s">
-        <v>144</v>
       </c>
       <c r="F85" s="40" t="s">
         <v>30</v>
@@ -6651,7 +6567,7 @@
     </row>
     <row r="86" spans="1:7" ht="17.25" customHeight="1">
       <c r="A86" s="40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B86" s="42">
         <v>46416</v>
@@ -6660,10 +6576,10 @@
         <v>46418</v>
       </c>
       <c r="D86" s="40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F86" s="40" t="s">
         <v>30</v>
@@ -6674,7 +6590,7 @@
     </row>
     <row r="87" spans="1:7" ht="24.9" customHeight="1">
       <c r="A87" s="40" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B87" s="42">
         <v>46417</v>
@@ -6683,10 +6599,10 @@
         <v>46418</v>
       </c>
       <c r="D87" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="E87" s="40" t="s">
         <v>148</v>
-      </c>
-      <c r="E87" s="40" t="s">
-        <v>149</v>
       </c>
       <c r="F87" s="40" t="s">
         <v>30</v>
@@ -6697,7 +6613,7 @@
     </row>
     <row r="88" spans="1:7" ht="16.8">
       <c r="A88" s="41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B88" s="41"/>
       <c r="C88" s="41"/>
@@ -6708,7 +6624,7 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B89" s="42">
         <v>46422</v>
@@ -6717,10 +6633,10 @@
         <v>46422</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F89" s="40" t="s">
         <v>30</v>
@@ -6731,7 +6647,7 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B90" s="42">
         <v>46422</v>
@@ -6740,10 +6656,10 @@
         <v>46423</v>
       </c>
       <c r="D90" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E90" s="40" t="s">
         <v>47</v>
-      </c>
-      <c r="E90" s="40" t="s">
-        <v>48</v>
       </c>
       <c r="F90" s="40" t="s">
         <v>30</v>
@@ -6754,7 +6670,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B91" s="42">
         <v>46424</v>
@@ -6763,10 +6679,10 @@
         <v>46424</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F91" s="40" t="s">
         <v>30</v>
@@ -6777,7 +6693,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="40" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B92" s="42">
         <v>46424</v>
@@ -6786,10 +6702,10 @@
         <v>46425</v>
       </c>
       <c r="D92" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F92" s="40" t="s">
         <v>30</v>
@@ -6800,7 +6716,7 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B93" s="42">
         <v>46431</v>
@@ -6809,10 +6725,10 @@
         <v>46431</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F93" s="40" t="s">
         <v>30</v>
@@ -6823,7 +6739,7 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="40" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B94" s="42">
         <v>46431</v>
@@ -6832,10 +6748,10 @@
         <v>46432</v>
       </c>
       <c r="D94" s="40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F94" s="40" t="s">
         <v>30</v>
@@ -6846,7 +6762,7 @@
     </row>
     <row r="95" spans="1:7" ht="17.25" customHeight="1">
       <c r="A95" s="40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B95" s="42">
         <v>46438</v>
@@ -6855,10 +6771,10 @@
         <v>46438</v>
       </c>
       <c r="D95" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="E95" s="40" t="s">
         <v>90</v>
-      </c>
-      <c r="E95" s="40" t="s">
-        <v>91</v>
       </c>
       <c r="F95" s="40" t="s">
         <v>30</v>
@@ -6869,7 +6785,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B96" s="42">
         <v>46445</v>
@@ -6878,10 +6794,10 @@
         <v>46446</v>
       </c>
       <c r="D96" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="E96" s="40" t="s">
         <v>159</v>
-      </c>
-      <c r="E96" s="40" t="s">
-        <v>160</v>
       </c>
       <c r="F96" s="40" t="s">
         <v>30</v>
@@ -6892,7 +6808,7 @@
     </row>
     <row r="97" spans="1:7" ht="16.8">
       <c r="A97" s="41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B97" s="41"/>
       <c r="C97" s="41"/>
@@ -6903,7 +6819,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B98" s="42">
         <v>46447</v>
@@ -6912,10 +6828,10 @@
         <v>46447</v>
       </c>
       <c r="D98" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E98" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F98" s="40" t="s">
         <v>30</v>
@@ -6926,7 +6842,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B99" s="42">
         <v>46448</v>
@@ -6935,10 +6851,10 @@
         <v>46448</v>
       </c>
       <c r="D99" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E99" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F99" s="40" t="s">
         <v>30</v>
@@ -6949,7 +6865,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B100" s="42">
         <v>46449</v>
@@ -6958,10 +6874,10 @@
         <v>46449</v>
       </c>
       <c r="D100" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E100" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F100" s="40" t="s">
         <v>30</v>
@@ -6972,7 +6888,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B101" s="42">
         <v>46450</v>
@@ -6981,10 +6897,10 @@
         <v>46450</v>
       </c>
       <c r="D101" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E101" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F101" s="40" t="s">
         <v>30</v>
@@ -6995,7 +6911,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B102" s="42">
         <v>46462</v>
@@ -7004,10 +6920,10 @@
         <v>46464</v>
       </c>
       <c r="D102" s="40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E102" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F102" s="40" t="s">
         <v>30</v>
@@ -7018,7 +6934,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B103" s="42">
         <v>46465</v>
@@ -7027,10 +6943,10 @@
         <v>46469</v>
       </c>
       <c r="D103" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E103" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F103" s="40" t="s">
         <v>30</v>
@@ -7109,7 +7025,7 @@
     </row>
     <row r="108" spans="1:7" ht="24.9" customHeight="1">
       <c r="A108" s="40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B108" s="42">
         <v>46477</v>
@@ -7118,10 +7034,10 @@
         <v>46477</v>
       </c>
       <c r="D108" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E108" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F108" s="40" t="s">
         <v>30</v>
@@ -7132,7 +7048,7 @@
     </row>
     <row r="109" spans="1:7" ht="16.8">
       <c r="A109" s="41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B109" s="41"/>
       <c r="C109" s="41"/>
@@ -7143,7 +7059,7 @@
     </row>
     <row r="110" spans="1:7" ht="24.9" customHeight="1">
       <c r="A110" s="40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B110" s="42">
         <v>46478</v>
@@ -7152,10 +7068,10 @@
         <v>46480</v>
       </c>
       <c r="D110" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E110" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F110" s="40" t="s">
         <v>30</v>
@@ -7166,7 +7082,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B111" s="42">
         <v>46482</v>
@@ -7175,10 +7091,10 @@
         <v>46484</v>
       </c>
       <c r="D111" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E111" s="40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F111" s="40" t="s">
         <v>30</v>
@@ -7187,9 +7103,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" s="48" customFormat="1">
+    <row r="112" spans="1:7" s="44" customFormat="1">
       <c r="A112" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B112" s="42">
         <v>46485</v>
@@ -7198,10 +7114,10 @@
         <v>46489</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E112" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F112" s="40" t="s">
         <v>30</v>
@@ -7212,7 +7128,7 @@
     </row>
     <row r="113" spans="1:7" s="24" customFormat="1">
       <c r="A113" s="40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B113" s="42">
         <v>46490</v>
@@ -7221,10 +7137,10 @@
         <v>46494</v>
       </c>
       <c r="D113" s="40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E113" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F113" s="40" t="s">
         <v>30</v>
@@ -7235,7 +7151,7 @@
     </row>
     <row r="114" spans="1:7" ht="13.2" customHeight="1">
       <c r="A114" s="40" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B114" s="42">
         <v>46500</v>
@@ -7244,10 +7160,10 @@
         <v>46504</v>
       </c>
       <c r="D114" s="40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E114" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F114" s="40" t="s">
         <v>30</v>
@@ -7275,7 +7191,7 @@
     </row>
     <row r="116" spans="1:7" ht="17.25" customHeight="1">
       <c r="A116" s="41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B116" s="41"/>
       <c r="C116" s="41"/>
@@ -7303,7 +7219,7 @@
     </row>
     <row r="118" spans="1:7" ht="17.25" customHeight="1">
       <c r="A118" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B118" s="41"/>
       <c r="C118" s="41"/>
@@ -7331,7 +7247,7 @@
     </row>
     <row r="120" spans="1:7" ht="17.25" customHeight="1">
       <c r="A120" s="41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B120" s="41"/>
       <c r="C120" s="41"/>
@@ -7342,7 +7258,7 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B121" s="42">
         <v>46608</v>
@@ -7359,7 +7275,7 @@
     </row>
     <row r="122" spans="1:7" ht="17.25" customHeight="1">
       <c r="A122" s="41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B122" s="41"/>
       <c r="C122" s="41"/>
@@ -7370,7 +7286,7 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B123" s="42">
         <v>46654</v>
@@ -7387,7 +7303,7 @@
     </row>
     <row r="124" spans="1:7" ht="16.8">
       <c r="A124" s="41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B124" s="41"/>
       <c r="C124" s="41"/>
@@ -7398,7 +7314,7 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B125" s="42">
         <v>46737</v>
@@ -7415,7 +7331,7 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B126" s="42">
         <v>46746</v>
@@ -7432,7 +7348,7 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B127" s="42">
         <v>46747</v>
@@ -7449,7 +7365,7 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B128" s="42">
         <v>46748</v>
@@ -7469,25 +7385,25 @@
     <mergeCell ref="B1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A10:G128">
-    <cfRule type="expression" dxfId="20" priority="8">
+    <cfRule type="expression" dxfId="6" priority="8">
       <formula>$G10="National gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="9">
+    <cfRule type="expression" dxfId="5" priority="9">
       <formula>$G10="Provincial gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="10">
+    <cfRule type="expression" dxfId="4" priority="10">
       <formula>$G10="District gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="11">
+    <cfRule type="expression" dxfId="3" priority="11">
       <formula>$G10="Schools gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="12">
+    <cfRule type="expression" dxfId="2" priority="12">
       <formula>$G10="Club gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="1" priority="13">
       <formula>$G10="Open Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>$G10="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -640,7 +640,7 @@
     <t>EDA Gala 1&amp; 2 SC</t>
   </si>
   <si>
-    <t>Prestige Championships</t>
+    <t>Prestige SC Championships</t>
   </si>
 </sst>
 </file>
@@ -1067,11 +1067,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1153,7 +1153,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1198,7 +1198,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1544,7 +1544,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>
@@ -1562,7 +1562,7 @@
       <c r="G2" s="46"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="47" t="s">
         <v>180</v>
       </c>
       <c r="B5" s="46"/>
@@ -1836,7 +1836,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="47" t="s">
         <v>188</v>
       </c>
       <c r="B18" s="46"/>
@@ -2115,7 +2115,7 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="47" t="s">
         <v>189</v>
       </c>
       <c r="B31" s="46"/>
@@ -2412,7 +2412,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="45" t="s">
+      <c r="A46" s="47" t="s">
         <v>190</v>
       </c>
       <c r="B46" s="46"/>
@@ -2686,7 +2686,7 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="45" t="s">
+      <c r="A59" s="47" t="s">
         <v>191</v>
       </c>
       <c r="B59" s="46"/>
@@ -2965,7 +2965,7 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="45" t="s">
+      <c r="A72" s="47" t="s">
         <v>192</v>
       </c>
       <c r="B72" s="46"/>
@@ -3257,7 +3257,7 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="45" t="s">
+      <c r="A87" s="47" t="s">
         <v>193</v>
       </c>
       <c r="B87" s="46"/>
@@ -3536,7 +3536,7 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="45" t="s">
+      <c r="A100" s="47" t="s">
         <v>194</v>
       </c>
       <c r="B100" s="46"/>
@@ -3815,7 +3815,7 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="45" t="s">
+      <c r="A113" s="47" t="s">
         <v>195</v>
       </c>
       <c r="B113" s="46"/>
@@ -4061,7 +4061,7 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="45" t="s">
+      <c r="A124" s="47" t="s">
         <v>196</v>
       </c>
       <c r="B124" s="46"/>
@@ -4340,7 +4340,7 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="45" t="s">
+      <c r="A137" s="47" t="s">
         <v>197</v>
       </c>
       <c r="B137" s="46"/>
@@ -4614,7 +4614,7 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="45" t="s">
+      <c r="A150" s="47" t="s">
         <v>198</v>
       </c>
       <c r="B150" s="46"/>
@@ -4912,6 +4912,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -4920,12 +4926,6 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -4946,7 +4946,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="204">
   <si>
     <t>KZNA Calendar Season 2026–2027</t>
   </si>
@@ -1067,11 +1067,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1153,7 +1153,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1198,7 +1198,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1233,8 +1233,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G128">
-  <autoFilter ref="A9:G128"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G127">
+  <autoFilter ref="A9:G127"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Event Name"/>
     <tableColumn id="2" name="Start Date"/>
@@ -1544,7 +1544,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="47" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>
@@ -1562,7 +1562,7 @@
       <c r="G2" s="46"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="45" t="s">
         <v>180</v>
       </c>
       <c r="B5" s="46"/>
@@ -1836,7 +1836,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="45" t="s">
         <v>188</v>
       </c>
       <c r="B18" s="46"/>
@@ -2115,7 +2115,7 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="47" t="s">
+      <c r="A31" s="45" t="s">
         <v>189</v>
       </c>
       <c r="B31" s="46"/>
@@ -2412,7 +2412,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="47" t="s">
+      <c r="A46" s="45" t="s">
         <v>190</v>
       </c>
       <c r="B46" s="46"/>
@@ -2686,7 +2686,7 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="47" t="s">
+      <c r="A59" s="45" t="s">
         <v>191</v>
       </c>
       <c r="B59" s="46"/>
@@ -2965,7 +2965,7 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="47" t="s">
+      <c r="A72" s="45" t="s">
         <v>192</v>
       </c>
       <c r="B72" s="46"/>
@@ -3257,7 +3257,7 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="47" t="s">
+      <c r="A87" s="45" t="s">
         <v>193</v>
       </c>
       <c r="B87" s="46"/>
@@ -3536,7 +3536,7 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="47" t="s">
+      <c r="A100" s="45" t="s">
         <v>194</v>
       </c>
       <c r="B100" s="46"/>
@@ -3815,7 +3815,7 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="47" t="s">
+      <c r="A113" s="45" t="s">
         <v>195</v>
       </c>
       <c r="B113" s="46"/>
@@ -4061,7 +4061,7 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="47" t="s">
+      <c r="A124" s="45" t="s">
         <v>196</v>
       </c>
       <c r="B124" s="46"/>
@@ -4340,7 +4340,7 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="47" t="s">
+      <c r="A137" s="45" t="s">
         <v>197</v>
       </c>
       <c r="B137" s="46"/>
@@ -4614,7 +4614,7 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="47" t="s">
+      <c r="A150" s="45" t="s">
         <v>198</v>
       </c>
       <c r="B150" s="46"/>
@@ -4912,12 +4912,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -4926,6 +4920,12 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -4934,7 +4934,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -4946,7 +4946,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="47" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>
@@ -6932,38 +6932,32 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" ht="13.2" customHeight="1">
       <c r="A103" s="40" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c r="B103" s="42">
-        <v>46465</v>
+        <v>46467</v>
       </c>
       <c r="C103" s="42">
-        <v>46469</v>
-      </c>
-      <c r="D103" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="E103" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F103" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46467</v>
+      </c>
+      <c r="D103" s="40"/>
+      <c r="E103" s="40"/>
+      <c r="F103" s="40"/>
       <c r="G103" s="40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="24.9" customHeight="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104" s="40" t="s">
         <v>19</v>
       </c>
       <c r="B104" s="42">
-        <v>46467</v>
+        <v>46468</v>
       </c>
       <c r="C104" s="42">
-        <v>46467</v>
+        <v>46468</v>
       </c>
       <c r="D104" s="40"/>
       <c r="E104" s="40"/>
@@ -6972,15 +6966,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" ht="24.9" customHeight="1">
       <c r="A105" s="40" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B105" s="42">
-        <v>46468</v>
+        <v>46472</v>
       </c>
       <c r="C105" s="42">
-        <v>46468</v>
+        <v>46472</v>
       </c>
       <c r="D105" s="40"/>
       <c r="E105" s="40"/>
@@ -6989,15 +6983,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="24.9" customHeight="1">
+    <row r="106" spans="1:7" ht="17.25" customHeight="1">
       <c r="A106" s="40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B106" s="42">
-        <v>46472</v>
+        <v>46475</v>
       </c>
       <c r="C106" s="42">
-        <v>46472</v>
+        <v>46475</v>
       </c>
       <c r="D106" s="40"/>
       <c r="E106" s="40"/>
@@ -7006,72 +7000,78 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="17.25" customHeight="1">
+    <row r="107" spans="1:7" ht="24.9" customHeight="1">
       <c r="A107" s="40" t="s">
-        <v>22</v>
+        <v>169</v>
       </c>
       <c r="B107" s="42">
-        <v>46475</v>
+        <v>46477</v>
       </c>
       <c r="C107" s="42">
-        <v>46475</v>
-      </c>
-      <c r="D107" s="40"/>
-      <c r="E107" s="40"/>
-      <c r="F107" s="40"/>
+        <v>46477</v>
+      </c>
+      <c r="D107" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E107" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="F107" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G107" s="40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A108" s="40" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="16.8">
+      <c r="A108" s="41" t="s">
+        <v>171</v>
+      </c>
+      <c r="B108" s="41"/>
+      <c r="C108" s="41"/>
+      <c r="D108" s="41"/>
+      <c r="E108" s="41"/>
+      <c r="F108" s="41"/>
+      <c r="G108" s="41"/>
+    </row>
+    <row r="109" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A109" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="B108" s="42">
-        <v>46477</v>
-      </c>
-      <c r="C108" s="42">
-        <v>46477</v>
-      </c>
-      <c r="D108" s="40" t="s">
+      <c r="B109" s="42">
+        <v>46478</v>
+      </c>
+      <c r="C109" s="42">
+        <v>46480</v>
+      </c>
+      <c r="D109" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="E108" s="40" t="s">
+      <c r="E109" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="F108" s="40" t="s">
+      <c r="F109" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G108" s="40" t="s">
+      <c r="G109" s="40" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="16.8">
-      <c r="A109" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="B109" s="41"/>
-      <c r="C109" s="41"/>
-      <c r="D109" s="41"/>
-      <c r="E109" s="41"/>
-      <c r="F109" s="41"/>
-      <c r="G109" s="41"/>
-    </row>
-    <row r="110" spans="1:7" ht="24.9" customHeight="1">
+    <row r="110" spans="1:7">
       <c r="A110" s="40" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B110" s="42">
-        <v>46478</v>
+        <v>46482</v>
       </c>
       <c r="C110" s="42">
-        <v>46480</v>
+        <v>46484</v>
       </c>
       <c r="D110" s="40" t="s">
         <v>47</v>
       </c>
       <c r="E110" s="40" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F110" s="40" t="s">
         <v>30</v>
@@ -7080,21 +7080,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" s="44" customFormat="1">
       <c r="A111" s="40" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B111" s="42">
-        <v>46482</v>
+        <v>46485</v>
       </c>
       <c r="C111" s="42">
-        <v>46484</v>
+        <v>46489</v>
       </c>
       <c r="D111" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="E111" s="40" t="s">
         <v>47</v>
-      </c>
-      <c r="E111" s="40" t="s">
-        <v>173</v>
       </c>
       <c r="F111" s="40" t="s">
         <v>30</v>
@@ -7103,18 +7103,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" s="44" customFormat="1">
+    <row r="112" spans="1:7" s="24" customFormat="1">
       <c r="A112" s="40" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B112" s="42">
-        <v>46485</v>
+        <v>46490</v>
       </c>
       <c r="C112" s="42">
-        <v>46489</v>
+        <v>46494</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>68</v>
+        <v>167</v>
       </c>
       <c r="E112" s="40" t="s">
         <v>47</v>
@@ -7126,18 +7126,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" s="24" customFormat="1">
+    <row r="113" spans="1:7" ht="13.2" customHeight="1">
       <c r="A113" s="40" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="B113" s="42">
-        <v>46490</v>
+        <v>46500</v>
       </c>
       <c r="C113" s="42">
-        <v>46494</v>
+        <v>46504</v>
       </c>
       <c r="D113" s="40" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="E113" s="40" t="s">
         <v>47</v>
@@ -7146,181 +7146,175 @@
         <v>30</v>
       </c>
       <c r="G113" s="40" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="13.2" customHeight="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" s="40" t="s">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="B114" s="42">
-        <v>46500</v>
+        <v>46504</v>
       </c>
       <c r="C114" s="42">
         <v>46504</v>
       </c>
-      <c r="D114" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="E114" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F114" s="40" t="s">
-        <v>30</v>
-      </c>
+      <c r="D114" s="40"/>
+      <c r="E114" s="40"/>
+      <c r="F114" s="40"/>
       <c r="G114" s="40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
-      <c r="A115" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B115" s="42">
-        <v>46504</v>
-      </c>
-      <c r="C115" s="42">
-        <v>46504</v>
-      </c>
-      <c r="D115" s="40"/>
-      <c r="E115" s="40"/>
-      <c r="F115" s="40"/>
-      <c r="G115" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A116" s="41" t="s">
+    <row r="115" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A115" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="B116" s="41"/>
-      <c r="C116" s="41"/>
-      <c r="D116" s="41"/>
-      <c r="E116" s="41"/>
-      <c r="F116" s="41"/>
-      <c r="G116" s="41"/>
-    </row>
-    <row r="117" spans="1:7">
-      <c r="A117" s="40" t="s">
+      <c r="B115" s="41"/>
+      <c r="C115" s="41"/>
+      <c r="D115" s="41"/>
+      <c r="E115" s="41"/>
+      <c r="F115" s="41"/>
+      <c r="G115" s="41"/>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="B117" s="42">
+      <c r="B116" s="42">
         <v>46508</v>
       </c>
-      <c r="C117" s="42">
+      <c r="C116" s="42">
         <v>46508</v>
       </c>
-      <c r="D117" s="40"/>
-      <c r="E117" s="40"/>
-      <c r="F117" s="40"/>
-      <c r="G117" s="40" t="s">
+      <c r="D116" s="40"/>
+      <c r="E116" s="40"/>
+      <c r="F116" s="40"/>
+      <c r="G116" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A118" s="41" t="s">
+    <row r="117" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A117" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="B118" s="41"/>
-      <c r="C118" s="41"/>
-      <c r="D118" s="41"/>
-      <c r="E118" s="41"/>
-      <c r="F118" s="41"/>
-      <c r="G118" s="41"/>
-    </row>
-    <row r="119" spans="1:7">
-      <c r="A119" s="40" t="s">
+      <c r="B117" s="41"/>
+      <c r="C117" s="41"/>
+      <c r="D117" s="41"/>
+      <c r="E117" s="41"/>
+      <c r="F117" s="41"/>
+      <c r="G117" s="41"/>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B119" s="42">
+      <c r="B118" s="42">
         <v>46554</v>
       </c>
-      <c r="C119" s="42">
+      <c r="C118" s="42">
         <v>46554</v>
       </c>
-      <c r="D119" s="40"/>
-      <c r="E119" s="40"/>
-      <c r="F119" s="40"/>
-      <c r="G119" s="40" t="s">
+      <c r="D118" s="40"/>
+      <c r="E118" s="40"/>
+      <c r="F118" s="40"/>
+      <c r="G118" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A120" s="41" t="s">
+    <row r="119" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A119" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="B120" s="41"/>
-      <c r="C120" s="41"/>
-      <c r="D120" s="41"/>
-      <c r="E120" s="41"/>
-      <c r="F120" s="41"/>
-      <c r="G120" s="41"/>
-    </row>
-    <row r="121" spans="1:7">
-      <c r="A121" s="40" t="s">
+      <c r="B119" s="41"/>
+      <c r="C119" s="41"/>
+      <c r="D119" s="41"/>
+      <c r="E119" s="41"/>
+      <c r="F119" s="41"/>
+      <c r="G119" s="41"/>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B121" s="42">
+      <c r="B120" s="42">
         <v>46608</v>
       </c>
-      <c r="C121" s="42">
+      <c r="C120" s="42">
         <v>46608</v>
       </c>
-      <c r="D121" s="40"/>
-      <c r="E121" s="40"/>
-      <c r="F121" s="40"/>
-      <c r="G121" s="40" t="s">
+      <c r="D120" s="40"/>
+      <c r="E120" s="40"/>
+      <c r="F120" s="40"/>
+      <c r="G120" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A122" s="41" t="s">
+    <row r="121" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A121" s="41" t="s">
         <v>178</v>
       </c>
-      <c r="B122" s="41"/>
-      <c r="C122" s="41"/>
-      <c r="D122" s="41"/>
-      <c r="E122" s="41"/>
-      <c r="F122" s="41"/>
-      <c r="G122" s="41"/>
-    </row>
-    <row r="123" spans="1:7">
-      <c r="A123" s="40" t="s">
+      <c r="B121" s="41"/>
+      <c r="C121" s="41"/>
+      <c r="D121" s="41"/>
+      <c r="E121" s="41"/>
+      <c r="F121" s="41"/>
+      <c r="G121" s="41"/>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="B123" s="42">
+      <c r="B122" s="42">
         <v>46654</v>
       </c>
-      <c r="C123" s="42">
+      <c r="C122" s="42">
         <v>46654</v>
       </c>
-      <c r="D123" s="40"/>
-      <c r="E123" s="40"/>
-      <c r="F123" s="40"/>
-      <c r="G123" s="40" t="s">
+      <c r="D122" s="40"/>
+      <c r="E122" s="40"/>
+      <c r="F122" s="40"/>
+      <c r="G122" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="16.8">
-      <c r="A124" s="41" t="s">
+    <row r="123" spans="1:7" ht="16.8">
+      <c r="A123" s="41" t="s">
         <v>179</v>
       </c>
-      <c r="B124" s="41"/>
-      <c r="C124" s="41"/>
-      <c r="D124" s="41"/>
-      <c r="E124" s="41"/>
-      <c r="F124" s="41"/>
-      <c r="G124" s="41"/>
+      <c r="B123" s="41"/>
+      <c r="C123" s="41"/>
+      <c r="D123" s="41"/>
+      <c r="E123" s="41"/>
+      <c r="F123" s="41"/>
+      <c r="G123" s="41"/>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="B124" s="42">
+        <v>46737</v>
+      </c>
+      <c r="C124" s="42">
+        <v>46737</v>
+      </c>
+      <c r="D124" s="40"/>
+      <c r="E124" s="40"/>
+      <c r="F124" s="40"/>
+      <c r="G124" s="40" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="40" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B125" s="42">
-        <v>46737</v>
+        <v>46746</v>
       </c>
       <c r="C125" s="42">
-        <v>46737</v>
+        <v>46746</v>
       </c>
       <c r="D125" s="40"/>
       <c r="E125" s="40"/>
@@ -7331,13 +7325,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="40" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B126" s="42">
-        <v>46746</v>
+        <v>46747</v>
       </c>
       <c r="C126" s="42">
-        <v>46746</v>
+        <v>46747</v>
       </c>
       <c r="D126" s="40"/>
       <c r="E126" s="40"/>
@@ -7351,10 +7345,10 @@
         <v>115</v>
       </c>
       <c r="B127" s="42">
-        <v>46747</v>
+        <v>46748</v>
       </c>
       <c r="C127" s="42">
-        <v>46747</v>
+        <v>46748</v>
       </c>
       <c r="D127" s="40"/>
       <c r="E127" s="40"/>
@@ -7363,28 +7357,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
-      <c r="A128" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="B128" s="42">
-        <v>46748</v>
-      </c>
-      <c r="C128" s="42">
-        <v>46748</v>
-      </c>
-      <c r="D128" s="40"/>
-      <c r="E128" s="40"/>
-      <c r="F128" s="40"/>
-      <c r="G128" s="40" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A10:G128">
+  <conditionalFormatting sqref="A10:G127">
     <cfRule type="expression" dxfId="6" priority="8">
       <formula>$G10="National gala"</formula>
     </cfRule>
@@ -7408,7 +7385,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G204">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G203">
       <formula1>"Club gala,District gala,Provincial gala,National gala,Open Water,Schools gala,Public Holiday"</formula1>
     </dataValidation>
   </dataValidations>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -1067,11 +1067,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1153,7 +1153,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1198,7 +1198,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1544,7 +1544,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>
@@ -1562,7 +1562,7 @@
       <c r="G2" s="46"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="47" t="s">
         <v>180</v>
       </c>
       <c r="B5" s="46"/>
@@ -1836,7 +1836,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="47" t="s">
         <v>188</v>
       </c>
       <c r="B18" s="46"/>
@@ -2115,7 +2115,7 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="47" t="s">
         <v>189</v>
       </c>
       <c r="B31" s="46"/>
@@ -2412,7 +2412,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="45" t="s">
+      <c r="A46" s="47" t="s">
         <v>190</v>
       </c>
       <c r="B46" s="46"/>
@@ -2686,7 +2686,7 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="45" t="s">
+      <c r="A59" s="47" t="s">
         <v>191</v>
       </c>
       <c r="B59" s="46"/>
@@ -2965,7 +2965,7 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="45" t="s">
+      <c r="A72" s="47" t="s">
         <v>192</v>
       </c>
       <c r="B72" s="46"/>
@@ -3257,7 +3257,7 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="45" t="s">
+      <c r="A87" s="47" t="s">
         <v>193</v>
       </c>
       <c r="B87" s="46"/>
@@ -3536,7 +3536,7 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="45" t="s">
+      <c r="A100" s="47" t="s">
         <v>194</v>
       </c>
       <c r="B100" s="46"/>
@@ -3815,7 +3815,7 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="45" t="s">
+      <c r="A113" s="47" t="s">
         <v>195</v>
       </c>
       <c r="B113" s="46"/>
@@ -4061,7 +4061,7 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="45" t="s">
+      <c r="A124" s="47" t="s">
         <v>196</v>
       </c>
       <c r="B124" s="46"/>
@@ -4340,7 +4340,7 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="45" t="s">
+      <c r="A137" s="47" t="s">
         <v>197</v>
       </c>
       <c r="B137" s="46"/>
@@ -4614,7 +4614,7 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="45" t="s">
+      <c r="A150" s="47" t="s">
         <v>198</v>
       </c>
       <c r="B150" s="46"/>
@@ -4912,6 +4912,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -4920,12 +4926,6 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -4946,7 +4946,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="201">
   <si>
     <t>KZNA Calendar Season 2026–2027</t>
   </si>
@@ -266,15 +266,6 @@
   </si>
   <si>
     <t>OCTOBER 2026</t>
-  </si>
-  <si>
-    <t>Curro Elite</t>
-  </si>
-  <si>
-    <t>Curro</t>
-  </si>
-  <si>
-    <t>Aquazone</t>
   </si>
   <si>
     <t>KCD Age Group 1</t>
@@ -1067,11 +1058,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1153,7 +1144,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1198,7 +1189,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1544,7 +1535,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="47" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>
@@ -1562,8 +1553,8 @@
       <c r="G2" s="46"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="47" t="s">
-        <v>180</v>
+      <c r="A5" s="45" t="s">
+        <v>177</v>
       </c>
       <c r="B5" s="46"/>
       <c r="C5" s="46"/>
@@ -1574,25 +1565,25 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -1836,8 +1827,8 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="47" t="s">
-        <v>188</v>
+      <c r="A18" s="45" t="s">
+        <v>185</v>
       </c>
       <c r="B18" s="46"/>
       <c r="C18" s="46"/>
@@ -1848,25 +1839,25 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2115,8 +2106,8 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="47" t="s">
-        <v>189</v>
+      <c r="A31" s="45" t="s">
+        <v>186</v>
       </c>
       <c r="B31" s="46"/>
       <c r="C31" s="46"/>
@@ -2127,25 +2118,25 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2412,8 +2403,8 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="47" t="s">
-        <v>190</v>
+      <c r="A46" s="45" t="s">
+        <v>187</v>
       </c>
       <c r="B46" s="46"/>
       <c r="C46" s="46"/>
@@ -2424,25 +2415,25 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2686,8 +2677,8 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="47" t="s">
-        <v>191</v>
+      <c r="A59" s="45" t="s">
+        <v>188</v>
       </c>
       <c r="B59" s="46"/>
       <c r="C59" s="46"/>
@@ -2698,25 +2689,25 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2965,8 +2956,8 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="47" t="s">
-        <v>192</v>
+      <c r="A72" s="45" t="s">
+        <v>189</v>
       </c>
       <c r="B72" s="46"/>
       <c r="C72" s="46"/>
@@ -2977,25 +2968,25 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="G73" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3257,8 +3248,8 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="47" t="s">
-        <v>193</v>
+      <c r="A87" s="45" t="s">
+        <v>190</v>
       </c>
       <c r="B87" s="46"/>
       <c r="C87" s="46"/>
@@ -3269,25 +3260,25 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3536,8 +3527,8 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="47" t="s">
-        <v>194</v>
+      <c r="A100" s="45" t="s">
+        <v>191</v>
       </c>
       <c r="B100" s="46"/>
       <c r="C100" s="46"/>
@@ -3548,25 +3539,25 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="G101" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3815,8 +3806,8 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="47" t="s">
-        <v>195</v>
+      <c r="A113" s="45" t="s">
+        <v>192</v>
       </c>
       <c r="B113" s="46"/>
       <c r="C113" s="46"/>
@@ -3827,25 +3818,25 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D114" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="F114" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="G114" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4061,8 +4052,8 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="47" t="s">
-        <v>196</v>
+      <c r="A124" s="45" t="s">
+        <v>193</v>
       </c>
       <c r="B124" s="46"/>
       <c r="C124" s="46"/>
@@ -4073,25 +4064,25 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D125" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="E125" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="G125" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4340,8 +4331,8 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="47" t="s">
-        <v>197</v>
+      <c r="A137" s="45" t="s">
+        <v>194</v>
       </c>
       <c r="B137" s="46"/>
       <c r="C137" s="46"/>
@@ -4352,25 +4343,25 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D138" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="E138" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="F138" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="G138" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4614,8 +4605,8 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="47" t="s">
-        <v>198</v>
+      <c r="A150" s="45" t="s">
+        <v>195</v>
       </c>
       <c r="B150" s="46"/>
       <c r="C150" s="46"/>
@@ -4626,25 +4617,25 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D151" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="E151" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="F151" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="G151" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4912,12 +4903,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -4926,6 +4911,12 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -4946,7 +4937,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="47" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>
@@ -5324,7 +5315,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="40" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B27" s="42">
         <v>46210</v>
@@ -5336,7 +5327,7 @@
         <v>28</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F27" s="40" t="s">
         <v>30</v>
@@ -5370,7 +5361,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="40" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B29" s="42">
         <v>46228</v>
@@ -5775,31 +5766,17 @@
       <c r="G48" s="41"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="B49" s="42">
-        <v>46297</v>
-      </c>
-      <c r="C49" s="42">
-        <v>46299</v>
-      </c>
-      <c r="D49" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="E49" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="F49" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G49" s="40" t="s">
-        <v>5</v>
-      </c>
+      <c r="A49" s="40"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="40" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B50" s="42">
         <v>46298</v>
@@ -5808,7 +5785,7 @@
         <v>46298</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E50" s="40" t="s">
         <v>75</v>
@@ -5822,7 +5799,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="40" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B51" s="42">
         <v>46298</v>
@@ -5834,7 +5811,7 @@
         <v>55</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F51" s="40" t="s">
         <v>30</v>
@@ -5845,7 +5822,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="40" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B52" s="42">
         <v>46312</v>
@@ -5857,7 +5834,7 @@
         <v>42</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F52" s="40" t="s">
         <v>30</v>
@@ -5868,7 +5845,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="40" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B53" s="42">
         <v>46312</v>
@@ -5877,10 +5854,10 @@
         <v>46312</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F53" s="40" t="s">
         <v>30</v>
@@ -5891,7 +5868,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="40" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B54" s="42">
         <v>46318</v>
@@ -5900,10 +5877,10 @@
         <v>46320</v>
       </c>
       <c r="D54" s="40" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F54" s="40" t="s">
         <v>30</v>
@@ -5914,7 +5891,7 @@
     </row>
     <row r="55" spans="1:7" ht="24.9" customHeight="1">
       <c r="A55" s="40" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B55" s="42">
         <v>46326</v>
@@ -5923,7 +5900,7 @@
         <v>46326</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E55" s="40" t="s">
         <v>75</v>
@@ -5937,7 +5914,7 @@
     </row>
     <row r="56" spans="1:7" ht="17.25" customHeight="1">
       <c r="A56" s="41" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B56" s="41"/>
       <c r="C56" s="41"/>
@@ -5948,7 +5925,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="40" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B57" s="42">
         <v>46333</v>
@@ -5957,7 +5934,7 @@
         <v>46333</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E57" s="40" t="s">
         <v>47</v>
@@ -5971,7 +5948,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="40" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B58" s="42">
         <v>46340</v>
@@ -5980,10 +5957,10 @@
         <v>46341</v>
       </c>
       <c r="D58" s="40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F58" s="40" t="s">
         <v>30</v>
@@ -5994,7 +5971,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="40" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B59" s="42">
         <v>46347</v>
@@ -6003,10 +5980,10 @@
         <v>46347</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F59" s="40" t="s">
         <v>30</v>
@@ -6017,7 +5994,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="40" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B60" s="42">
         <v>46347</v>
@@ -6029,7 +6006,7 @@
         <v>53</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F60" s="40" t="s">
         <v>30</v>
@@ -6040,7 +6017,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="40" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B61" s="42">
         <v>46353</v>
@@ -6049,10 +6026,10 @@
         <v>46355</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F61" s="40" t="s">
         <v>30</v>
@@ -6063,7 +6040,7 @@
     </row>
     <row r="62" spans="1:7" ht="24.9" customHeight="1">
       <c r="A62" s="40" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B62" s="42">
         <v>46354</v>
@@ -6072,10 +6049,10 @@
         <v>46354</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F62" s="40" t="s">
         <v>30</v>
@@ -6086,7 +6063,7 @@
     </row>
     <row r="63" spans="1:7" ht="17.25" customHeight="1">
       <c r="A63" s="41" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B63" s="41"/>
       <c r="C63" s="41"/>
@@ -6097,7 +6074,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="40" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B64" s="42">
         <v>46360</v>
@@ -6106,7 +6083,7 @@
         <v>46361</v>
       </c>
       <c r="D64" s="40" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E64" s="40" t="s">
         <v>75</v>
@@ -6120,7 +6097,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="40" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B65" s="42">
         <v>46368</v>
@@ -6129,10 +6106,10 @@
         <v>46369</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F65" s="40" t="s">
         <v>30</v>
@@ -6143,7 +6120,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="40" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B66" s="42">
         <v>46366</v>
@@ -6152,10 +6129,10 @@
         <v>46370</v>
       </c>
       <c r="D66" s="40" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F66" s="40" t="s">
         <v>30</v>
@@ -6166,7 +6143,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="40" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B67" s="42">
         <v>46372</v>
@@ -6183,7 +6160,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="40" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B68" s="42">
         <v>46381</v>
@@ -6200,7 +6177,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="40" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B69" s="42">
         <v>46382</v>
@@ -6217,7 +6194,7 @@
     </row>
     <row r="70" spans="1:7" ht="17.25" customHeight="1">
       <c r="A70" s="41" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B70" s="41"/>
       <c r="C70" s="41"/>
@@ -6245,7 +6222,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="40" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B72" s="42">
         <v>46395</v>
@@ -6257,7 +6234,7 @@
         <v>68</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F72" s="40" t="s">
         <v>30</v>
@@ -6268,7 +6245,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="40" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B73" s="42">
         <v>46403</v>
@@ -6277,10 +6254,10 @@
         <v>46404</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F73" s="40" t="s">
         <v>30</v>
@@ -6291,7 +6268,7 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="40" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B74" s="42">
         <v>46403</v>
@@ -6300,10 +6277,10 @@
         <v>46404</v>
       </c>
       <c r="D74" s="40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F74" s="40" t="s">
         <v>30</v>
@@ -6314,7 +6291,7 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="40" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B75" s="42">
         <v>46403</v>
@@ -6323,10 +6300,10 @@
         <v>46403</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F75" s="40" t="s">
         <v>30</v>
@@ -6337,7 +6314,7 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="40" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B76" s="42">
         <v>46403</v>
@@ -6349,7 +6326,7 @@
         <v>74</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F76" s="40" t="s">
         <v>30</v>
@@ -6360,7 +6337,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="40" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B77" s="42">
         <v>46403</v>
@@ -6383,7 +6360,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="40" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B78" s="42">
         <v>46396</v>
@@ -6395,7 +6372,7 @@
         <v>44</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F78" s="40" t="s">
         <v>30</v>
@@ -6406,7 +6383,7 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="40" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B79" s="42">
         <v>46404</v>
@@ -6415,10 +6392,10 @@
         <v>46404</v>
       </c>
       <c r="D79" s="40" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F79" s="40" t="s">
         <v>30</v>
@@ -6429,7 +6406,7 @@
     </row>
     <row r="80" spans="1:7" ht="24.9" customHeight="1">
       <c r="A80" s="40" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B80" s="42">
         <v>46410</v>
@@ -6441,7 +6418,7 @@
         <v>61</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F80" s="40" t="s">
         <v>30</v>
@@ -6452,7 +6429,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="40" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B81" s="42">
         <v>46411</v>
@@ -6461,10 +6438,10 @@
         <v>46411</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F81" s="40" t="s">
         <v>30</v>
@@ -6475,7 +6452,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="40" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B82" s="42">
         <v>46415</v>
@@ -6484,7 +6461,7 @@
         <v>46415</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E82" s="40" t="s">
         <v>75</v>
@@ -6498,7 +6475,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="40" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B83" s="42">
         <v>46415</v>
@@ -6507,10 +6484,10 @@
         <v>46417</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F83" s="40" t="s">
         <v>30</v>
@@ -6521,7 +6498,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="40" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B84" s="42">
         <v>46416</v>
@@ -6530,10 +6507,10 @@
         <v>46416</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F84" s="40" t="s">
         <v>30</v>
@@ -6544,7 +6521,7 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B85" s="42">
         <v>46416</v>
@@ -6553,10 +6530,10 @@
         <v>46417</v>
       </c>
       <c r="D85" s="40" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F85" s="40" t="s">
         <v>30</v>
@@ -6567,7 +6544,7 @@
     </row>
     <row r="86" spans="1:7" ht="17.25" customHeight="1">
       <c r="A86" s="40" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B86" s="42">
         <v>46416</v>
@@ -6576,7 +6553,7 @@
         <v>46418</v>
       </c>
       <c r="D86" s="40" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E86" s="40" t="s">
         <v>75</v>
@@ -6590,7 +6567,7 @@
     </row>
     <row r="87" spans="1:7" ht="24.9" customHeight="1">
       <c r="A87" s="40" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B87" s="42">
         <v>46417</v>
@@ -6599,10 +6576,10 @@
         <v>46418</v>
       </c>
       <c r="D87" s="40" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F87" s="40" t="s">
         <v>30</v>
@@ -6613,7 +6590,7 @@
     </row>
     <row r="88" spans="1:7" ht="16.8">
       <c r="A88" s="41" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B88" s="41"/>
       <c r="C88" s="41"/>
@@ -6624,7 +6601,7 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="40" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B89" s="42">
         <v>46422</v>
@@ -6633,10 +6610,10 @@
         <v>46422</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F89" s="40" t="s">
         <v>30</v>
@@ -6670,7 +6647,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="40" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B91" s="42">
         <v>46424</v>
@@ -6679,7 +6656,7 @@
         <v>46424</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E91" s="40" t="s">
         <v>75</v>
@@ -6693,7 +6670,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="40" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B92" s="42">
         <v>46424</v>
@@ -6705,7 +6682,7 @@
         <v>55</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F92" s="40" t="s">
         <v>30</v>
@@ -6716,7 +6693,7 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="40" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B93" s="42">
         <v>46431</v>
@@ -6725,7 +6702,7 @@
         <v>46431</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E93" s="40" t="s">
         <v>47</v>
@@ -6739,7 +6716,7 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="40" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B94" s="42">
         <v>46431</v>
@@ -6748,10 +6725,10 @@
         <v>46432</v>
       </c>
       <c r="D94" s="40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F94" s="40" t="s">
         <v>30</v>
@@ -6762,7 +6739,7 @@
     </row>
     <row r="95" spans="1:7" ht="17.25" customHeight="1">
       <c r="A95" s="40" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B95" s="42">
         <v>46438</v>
@@ -6771,10 +6748,10 @@
         <v>46438</v>
       </c>
       <c r="D95" s="40" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F95" s="40" t="s">
         <v>30</v>
@@ -6785,7 +6762,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B96" s="42">
         <v>46445</v>
@@ -6794,10 +6771,10 @@
         <v>46446</v>
       </c>
       <c r="D96" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E96" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F96" s="40" t="s">
         <v>30</v>
@@ -6808,7 +6785,7 @@
     </row>
     <row r="97" spans="1:7" ht="16.8">
       <c r="A97" s="41" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B97" s="41"/>
       <c r="C97" s="41"/>
@@ -6819,7 +6796,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="40" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B98" s="42">
         <v>46447</v>
@@ -6828,7 +6805,7 @@
         <v>46447</v>
       </c>
       <c r="D98" s="40" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E98" s="40" t="s">
         <v>47</v>
@@ -6842,7 +6819,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="40" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B99" s="42">
         <v>46448</v>
@@ -6851,7 +6828,7 @@
         <v>46448</v>
       </c>
       <c r="D99" s="40" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E99" s="40" t="s">
         <v>47</v>
@@ -6865,7 +6842,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="40" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B100" s="42">
         <v>46449</v>
@@ -6874,7 +6851,7 @@
         <v>46449</v>
       </c>
       <c r="D100" s="40" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E100" s="40" t="s">
         <v>47</v>
@@ -6888,7 +6865,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="40" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B101" s="42">
         <v>46450</v>
@@ -6897,7 +6874,7 @@
         <v>46450</v>
       </c>
       <c r="D101" s="40" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E101" s="40" t="s">
         <v>47</v>
@@ -6911,7 +6888,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B102" s="42">
         <v>46462</v>
@@ -6920,7 +6897,7 @@
         <v>46464</v>
       </c>
       <c r="D102" s="40" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E102" s="40" t="s">
         <v>47</v>
@@ -7002,7 +6979,7 @@
     </row>
     <row r="107" spans="1:7" ht="24.9" customHeight="1">
       <c r="A107" s="40" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B107" s="42">
         <v>46477</v>
@@ -7014,7 +6991,7 @@
         <v>47</v>
       </c>
       <c r="E107" s="40" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F107" s="40" t="s">
         <v>30</v>
@@ -7025,7 +7002,7 @@
     </row>
     <row r="108" spans="1:7" ht="16.8">
       <c r="A108" s="41" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B108" s="41"/>
       <c r="C108" s="41"/>
@@ -7036,7 +7013,7 @@
     </row>
     <row r="109" spans="1:7" ht="24.9" customHeight="1">
       <c r="A109" s="40" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B109" s="42">
         <v>46478</v>
@@ -7048,7 +7025,7 @@
         <v>47</v>
       </c>
       <c r="E109" s="40" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F109" s="40" t="s">
         <v>30</v>
@@ -7059,7 +7036,7 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="40" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B110" s="42">
         <v>46482</v>
@@ -7071,7 +7048,7 @@
         <v>47</v>
       </c>
       <c r="E110" s="40" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F110" s="40" t="s">
         <v>30</v>
@@ -7082,7 +7059,7 @@
     </row>
     <row r="111" spans="1:7" s="44" customFormat="1">
       <c r="A111" s="40" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B111" s="42">
         <v>46485</v>
@@ -7105,7 +7082,7 @@
     </row>
     <row r="112" spans="1:7" s="24" customFormat="1">
       <c r="A112" s="40" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B112" s="42">
         <v>46490</v>
@@ -7114,7 +7091,7 @@
         <v>46494</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E112" s="40" t="s">
         <v>47</v>
@@ -7128,7 +7105,7 @@
     </row>
     <row r="113" spans="1:7" ht="13.2" customHeight="1">
       <c r="A113" s="40" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B113" s="42">
         <v>46500</v>
@@ -7137,7 +7114,7 @@
         <v>46504</v>
       </c>
       <c r="D113" s="40" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E113" s="40" t="s">
         <v>47</v>
@@ -7168,7 +7145,7 @@
     </row>
     <row r="115" spans="1:7" ht="17.25" customHeight="1">
       <c r="A115" s="41" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B115" s="41"/>
       <c r="C115" s="41"/>
@@ -7196,7 +7173,7 @@
     </row>
     <row r="117" spans="1:7" ht="17.25" customHeight="1">
       <c r="A117" s="41" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B117" s="41"/>
       <c r="C117" s="41"/>
@@ -7224,7 +7201,7 @@
     </row>
     <row r="119" spans="1:7" ht="17.25" customHeight="1">
       <c r="A119" s="41" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B119" s="41"/>
       <c r="C119" s="41"/>
@@ -7252,7 +7229,7 @@
     </row>
     <row r="121" spans="1:7" ht="17.25" customHeight="1">
       <c r="A121" s="41" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B121" s="41"/>
       <c r="C121" s="41"/>
@@ -7280,7 +7257,7 @@
     </row>
     <row r="123" spans="1:7" ht="16.8">
       <c r="A123" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B123" s="41"/>
       <c r="C123" s="41"/>
@@ -7291,7 +7268,7 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="40" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B124" s="42">
         <v>46737</v>
@@ -7308,7 +7285,7 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="40" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B125" s="42">
         <v>46746</v>
@@ -7325,7 +7302,7 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="40" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B126" s="42">
         <v>46747</v>
@@ -7342,7 +7319,7 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="40" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B127" s="42">
         <v>46748</v>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="200">
   <si>
     <t>KZNA Calendar Season 2026–2027</t>
   </si>
@@ -185,9 +185,6 @@
   </si>
   <si>
     <t>UDA District Gala</t>
-  </si>
-  <si>
-    <t>AG Gala - Penguins</t>
   </si>
   <si>
     <t>Penguins</t>
@@ -1058,11 +1055,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1144,7 +1141,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1189,7 +1186,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1224,8 +1221,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G127">
-  <autoFilter ref="A9:G127"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G126">
+  <autoFilter ref="A9:G126"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Event Name"/>
     <tableColumn id="2" name="Start Date"/>
@@ -1535,7 +1532,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>
@@ -1553,8 +1550,8 @@
       <c r="G2" s="46"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="45" t="s">
-        <v>177</v>
+      <c r="A5" s="47" t="s">
+        <v>176</v>
       </c>
       <c r="B5" s="46"/>
       <c r="C5" s="46"/>
@@ -1565,25 +1562,25 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -1827,8 +1824,8 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="45" t="s">
-        <v>185</v>
+      <c r="A18" s="47" t="s">
+        <v>184</v>
       </c>
       <c r="B18" s="46"/>
       <c r="C18" s="46"/>
@@ -1839,25 +1836,25 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2106,8 +2103,8 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="45" t="s">
-        <v>186</v>
+      <c r="A31" s="47" t="s">
+        <v>185</v>
       </c>
       <c r="B31" s="46"/>
       <c r="C31" s="46"/>
@@ -2118,25 +2115,25 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2403,8 +2400,8 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="45" t="s">
-        <v>187</v>
+      <c r="A46" s="47" t="s">
+        <v>186</v>
       </c>
       <c r="B46" s="46"/>
       <c r="C46" s="46"/>
@@ -2415,25 +2412,25 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2677,8 +2674,8 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="45" t="s">
-        <v>188</v>
+      <c r="A59" s="47" t="s">
+        <v>187</v>
       </c>
       <c r="B59" s="46"/>
       <c r="C59" s="46"/>
@@ -2689,25 +2686,25 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -2956,8 +2953,8 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="45" t="s">
-        <v>189</v>
+      <c r="A72" s="47" t="s">
+        <v>188</v>
       </c>
       <c r="B72" s="46"/>
       <c r="C72" s="46"/>
@@ -2968,25 +2965,25 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="G73" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3248,8 +3245,8 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="45" t="s">
-        <v>190</v>
+      <c r="A87" s="47" t="s">
+        <v>189</v>
       </c>
       <c r="B87" s="46"/>
       <c r="C87" s="46"/>
@@ -3260,25 +3257,25 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3527,8 +3524,8 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="45" t="s">
-        <v>191</v>
+      <c r="A100" s="47" t="s">
+        <v>190</v>
       </c>
       <c r="B100" s="46"/>
       <c r="C100" s="46"/>
@@ -3539,25 +3536,25 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F101" s="2" t="s">
+      <c r="G101" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -3806,8 +3803,8 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="45" t="s">
-        <v>192</v>
+      <c r="A113" s="47" t="s">
+        <v>191</v>
       </c>
       <c r="B113" s="46"/>
       <c r="C113" s="46"/>
@@ -3818,25 +3815,25 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="F114" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F114" s="2" t="s">
+      <c r="G114" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4052,8 +4049,8 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="45" t="s">
-        <v>193</v>
+      <c r="A124" s="47" t="s">
+        <v>192</v>
       </c>
       <c r="B124" s="46"/>
       <c r="C124" s="46"/>
@@ -4064,25 +4061,25 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="E125" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="G125" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4331,8 +4328,8 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="45" t="s">
-        <v>194</v>
+      <c r="A137" s="47" t="s">
+        <v>193</v>
       </c>
       <c r="B137" s="46"/>
       <c r="C137" s="46"/>
@@ -4343,25 +4340,25 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="D138" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="E138" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="F138" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F138" s="2" t="s">
+      <c r="G138" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4605,8 +4602,8 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="45" t="s">
-        <v>195</v>
+      <c r="A150" s="47" t="s">
+        <v>194</v>
       </c>
       <c r="B150" s="46"/>
       <c r="C150" s="46"/>
@@ -4617,25 +4614,25 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C151" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="D151" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="E151" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="F151" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F151" s="2" t="s">
+      <c r="G151" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -4903,6 +4900,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -4911,12 +4914,6 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -4925,7 +4922,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -4937,7 +4934,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>
@@ -5315,7 +5312,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="40" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B27" s="42">
         <v>46210</v>
@@ -5327,7 +5324,7 @@
         <v>28</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F27" s="40" t="s">
         <v>30</v>
@@ -5361,7 +5358,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B29" s="42">
         <v>46228</v>
@@ -5498,105 +5495,105 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B36" s="42">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="C36" s="42">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="D36" s="40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E36" s="40" t="s">
         <v>47</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G36" s="40" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B37" s="42">
-        <v>46256</v>
+        <v>46277</v>
       </c>
       <c r="C37" s="42">
-        <v>46257</v>
+        <v>46278</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G37" s="40" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="42">
-        <v>46277</v>
-      </c>
-      <c r="C38" s="42">
-        <v>46278</v>
-      </c>
-      <c r="D38" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="E38" s="40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A38" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="F38" s="40" t="s">
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
+    </row>
+    <row r="39" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A39" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="42">
+        <v>46270</v>
+      </c>
+      <c r="C39" s="42">
+        <v>46270</v>
+      </c>
+      <c r="D39" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G38" s="40" t="s">
+      <c r="G39" s="40" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A39" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="41"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-    </row>
-    <row r="40" spans="1:7" ht="24.9" customHeight="1">
+    <row r="40" spans="1:7">
       <c r="A40" s="40" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B40" s="42">
         <v>46270</v>
       </c>
       <c r="C40" s="42">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="F40" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G40" s="40" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -5604,16 +5601,16 @@
         <v>63</v>
       </c>
       <c r="B41" s="42">
-        <v>46270</v>
+        <v>46285</v>
       </c>
       <c r="C41" s="42">
-        <v>46271</v>
+        <v>46285</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F41" s="40" t="s">
         <v>30</v>
@@ -5624,48 +5621,42 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="40" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B42" s="42">
-        <v>46285</v>
+        <v>46289</v>
       </c>
       <c r="C42" s="42">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="F42" s="40" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G42" s="40" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B43" s="42">
         <v>46289</v>
       </c>
       <c r="C43" s="42">
-        <v>46292</v>
-      </c>
-      <c r="D43" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="E43" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F43" s="40" t="s">
-        <v>47</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
       <c r="G43" s="40" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -5673,33 +5664,39 @@
         <v>69</v>
       </c>
       <c r="B44" s="42">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C44" s="42">
-        <v>46289</v>
-      </c>
-      <c r="D44" s="40"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="40"/>
+        <v>46292</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="E44" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G44" s="40" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="40" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B45" s="42">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C45" s="42">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F45" s="40" t="s">
         <v>30</v>
@@ -5710,19 +5707,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="40" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B46" s="42">
         <v>46291</v>
       </c>
       <c r="C46" s="42">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="F46" s="40" t="s">
         <v>30</v>
@@ -5731,98 +5728,98 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="B47" s="42">
-        <v>46291</v>
-      </c>
-      <c r="C47" s="42">
-        <v>46293</v>
-      </c>
-      <c r="D47" s="40" t="s">
+    <row r="47" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A47" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="E47" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F47" s="40" t="s">
+      <c r="B47" s="41"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="40"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B49" s="42">
+        <v>46298</v>
+      </c>
+      <c r="C49" s="42">
+        <v>46298</v>
+      </c>
+      <c r="D49" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="F49" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G47" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A48" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="B48" s="41"/>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="40"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="42"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="40"/>
+      <c r="G49" s="40" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B50" s="42">
         <v>46298</v>
       </c>
       <c r="C50" s="42">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F50" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B51" s="42">
-        <v>46298</v>
+        <v>46312</v>
       </c>
       <c r="C51" s="42">
-        <v>46299</v>
+        <v>46312</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F51" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G51" s="40" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B52" s="42">
         <v>46312</v>
@@ -5831,10 +5828,10 @@
         <v>46312</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F52" s="40" t="s">
         <v>30</v>
@@ -5845,254 +5842,254 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="40" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B53" s="42">
-        <v>46312</v>
+        <v>46318</v>
       </c>
       <c r="C53" s="42">
-        <v>46312</v>
+        <v>46320</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F53" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G53" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="24.9" customHeight="1">
       <c r="A54" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B54" s="42">
-        <v>46318</v>
+        <v>46326</v>
       </c>
       <c r="C54" s="42">
-        <v>46320</v>
+        <v>46326</v>
       </c>
       <c r="D54" s="40" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="F54" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G54" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A55" s="40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A55" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="B55" s="42">
-        <v>46326</v>
-      </c>
-      <c r="C55" s="42">
-        <v>46326</v>
-      </c>
-      <c r="D55" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="E55" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="F55" s="40" t="s">
+      <c r="B55" s="41"/>
+      <c r="C55" s="41"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56" s="42">
+        <v>46333</v>
+      </c>
+      <c r="C56" s="42">
+        <v>46333</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E56" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F56" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G55" s="40" t="s">
+      <c r="G56" s="40" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A56" s="41" t="s">
-        <v>92</v>
-      </c>
-      <c r="B56" s="41"/>
-      <c r="C56" s="41"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B57" s="42">
-        <v>46333</v>
+        <v>46340</v>
       </c>
       <c r="C57" s="42">
-        <v>46333</v>
+        <v>46341</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="F57" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G57" s="40" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="40" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B58" s="42">
-        <v>46340</v>
+        <v>46347</v>
       </c>
       <c r="C58" s="42">
-        <v>46341</v>
+        <v>46347</v>
       </c>
       <c r="D58" s="40" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F58" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G58" s="40" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B59" s="42">
         <v>46347</v>
       </c>
       <c r="C59" s="42">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F59" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G59" s="40" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B60" s="42">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="C60" s="42">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="F60" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G60" s="40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="24.9" customHeight="1">
       <c r="A61" s="40" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B61" s="42">
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="C61" s="42">
-        <v>46355</v>
+        <v>46354</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F61" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G61" s="40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A62" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="B62" s="41"/>
+      <c r="C62" s="41"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="41"/>
+      <c r="G62" s="41"/>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="B63" s="42">
+        <v>46360</v>
+      </c>
+      <c r="C63" s="42">
+        <v>46361</v>
+      </c>
+      <c r="D63" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="E63" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="F63" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G63" s="40" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A62" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="B62" s="42">
-        <v>46354</v>
-      </c>
-      <c r="C62" s="42">
-        <v>46354</v>
-      </c>
-      <c r="D62" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="E62" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="F62" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G62" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A63" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="B63" s="41"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="41"/>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="40" t="s">
         <v>106</v>
       </c>
       <c r="B64" s="42">
-        <v>46360</v>
+        <v>46368</v>
       </c>
       <c r="C64" s="42">
-        <v>46361</v>
+        <v>46369</v>
       </c>
       <c r="D64" s="40" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="F64" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G64" s="40" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -6100,45 +6097,39 @@
         <v>107</v>
       </c>
       <c r="B65" s="42">
-        <v>46368</v>
+        <v>46366</v>
       </c>
       <c r="C65" s="42">
-        <v>46369</v>
+        <v>46370</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="F65" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G65" s="40" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B66" s="42">
-        <v>46366</v>
+        <v>46372</v>
       </c>
       <c r="C66" s="42">
-        <v>46370</v>
-      </c>
-      <c r="D66" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="E66" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="F66" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46372</v>
+      </c>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
       <c r="G66" s="40" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -6146,10 +6137,10 @@
         <v>110</v>
       </c>
       <c r="B67" s="42">
-        <v>46372</v>
+        <v>46381</v>
       </c>
       <c r="C67" s="42">
-        <v>46372</v>
+        <v>46381</v>
       </c>
       <c r="D67" s="40"/>
       <c r="E67" s="40"/>
@@ -6163,10 +6154,10 @@
         <v>111</v>
       </c>
       <c r="B68" s="42">
-        <v>46381</v>
+        <v>46382</v>
       </c>
       <c r="C68" s="42">
-        <v>46381</v>
+        <v>46382</v>
       </c>
       <c r="D68" s="40"/>
       <c r="E68" s="40"/>
@@ -6175,72 +6166,78 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="40" t="s">
+    <row r="69" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A69" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="B69" s="42">
-        <v>46382</v>
-      </c>
-      <c r="C69" s="42">
-        <v>46382</v>
-      </c>
-      <c r="D69" s="40"/>
-      <c r="E69" s="40"/>
-      <c r="F69" s="40"/>
-      <c r="G69" s="40" t="s">
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="41"/>
+      <c r="G69" s="41"/>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="B70" s="42">
+        <v>46388</v>
+      </c>
+      <c r="C70" s="42">
+        <v>46388</v>
+      </c>
+      <c r="D70" s="40"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="40" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A70" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="B70" s="41"/>
-      <c r="C70" s="41"/>
-      <c r="D70" s="41"/>
-      <c r="E70" s="41"/>
-      <c r="F70" s="41"/>
-      <c r="G70" s="41"/>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="40" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B71" s="42">
-        <v>46388</v>
+        <v>46395</v>
       </c>
       <c r="C71" s="42">
-        <v>46388</v>
-      </c>
-      <c r="D71" s="40"/>
-      <c r="E71" s="40"/>
-      <c r="F71" s="40"/>
+        <v>46396</v>
+      </c>
+      <c r="D71" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="E71" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F71" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G71" s="40" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="40" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B72" s="42">
-        <v>46395</v>
+        <v>46403</v>
       </c>
       <c r="C72" s="42">
-        <v>46396</v>
+        <v>46404</v>
       </c>
       <c r="D72" s="40" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="F72" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G72" s="40" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -6254,16 +6251,16 @@
         <v>46404</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F73" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G73" s="40" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -6274,19 +6271,19 @@
         <v>46403</v>
       </c>
       <c r="C74" s="42">
-        <v>46404</v>
+        <v>46403</v>
       </c>
       <c r="D74" s="40" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F74" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G74" s="40" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -6300,21 +6297,21 @@
         <v>46403</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="F75" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G75" s="40" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="40" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B76" s="42">
         <v>46403</v>
@@ -6323,16 +6320,16 @@
         <v>46403</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F76" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G76" s="40" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -6340,22 +6337,22 @@
         <v>121</v>
       </c>
       <c r="B77" s="42">
-        <v>46403</v>
+        <v>46396</v>
       </c>
       <c r="C77" s="42">
-        <v>46403</v>
+        <v>46397</v>
       </c>
       <c r="D77" s="40" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="F77" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G77" s="40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -6363,85 +6360,85 @@
         <v>122</v>
       </c>
       <c r="B78" s="42">
-        <v>46396</v>
+        <v>46404</v>
       </c>
       <c r="C78" s="42">
-        <v>46397</v>
+        <v>46404</v>
       </c>
       <c r="D78" s="40" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="F78" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G78" s="40" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="24.9" customHeight="1">
       <c r="A79" s="40" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B79" s="42">
-        <v>46404</v>
+        <v>46410</v>
       </c>
       <c r="C79" s="42">
-        <v>46404</v>
+        <v>46410</v>
       </c>
       <c r="D79" s="40" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F79" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G79" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="24.9" customHeight="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B80" s="42">
-        <v>46410</v>
+        <v>46411</v>
       </c>
       <c r="C80" s="42">
-        <v>46410</v>
+        <v>46411</v>
       </c>
       <c r="D80" s="40" t="s">
-        <v>61</v>
+        <v>128</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F80" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G80" s="40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="40" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B81" s="42">
-        <v>46411</v>
+        <v>46415</v>
       </c>
       <c r="C81" s="42">
-        <v>46411</v>
+        <v>46415</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="F81" s="40" t="s">
         <v>30</v>
@@ -6452,19 +6449,19 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="40" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B82" s="42">
         <v>46415</v>
       </c>
       <c r="C82" s="42">
-        <v>46415</v>
+        <v>46417</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="F82" s="40" t="s">
         <v>30</v>
@@ -6475,19 +6472,19 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="40" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B83" s="42">
-        <v>46415</v>
+        <v>46416</v>
       </c>
       <c r="C83" s="42">
-        <v>46417</v>
+        <v>46416</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F83" s="40" t="s">
         <v>30</v>
@@ -6498,19 +6495,19 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B84" s="42">
         <v>46416</v>
       </c>
       <c r="C84" s="42">
-        <v>46416</v>
+        <v>46417</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F84" s="40" t="s">
         <v>30</v>
@@ -6519,130 +6516,130 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" ht="17.25" customHeight="1">
       <c r="A85" s="40" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B85" s="42">
         <v>46416</v>
       </c>
       <c r="C85" s="42">
-        <v>46417</v>
+        <v>46418</v>
       </c>
       <c r="D85" s="40" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="F85" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G85" s="40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="17.25" customHeight="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="24.9" customHeight="1">
       <c r="A86" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B86" s="42">
-        <v>46416</v>
+        <v>46417</v>
       </c>
       <c r="C86" s="42">
         <v>46418</v>
       </c>
       <c r="D86" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="F86" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G86" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A87" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="B87" s="42">
-        <v>46417</v>
-      </c>
-      <c r="C87" s="42">
-        <v>46418</v>
-      </c>
-      <c r="D87" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="E87" s="40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="16.8">
+      <c r="A87" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="F87" s="40" t="s">
+      <c r="B87" s="41"/>
+      <c r="C87" s="41"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="41"/>
+      <c r="F87" s="41"/>
+      <c r="G87" s="41"/>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="B88" s="42">
+        <v>46422</v>
+      </c>
+      <c r="C88" s="42">
+        <v>46422</v>
+      </c>
+      <c r="D88" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="E88" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="F88" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G87" s="40" t="s">
+      <c r="G88" s="40" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" ht="16.8">
-      <c r="A88" s="41" t="s">
-        <v>146</v>
-      </c>
-      <c r="B88" s="41"/>
-      <c r="C88" s="41"/>
-      <c r="D88" s="41"/>
-      <c r="E88" s="41"/>
-      <c r="F88" s="41"/>
-      <c r="G88" s="41"/>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="40" t="s">
-        <v>147</v>
+        <v>45</v>
       </c>
       <c r="B89" s="42">
         <v>46422</v>
       </c>
       <c r="C89" s="42">
-        <v>46422</v>
+        <v>46423</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F89" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G89" s="40" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="40" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="B90" s="42">
-        <v>46422</v>
+        <v>46424</v>
       </c>
       <c r="C90" s="42">
-        <v>46423</v>
+        <v>46424</v>
       </c>
       <c r="D90" s="40" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="F90" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G90" s="40" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6653,19 +6650,19 @@
         <v>46424</v>
       </c>
       <c r="C91" s="42">
-        <v>46424</v>
+        <v>46425</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F91" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G91" s="40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6673,22 +6670,22 @@
         <v>150</v>
       </c>
       <c r="B92" s="42">
-        <v>46424</v>
+        <v>46431</v>
       </c>
       <c r="C92" s="42">
-        <v>46425</v>
+        <v>46431</v>
       </c>
       <c r="D92" s="40" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="F92" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G92" s="40" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6699,113 +6696,113 @@
         <v>46431</v>
       </c>
       <c r="C93" s="42">
-        <v>46431</v>
+        <v>46432</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="F93" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G93" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="17.25" customHeight="1">
       <c r="A94" s="40" t="s">
         <v>152</v>
       </c>
       <c r="B94" s="42">
-        <v>46431</v>
+        <v>46438</v>
       </c>
       <c r="C94" s="42">
-        <v>46432</v>
+        <v>46438</v>
       </c>
       <c r="D94" s="40" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F94" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G94" s="40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="17.25" customHeight="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" s="40" t="s">
         <v>153</v>
       </c>
       <c r="B95" s="42">
-        <v>46438</v>
+        <v>46445</v>
       </c>
       <c r="C95" s="42">
-        <v>46438</v>
+        <v>46446</v>
       </c>
       <c r="D95" s="40" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="F95" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G95" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="A96" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="B96" s="42">
-        <v>46445</v>
-      </c>
-      <c r="C96" s="42">
-        <v>46446</v>
-      </c>
-      <c r="D96" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="E96" s="40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="16.8">
+      <c r="A96" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="F96" s="40" t="s">
+      <c r="B96" s="41"/>
+      <c r="C96" s="41"/>
+      <c r="D96" s="41"/>
+      <c r="E96" s="41"/>
+      <c r="F96" s="41"/>
+      <c r="G96" s="41"/>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="B97" s="42">
+        <v>46447</v>
+      </c>
+      <c r="C97" s="42">
+        <v>46447</v>
+      </c>
+      <c r="D97" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="E97" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F97" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G96" s="40" t="s">
+      <c r="G97" s="40" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" ht="16.8">
-      <c r="A97" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="B97" s="41"/>
-      <c r="C97" s="41"/>
-      <c r="D97" s="41"/>
-      <c r="E97" s="41"/>
-      <c r="F97" s="41"/>
-      <c r="G97" s="41"/>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="B98" s="42">
+        <v>46448</v>
+      </c>
+      <c r="C98" s="42">
+        <v>46448</v>
+      </c>
+      <c r="D98" s="40" t="s">
         <v>158</v>
-      </c>
-      <c r="B98" s="42">
-        <v>46447</v>
-      </c>
-      <c r="C98" s="42">
-        <v>46447</v>
-      </c>
-      <c r="D98" s="40" t="s">
-        <v>159</v>
       </c>
       <c r="E98" s="40" t="s">
         <v>47</v>
@@ -6822,13 +6819,13 @@
         <v>160</v>
       </c>
       <c r="B99" s="42">
-        <v>46448</v>
+        <v>46449</v>
       </c>
       <c r="C99" s="42">
-        <v>46448</v>
+        <v>46449</v>
       </c>
       <c r="D99" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E99" s="40" t="s">
         <v>47</v>
@@ -6845,13 +6842,13 @@
         <v>161</v>
       </c>
       <c r="B100" s="42">
-        <v>46449</v>
+        <v>46450</v>
       </c>
       <c r="C100" s="42">
-        <v>46449</v>
+        <v>46450</v>
       </c>
       <c r="D100" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E100" s="40" t="s">
         <v>47</v>
@@ -6868,13 +6865,13 @@
         <v>162</v>
       </c>
       <c r="B101" s="42">
-        <v>46450</v>
+        <v>46462</v>
       </c>
       <c r="C101" s="42">
-        <v>46450</v>
+        <v>46464</v>
       </c>
       <c r="D101" s="40" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E101" s="40" t="s">
         <v>47</v>
@@ -6886,38 +6883,32 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" ht="13.2" customHeight="1">
       <c r="A102" s="40" t="s">
-        <v>163</v>
+        <v>19</v>
       </c>
       <c r="B102" s="42">
-        <v>46462</v>
+        <v>46467</v>
       </c>
       <c r="C102" s="42">
-        <v>46464</v>
-      </c>
-      <c r="D102" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="E102" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F102" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46467</v>
+      </c>
+      <c r="D102" s="40"/>
+      <c r="E102" s="40"/>
+      <c r="F102" s="40"/>
       <c r="G102" s="40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="13.2" customHeight="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103" s="40" t="s">
         <v>19</v>
       </c>
       <c r="B103" s="42">
-        <v>46467</v>
+        <v>46468</v>
       </c>
       <c r="C103" s="42">
-        <v>46467</v>
+        <v>46468</v>
       </c>
       <c r="D103" s="40"/>
       <c r="E103" s="40"/>
@@ -6926,15 +6917,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" ht="24.9" customHeight="1">
       <c r="A104" s="40" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B104" s="42">
-        <v>46468</v>
+        <v>46472</v>
       </c>
       <c r="C104" s="42">
-        <v>46468</v>
+        <v>46472</v>
       </c>
       <c r="D104" s="40"/>
       <c r="E104" s="40"/>
@@ -6943,15 +6934,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="24.9" customHeight="1">
+    <row r="105" spans="1:7" ht="17.25" customHeight="1">
       <c r="A105" s="40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B105" s="42">
-        <v>46472</v>
+        <v>46475</v>
       </c>
       <c r="C105" s="42">
-        <v>46472</v>
+        <v>46475</v>
       </c>
       <c r="D105" s="40"/>
       <c r="E105" s="40"/>
@@ -6960,72 +6951,78 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="17.25" customHeight="1">
+    <row r="106" spans="1:7" ht="24.9" customHeight="1">
       <c r="A106" s="40" t="s">
-        <v>22</v>
+        <v>165</v>
       </c>
       <c r="B106" s="42">
-        <v>46475</v>
+        <v>46477</v>
       </c>
       <c r="C106" s="42">
-        <v>46475</v>
-      </c>
-      <c r="D106" s="40"/>
-      <c r="E106" s="40"/>
-      <c r="F106" s="40"/>
+        <v>46477</v>
+      </c>
+      <c r="D106" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E106" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="F106" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G106" s="40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A107" s="40" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="16.8">
+      <c r="A107" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="B107" s="41"/>
+      <c r="C107" s="41"/>
+      <c r="D107" s="41"/>
+      <c r="E107" s="41"/>
+      <c r="F107" s="41"/>
+      <c r="G107" s="41"/>
+    </row>
+    <row r="108" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A108" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B108" s="42">
+        <v>46478</v>
+      </c>
+      <c r="C108" s="42">
+        <v>46480</v>
+      </c>
+      <c r="D108" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E108" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="B107" s="42">
-        <v>46477</v>
-      </c>
-      <c r="C107" s="42">
-        <v>46477</v>
-      </c>
-      <c r="D107" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="E107" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="F107" s="40" t="s">
+      <c r="F108" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G107" s="40" t="s">
+      <c r="G108" s="40" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="16.8">
-      <c r="A108" s="41" t="s">
+    <row r="109" spans="1:7">
+      <c r="A109" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="B108" s="41"/>
-      <c r="C108" s="41"/>
-      <c r="D108" s="41"/>
-      <c r="E108" s="41"/>
-      <c r="F108" s="41"/>
-      <c r="G108" s="41"/>
-    </row>
-    <row r="109" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A109" s="40" t="s">
-        <v>166</v>
-      </c>
       <c r="B109" s="42">
-        <v>46478</v>
+        <v>46482</v>
       </c>
       <c r="C109" s="42">
-        <v>46480</v>
+        <v>46484</v>
       </c>
       <c r="D109" s="40" t="s">
         <v>47</v>
       </c>
       <c r="E109" s="40" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F109" s="40" t="s">
         <v>30</v>
@@ -7034,21 +7031,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" s="44" customFormat="1">
       <c r="A110" s="40" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B110" s="42">
-        <v>46482</v>
+        <v>46485</v>
       </c>
       <c r="C110" s="42">
-        <v>46484</v>
+        <v>46489</v>
       </c>
       <c r="D110" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="E110" s="40" t="s">
         <v>47</v>
-      </c>
-      <c r="E110" s="40" t="s">
-        <v>170</v>
       </c>
       <c r="F110" s="40" t="s">
         <v>30</v>
@@ -7057,18 +7054,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" s="44" customFormat="1">
+    <row r="111" spans="1:7" s="24" customFormat="1">
       <c r="A111" s="40" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B111" s="42">
-        <v>46485</v>
+        <v>46490</v>
       </c>
       <c r="C111" s="42">
-        <v>46489</v>
+        <v>46494</v>
       </c>
       <c r="D111" s="40" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="E111" s="40" t="s">
         <v>47</v>
@@ -7080,18 +7077,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" s="24" customFormat="1">
+    <row r="112" spans="1:7" ht="13.2" customHeight="1">
       <c r="A112" s="40" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="B112" s="42">
-        <v>46490</v>
+        <v>46500</v>
       </c>
       <c r="C112" s="42">
-        <v>46494</v>
+        <v>46504</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="E112" s="40" t="s">
         <v>47</v>
@@ -7100,181 +7097,175 @@
         <v>30</v>
       </c>
       <c r="G112" s="40" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="13.2" customHeight="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" s="40" t="s">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="B113" s="42">
-        <v>46500</v>
+        <v>46504</v>
       </c>
       <c r="C113" s="42">
         <v>46504</v>
       </c>
-      <c r="D113" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="E113" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F113" s="40" t="s">
-        <v>30</v>
-      </c>
+      <c r="D113" s="40"/>
+      <c r="E113" s="40"/>
+      <c r="F113" s="40"/>
       <c r="G113" s="40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
-      <c r="A114" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B114" s="42">
-        <v>46504</v>
-      </c>
-      <c r="C114" s="42">
-        <v>46504</v>
-      </c>
-      <c r="D114" s="40"/>
-      <c r="E114" s="40"/>
-      <c r="F114" s="40"/>
-      <c r="G114" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A115" s="41" t="s">
+    <row r="114" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A114" s="41" t="s">
+        <v>171</v>
+      </c>
+      <c r="B114" s="41"/>
+      <c r="C114" s="41"/>
+      <c r="D114" s="41"/>
+      <c r="E114" s="41"/>
+      <c r="F114" s="41"/>
+      <c r="G114" s="41"/>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B115" s="42">
+        <v>46508</v>
+      </c>
+      <c r="C115" s="42">
+        <v>46508</v>
+      </c>
+      <c r="D115" s="40"/>
+      <c r="E115" s="40"/>
+      <c r="F115" s="40"/>
+      <c r="G115" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A116" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="B115" s="41"/>
-      <c r="C115" s="41"/>
-      <c r="D115" s="41"/>
-      <c r="E115" s="41"/>
-      <c r="F115" s="41"/>
-      <c r="G115" s="41"/>
-    </row>
-    <row r="116" spans="1:7">
-      <c r="A116" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B116" s="42">
-        <v>46508</v>
-      </c>
-      <c r="C116" s="42">
-        <v>46508</v>
-      </c>
-      <c r="D116" s="40"/>
-      <c r="E116" s="40"/>
-      <c r="F116" s="40"/>
-      <c r="G116" s="40" t="s">
+      <c r="B116" s="41"/>
+      <c r="C116" s="41"/>
+      <c r="D116" s="41"/>
+      <c r="E116" s="41"/>
+      <c r="F116" s="41"/>
+      <c r="G116" s="41"/>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B117" s="42">
+        <v>46554</v>
+      </c>
+      <c r="C117" s="42">
+        <v>46554</v>
+      </c>
+      <c r="D117" s="40"/>
+      <c r="E117" s="40"/>
+      <c r="F117" s="40"/>
+      <c r="G117" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A117" s="41" t="s">
+    <row r="118" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A118" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="B117" s="41"/>
-      <c r="C117" s="41"/>
-      <c r="D117" s="41"/>
-      <c r="E117" s="41"/>
-      <c r="F117" s="41"/>
-      <c r="G117" s="41"/>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="B118" s="42">
-        <v>46554</v>
-      </c>
-      <c r="C118" s="42">
-        <v>46554</v>
-      </c>
-      <c r="D118" s="40"/>
-      <c r="E118" s="40"/>
-      <c r="F118" s="40"/>
-      <c r="G118" s="40" t="s">
+      <c r="B118" s="41"/>
+      <c r="C118" s="41"/>
+      <c r="D118" s="41"/>
+      <c r="E118" s="41"/>
+      <c r="F118" s="41"/>
+      <c r="G118" s="41"/>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B119" s="42">
+        <v>46608</v>
+      </c>
+      <c r="C119" s="42">
+        <v>46608</v>
+      </c>
+      <c r="D119" s="40"/>
+      <c r="E119" s="40"/>
+      <c r="F119" s="40"/>
+      <c r="G119" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A119" s="41" t="s">
+    <row r="120" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A120" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="B119" s="41"/>
-      <c r="C119" s="41"/>
-      <c r="D119" s="41"/>
-      <c r="E119" s="41"/>
-      <c r="F119" s="41"/>
-      <c r="G119" s="41"/>
-    </row>
-    <row r="120" spans="1:7">
-      <c r="A120" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="B120" s="42">
-        <v>46608</v>
-      </c>
-      <c r="C120" s="42">
-        <v>46608</v>
-      </c>
-      <c r="D120" s="40"/>
-      <c r="E120" s="40"/>
-      <c r="F120" s="40"/>
-      <c r="G120" s="40" t="s">
+      <c r="B120" s="41"/>
+      <c r="C120" s="41"/>
+      <c r="D120" s="41"/>
+      <c r="E120" s="41"/>
+      <c r="F120" s="41"/>
+      <c r="G120" s="41"/>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B121" s="42">
+        <v>46654</v>
+      </c>
+      <c r="C121" s="42">
+        <v>46654</v>
+      </c>
+      <c r="D121" s="40"/>
+      <c r="E121" s="40"/>
+      <c r="F121" s="40"/>
+      <c r="G121" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A121" s="41" t="s">
+    <row r="122" spans="1:7" ht="16.8">
+      <c r="A122" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="B121" s="41"/>
-      <c r="C121" s="41"/>
-      <c r="D121" s="41"/>
-      <c r="E121" s="41"/>
-      <c r="F121" s="41"/>
-      <c r="G121" s="41"/>
-    </row>
-    <row r="122" spans="1:7">
-      <c r="A122" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="B122" s="42">
-        <v>46654</v>
-      </c>
-      <c r="C122" s="42">
-        <v>46654</v>
-      </c>
-      <c r="D122" s="40"/>
-      <c r="E122" s="40"/>
-      <c r="F122" s="40"/>
-      <c r="G122" s="40" t="s">
+      <c r="B122" s="41"/>
+      <c r="C122" s="41"/>
+      <c r="D122" s="41"/>
+      <c r="E122" s="41"/>
+      <c r="F122" s="41"/>
+      <c r="G122" s="41"/>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="B123" s="42">
+        <v>46737</v>
+      </c>
+      <c r="C123" s="42">
+        <v>46737</v>
+      </c>
+      <c r="D123" s="40"/>
+      <c r="E123" s="40"/>
+      <c r="F123" s="40"/>
+      <c r="G123" s="40" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" ht="16.8">
-      <c r="A123" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="B123" s="41"/>
-      <c r="C123" s="41"/>
-      <c r="D123" s="41"/>
-      <c r="E123" s="41"/>
-      <c r="F123" s="41"/>
-      <c r="G123" s="41"/>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="40" t="s">
         <v>110</v>
       </c>
       <c r="B124" s="42">
-        <v>46737</v>
+        <v>46746</v>
       </c>
       <c r="C124" s="42">
-        <v>46737</v>
+        <v>46746</v>
       </c>
       <c r="D124" s="40"/>
       <c r="E124" s="40"/>
@@ -7288,10 +7279,10 @@
         <v>111</v>
       </c>
       <c r="B125" s="42">
-        <v>46746</v>
+        <v>46747</v>
       </c>
       <c r="C125" s="42">
-        <v>46746</v>
+        <v>46747</v>
       </c>
       <c r="D125" s="40"/>
       <c r="E125" s="40"/>
@@ -7302,13 +7293,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B126" s="42">
-        <v>46747</v>
+        <v>46748</v>
       </c>
       <c r="C126" s="42">
-        <v>46747</v>
+        <v>46748</v>
       </c>
       <c r="D126" s="40"/>
       <c r="E126" s="40"/>
@@ -7317,28 +7308,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
-      <c r="A127" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="B127" s="42">
-        <v>46748</v>
-      </c>
-      <c r="C127" s="42">
-        <v>46748</v>
-      </c>
-      <c r="D127" s="40"/>
-      <c r="E127" s="40"/>
-      <c r="F127" s="40"/>
-      <c r="G127" s="40" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A10:G127">
+  <conditionalFormatting sqref="A10:G126">
     <cfRule type="expression" dxfId="6" priority="8">
       <formula>$G10="National gala"</formula>
     </cfRule>
@@ -7362,7 +7336,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G203">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
       <formula1>"Club gala,District gala,Provincial gala,National gala,Open Water,Schools gala,Public Holiday"</formula1>
     </dataValidation>
   </dataValidations>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -1055,11 +1055,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1141,7 +1141,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1186,7 +1186,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1532,7 +1532,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="47" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>
@@ -1550,7 +1550,7 @@
       <c r="G2" s="46"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="45" t="s">
         <v>176</v>
       </c>
       <c r="B5" s="46"/>
@@ -1824,7 +1824,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="45" t="s">
         <v>184</v>
       </c>
       <c r="B18" s="46"/>
@@ -2103,7 +2103,7 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="47" t="s">
+      <c r="A31" s="45" t="s">
         <v>185</v>
       </c>
       <c r="B31" s="46"/>
@@ -2400,7 +2400,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="47" t="s">
+      <c r="A46" s="45" t="s">
         <v>186</v>
       </c>
       <c r="B46" s="46"/>
@@ -2674,7 +2674,7 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="47" t="s">
+      <c r="A59" s="45" t="s">
         <v>187</v>
       </c>
       <c r="B59" s="46"/>
@@ -2953,7 +2953,7 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="47" t="s">
+      <c r="A72" s="45" t="s">
         <v>188</v>
       </c>
       <c r="B72" s="46"/>
@@ -3245,7 +3245,7 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="47" t="s">
+      <c r="A87" s="45" t="s">
         <v>189</v>
       </c>
       <c r="B87" s="46"/>
@@ -3524,7 +3524,7 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="47" t="s">
+      <c r="A100" s="45" t="s">
         <v>190</v>
       </c>
       <c r="B100" s="46"/>
@@ -3803,7 +3803,7 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="47" t="s">
+      <c r="A113" s="45" t="s">
         <v>191</v>
       </c>
       <c r="B113" s="46"/>
@@ -4049,7 +4049,7 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="47" t="s">
+      <c r="A124" s="45" t="s">
         <v>192</v>
       </c>
       <c r="B124" s="46"/>
@@ -4328,7 +4328,7 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="47" t="s">
+      <c r="A137" s="45" t="s">
         <v>193</v>
       </c>
       <c r="B137" s="46"/>
@@ -4602,7 +4602,7 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="47" t="s">
+      <c r="A150" s="45" t="s">
         <v>194</v>
       </c>
       <c r="B150" s="46"/>
@@ -4900,12 +4900,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -4914,6 +4908,12 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -4934,7 +4934,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="47" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>
@@ -6071,65 +6071,65 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="40" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B64" s="42">
-        <v>46368</v>
+        <v>46366</v>
       </c>
       <c r="C64" s="42">
-        <v>46369</v>
+        <v>46370</v>
       </c>
       <c r="D64" s="40" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F64" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G64" s="40" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="40" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B65" s="42">
-        <v>46366</v>
+        <v>46372</v>
       </c>
       <c r="C65" s="42">
-        <v>46370</v>
-      </c>
-      <c r="D65" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="E65" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="F65" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46372</v>
+      </c>
+      <c r="D65" s="40"/>
+      <c r="E65" s="40"/>
+      <c r="F65" s="40"/>
       <c r="G65" s="40" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="40" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B66" s="42">
-        <v>46372</v>
+        <v>46375</v>
       </c>
       <c r="C66" s="42">
-        <v>46372</v>
-      </c>
-      <c r="D66" s="40"/>
-      <c r="E66" s="40"/>
-      <c r="F66" s="40"/>
+        <v>46376</v>
+      </c>
+      <c r="D66" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E66" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="F66" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G66" s="40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -7336,7 +7336,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G63 G64:G202">
       <formula1>"Club gala,District gala,Provincial gala,National gala,Open Water,Schools gala,Public Holiday"</formula1>
     </dataValidation>
   </dataValidations>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="200">
   <si>
     <t>KZNA Calendar Season 2026–2027</t>
   </si>
@@ -941,7 +941,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1055,11 +1055,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1070,7 +1071,259 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="pro_day_only_🏊UnsanctionedCalendar" xfId="3"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="49">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9F1239"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC026D3"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF15803D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFA16207"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7E22CE"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF0369A1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFEA580C"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9F1239"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC026D3"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF15803D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFA16207"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7E22CE"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF0369A1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFEA580C"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9F1239"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC026D3"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF15803D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFA16207"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7E22CE"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF0369A1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFEA580C"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9F1239"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC026D3"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF15803D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFA16207"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7E22CE"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF0369A1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFEA580C"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9F1239"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC026D3"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF15803D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFA16207"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7E22CE"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF0369A1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFEA580C"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9F1239"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC026D3"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF15803D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFA16207"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7E22CE"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF0369A1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFEA580C"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1141,7 +1394,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1186,7 +1439,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1221,8 +1474,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G126">
-  <autoFilter ref="A9:G126"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G127">
+  <autoFilter ref="A9:G127"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Event Name"/>
     <tableColumn id="2" name="Start Date"/>
@@ -1532,33 +1785,33 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="2" spans="1:7" ht="24.9" customHeight="1">
-      <c r="B2" s="48"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
@@ -1824,15 +2077,15 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
@@ -2103,15 +2356,15 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
@@ -2400,15 +2653,15 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="45" t="s">
+      <c r="A46" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="B46" s="46"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="46"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
@@ -2674,15 +2927,15 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="45" t="s">
+      <c r="A59" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="B59" s="46"/>
-      <c r="C59" s="46"/>
-      <c r="D59" s="46"/>
-      <c r="E59" s="46"/>
-      <c r="F59" s="46"/>
-      <c r="G59" s="46"/>
+      <c r="B59" s="47"/>
+      <c r="C59" s="47"/>
+      <c r="D59" s="47"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="47"/>
+      <c r="G59" s="47"/>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
@@ -2953,15 +3206,15 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="45" t="s">
+      <c r="A72" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="B72" s="46"/>
-      <c r="C72" s="46"/>
-      <c r="D72" s="46"/>
-      <c r="E72" s="46"/>
-      <c r="F72" s="46"/>
-      <c r="G72" s="46"/>
+      <c r="B72" s="47"/>
+      <c r="C72" s="47"/>
+      <c r="D72" s="47"/>
+      <c r="E72" s="47"/>
+      <c r="F72" s="47"/>
+      <c r="G72" s="47"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
@@ -3245,15 +3498,15 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="45" t="s">
+      <c r="A87" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="B87" s="46"/>
-      <c r="C87" s="46"/>
-      <c r="D87" s="46"/>
-      <c r="E87" s="46"/>
-      <c r="F87" s="46"/>
-      <c r="G87" s="46"/>
+      <c r="B87" s="47"/>
+      <c r="C87" s="47"/>
+      <c r="D87" s="47"/>
+      <c r="E87" s="47"/>
+      <c r="F87" s="47"/>
+      <c r="G87" s="47"/>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
@@ -3524,15 +3777,15 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="45" t="s">
+      <c r="A100" s="48" t="s">
         <v>190</v>
       </c>
-      <c r="B100" s="46"/>
-      <c r="C100" s="46"/>
-      <c r="D100" s="46"/>
-      <c r="E100" s="46"/>
-      <c r="F100" s="46"/>
-      <c r="G100" s="46"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
@@ -3803,15 +4056,15 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="45" t="s">
+      <c r="A113" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="B113" s="46"/>
-      <c r="C113" s="46"/>
-      <c r="D113" s="46"/>
-      <c r="E113" s="46"/>
-      <c r="F113" s="46"/>
-      <c r="G113" s="46"/>
+      <c r="B113" s="47"/>
+      <c r="C113" s="47"/>
+      <c r="D113" s="47"/>
+      <c r="E113" s="47"/>
+      <c r="F113" s="47"/>
+      <c r="G113" s="47"/>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
@@ -4049,15 +4302,15 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="45" t="s">
+      <c r="A124" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B124" s="46"/>
-      <c r="C124" s="46"/>
-      <c r="D124" s="46"/>
-      <c r="E124" s="46"/>
-      <c r="F124" s="46"/>
-      <c r="G124" s="46"/>
+      <c r="B124" s="47"/>
+      <c r="C124" s="47"/>
+      <c r="D124" s="47"/>
+      <c r="E124" s="47"/>
+      <c r="F124" s="47"/>
+      <c r="G124" s="47"/>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
@@ -4328,15 +4581,15 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="45" t="s">
+      <c r="A137" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="B137" s="46"/>
-      <c r="C137" s="46"/>
-      <c r="D137" s="46"/>
-      <c r="E137" s="46"/>
-      <c r="F137" s="46"/>
-      <c r="G137" s="46"/>
+      <c r="B137" s="47"/>
+      <c r="C137" s="47"/>
+      <c r="D137" s="47"/>
+      <c r="E137" s="47"/>
+      <c r="F137" s="47"/>
+      <c r="G137" s="47"/>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
@@ -4602,15 +4855,15 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="45" t="s">
+      <c r="A150" s="48" t="s">
         <v>194</v>
       </c>
-      <c r="B150" s="46"/>
-      <c r="C150" s="46"/>
-      <c r="D150" s="46"/>
-      <c r="E150" s="46"/>
-      <c r="F150" s="46"/>
-      <c r="G150" s="46"/>
+      <c r="B150" s="47"/>
+      <c r="C150" s="47"/>
+      <c r="D150" s="47"/>
+      <c r="E150" s="47"/>
+      <c r="F150" s="47"/>
+      <c r="G150" s="47"/>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2" t="s">
@@ -4900,6 +5153,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -4908,12 +5167,6 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -4922,7 +5175,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -4934,13 +5187,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
       <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7" ht="24.9" customHeight="1">
@@ -5498,119 +5751,119 @@
         <v>53</v>
       </c>
       <c r="B36" s="42">
-        <v>46256</v>
+        <v>46249</v>
       </c>
       <c r="C36" s="42">
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="D36" s="40" t="s">
         <v>54</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G36" s="40" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" s="45" customFormat="1">
       <c r="A37" s="40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B37" s="42">
-        <v>46277</v>
+        <v>46256</v>
       </c>
       <c r="C37" s="42">
-        <v>46278</v>
+        <v>46257</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>57</v>
+        <v>197</v>
       </c>
       <c r="F37" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G37" s="40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="42">
+        <v>46277</v>
+      </c>
+      <c r="C38" s="42">
+        <v>46278</v>
+      </c>
+      <c r="D38" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G38" s="40" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A38" s="41" t="s">
+    <row r="39" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A39" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="41"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-    </row>
-    <row r="39" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A39" s="40" t="s">
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="41"/>
+    </row>
+    <row r="40" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A40" s="40" t="s">
         <v>59</v>
-      </c>
-      <c r="B39" s="42">
-        <v>46270</v>
-      </c>
-      <c r="C39" s="42">
-        <v>46270</v>
-      </c>
-      <c r="D39" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="F39" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G39" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="40" t="s">
-        <v>62</v>
       </c>
       <c r="B40" s="42">
         <v>46270</v>
       </c>
       <c r="C40" s="42">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F40" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G40" s="40" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B41" s="42">
-        <v>46285</v>
+        <v>46270</v>
       </c>
       <c r="C41" s="42">
-        <v>46285</v>
+        <v>46271</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F41" s="40" t="s">
         <v>30</v>
@@ -5621,82 +5874,82 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="40" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B42" s="42">
-        <v>46289</v>
+        <v>46285</v>
       </c>
       <c r="C42" s="42">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F42" s="40" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G42" s="40" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B43" s="42">
         <v>46289</v>
       </c>
       <c r="C43" s="42">
-        <v>46289</v>
-      </c>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
+        <v>46292</v>
+      </c>
+      <c r="D43" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="E43" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F43" s="40" t="s">
+        <v>47</v>
+      </c>
       <c r="G43" s="40" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B44" s="42">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="C44" s="42">
-        <v>46292</v>
-      </c>
-      <c r="D44" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="E44" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="F44" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
       <c r="G44" s="40" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="40" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B45" s="42">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="C45" s="42">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F45" s="40" t="s">
         <v>30</v>
@@ -5707,19 +5960,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="40" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B46" s="42">
         <v>46291</v>
       </c>
       <c r="C46" s="42">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="F46" s="40" t="s">
         <v>30</v>
@@ -5728,98 +5981,98 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A47" s="41" t="s">
+    <row r="47" spans="1:7">
+      <c r="A47" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B47" s="42">
+        <v>46291</v>
+      </c>
+      <c r="C47" s="42">
+        <v>46293</v>
+      </c>
+      <c r="D47" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="E47" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F47" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G47" s="40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A48" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="B47" s="41"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="40"/>
-      <c r="B48" s="42"/>
-      <c r="C48" s="42"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="40"/>
-      <c r="F48" s="40"/>
-      <c r="G48" s="40"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="B49" s="42">
-        <v>46298</v>
-      </c>
-      <c r="C49" s="42">
-        <v>46298</v>
-      </c>
-      <c r="D49" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="E49" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="F49" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G49" s="40" t="s">
-        <v>4</v>
-      </c>
+      <c r="A49" s="40"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B50" s="42">
         <v>46298</v>
       </c>
       <c r="C50" s="42">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F50" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B51" s="42">
-        <v>46312</v>
+        <v>46298</v>
       </c>
       <c r="C51" s="42">
-        <v>46312</v>
+        <v>46299</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F51" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G51" s="40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B52" s="42">
         <v>46312</v>
@@ -5828,10 +6081,10 @@
         <v>46312</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F52" s="40" t="s">
         <v>30</v>
@@ -5842,322 +6095,328 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B53" s="42">
-        <v>46318</v>
+        <v>46312</v>
       </c>
       <c r="C53" s="42">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F53" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G53" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="24.9" customHeight="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="40" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B54" s="42">
-        <v>46326</v>
+        <v>46318</v>
       </c>
       <c r="C54" s="42">
-        <v>46326</v>
+        <v>46320</v>
       </c>
       <c r="D54" s="40" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F54" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G54" s="40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A55" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="B55" s="42">
+        <v>46326</v>
+      </c>
+      <c r="C55" s="42">
+        <v>46326</v>
+      </c>
+      <c r="D55" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="F55" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G55" s="40" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A55" s="41" t="s">
+    <row r="56" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A56" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="B55" s="41"/>
-      <c r="C55" s="41"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="B56" s="42">
-        <v>46333</v>
-      </c>
-      <c r="C56" s="42">
-        <v>46333</v>
-      </c>
-      <c r="D56" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="E56" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F56" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G56" s="40" t="s">
-        <v>4</v>
-      </c>
+      <c r="B56" s="41"/>
+      <c r="C56" s="41"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41"/>
+      <c r="G56" s="41"/>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B57" s="42">
-        <v>46340</v>
+        <v>46333</v>
       </c>
       <c r="C57" s="42">
-        <v>46341</v>
+        <v>46333</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="F57" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G57" s="40" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="40" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B58" s="42">
-        <v>46347</v>
+        <v>46340</v>
       </c>
       <c r="C58" s="42">
-        <v>46347</v>
+        <v>46341</v>
       </c>
       <c r="D58" s="40" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F58" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G58" s="40" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="40" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B59" s="42">
         <v>46347</v>
       </c>
       <c r="C59" s="42">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F59" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G59" s="40" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="40" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B60" s="42">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="C60" s="42">
-        <v>46355</v>
+        <v>46348</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F60" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G60" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="24.9" customHeight="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" s="40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B61" s="42">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="C61" s="42">
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F61" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G61" s="40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A62" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="B62" s="42">
+        <v>46354</v>
+      </c>
+      <c r="C62" s="42">
+        <v>46354</v>
+      </c>
+      <c r="D62" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="E62" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="F62" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G62" s="40" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A62" s="41" t="s">
+    <row r="63" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A63" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="B62" s="41"/>
-      <c r="C62" s="41"/>
-      <c r="D62" s="41"/>
-      <c r="E62" s="41"/>
-      <c r="F62" s="41"/>
-      <c r="G62" s="41"/>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="B63" s="42">
-        <v>46360</v>
-      </c>
-      <c r="C63" s="42">
-        <v>46361</v>
-      </c>
-      <c r="D63" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="E63" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="F63" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G63" s="40" t="s">
-        <v>6</v>
-      </c>
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="41"/>
+      <c r="G63" s="41"/>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="40" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B64" s="42">
-        <v>46366</v>
+        <v>46360</v>
       </c>
       <c r="C64" s="42">
-        <v>46370</v>
+        <v>46361</v>
       </c>
       <c r="D64" s="40" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F64" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G64" s="40" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B65" s="42">
-        <v>46372</v>
+        <v>46366</v>
       </c>
       <c r="C65" s="42">
-        <v>46372</v>
-      </c>
-      <c r="D65" s="40"/>
-      <c r="E65" s="40"/>
-      <c r="F65" s="40"/>
+        <v>46370</v>
+      </c>
+      <c r="D65" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="E65" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F65" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G65" s="40" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="40" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B66" s="42">
-        <v>46375</v>
+        <v>46372</v>
       </c>
       <c r="C66" s="42">
-        <v>46376</v>
-      </c>
-      <c r="D66" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="E66" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="F66" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46372</v>
+      </c>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
       <c r="G66" s="40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="40" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B67" s="42">
-        <v>46381</v>
+        <v>46375</v>
       </c>
       <c r="C67" s="42">
-        <v>46381</v>
-      </c>
-      <c r="D67" s="40"/>
-      <c r="E67" s="40"/>
-      <c r="F67" s="40"/>
+        <v>46376</v>
+      </c>
+      <c r="D67" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E67" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="F67" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G67" s="40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B68" s="42">
-        <v>46382</v>
+        <v>46381</v>
       </c>
       <c r="C68" s="42">
-        <v>46382</v>
+        <v>46381</v>
       </c>
       <c r="D68" s="40"/>
       <c r="E68" s="40"/>
@@ -6166,83 +6425,77 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A69" s="41" t="s">
+    <row r="69" spans="1:7">
+      <c r="A69" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B69" s="42">
+        <v>46382</v>
+      </c>
+      <c r="C69" s="42">
+        <v>46382</v>
+      </c>
+      <c r="D69" s="40"/>
+      <c r="E69" s="40"/>
+      <c r="F69" s="40"/>
+      <c r="G69" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A70" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="B69" s="41"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="41"/>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="B70" s="42">
-        <v>46388</v>
-      </c>
-      <c r="C70" s="42">
-        <v>46388</v>
-      </c>
-      <c r="D70" s="40"/>
-      <c r="E70" s="40"/>
-      <c r="F70" s="40"/>
-      <c r="G70" s="40" t="s">
-        <v>8</v>
-      </c>
+      <c r="B70" s="41"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="41"/>
+      <c r="E70" s="41"/>
+      <c r="F70" s="41"/>
+      <c r="G70" s="41"/>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="40" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="B71" s="42">
-        <v>46395</v>
+        <v>46388</v>
       </c>
       <c r="C71" s="42">
-        <v>46396</v>
-      </c>
-      <c r="D71" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="E71" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="F71" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46388</v>
+      </c>
+      <c r="D71" s="40"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="40"/>
       <c r="G71" s="40" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B72" s="42">
-        <v>46403</v>
+        <v>46395</v>
       </c>
       <c r="C72" s="42">
-        <v>46404</v>
+        <v>46396</v>
       </c>
       <c r="D72" s="40" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="F72" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G72" s="40" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B73" s="42">
         <v>46403</v>
@@ -6251,44 +6504,44 @@
         <v>46404</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F73" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G73" s="40" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B74" s="42">
         <v>46403</v>
       </c>
       <c r="C74" s="42">
-        <v>46403</v>
+        <v>46404</v>
       </c>
       <c r="D74" s="40" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F74" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G74" s="40" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B75" s="42">
         <v>46403</v>
@@ -6297,21 +6550,21 @@
         <v>46403</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="F75" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G75" s="40" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B76" s="42">
         <v>46403</v>
@@ -6320,125 +6573,125 @@
         <v>46403</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="F76" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G76" s="40" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B77" s="42">
-        <v>46396</v>
+        <v>46403</v>
       </c>
       <c r="C77" s="42">
-        <v>46397</v>
+        <v>46403</v>
       </c>
       <c r="D77" s="40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="F77" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G77" s="40" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B78" s="42">
-        <v>46404</v>
+        <v>46396</v>
       </c>
       <c r="C78" s="42">
-        <v>46404</v>
+        <v>46397</v>
       </c>
       <c r="D78" s="40" t="s">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="F78" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G78" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="24.9" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" s="40" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B79" s="42">
-        <v>46410</v>
+        <v>46404</v>
       </c>
       <c r="C79" s="42">
-        <v>46410</v>
+        <v>46404</v>
       </c>
       <c r="D79" s="40" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F79" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G79" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="24.9" customHeight="1">
       <c r="A80" s="40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B80" s="42">
-        <v>46411</v>
+        <v>46410</v>
       </c>
       <c r="C80" s="42">
-        <v>46411</v>
+        <v>46410</v>
       </c>
       <c r="D80" s="40" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F80" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G80" s="40" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="40" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B81" s="42">
-        <v>46415</v>
+        <v>46411</v>
       </c>
       <c r="C81" s="42">
-        <v>46415</v>
+        <v>46411</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="F81" s="40" t="s">
         <v>30</v>
@@ -6449,19 +6702,19 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="40" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B82" s="42">
         <v>46415</v>
       </c>
       <c r="C82" s="42">
-        <v>46417</v>
+        <v>46415</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="F82" s="40" t="s">
         <v>30</v>
@@ -6472,19 +6725,19 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="40" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B83" s="42">
-        <v>46416</v>
+        <v>46415</v>
       </c>
       <c r="C83" s="42">
-        <v>46416</v>
+        <v>46417</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F83" s="40" t="s">
         <v>30</v>
@@ -6495,19 +6748,19 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B84" s="42">
         <v>46416</v>
       </c>
       <c r="C84" s="42">
-        <v>46417</v>
+        <v>46416</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F84" s="40" t="s">
         <v>30</v>
@@ -6516,290 +6769,290 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="17.25" customHeight="1">
+    <row r="85" spans="1:7">
       <c r="A85" s="40" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B85" s="42">
         <v>46416</v>
       </c>
       <c r="C85" s="42">
-        <v>46418</v>
+        <v>46417</v>
       </c>
       <c r="D85" s="40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="F85" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G85" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="24.9" customHeight="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="17.25" customHeight="1">
       <c r="A86" s="40" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B86" s="42">
-        <v>46417</v>
+        <v>46416</v>
       </c>
       <c r="C86" s="42">
         <v>46418</v>
       </c>
       <c r="D86" s="40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="F86" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G86" s="40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A87" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="B87" s="42">
+        <v>46417</v>
+      </c>
+      <c r="C87" s="42">
+        <v>46418</v>
+      </c>
+      <c r="D87" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="E87" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="F87" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G87" s="40" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="16.8">
-      <c r="A87" s="41" t="s">
+    <row r="88" spans="1:7" ht="16.8">
+      <c r="A88" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="B87" s="41"/>
-      <c r="C87" s="41"/>
-      <c r="D87" s="41"/>
-      <c r="E87" s="41"/>
-      <c r="F87" s="41"/>
-      <c r="G87" s="41"/>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="B88" s="42">
-        <v>46422</v>
-      </c>
-      <c r="C88" s="42">
-        <v>46422</v>
-      </c>
-      <c r="D88" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="E88" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="F88" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G88" s="40" t="s">
-        <v>5</v>
-      </c>
+      <c r="B88" s="41"/>
+      <c r="C88" s="41"/>
+      <c r="D88" s="41"/>
+      <c r="E88" s="41"/>
+      <c r="F88" s="41"/>
+      <c r="G88" s="41"/>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="40" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="B89" s="42">
         <v>46422</v>
       </c>
       <c r="C89" s="42">
-        <v>46423</v>
+        <v>46422</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="F89" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G89" s="40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="40" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="B90" s="42">
-        <v>46424</v>
+        <v>46422</v>
       </c>
       <c r="C90" s="42">
-        <v>46424</v>
+        <v>46423</v>
       </c>
       <c r="D90" s="40" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="F90" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G90" s="40" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="40" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B91" s="42">
         <v>46424</v>
       </c>
       <c r="C91" s="42">
-        <v>46425</v>
+        <v>46424</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F91" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G91" s="40" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B92" s="42">
-        <v>46431</v>
+        <v>46424</v>
       </c>
       <c r="C92" s="42">
-        <v>46431</v>
+        <v>46425</v>
       </c>
       <c r="D92" s="40" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F92" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G92" s="40" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B93" s="42">
         <v>46431</v>
       </c>
       <c r="C93" s="42">
-        <v>46432</v>
+        <v>46431</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="F93" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G93" s="40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="17.25" customHeight="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B94" s="42">
-        <v>46438</v>
+        <v>46431</v>
       </c>
       <c r="C94" s="42">
-        <v>46438</v>
+        <v>46432</v>
       </c>
       <c r="D94" s="40" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F94" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G94" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="17.25" customHeight="1">
       <c r="A95" s="40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B95" s="42">
-        <v>46445</v>
+        <v>46438</v>
       </c>
       <c r="C95" s="42">
-        <v>46446</v>
+        <v>46438</v>
       </c>
       <c r="D95" s="40" t="s">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="F95" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G95" s="40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="B96" s="42">
+        <v>46445</v>
+      </c>
+      <c r="C96" s="42">
+        <v>46446</v>
+      </c>
+      <c r="D96" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="E96" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="F96" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G96" s="40" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="16.8">
-      <c r="A96" s="41" t="s">
+    <row r="97" spans="1:7" ht="16.8">
+      <c r="A97" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="B96" s="41"/>
-      <c r="C96" s="41"/>
-      <c r="D96" s="41"/>
-      <c r="E96" s="41"/>
-      <c r="F96" s="41"/>
-      <c r="G96" s="41"/>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="B97" s="42">
-        <v>46447</v>
-      </c>
-      <c r="C97" s="42">
-        <v>46447</v>
-      </c>
-      <c r="D97" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="E97" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F97" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G97" s="40" t="s">
-        <v>5</v>
-      </c>
+      <c r="B97" s="41"/>
+      <c r="C97" s="41"/>
+      <c r="D97" s="41"/>
+      <c r="E97" s="41"/>
+      <c r="F97" s="41"/>
+      <c r="G97" s="41"/>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="40" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B98" s="42">
-        <v>46448</v>
+        <v>46447</v>
       </c>
       <c r="C98" s="42">
-        <v>46448</v>
+        <v>46447</v>
       </c>
       <c r="D98" s="40" t="s">
         <v>158</v>
@@ -6816,13 +7069,13 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B99" s="42">
-        <v>46449</v>
+        <v>46448</v>
       </c>
       <c r="C99" s="42">
-        <v>46449</v>
+        <v>46448</v>
       </c>
       <c r="D99" s="40" t="s">
         <v>158</v>
@@ -6839,13 +7092,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B100" s="42">
-        <v>46450</v>
+        <v>46449</v>
       </c>
       <c r="C100" s="42">
-        <v>46450</v>
+        <v>46449</v>
       </c>
       <c r="D100" s="40" t="s">
         <v>158</v>
@@ -6862,16 +7115,16 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B101" s="42">
-        <v>46462</v>
+        <v>46450</v>
       </c>
       <c r="C101" s="42">
-        <v>46464</v>
+        <v>46450</v>
       </c>
       <c r="D101" s="40" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E101" s="40" t="s">
         <v>47</v>
@@ -6883,32 +7136,38 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="13.2" customHeight="1">
+    <row r="102" spans="1:7">
       <c r="A102" s="40" t="s">
-        <v>19</v>
+        <v>162</v>
       </c>
       <c r="B102" s="42">
-        <v>46467</v>
+        <v>46462</v>
       </c>
       <c r="C102" s="42">
-        <v>46467</v>
-      </c>
-      <c r="D102" s="40"/>
-      <c r="E102" s="40"/>
-      <c r="F102" s="40"/>
+        <v>46464</v>
+      </c>
+      <c r="D102" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="E102" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F102" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G102" s="40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="13.2" customHeight="1">
       <c r="A103" s="40" t="s">
         <v>19</v>
       </c>
       <c r="B103" s="42">
-        <v>46468</v>
+        <v>46467</v>
       </c>
       <c r="C103" s="42">
-        <v>46468</v>
+        <v>46467</v>
       </c>
       <c r="D103" s="40"/>
       <c r="E103" s="40"/>
@@ -6917,15 +7176,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="24.9" customHeight="1">
+    <row r="104" spans="1:7">
       <c r="A104" s="40" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B104" s="42">
-        <v>46472</v>
+        <v>46468</v>
       </c>
       <c r="C104" s="42">
-        <v>46472</v>
+        <v>46468</v>
       </c>
       <c r="D104" s="40"/>
       <c r="E104" s="40"/>
@@ -6934,15 +7193,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="17.25" customHeight="1">
+    <row r="105" spans="1:7" ht="24.9" customHeight="1">
       <c r="A105" s="40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B105" s="42">
-        <v>46475</v>
+        <v>46472</v>
       </c>
       <c r="C105" s="42">
-        <v>46475</v>
+        <v>46472</v>
       </c>
       <c r="D105" s="40"/>
       <c r="E105" s="40"/>
@@ -6951,78 +7210,72 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="24.9" customHeight="1">
+    <row r="106" spans="1:7" ht="17.25" customHeight="1">
       <c r="A106" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="B106" s="42">
+        <v>46475</v>
+      </c>
+      <c r="C106" s="42">
+        <v>46475</v>
+      </c>
+      <c r="D106" s="40"/>
+      <c r="E106" s="40"/>
+      <c r="F106" s="40"/>
+      <c r="G106" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A107" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="B106" s="42">
+      <c r="B107" s="42">
         <v>46477</v>
       </c>
-      <c r="C106" s="42">
+      <c r="C107" s="42">
         <v>46477</v>
       </c>
-      <c r="D106" s="40" t="s">
+      <c r="D107" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="E106" s="40" t="s">
+      <c r="E107" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="F106" s="40" t="s">
+      <c r="F107" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G106" s="40" t="s">
+      <c r="G107" s="40" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="16.8">
-      <c r="A107" s="41" t="s">
+    <row r="108" spans="1:7" ht="16.8">
+      <c r="A108" s="41" t="s">
         <v>167</v>
       </c>
-      <c r="B107" s="41"/>
-      <c r="C107" s="41"/>
-      <c r="D107" s="41"/>
-      <c r="E107" s="41"/>
-      <c r="F107" s="41"/>
-      <c r="G107" s="41"/>
-    </row>
-    <row r="108" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A108" s="40" t="s">
+      <c r="B108" s="41"/>
+      <c r="C108" s="41"/>
+      <c r="D108" s="41"/>
+      <c r="E108" s="41"/>
+      <c r="F108" s="41"/>
+      <c r="G108" s="41"/>
+    </row>
+    <row r="109" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A109" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="B108" s="42">
+      <c r="B109" s="42">
         <v>46478</v>
       </c>
-      <c r="C108" s="42">
+      <c r="C109" s="42">
         <v>46480</v>
-      </c>
-      <c r="D108" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="E108" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="F108" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G108" s="40" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
-      <c r="A109" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="B109" s="42">
-        <v>46482</v>
-      </c>
-      <c r="C109" s="42">
-        <v>46484</v>
       </c>
       <c r="D109" s="40" t="s">
         <v>47</v>
       </c>
       <c r="E109" s="40" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F109" s="40" t="s">
         <v>30</v>
@@ -7031,21 +7284,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:7" s="44" customFormat="1">
+    <row r="110" spans="1:7">
       <c r="A110" s="40" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B110" s="42">
-        <v>46485</v>
+        <v>46482</v>
       </c>
       <c r="C110" s="42">
-        <v>46489</v>
+        <v>46484</v>
       </c>
       <c r="D110" s="40" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E110" s="40" t="s">
-        <v>47</v>
+        <v>169</v>
       </c>
       <c r="F110" s="40" t="s">
         <v>30</v>
@@ -7054,18 +7307,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" s="24" customFormat="1">
+    <row r="111" spans="1:7" s="44" customFormat="1">
       <c r="A111" s="40" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B111" s="42">
-        <v>46490</v>
+        <v>46485</v>
       </c>
       <c r="C111" s="42">
-        <v>46494</v>
+        <v>46489</v>
       </c>
       <c r="D111" s="40" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="E111" s="40" t="s">
         <v>47</v>
@@ -7077,18 +7330,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="13.2" customHeight="1">
+    <row r="112" spans="1:7" s="24" customFormat="1">
       <c r="A112" s="40" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="B112" s="42">
-        <v>46500</v>
+        <v>46490</v>
       </c>
       <c r="C112" s="42">
-        <v>46504</v>
+        <v>46494</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="E112" s="40" t="s">
         <v>47</v>
@@ -7097,175 +7350,181 @@
         <v>30</v>
       </c>
       <c r="G112" s="40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="13.2" customHeight="1">
       <c r="A113" s="40" t="s">
-        <v>23</v>
+        <v>195</v>
       </c>
       <c r="B113" s="42">
-        <v>46504</v>
+        <v>46500</v>
       </c>
       <c r="C113" s="42">
         <v>46504</v>
       </c>
-      <c r="D113" s="40"/>
-      <c r="E113" s="40"/>
-      <c r="F113" s="40"/>
+      <c r="D113" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="E113" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F113" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G113" s="40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B114" s="42">
+        <v>46504</v>
+      </c>
+      <c r="C114" s="42">
+        <v>46504</v>
+      </c>
+      <c r="D114" s="40"/>
+      <c r="E114" s="40"/>
+      <c r="F114" s="40"/>
+      <c r="G114" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A114" s="41" t="s">
+    <row r="115" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A115" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="B114" s="41"/>
-      <c r="C114" s="41"/>
-      <c r="D114" s="41"/>
-      <c r="E114" s="41"/>
-      <c r="F114" s="41"/>
-      <c r="G114" s="41"/>
-    </row>
-    <row r="115" spans="1:7">
-      <c r="A115" s="40" t="s">
+      <c r="B115" s="41"/>
+      <c r="C115" s="41"/>
+      <c r="D115" s="41"/>
+      <c r="E115" s="41"/>
+      <c r="F115" s="41"/>
+      <c r="G115" s="41"/>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="B115" s="42">
+      <c r="B116" s="42">
         <v>46508</v>
       </c>
-      <c r="C115" s="42">
+      <c r="C116" s="42">
         <v>46508</v>
       </c>
-      <c r="D115" s="40"/>
-      <c r="E115" s="40"/>
-      <c r="F115" s="40"/>
-      <c r="G115" s="40" t="s">
+      <c r="D116" s="40"/>
+      <c r="E116" s="40"/>
+      <c r="F116" s="40"/>
+      <c r="G116" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A116" s="41" t="s">
+    <row r="117" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A117" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="B116" s="41"/>
-      <c r="C116" s="41"/>
-      <c r="D116" s="41"/>
-      <c r="E116" s="41"/>
-      <c r="F116" s="41"/>
-      <c r="G116" s="41"/>
-    </row>
-    <row r="117" spans="1:7">
-      <c r="A117" s="40" t="s">
+      <c r="B117" s="41"/>
+      <c r="C117" s="41"/>
+      <c r="D117" s="41"/>
+      <c r="E117" s="41"/>
+      <c r="F117" s="41"/>
+      <c r="G117" s="41"/>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B117" s="42">
+      <c r="B118" s="42">
         <v>46554</v>
       </c>
-      <c r="C117" s="42">
+      <c r="C118" s="42">
         <v>46554</v>
       </c>
-      <c r="D117" s="40"/>
-      <c r="E117" s="40"/>
-      <c r="F117" s="40"/>
-      <c r="G117" s="40" t="s">
+      <c r="D118" s="40"/>
+      <c r="E118" s="40"/>
+      <c r="F118" s="40"/>
+      <c r="G118" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A118" s="41" t="s">
+    <row r="119" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A119" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="B118" s="41"/>
-      <c r="C118" s="41"/>
-      <c r="D118" s="41"/>
-      <c r="E118" s="41"/>
-      <c r="F118" s="41"/>
-      <c r="G118" s="41"/>
-    </row>
-    <row r="119" spans="1:7">
-      <c r="A119" s="40" t="s">
+      <c r="B119" s="41"/>
+      <c r="C119" s="41"/>
+      <c r="D119" s="41"/>
+      <c r="E119" s="41"/>
+      <c r="F119" s="41"/>
+      <c r="G119" s="41"/>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B119" s="42">
+      <c r="B120" s="42">
         <v>46608</v>
       </c>
-      <c r="C119" s="42">
+      <c r="C120" s="42">
         <v>46608</v>
       </c>
-      <c r="D119" s="40"/>
-      <c r="E119" s="40"/>
-      <c r="F119" s="40"/>
-      <c r="G119" s="40" t="s">
+      <c r="D120" s="40"/>
+      <c r="E120" s="40"/>
+      <c r="F120" s="40"/>
+      <c r="G120" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A120" s="41" t="s">
+    <row r="121" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A121" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="B120" s="41"/>
-      <c r="C120" s="41"/>
-      <c r="D120" s="41"/>
-      <c r="E120" s="41"/>
-      <c r="F120" s="41"/>
-      <c r="G120" s="41"/>
-    </row>
-    <row r="121" spans="1:7">
-      <c r="A121" s="40" t="s">
+      <c r="B121" s="41"/>
+      <c r="C121" s="41"/>
+      <c r="D121" s="41"/>
+      <c r="E121" s="41"/>
+      <c r="F121" s="41"/>
+      <c r="G121" s="41"/>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="B121" s="42">
+      <c r="B122" s="42">
         <v>46654</v>
       </c>
-      <c r="C121" s="42">
+      <c r="C122" s="42">
         <v>46654</v>
       </c>
-      <c r="D121" s="40"/>
-      <c r="E121" s="40"/>
-      <c r="F121" s="40"/>
-      <c r="G121" s="40" t="s">
+      <c r="D122" s="40"/>
+      <c r="E122" s="40"/>
+      <c r="F122" s="40"/>
+      <c r="G122" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="16.8">
-      <c r="A122" s="41" t="s">
+    <row r="123" spans="1:7" ht="16.8">
+      <c r="A123" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="B122" s="41"/>
-      <c r="C122" s="41"/>
-      <c r="D122" s="41"/>
-      <c r="E122" s="41"/>
-      <c r="F122" s="41"/>
-      <c r="G122" s="41"/>
-    </row>
-    <row r="123" spans="1:7">
-      <c r="A123" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="B123" s="42">
-        <v>46737</v>
-      </c>
-      <c r="C123" s="42">
-        <v>46737</v>
-      </c>
-      <c r="D123" s="40"/>
-      <c r="E123" s="40"/>
-      <c r="F123" s="40"/>
-      <c r="G123" s="40" t="s">
-        <v>8</v>
-      </c>
+      <c r="B123" s="41"/>
+      <c r="C123" s="41"/>
+      <c r="D123" s="41"/>
+      <c r="E123" s="41"/>
+      <c r="F123" s="41"/>
+      <c r="G123" s="41"/>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B124" s="42">
-        <v>46746</v>
+        <v>46737</v>
       </c>
       <c r="C124" s="42">
-        <v>46746</v>
+        <v>46737</v>
       </c>
       <c r="D124" s="40"/>
       <c r="E124" s="40"/>
@@ -7276,13 +7535,13 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B125" s="42">
-        <v>46747</v>
+        <v>46746</v>
       </c>
       <c r="C125" s="42">
-        <v>46747</v>
+        <v>46746</v>
       </c>
       <c r="D125" s="40"/>
       <c r="E125" s="40"/>
@@ -7296,10 +7555,10 @@
         <v>111</v>
       </c>
       <c r="B126" s="42">
-        <v>46748</v>
+        <v>46747</v>
       </c>
       <c r="C126" s="42">
-        <v>46748</v>
+        <v>46747</v>
       </c>
       <c r="D126" s="40"/>
       <c r="E126" s="40"/>
@@ -7308,35 +7567,121 @@
         <v>8</v>
       </c>
     </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B127" s="42">
+        <v>46748</v>
+      </c>
+      <c r="C127" s="42">
+        <v>46748</v>
+      </c>
+      <c r="D127" s="40"/>
+      <c r="E127" s="40"/>
+      <c r="F127" s="40"/>
+      <c r="G127" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A10:G126">
-    <cfRule type="expression" dxfId="6" priority="8">
+  <conditionalFormatting sqref="A10:G35 A38:G127 A36:D36 G36:G37 E36:E37">
+    <cfRule type="expression" dxfId="41" priority="29">
       <formula>$G10="National gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="9">
+    <cfRule type="expression" dxfId="40" priority="30">
       <formula>$G10="Provincial gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="10">
+    <cfRule type="expression" dxfId="39" priority="31">
       <formula>$G10="District gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="11">
+    <cfRule type="expression" dxfId="38" priority="32">
       <formula>$G10="Schools gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="12">
+    <cfRule type="expression" dxfId="37" priority="33">
       <formula>$G10="Club gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="13">
+    <cfRule type="expression" dxfId="36" priority="34">
       <formula>$G10="Open Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="35" priority="35">
       <formula>$G10="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A37:D37">
+    <cfRule type="expression" dxfId="34" priority="15">
+      <formula>$G37="National gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="16">
+      <formula>$G37="Provincial gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="17">
+      <formula>$G37="District gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="18">
+      <formula>$G37="Schools gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="19">
+      <formula>$G37="Club gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="20">
+      <formula>$G37="Open Water"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="21">
+      <formula>$G37="Public Holiday"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F36">
+    <cfRule type="expression" dxfId="27" priority="8">
+      <formula>$G36="National gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="9">
+      <formula>$G36="Provincial gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="10">
+      <formula>$G36="District gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="11">
+      <formula>$G36="Schools gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="12">
+      <formula>$G36="Club gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="13">
+      <formula>$G36="Open Water"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="14">
+      <formula>$G36="Public Holiday"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F37">
+    <cfRule type="expression" dxfId="13" priority="1">
+      <formula>$G37="National gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="2">
+      <formula>$G37="Provincial gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>$G37="District gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="4">
+      <formula>$G37="Schools gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="5">
+      <formula>$G37="Club gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="6">
+      <formula>$G37="Open Water"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="7">
+      <formula>$G37="Public Holiday"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G63 G64:G202">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G203">
       <formula1>"Club gala,District gala,Provincial gala,National gala,Open Water,Schools gala,Public Holiday"</formula1>
     </dataValidation>
   </dataValidations>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="201">
   <si>
     <t>KZNA Calendar Season 2026–2027</t>
   </si>
@@ -629,6 +629,9 @@
   </si>
   <si>
     <t>Prestige SC Championships</t>
+  </si>
+  <si>
+    <t>SSA National Gala</t>
   </si>
 </sst>
 </file>
@@ -652,7 +655,7 @@
     <numFmt numFmtId="177" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -808,6 +811,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -941,7 +952,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1056,14 +1067,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="26" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="datetime" xfId="1"/>
@@ -1071,133 +1085,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="pro_day_only_🏊UnsanctionedCalendar" xfId="3"/>
   </cellStyles>
-  <dxfs count="49">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9F1239"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFC026D3"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF15803D"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFA16207"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7E22CE"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF0369A1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFEA580C"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9F1239"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFC026D3"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF15803D"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFA16207"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7E22CE"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF0369A1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFEA580C"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9F1239"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFC026D3"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF15803D"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFA16207"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7E22CE"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF0369A1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFEA580C"/>
-      </font>
-    </dxf>
+  <dxfs count="28">
     <dxf>
       <font>
         <b/>
@@ -1394,7 +1282,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1439,7 +1327,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1785,7 +1673,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="48" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="47"/>
@@ -1803,7 +1691,7 @@
       <c r="G2" s="47"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="46" t="s">
         <v>176</v>
       </c>
       <c r="B5" s="47"/>
@@ -2077,7 +1965,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="48" t="s">
+      <c r="A18" s="46" t="s">
         <v>184</v>
       </c>
       <c r="B18" s="47"/>
@@ -2356,7 +2244,7 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="48" t="s">
+      <c r="A31" s="46" t="s">
         <v>185</v>
       </c>
       <c r="B31" s="47"/>
@@ -2653,7 +2541,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="48" t="s">
+      <c r="A46" s="46" t="s">
         <v>186</v>
       </c>
       <c r="B46" s="47"/>
@@ -2927,7 +2815,7 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="48" t="s">
+      <c r="A59" s="46" t="s">
         <v>187</v>
       </c>
       <c r="B59" s="47"/>
@@ -3206,7 +3094,7 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="48" t="s">
+      <c r="A72" s="46" t="s">
         <v>188</v>
       </c>
       <c r="B72" s="47"/>
@@ -3498,7 +3386,7 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="48" t="s">
+      <c r="A87" s="46" t="s">
         <v>189</v>
       </c>
       <c r="B87" s="47"/>
@@ -3777,7 +3665,7 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="48" t="s">
+      <c r="A100" s="46" t="s">
         <v>190</v>
       </c>
       <c r="B100" s="47"/>
@@ -4056,7 +3944,7 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="48" t="s">
+      <c r="A113" s="46" t="s">
         <v>191</v>
       </c>
       <c r="B113" s="47"/>
@@ -4302,7 +4190,7 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="48" t="s">
+      <c r="A124" s="46" t="s">
         <v>192</v>
       </c>
       <c r="B124" s="47"/>
@@ -4581,7 +4469,7 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="48" t="s">
+      <c r="A137" s="46" t="s">
         <v>193</v>
       </c>
       <c r="B137" s="47"/>
@@ -4855,7 +4743,7 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="48" t="s">
+      <c r="A150" s="46" t="s">
         <v>194</v>
       </c>
       <c r="B150" s="47"/>
@@ -5153,12 +5041,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -5167,6 +5049,12 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5187,7 +5075,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="48" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="47"/>
@@ -7136,27 +7024,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
-      <c r="A102" s="40" t="s">
+    <row r="102" spans="1:7" s="52" customFormat="1">
+      <c r="A102" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="B102" s="42">
+      <c r="B102" s="51">
         <v>46462</v>
       </c>
-      <c r="C102" s="42">
+      <c r="C102" s="51">
         <v>46464</v>
       </c>
-      <c r="D102" s="40" t="s">
+      <c r="D102" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="E102" s="40" t="s">
+      <c r="E102" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="F102" s="40" t="s">
+      <c r="F102" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="G102" s="40" t="s">
-        <v>5</v>
+      <c r="G102" s="50" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="13.2" customHeight="1">
@@ -7335,10 +7223,10 @@
         <v>170</v>
       </c>
       <c r="B112" s="42">
-        <v>46490</v>
+        <v>46491</v>
       </c>
       <c r="C112" s="42">
-        <v>46494</v>
+        <v>46495</v>
       </c>
       <c r="D112" s="40" t="s">
         <v>163</v>
@@ -7589,94 +7477,94 @@
     <mergeCell ref="B1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="A10:G35 A38:G127 A36:D36 G36:G37 E36:E37">
-    <cfRule type="expression" dxfId="41" priority="29">
+    <cfRule type="expression" dxfId="27" priority="29">
       <formula>$G10="National gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="30">
+    <cfRule type="expression" dxfId="26" priority="30">
       <formula>$G10="Provincial gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="31">
+    <cfRule type="expression" dxfId="25" priority="31">
       <formula>$G10="District gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="32">
+    <cfRule type="expression" dxfId="24" priority="32">
       <formula>$G10="Schools gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="33">
+    <cfRule type="expression" dxfId="23" priority="33">
       <formula>$G10="Club gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="34">
+    <cfRule type="expression" dxfId="22" priority="34">
       <formula>$G10="Open Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="35">
+    <cfRule type="expression" dxfId="21" priority="35">
       <formula>$G10="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:D37">
-    <cfRule type="expression" dxfId="34" priority="15">
+    <cfRule type="expression" dxfId="20" priority="15">
       <formula>$G37="National gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="16">
+    <cfRule type="expression" dxfId="19" priority="16">
       <formula>$G37="Provincial gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="17">
+    <cfRule type="expression" dxfId="18" priority="17">
       <formula>$G37="District gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="18">
+    <cfRule type="expression" dxfId="17" priority="18">
       <formula>$G37="Schools gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="19">
+    <cfRule type="expression" dxfId="16" priority="19">
       <formula>$G37="Club gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="20">
+    <cfRule type="expression" dxfId="15" priority="20">
       <formula>$G37="Open Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="21">
+    <cfRule type="expression" dxfId="14" priority="21">
       <formula>$G37="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36">
-    <cfRule type="expression" dxfId="27" priority="8">
+    <cfRule type="expression" dxfId="13" priority="8">
       <formula>$G36="National gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="9">
+    <cfRule type="expression" dxfId="12" priority="9">
       <formula>$G36="Provincial gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="10">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>$G36="District gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$G36="Schools gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="12">
+    <cfRule type="expression" dxfId="9" priority="12">
       <formula>$G36="Club gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="13">
+    <cfRule type="expression" dxfId="8" priority="13">
       <formula>$G36="Open Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="14">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>$G36="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F37">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>$G37="National gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>$G37="Provincial gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>$G37="District gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$G37="Schools gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>$G37="Club gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="6">
+    <cfRule type="expression" dxfId="1" priority="6">
       <formula>$G37="Open Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>$G37="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7689,9 +7577,10 @@
     <hyperlink ref="E2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -1067,17 +1067,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="26" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="26" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="datetime" xfId="1"/>
@@ -1282,7 +1282,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1327,7 +1327,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1673,33 +1673,33 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" spans="1:7" ht="24.9" customHeight="1">
-      <c r="B2" s="49"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
@@ -1965,15 +1965,15 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="51" t="s">
         <v>184</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
@@ -2244,15 +2244,15 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="B31" s="47"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
@@ -2541,15 +2541,15 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="46" t="s">
+      <c r="A46" s="51" t="s">
         <v>186</v>
       </c>
-      <c r="B46" s="47"/>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="47"/>
+      <c r="B46" s="50"/>
+      <c r="C46" s="50"/>
+      <c r="D46" s="50"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="50"/>
+      <c r="G46" s="50"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
@@ -2815,15 +2815,15 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="46" t="s">
+      <c r="A59" s="51" t="s">
         <v>187</v>
       </c>
-      <c r="B59" s="47"/>
-      <c r="C59" s="47"/>
-      <c r="D59" s="47"/>
-      <c r="E59" s="47"/>
-      <c r="F59" s="47"/>
-      <c r="G59" s="47"/>
+      <c r="B59" s="50"/>
+      <c r="C59" s="50"/>
+      <c r="D59" s="50"/>
+      <c r="E59" s="50"/>
+      <c r="F59" s="50"/>
+      <c r="G59" s="50"/>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
@@ -3094,15 +3094,15 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="46" t="s">
+      <c r="A72" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="B72" s="47"/>
-      <c r="C72" s="47"/>
-      <c r="D72" s="47"/>
-      <c r="E72" s="47"/>
-      <c r="F72" s="47"/>
-      <c r="G72" s="47"/>
+      <c r="B72" s="50"/>
+      <c r="C72" s="50"/>
+      <c r="D72" s="50"/>
+      <c r="E72" s="50"/>
+      <c r="F72" s="50"/>
+      <c r="G72" s="50"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
@@ -3386,15 +3386,15 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="46" t="s">
+      <c r="A87" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="B87" s="47"/>
-      <c r="C87" s="47"/>
-      <c r="D87" s="47"/>
-      <c r="E87" s="47"/>
-      <c r="F87" s="47"/>
-      <c r="G87" s="47"/>
+      <c r="B87" s="50"/>
+      <c r="C87" s="50"/>
+      <c r="D87" s="50"/>
+      <c r="E87" s="50"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50"/>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
@@ -3665,15 +3665,15 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="46" t="s">
+      <c r="A100" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="B100" s="47"/>
-      <c r="C100" s="47"/>
-      <c r="D100" s="47"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="47"/>
-      <c r="G100" s="47"/>
+      <c r="B100" s="50"/>
+      <c r="C100" s="50"/>
+      <c r="D100" s="50"/>
+      <c r="E100" s="50"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
@@ -3944,15 +3944,15 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="46" t="s">
+      <c r="A113" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="B113" s="47"/>
-      <c r="C113" s="47"/>
-      <c r="D113" s="47"/>
-      <c r="E113" s="47"/>
-      <c r="F113" s="47"/>
-      <c r="G113" s="47"/>
+      <c r="B113" s="50"/>
+      <c r="C113" s="50"/>
+      <c r="D113" s="50"/>
+      <c r="E113" s="50"/>
+      <c r="F113" s="50"/>
+      <c r="G113" s="50"/>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
@@ -4190,15 +4190,15 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="46" t="s">
+      <c r="A124" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="B124" s="47"/>
-      <c r="C124" s="47"/>
-      <c r="D124" s="47"/>
-      <c r="E124" s="47"/>
-      <c r="F124" s="47"/>
-      <c r="G124" s="47"/>
+      <c r="B124" s="50"/>
+      <c r="C124" s="50"/>
+      <c r="D124" s="50"/>
+      <c r="E124" s="50"/>
+      <c r="F124" s="50"/>
+      <c r="G124" s="50"/>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
@@ -4469,15 +4469,15 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="46" t="s">
+      <c r="A137" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="B137" s="47"/>
-      <c r="C137" s="47"/>
-      <c r="D137" s="47"/>
-      <c r="E137" s="47"/>
-      <c r="F137" s="47"/>
-      <c r="G137" s="47"/>
+      <c r="B137" s="50"/>
+      <c r="C137" s="50"/>
+      <c r="D137" s="50"/>
+      <c r="E137" s="50"/>
+      <c r="F137" s="50"/>
+      <c r="G137" s="50"/>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
@@ -4743,15 +4743,15 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="46" t="s">
+      <c r="A150" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="B150" s="47"/>
-      <c r="C150" s="47"/>
-      <c r="D150" s="47"/>
-      <c r="E150" s="47"/>
-      <c r="F150" s="47"/>
-      <c r="G150" s="47"/>
+      <c r="B150" s="50"/>
+      <c r="C150" s="50"/>
+      <c r="D150" s="50"/>
+      <c r="E150" s="50"/>
+      <c r="F150" s="50"/>
+      <c r="G150" s="50"/>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2" t="s">
@@ -5041,6 +5041,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -5049,12 +5055,6 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5075,13 +5075,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
       <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7" ht="24.9" customHeight="1">
@@ -7024,26 +7024,26 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:7" s="52" customFormat="1">
-      <c r="A102" s="50" t="s">
+    <row r="102" spans="1:7" s="48" customFormat="1">
+      <c r="A102" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="B102" s="51">
-        <v>46462</v>
-      </c>
-      <c r="C102" s="51">
-        <v>46464</v>
-      </c>
-      <c r="D102" s="50" t="s">
+      <c r="B102" s="47">
+        <v>46466</v>
+      </c>
+      <c r="C102" s="47">
+        <v>46468</v>
+      </c>
+      <c r="D102" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="E102" s="50" t="s">
+      <c r="E102" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F102" s="50" t="s">
+      <c r="F102" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="G102" s="50" t="s">
+      <c r="G102" s="46" t="s">
         <v>200</v>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A10:G35 A38:G127 A36:D36 G36:G37 E36:E37">
+  <conditionalFormatting sqref="A10:G35 A36:D36 G36:G37 E36:E37 A38:G127">
     <cfRule type="expression" dxfId="27" priority="29">
       <formula>$G10="National gala"</formula>
     </cfRule>

--- a/KZN Calendar 05 May 2026 -2026_2027.xlsx
+++ b/KZN Calendar 05 May 2026 -2026_2027.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="206">
   <si>
     <t>KZNA Calendar Season 2026–2027</t>
   </si>
@@ -632,6 +632,21 @@
   </si>
   <si>
     <t>SSA National Gala</t>
+  </si>
+  <si>
+    <t>Grand Prix 1</t>
+  </si>
+  <si>
+    <t>07/08/2026</t>
+  </si>
+  <si>
+    <t>09/08/2026</t>
+  </si>
+  <si>
+    <t>National Gala</t>
+  </si>
+  <si>
+    <t>Jolliffe Swimming Pool </t>
   </si>
 </sst>
 </file>
@@ -655,7 +670,7 @@
     <numFmt numFmtId="177" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -819,8 +834,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6B7280"/>
+      <name val="Karla"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -856,6 +891,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF3B82F6"/>
         <bgColor rgb="FF3B82F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -952,7 +993,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1070,14 +1111,22 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="26" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="datetime" xfId="1"/>
@@ -1282,7 +1331,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1327,7 +1376,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1362,8 +1411,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G127">
-  <autoFilter ref="A9:G127"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A9:G128">
+  <autoFilter ref="A9:G128"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Event Name"/>
     <tableColumn id="2" name="Start Date"/>
@@ -1673,7 +1722,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="50"/>
@@ -1691,7 +1740,7 @@
       <c r="G2" s="50"/>
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="49" t="s">
         <v>176</v>
       </c>
       <c r="B5" s="50"/>
@@ -1965,7 +2014,7 @@
       <c r="G16" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="49" t="s">
         <v>184</v>
       </c>
       <c r="B18" s="50"/>
@@ -2244,7 +2293,7 @@
       <c r="G29" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A31" s="51" t="s">
+      <c r="A31" s="49" t="s">
         <v>185</v>
       </c>
       <c r="B31" s="50"/>
@@ -2541,7 +2590,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A46" s="51" t="s">
+      <c r="A46" s="49" t="s">
         <v>186</v>
       </c>
       <c r="B46" s="50"/>
@@ -2815,7 +2864,7 @@
       <c r="G57" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A59" s="51" t="s">
+      <c r="A59" s="49" t="s">
         <v>187</v>
       </c>
       <c r="B59" s="50"/>
@@ -3094,7 +3143,7 @@
       <c r="G70" s="11"/>
     </row>
     <row r="72" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A72" s="51" t="s">
+      <c r="A72" s="49" t="s">
         <v>188</v>
       </c>
       <c r="B72" s="50"/>
@@ -3386,7 +3435,7 @@
       <c r="G85" s="11"/>
     </row>
     <row r="87" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A87" s="51" t="s">
+      <c r="A87" s="49" t="s">
         <v>189</v>
       </c>
       <c r="B87" s="50"/>
@@ -3665,7 +3714,7 @@
       <c r="G98" s="11"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A100" s="51" t="s">
+      <c r="A100" s="49" t="s">
         <v>190</v>
       </c>
       <c r="B100" s="50"/>
@@ -3944,7 +3993,7 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A113" s="51" t="s">
+      <c r="A113" s="49" t="s">
         <v>191</v>
       </c>
       <c r="B113" s="50"/>
@@ -4190,7 +4239,7 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A124" s="51" t="s">
+      <c r="A124" s="49" t="s">
         <v>192</v>
       </c>
       <c r="B124" s="50"/>
@@ -4469,7 +4518,7 @@
       <c r="G135" s="11"/>
     </row>
     <row r="137" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A137" s="51" t="s">
+      <c r="A137" s="49" t="s">
         <v>193</v>
       </c>
       <c r="B137" s="50"/>
@@ -4743,7 +4792,7 @@
       <c r="G148" s="11"/>
     </row>
     <row r="150" spans="1:7" ht="35.1" customHeight="1">
-      <c r="A150" s="51" t="s">
+      <c r="A150" s="49" t="s">
         <v>194</v>
       </c>
       <c r="B150" s="50"/>
@@ -5041,12 +5090,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A137:G137"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A72:G72"/>
@@ -5055,6 +5098,12 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A137:G137"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5063,7 +5112,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -5075,7 +5124,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1">
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="50"/>
@@ -5554,44 +5603,50 @@
       <c r="F31" s="41"/>
       <c r="G31" s="41"/>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="42">
-        <v>46242</v>
-      </c>
-      <c r="C32" s="42">
-        <v>46243</v>
-      </c>
-      <c r="D32" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E32" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="40" t="s">
+    <row r="32" spans="1:7" s="54" customFormat="1" ht="16.8" customHeight="1">
+      <c r="A32" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="B32" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="C32" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="G32" s="40" t="s">
-        <v>6</v>
+      <c r="G32" s="53" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B33" s="42">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="C33" s="42">
         <v>46243</v>
       </c>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
+      <c r="D33" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G33" s="40" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -5599,10 +5654,10 @@
         <v>50</v>
       </c>
       <c r="B34" s="42">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="C34" s="42">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="D34" s="40"/>
       <c r="E34" s="40"/>
@@ -5613,59 +5668,53 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B35" s="42">
-        <v>46249</v>
+        <v>46244</v>
       </c>
       <c r="C35" s="42">
-        <v>46249</v>
-      </c>
-      <c r="D35" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="E35" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46244</v>
+      </c>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
       <c r="G35" s="40" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B36" s="42">
         <v>46249</v>
       </c>
       <c r="C36" s="42">
-        <v>46250</v>
+        <v>46249</v>
       </c>
       <c r="D36" s="40" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>197</v>
+        <v>43</v>
       </c>
       <c r="F36" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G36" s="40" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" s="45" customFormat="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="40" t="s">
         <v>53</v>
       </c>
       <c r="B37" s="42">
-        <v>46256</v>
+        <v>46249</v>
       </c>
       <c r="C37" s="42">
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="D37" s="40" t="s">
         <v>54</v>
@@ -5680,101 +5729,101 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" s="45" customFormat="1">
       <c r="A38" s="40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B38" s="42">
-        <v>46277</v>
+        <v>46256</v>
       </c>
       <c r="C38" s="42">
-        <v>46278</v>
+        <v>46257</v>
       </c>
       <c r="D38" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E38" s="40" t="s">
-        <v>57</v>
+        <v>197</v>
       </c>
       <c r="F38" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G38" s="40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="42">
+        <v>46277</v>
+      </c>
+      <c r="C39" s="42">
+        <v>46278</v>
+      </c>
+      <c r="D39" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="F39" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G39" s="40" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A39" s="41" t="s">
+    <row r="40" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A40" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="B39" s="41"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-    </row>
-    <row r="40" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A40" s="40" t="s">
+      <c r="B40" s="41"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="41"/>
+    </row>
+    <row r="41" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A41" s="40" t="s">
         <v>59</v>
-      </c>
-      <c r="B40" s="42">
-        <v>46270</v>
-      </c>
-      <c r="C40" s="42">
-        <v>46270</v>
-      </c>
-      <c r="D40" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="E40" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="F40" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G40" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="40" t="s">
-        <v>62</v>
       </c>
       <c r="B41" s="42">
         <v>46270</v>
       </c>
       <c r="C41" s="42">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F41" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G41" s="40" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B42" s="42">
-        <v>46285</v>
+        <v>46270</v>
       </c>
       <c r="C42" s="42">
-        <v>46285</v>
+        <v>46271</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F42" s="40" t="s">
         <v>30</v>
@@ -5785,105 +5834,82 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="40" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B43" s="42">
-        <v>46289</v>
+        <v>46285</v>
       </c>
       <c r="C43" s="42">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F43" s="40" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G43" s="40" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B44" s="42">
         <v>46289</v>
       </c>
       <c r="C44" s="42">
-        <v>46289</v>
-      </c>
-      <c r="D44" s="40"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="40"/>
+        <v>46292</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="F44" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G44" s="40" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B45" s="42">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="C45" s="42">
-        <v>46292</v>
-      </c>
-      <c r="D45" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="E45" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="F45" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
       <c r="G45" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="B46" s="42">
-        <v>46291</v>
-      </c>
-      <c r="C46" s="42">
-        <v>46291</v>
-      </c>
-      <c r="D46" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="E46" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="F46" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G46" s="40" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="40" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B47" s="42">
         <v>46291</v>
       </c>
       <c r="C47" s="42">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="D47" s="40" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="F47" s="40" t="s">
         <v>30</v>
@@ -5892,25 +5918,39 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A48" s="41" t="s">
+    <row r="48" spans="1:7">
+      <c r="A48" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" s="42">
+        <v>46291</v>
+      </c>
+      <c r="C48" s="42">
+        <v>46293</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" s="40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A49" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="41"/>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="40"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="42"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="40"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="40" t="s">
@@ -6063,265 +6103,271 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="40" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="B57" s="42">
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="C57" s="42">
-        <v>46333</v>
+        <v>46334</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F57" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G57" s="40" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B58" s="42">
-        <v>46340</v>
+        <v>46333</v>
       </c>
       <c r="C58" s="42">
-        <v>46341</v>
+        <v>46333</v>
       </c>
       <c r="D58" s="40" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="F58" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G58" s="40" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="40" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B59" s="42">
-        <v>46347</v>
+        <v>46340</v>
       </c>
       <c r="C59" s="42">
-        <v>46347</v>
+        <v>46341</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F59" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G59" s="40" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="40" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B60" s="42">
         <v>46347</v>
       </c>
       <c r="C60" s="42">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F60" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G60" s="40" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="40" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B61" s="42">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="C61" s="42">
-        <v>46355</v>
+        <v>46348</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F61" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G61" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="24.9" customHeight="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" s="40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B62" s="42">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="C62" s="42">
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F62" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G62" s="40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A63" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63" s="42">
+        <v>46354</v>
+      </c>
+      <c r="C63" s="42">
+        <v>46354</v>
+      </c>
+      <c r="D63" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="E63" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="F63" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G63" s="40" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A63" s="41" t="s">
+    <row r="64" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A64" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="B63" s="41"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="41"/>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="B64" s="42">
-        <v>46360</v>
-      </c>
-      <c r="C64" s="42">
-        <v>46361</v>
-      </c>
-      <c r="D64" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="E64" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="F64" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G64" s="40" t="s">
-        <v>6</v>
-      </c>
+      <c r="B64" s="41"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="41"/>
+      <c r="G64" s="41"/>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="40" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B65" s="42">
-        <v>46366</v>
+        <v>46360</v>
       </c>
       <c r="C65" s="42">
-        <v>46370</v>
+        <v>46361</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F65" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G65" s="40" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B66" s="42">
-        <v>46372</v>
+        <v>46366</v>
       </c>
       <c r="C66" s="42">
-        <v>46372</v>
-      </c>
-      <c r="D66" s="40"/>
-      <c r="E66" s="40"/>
-      <c r="F66" s="40"/>
+        <v>46370</v>
+      </c>
+      <c r="D66" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="E66" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F66" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G66" s="40" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="40" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B67" s="42">
-        <v>46375</v>
+        <v>46372</v>
       </c>
       <c r="C67" s="42">
-        <v>46376</v>
-      </c>
-      <c r="D67" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="E67" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="F67" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46372</v>
+      </c>
+      <c r="D67" s="40"/>
+      <c r="E67" s="40"/>
+      <c r="F67" s="40"/>
       <c r="G67" s="40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="40" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B68" s="42">
-        <v>46381</v>
+        <v>46375</v>
       </c>
       <c r="C68" s="42">
-        <v>46381</v>
-      </c>
-      <c r="D68" s="40"/>
-      <c r="E68" s="40"/>
-      <c r="F68" s="40"/>
+        <v>46376</v>
+      </c>
+      <c r="D68" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E68" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="F68" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G68" s="40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B69" s="42">
-        <v>46382</v>
+        <v>46381</v>
       </c>
       <c r="C69" s="42">
-        <v>46382</v>
+        <v>46381</v>
       </c>
       <c r="D69" s="40"/>
       <c r="E69" s="40"/>
@@ -6330,83 +6376,77 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A70" s="41" t="s">
+    <row r="70" spans="1:7">
+      <c r="A70" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B70" s="42">
+        <v>46382</v>
+      </c>
+      <c r="C70" s="42">
+        <v>46382</v>
+      </c>
+      <c r="D70" s="40"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A71" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="B70" s="41"/>
-      <c r="C70" s="41"/>
-      <c r="D70" s="41"/>
-      <c r="E70" s="41"/>
-      <c r="F70" s="41"/>
-      <c r="G70" s="41"/>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="B71" s="42">
-        <v>46388</v>
-      </c>
-      <c r="C71" s="42">
-        <v>46388</v>
-      </c>
-      <c r="D71" s="40"/>
-      <c r="E71" s="40"/>
-      <c r="F71" s="40"/>
-      <c r="G71" s="40" t="s">
-        <v>8</v>
-      </c>
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="41"/>
+      <c r="F71" s="41"/>
+      <c r="G71" s="41"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="40" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="B72" s="42">
-        <v>46395</v>
+        <v>46388</v>
       </c>
       <c r="C72" s="42">
-        <v>46396</v>
-      </c>
-      <c r="D72" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="E72" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="F72" s="40" t="s">
-        <v>30</v>
-      </c>
+        <v>46388</v>
+      </c>
+      <c r="D72" s="40"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="40"/>
       <c r="G72" s="40" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B73" s="42">
-        <v>46403</v>
+        <v>46395</v>
       </c>
       <c r="C73" s="42">
-        <v>46404</v>
+        <v>46396</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="F73" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G73" s="40" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B74" s="42">
         <v>46403</v>
@@ -6415,44 +6455,44 @@
         <v>46404</v>
       </c>
       <c r="D74" s="40" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F74" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G74" s="40" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B75" s="42">
         <v>46403</v>
       </c>
       <c r="C75" s="42">
-        <v>46403</v>
+        <v>46404</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F75" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G75" s="40" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B76" s="42">
         <v>46403</v>
@@ -6461,21 +6501,21 @@
         <v>46403</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="F76" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G76" s="40" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B77" s="42">
         <v>46403</v>
@@ -6484,125 +6524,125 @@
         <v>46403</v>
       </c>
       <c r="D77" s="40" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="F77" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G77" s="40" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B78" s="42">
-        <v>46396</v>
+        <v>46403</v>
       </c>
       <c r="C78" s="42">
-        <v>46397</v>
+        <v>46403</v>
       </c>
       <c r="D78" s="40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="F78" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G78" s="40" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B79" s="42">
-        <v>46404</v>
+        <v>46396</v>
       </c>
       <c r="C79" s="42">
-        <v>46404</v>
+        <v>46397</v>
       </c>
       <c r="D79" s="40" t="s">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="F79" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G79" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="24.9" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" s="40" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B80" s="42">
-        <v>46410</v>
+        <v>46404</v>
       </c>
       <c r="C80" s="42">
-        <v>46410</v>
+        <v>46404</v>
       </c>
       <c r="D80" s="40" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F80" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G80" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="24.9" customHeight="1">
       <c r="A81" s="40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B81" s="42">
-        <v>46411</v>
+        <v>46410</v>
       </c>
       <c r="C81" s="42">
-        <v>46411</v>
+        <v>46410</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F81" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G81" s="40" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="40" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B82" s="42">
-        <v>46415</v>
+        <v>46411</v>
       </c>
       <c r="C82" s="42">
-        <v>46415</v>
+        <v>46411</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="F82" s="40" t="s">
         <v>30</v>
@@ -6613,19 +6653,19 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="40" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B83" s="42">
         <v>46415</v>
       </c>
       <c r="C83" s="42">
-        <v>46417</v>
+        <v>46415</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="F83" s="40" t="s">
         <v>30</v>
@@ -6636,19 +6676,19 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="40" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B84" s="42">
-        <v>46416</v>
+        <v>46415</v>
       </c>
       <c r="C84" s="42">
-        <v>46416</v>
+        <v>46417</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F84" s="40" t="s">
         <v>30</v>
@@ -6659,19 +6699,19 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B85" s="42">
         <v>46416</v>
       </c>
       <c r="C85" s="42">
-        <v>46417</v>
+        <v>46416</v>
       </c>
       <c r="D85" s="40" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F85" s="40" t="s">
         <v>30</v>
@@ -6680,290 +6720,290 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="17.25" customHeight="1">
+    <row r="86" spans="1:7">
       <c r="A86" s="40" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B86" s="42">
         <v>46416</v>
       </c>
       <c r="C86" s="42">
-        <v>46418</v>
+        <v>46417</v>
       </c>
       <c r="D86" s="40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="F86" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G86" s="40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="24.9" customHeight="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="17.25" customHeight="1">
       <c r="A87" s="40" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B87" s="42">
-        <v>46417</v>
+        <v>46416</v>
       </c>
       <c r="C87" s="42">
         <v>46418</v>
       </c>
       <c r="D87" s="40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="F87" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G87" s="40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A88" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="B88" s="42">
+        <v>46417</v>
+      </c>
+      <c r="C88" s="42">
+        <v>46418</v>
+      </c>
+      <c r="D88" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="E88" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="F88" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G88" s="40" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="16.8">
-      <c r="A88" s="41" t="s">
+    <row r="89" spans="1:7" ht="16.8">
+      <c r="A89" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="B88" s="41"/>
-      <c r="C88" s="41"/>
-      <c r="D88" s="41"/>
-      <c r="E88" s="41"/>
-      <c r="F88" s="41"/>
-      <c r="G88" s="41"/>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="B89" s="42">
-        <v>46422</v>
-      </c>
-      <c r="C89" s="42">
-        <v>46422</v>
-      </c>
-      <c r="D89" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="E89" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="F89" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G89" s="40" t="s">
-        <v>5</v>
-      </c>
+      <c r="B89" s="41"/>
+      <c r="C89" s="41"/>
+      <c r="D89" s="41"/>
+      <c r="E89" s="41"/>
+      <c r="F89" s="41"/>
+      <c r="G89" s="41"/>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="40" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="B90" s="42">
         <v>46422</v>
       </c>
       <c r="C90" s="42">
-        <v>46423</v>
+        <v>46422</v>
       </c>
       <c r="D90" s="40" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="F90" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G90" s="40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="40" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="B91" s="42">
-        <v>46424</v>
+        <v>46422</v>
       </c>
       <c r="C91" s="42">
-        <v>46424</v>
+        <v>46423</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="F91" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G91" s="40" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="40" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B92" s="42">
         <v>46424</v>
       </c>
       <c r="C92" s="42">
-        <v>46425</v>
+        <v>46424</v>
       </c>
       <c r="D92" s="40" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F92" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G92" s="40" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B93" s="42">
-        <v>46431</v>
+        <v>46424</v>
       </c>
       <c r="C93" s="42">
-        <v>46431</v>
+        <v>46425</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F93" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G93" s="40" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B94" s="42">
         <v>46431</v>
       </c>
       <c r="C94" s="42">
-        <v>46432</v>
+        <v>46431</v>
       </c>
       <c r="D94" s="40" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="F94" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G94" s="40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="17.25" customHeight="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B95" s="42">
-        <v>46438</v>
+        <v>46431</v>
       </c>
       <c r="C95" s="42">
-        <v>46438</v>
+        <v>46432</v>
       </c>
       <c r="D95" s="40" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F95" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G95" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="17.25" customHeight="1">
       <c r="A96" s="40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B96" s="42">
-        <v>46445</v>
+        <v>46438</v>
       </c>
       <c r="C96" s="42">
-        <v>46446</v>
+        <v>46438</v>
       </c>
       <c r="D96" s="40" t="s">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="E96" s="40" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="F96" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G96" s="40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="B97" s="42">
+        <v>46445</v>
+      </c>
+      <c r="C97" s="42">
+        <v>46446</v>
+      </c>
+      <c r="D97" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="E97" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="F97" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G97" s="40" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="16.8">
-      <c r="A97" s="41" t="s">
+    <row r="98" spans="1:7" ht="16.8">
+      <c r="A98" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="B97" s="41"/>
-      <c r="C97" s="41"/>
-      <c r="D97" s="41"/>
-      <c r="E97" s="41"/>
-      <c r="F97" s="41"/>
-      <c r="G97" s="41"/>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="B98" s="42">
-        <v>46447</v>
-      </c>
-      <c r="C98" s="42">
-        <v>46447</v>
-      </c>
-      <c r="D98" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="E98" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F98" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G98" s="40" t="s">
-        <v>5</v>
-      </c>
+      <c r="B98" s="41"/>
+      <c r="C98" s="41"/>
+      <c r="D98" s="41"/>
+      <c r="E98" s="41"/>
+      <c r="F98" s="41"/>
+      <c r="G98" s="41"/>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="40" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B99" s="42">
-        <v>46448</v>
+        <v>46447</v>
       </c>
       <c r="C99" s="42">
-        <v>46448</v>
+        <v>46447</v>
       </c>
       <c r="D99" s="40" t="s">
         <v>158</v>
@@ -6980,13 +7020,13 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B100" s="42">
-        <v>46449</v>
+        <v>46448</v>
       </c>
       <c r="C100" s="42">
-        <v>46449</v>
+        <v>46448</v>
       </c>
       <c r="D100" s="40" t="s">
         <v>158</v>
@@ -7003,13 +7043,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B101" s="42">
-        <v>46450</v>
+        <v>46449</v>
       </c>
       <c r="C101" s="42">
-        <v>46450</v>
+        <v>46449</v>
       </c>
       <c r="D101" s="40" t="s">
         <v>158</v>
@@ -7024,55 +7064,61 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:7" s="48" customFormat="1">
-      <c r="A102" s="46" t="s">
+    <row r="102" spans="1:7">
+      <c r="A102" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B102" s="42">
+        <v>46450</v>
+      </c>
+      <c r="C102" s="42">
+        <v>46450</v>
+      </c>
+      <c r="D102" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="E102" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F102" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G102" s="40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" s="48" customFormat="1">
+      <c r="A103" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="B102" s="47">
-        <v>46466</v>
-      </c>
-      <c r="C102" s="47">
-        <v>46468</v>
-      </c>
-      <c r="D102" s="46" t="s">
+      <c r="B103" s="47">
+        <v>46462</v>
+      </c>
+      <c r="C103" s="47">
+        <v>46464</v>
+      </c>
+      <c r="D103" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="E102" s="46" t="s">
+      <c r="E103" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F102" s="46" t="s">
+      <c r="F103" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="G102" s="46" t="s">
+      <c r="G103" s="46" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="13.2" customHeight="1">
-      <c r="A103" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="B103" s="42">
-        <v>46467</v>
-      </c>
-      <c r="C103" s="42">
-        <v>46467</v>
-      </c>
-      <c r="D103" s="40"/>
-      <c r="E103" s="40"/>
-      <c r="F103" s="40"/>
-      <c r="G103" s="40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" ht="13.2" customHeight="1">
       <c r="A104" s="40" t="s">
         <v>19</v>
       </c>
       <c r="B104" s="42">
-        <v>46468</v>
+        <v>46467</v>
       </c>
       <c r="C104" s="42">
-        <v>46468</v>
+        <v>46467</v>
       </c>
       <c r="D104" s="40"/>
       <c r="E104" s="40"/>
@@ -7081,15 +7127,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="24.9" customHeight="1">
+    <row r="105" spans="1:7">
       <c r="A105" s="40" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B105" s="42">
-        <v>46472</v>
+        <v>46468</v>
       </c>
       <c r="C105" s="42">
-        <v>46472</v>
+        <v>46468</v>
       </c>
       <c r="D105" s="40"/>
       <c r="E105" s="40"/>
@@ -7098,15 +7144,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="17.25" customHeight="1">
+    <row r="106" spans="1:7" ht="24.9" customHeight="1">
       <c r="A106" s="40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B106" s="42">
-        <v>46475</v>
+        <v>46472</v>
       </c>
       <c r="C106" s="42">
-        <v>46475</v>
+        <v>46472</v>
       </c>
       <c r="D106" s="40"/>
       <c r="E106" s="40"/>
@@ -7115,78 +7161,72 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="24.9" customHeight="1">
+    <row r="107" spans="1:7" ht="17.25" customHeight="1">
       <c r="A107" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="B107" s="42">
+        <v>46475</v>
+      </c>
+      <c r="C107" s="42">
+        <v>46475</v>
+      </c>
+      <c r="D107" s="40"/>
+      <c r="E107" s="40"/>
+      <c r="F107" s="40"/>
+      <c r="G107" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A108" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="B107" s="42">
+      <c r="B108" s="42">
         <v>46477</v>
       </c>
-      <c r="C107" s="42">
+      <c r="C108" s="42">
         <v>46477</v>
       </c>
-      <c r="D107" s="40" t="s">
+      <c r="D108" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="E107" s="40" t="s">
+      <c r="E108" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="F107" s="40" t="s">
+      <c r="F108" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G107" s="40" t="s">
+      <c r="G108" s="40" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="16.8">
-      <c r="A108" s="41" t="s">
+    <row r="109" spans="1:7" ht="16.8">
+      <c r="A109" s="41" t="s">
         <v>167</v>
       </c>
-      <c r="B108" s="41"/>
-      <c r="C108" s="41"/>
-      <c r="D108" s="41"/>
-      <c r="E108" s="41"/>
-      <c r="F108" s="41"/>
-      <c r="G108" s="41"/>
-    </row>
-    <row r="109" spans="1:7" ht="24.9" customHeight="1">
-      <c r="A109" s="40" t="s">
+      <c r="B109" s="41"/>
+      <c r="C109" s="41"/>
+      <c r="D109" s="41"/>
+      <c r="E109" s="41"/>
+      <c r="F109" s="41"/>
+      <c r="G109" s="41"/>
+    </row>
+    <row r="110" spans="1:7" ht="24.9" customHeight="1">
+      <c r="A110" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="B109" s="42">
+      <c r="B110" s="42">
         <v>46478</v>
       </c>
-      <c r="C109" s="42">
+      <c r="C110" s="42">
         <v>46480</v>
-      </c>
-      <c r="D109" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="E109" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="F109" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="G109" s="40" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
-      <c r="A110" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="B110" s="42">
-        <v>46482</v>
-      </c>
-      <c r="C110" s="42">
-        <v>46484</v>
       </c>
       <c r="D110" s="40" t="s">
         <v>47</v>
       </c>
       <c r="E110" s="40" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F110" s="40" t="s">
         <v>30</v>
@@ -7195,21 +7235,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" s="44" customFormat="1">
+    <row r="111" spans="1:7">
       <c r="A111" s="40" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B111" s="42">
-        <v>46485</v>
+        <v>46482</v>
       </c>
       <c r="C111" s="42">
-        <v>46489</v>
+        <v>46484</v>
       </c>
       <c r="D111" s="40" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E111" s="40" t="s">
-        <v>47</v>
+        <v>169</v>
       </c>
       <c r="F111" s="40" t="s">
         <v>30</v>
@@ -7218,18 +7258,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" s="24" customFormat="1">
+    <row r="112" spans="1:7" s="44" customFormat="1">
       <c r="A112" s="40" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B112" s="42">
-        <v>46491</v>
+        <v>46485</v>
       </c>
       <c r="C112" s="42">
-        <v>46495</v>
+        <v>46489</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="E112" s="40" t="s">
         <v>47</v>
@@ -7241,18 +7281,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="13.2" customHeight="1">
+    <row r="113" spans="1:7" s="24" customFormat="1">
       <c r="A113" s="40" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="B113" s="42">
-        <v>46500</v>
+        <v>46490</v>
       </c>
       <c r="C113" s="42">
-        <v>46504</v>
+        <v>46494</v>
       </c>
       <c r="D113" s="40" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="E113" s="40" t="s">
         <v>47</v>
@@ -7261,175 +7301,181 @@
         <v>30</v>
       </c>
       <c r="G113" s="40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="13.2" customHeight="1">
       <c r="A114" s="40" t="s">
-        <v>23</v>
+        <v>195</v>
       </c>
       <c r="B114" s="42">
-        <v>46504</v>
+        <v>46500</v>
       </c>
       <c r="C114" s="42">
         <v>46504</v>
       </c>
-      <c r="D114" s="40"/>
-      <c r="E114" s="40"/>
-      <c r="F114" s="40"/>
+      <c r="D114" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="E114" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F114" s="40" t="s">
+        <v>30</v>
+      </c>
       <c r="G114" s="40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B115" s="42">
+        <v>46504</v>
+      </c>
+      <c r="C115" s="42">
+        <v>46504</v>
+      </c>
+      <c r="D115" s="40"/>
+      <c r="E115" s="40"/>
+      <c r="F115" s="40"/>
+      <c r="G115" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A115" s="41" t="s">
+    <row r="116" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A116" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="B115" s="41"/>
-      <c r="C115" s="41"/>
-      <c r="D115" s="41"/>
-      <c r="E115" s="41"/>
-      <c r="F115" s="41"/>
-      <c r="G115" s="41"/>
-    </row>
-    <row r="116" spans="1:7">
-      <c r="A116" s="40" t="s">
+      <c r="B116" s="41"/>
+      <c r="C116" s="41"/>
+      <c r="D116" s="41"/>
+      <c r="E116" s="41"/>
+      <c r="F116" s="41"/>
+      <c r="G116" s="41"/>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="B116" s="42">
+      <c r="B117" s="42">
         <v>46508</v>
       </c>
-      <c r="C116" s="42">
+      <c r="C117" s="42">
         <v>46508</v>
       </c>
-      <c r="D116" s="40"/>
-      <c r="E116" s="40"/>
-      <c r="F116" s="40"/>
-      <c r="G116" s="40" t="s">
+      <c r="D117" s="40"/>
+      <c r="E117" s="40"/>
+      <c r="F117" s="40"/>
+      <c r="G117" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A117" s="41" t="s">
+    <row r="118" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A118" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="B117" s="41"/>
-      <c r="C117" s="41"/>
-      <c r="D117" s="41"/>
-      <c r="E117" s="41"/>
-      <c r="F117" s="41"/>
-      <c r="G117" s="41"/>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118" s="40" t="s">
+      <c r="B118" s="41"/>
+      <c r="C118" s="41"/>
+      <c r="D118" s="41"/>
+      <c r="E118" s="41"/>
+      <c r="F118" s="41"/>
+      <c r="G118" s="41"/>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B118" s="42">
+      <c r="B119" s="42">
         <v>46554</v>
       </c>
-      <c r="C118" s="42">
+      <c r="C119" s="42">
         <v>46554</v>
       </c>
-      <c r="D118" s="40"/>
-      <c r="E118" s="40"/>
-      <c r="F118" s="40"/>
-      <c r="G118" s="40" t="s">
+      <c r="D119" s="40"/>
+      <c r="E119" s="40"/>
+      <c r="F119" s="40"/>
+      <c r="G119" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A119" s="41" t="s">
+    <row r="120" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A120" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="B119" s="41"/>
-      <c r="C119" s="41"/>
-      <c r="D119" s="41"/>
-      <c r="E119" s="41"/>
-      <c r="F119" s="41"/>
-      <c r="G119" s="41"/>
-    </row>
-    <row r="120" spans="1:7">
-      <c r="A120" s="40" t="s">
+      <c r="B120" s="41"/>
+      <c r="C120" s="41"/>
+      <c r="D120" s="41"/>
+      <c r="E120" s="41"/>
+      <c r="F120" s="41"/>
+      <c r="G120" s="41"/>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B120" s="42">
+      <c r="B121" s="42">
         <v>46608</v>
       </c>
-      <c r="C120" s="42">
+      <c r="C121" s="42">
         <v>46608</v>
       </c>
-      <c r="D120" s="40"/>
-      <c r="E120" s="40"/>
-      <c r="F120" s="40"/>
-      <c r="G120" s="40" t="s">
+      <c r="D121" s="40"/>
+      <c r="E121" s="40"/>
+      <c r="F121" s="40"/>
+      <c r="G121" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="17.25" customHeight="1">
-      <c r="A121" s="41" t="s">
+    <row r="122" spans="1:7" ht="17.25" customHeight="1">
+      <c r="A122" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="B121" s="41"/>
-      <c r="C121" s="41"/>
-      <c r="D121" s="41"/>
-      <c r="E121" s="41"/>
-      <c r="F121" s="41"/>
-      <c r="G121" s="41"/>
-    </row>
-    <row r="122" spans="1:7">
-      <c r="A122" s="40" t="s">
+      <c r="B122" s="41"/>
+      <c r="C122" s="41"/>
+      <c r="D122" s="41"/>
+      <c r="E122" s="41"/>
+      <c r="F122" s="41"/>
+      <c r="G122" s="41"/>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="B122" s="42">
+      <c r="B123" s="42">
         <v>46654</v>
       </c>
-      <c r="C122" s="42">
+      <c r="C123" s="42">
         <v>46654</v>
       </c>
-      <c r="D122" s="40"/>
-      <c r="E122" s="40"/>
-      <c r="F122" s="40"/>
-      <c r="G122" s="40" t="s">
+      <c r="D123" s="40"/>
+      <c r="E123" s="40"/>
+      <c r="F123" s="40"/>
+      <c r="G123" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="16.8">
-      <c r="A123" s="41" t="s">
+    <row r="124" spans="1:7" ht="16.8">
+      <c r="A124" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="B123" s="41"/>
-      <c r="C123" s="41"/>
-      <c r="D123" s="41"/>
-      <c r="E123" s="41"/>
-      <c r="F123" s="41"/>
-      <c r="G123" s="41"/>
-    </row>
-    <row r="124" spans="1:7">
-      <c r="A124" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="B124" s="42">
-        <v>46737</v>
-      </c>
-      <c r="C124" s="42">
-        <v>46737</v>
-      </c>
-      <c r="D124" s="40"/>
-      <c r="E124" s="40"/>
-      <c r="F124" s="40"/>
-      <c r="G124" s="40" t="s">
-        <v>8</v>
-      </c>
+      <c r="B124" s="41"/>
+      <c r="C124" s="41"/>
+      <c r="D124" s="41"/>
+      <c r="E124" s="41"/>
+      <c r="F124" s="41"/>
+      <c r="G124" s="41"/>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B125" s="42">
-        <v>46746</v>
+        <v>46737</v>
       </c>
       <c r="C125" s="42">
-        <v>46746</v>
+        <v>46737</v>
       </c>
       <c r="D125" s="40"/>
       <c r="E125" s="40"/>
@@ -7440,13 +7486,13 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B126" s="42">
-        <v>46747</v>
+        <v>46746</v>
       </c>
       <c r="C126" s="42">
-        <v>46747</v>
+        <v>46746</v>
       </c>
       <c r="D126" s="40"/>
       <c r="E126" s="40"/>
@@ -7460,10 +7506,10 @@
         <v>111</v>
       </c>
       <c r="B127" s="42">
-        <v>46748</v>
+        <v>46747</v>
       </c>
       <c r="C127" s="42">
-        <v>46748</v>
+        <v>46747</v>
       </c>
       <c r="D127" s="40"/>
       <c r="E127" s="40"/>
@@ -7472,11 +7518,28 @@
         <v>8</v>
       </c>
     </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B128" s="42">
+        <v>46748</v>
+      </c>
+      <c r="C128" s="42">
+        <v>46748</v>
+      </c>
+      <c r="D128" s="40"/>
+      <c r="E128" s="40"/>
+      <c r="F128" s="40"/>
+      <c r="G128" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A10:G35 A36:D36 G36:G37 E36:E37 A38:G127">
+  <conditionalFormatting sqref="A37:D37 G37:G38 E37:E38 A39:G43 A47:G128 A10:G36 A45:G45 A44:D44 F44:G44">
     <cfRule type="expression" dxfId="27" priority="29">
       <formula>$G10="National gala"</formula>
     </cfRule>
@@ -7499,77 +7562,77 @@
       <formula>$G10="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A37:D37">
+  <conditionalFormatting sqref="A38:D38">
     <cfRule type="expression" dxfId="20" priority="15">
+      <formula>$G38="National gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="16">
+      <formula>$G38="Provincial gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="17">
+      <formula>$G38="District gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>$G38="Schools gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="19">
+      <formula>$G38="Club gala"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="20">
+      <formula>$G38="Open Water"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="21">
+      <formula>$G38="Public Holiday"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F37">
+    <cfRule type="expression" dxfId="13" priority="8">
       <formula>$G37="National gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="16">
+    <cfRule type="expression" dxfId="12" priority="9">
       <formula>$G37="Provincial gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="17">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>$G37="District gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="18">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$G37="Schools gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="19">
+    <cfRule type="expression" dxfId="9" priority="12">
       <formula>$G37="Club gala"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="20">
+    <cfRule type="expression" dxfId="8" priority="13">
       <formula>$G37="Open Water"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="21">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>$G37="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
-    <cfRule type="expression" dxfId="13" priority="8">
-      <formula>$G36="National gala"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="9">
-      <formula>$G36="Provincial gala"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="10">
-      <formula>$G36="District gala"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>$G36="Schools gala"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="12">
-      <formula>$G36="Club gala"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="13">
-      <formula>$G36="Open Water"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="14">
-      <formula>$G36="Public Holiday"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
+  <conditionalFormatting sqref="F38">
     <cfRule type="expression" dxfId="6" priority="1">
-      <formula>$G37="National gala"</formula>
+      <formula>$G38="National gala"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="5" priority="2">
-      <formula>$G37="Provincial gala"</formula>
+      <formula>$G38="Provincial gala"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="3">
-      <formula>$G37="District gala"</formula>
+      <formula>$G38="District gala"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="4">
-      <formula>$G37="Schools gala"</formula>
+      <formula>$G38="Schools gala"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="5">
-      <formula>$G37="Club gala"</formula>
+      <formula>$G38="Club gala"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="6">
-      <formula>$G37="Open Water"</formula>
+      <formula>$G38="Open Water"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="7">
-      <formula>$G37="Public Holiday"</formula>
+      <formula>$G38="Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G203">
+    <dataValidation type="list" allowBlank="1" sqref="G47:G204 G2:G45">
       <formula1>"Club gala,District gala,Provincial gala,National gala,Open Water,Schools gala,Public Holiday"</formula1>
     </dataValidation>
   </dataValidations>
